--- a/STOK DEALER/STOK SRB.xlsx
+++ b/STOK DEALER/STOK SRB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AB5D5A6-5291-4F94-B10A-065B4661182E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DCF8E2E-9F59-4AE4-B268-3A93247BE913}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{46E7093F-A843-4D56-8D6E-D290D3117D3B}"/>
   </bookViews>
@@ -9704,13 +9704,13 @@
         <v>1625</v>
       </c>
       <c r="F3" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G3" s="2">
         <v>0</v>
       </c>
       <c r="H3" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -9759,10 +9759,10 @@
         <v>3</v>
       </c>
       <c r="G5" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -9782,13 +9782,13 @@
         <v>1627</v>
       </c>
       <c r="F6" s="2">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
       </c>
       <c r="H6" s="2">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -9811,10 +9811,10 @@
         <v>21</v>
       </c>
       <c r="G7" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H7" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -11394,13 +11394,13 @@
         <v>1682</v>
       </c>
       <c r="F68" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G68" s="2">
         <v>1</v>
       </c>
       <c r="H68" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
@@ -13288,13 +13288,13 @@
         <v>1782</v>
       </c>
       <c r="F141" s="2">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="G141" s="2">
         <v>2</v>
       </c>
       <c r="H141" s="2">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
@@ -13340,13 +13340,13 @@
         <v>1783</v>
       </c>
       <c r="F143" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G143" s="2">
         <v>1</v>
       </c>
       <c r="H143" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
@@ -13470,13 +13470,13 @@
         <v>1791</v>
       </c>
       <c r="F148" s="2">
-        <v>166</v>
+        <v>156</v>
       </c>
       <c r="G148" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H148" s="2">
-        <v>161</v>
+        <v>150</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
@@ -13756,13 +13756,13 @@
         <v>1791</v>
       </c>
       <c r="F159" s="2">
-        <v>649</v>
+        <v>640</v>
       </c>
       <c r="G159" s="2">
         <v>9</v>
       </c>
       <c r="H159" s="2">
-        <v>640</v>
+        <v>631</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
@@ -13915,10 +13915,10 @@
         <v>94</v>
       </c>
       <c r="G165" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H165" s="2">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
@@ -14718,13 +14718,13 @@
         <v>1817</v>
       </c>
       <c r="F196" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G196" s="2">
         <v>1</v>
       </c>
       <c r="H196" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.25">
@@ -15186,13 +15186,13 @@
         <v>1858</v>
       </c>
       <c r="F214" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G214" s="2">
         <v>0</v>
       </c>
       <c r="H214" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.25">
@@ -20022,13 +20022,13 @@
         <v>1814</v>
       </c>
       <c r="F400" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G400" s="2">
         <v>0</v>
       </c>
       <c r="H400" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="401" spans="1:8" x14ac:dyDescent="0.25">
@@ -23581,10 +23581,10 @@
         <v>6</v>
       </c>
       <c r="G537" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H537" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="538" spans="1:8" x14ac:dyDescent="0.25">
@@ -23711,10 +23711,10 @@
         <v>6</v>
       </c>
       <c r="G542" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H542" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="543" spans="1:8" x14ac:dyDescent="0.25">
@@ -25713,10 +25713,10 @@
         <v>7</v>
       </c>
       <c r="G619" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H619" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="620" spans="1:8" x14ac:dyDescent="0.25">
@@ -28521,10 +28521,10 @@
         <v>30</v>
       </c>
       <c r="G727" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H727" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="728" spans="1:8" x14ac:dyDescent="0.25">
@@ -31589,10 +31589,10 @@
         <v>1</v>
       </c>
       <c r="G845" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H845" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="846" spans="1:8" x14ac:dyDescent="0.25">
@@ -32132,13 +32132,13 @@
         <v>2167</v>
       </c>
       <c r="F866" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G866" s="2">
         <v>0</v>
       </c>
       <c r="H866" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="867" spans="1:8" x14ac:dyDescent="0.25">
@@ -33950,13 +33950,13 @@
         <v>2516</v>
       </c>
       <c r="F936" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G936" s="2">
         <v>0</v>
       </c>
       <c r="H936" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="937" spans="1:8" x14ac:dyDescent="0.25">
@@ -34054,13 +34054,13 @@
         <v>2626</v>
       </c>
       <c r="F940" s="2">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G940" s="2">
         <v>0</v>
       </c>
       <c r="H940" s="2">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="941" spans="1:8" x14ac:dyDescent="0.25">
@@ -34109,10 +34109,10 @@
         <v>23</v>
       </c>
       <c r="G942" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H942" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="943" spans="1:8" x14ac:dyDescent="0.25">
@@ -34808,13 +34808,13 @@
         <v>2645</v>
       </c>
       <c r="F969" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G969" s="2">
         <v>0</v>
       </c>
       <c r="H969" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="970" spans="1:8" x14ac:dyDescent="0.25">
@@ -36758,13 +36758,13 @@
         <v>2592</v>
       </c>
       <c r="F1044" s="2">
-        <v>79</v>
+        <v>64</v>
       </c>
       <c r="G1044" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H1044" s="2">
-        <v>78</v>
+        <v>61</v>
       </c>
     </row>
     <row r="1045" spans="1:8" x14ac:dyDescent="0.25">
@@ -37073,10 +37073,10 @@
         <v>1</v>
       </c>
       <c r="G1056" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1056" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1057" spans="1:8" x14ac:dyDescent="0.25">
@@ -38292,13 +38292,13 @@
         <v>2734</v>
       </c>
       <c r="F1103" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1103" s="2">
         <v>0</v>
       </c>
       <c r="H1103" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1104" spans="1:8" x14ac:dyDescent="0.25">
@@ -39124,13 +39124,13 @@
         <v>2719</v>
       </c>
       <c r="F1135" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G1135" s="2">
         <v>0</v>
       </c>
       <c r="H1135" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1136" spans="1:8" x14ac:dyDescent="0.25">
@@ -39176,13 +39176,13 @@
         <v>2729</v>
       </c>
       <c r="F1137" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G1137" s="2">
         <v>0</v>
       </c>
       <c r="H1137" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="1138" spans="1:8" x14ac:dyDescent="0.25">
@@ -39306,13 +39306,13 @@
         <v>2730</v>
       </c>
       <c r="F1142" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G1142" s="2">
         <v>0</v>
       </c>
       <c r="H1142" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1143" spans="1:8" x14ac:dyDescent="0.25">
@@ -39384,13 +39384,13 @@
         <v>2730</v>
       </c>
       <c r="F1145" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G1145" s="2">
         <v>0</v>
       </c>
       <c r="H1145" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1146" spans="1:8" x14ac:dyDescent="0.25">
@@ -40921,10 +40921,10 @@
         <v>8</v>
       </c>
       <c r="G1204" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H1204" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1205" spans="1:8" x14ac:dyDescent="0.25">
@@ -41594,13 +41594,13 @@
         <v>2306</v>
       </c>
       <c r="F1230" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G1230" s="2">
         <v>3</v>
       </c>
       <c r="H1230" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="1231" spans="1:8" x14ac:dyDescent="0.25">
@@ -41828,13 +41828,13 @@
         <v>2825</v>
       </c>
       <c r="F1239" s="2">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="G1239" s="2">
         <v>1</v>
       </c>
       <c r="H1239" s="2">
-        <v>117</v>
+        <v>112</v>
       </c>
     </row>
     <row r="1240" spans="1:8" x14ac:dyDescent="0.25">
@@ -42530,13 +42530,13 @@
         <v>2853</v>
       </c>
       <c r="F1266" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G1266" s="2">
         <v>0</v>
       </c>
       <c r="H1266" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1267" spans="1:8" x14ac:dyDescent="0.25">
@@ -42764,13 +42764,13 @@
         <v>2878</v>
       </c>
       <c r="F1275" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1275" s="2">
         <v>0</v>
       </c>
       <c r="H1275" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1276" spans="1:8" x14ac:dyDescent="0.25">
@@ -44064,13 +44064,13 @@
         <v>2826</v>
       </c>
       <c r="F1325" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G1325" s="2">
         <v>0</v>
       </c>
       <c r="H1325" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1326" spans="1:8" x14ac:dyDescent="0.25">
@@ -44584,13 +44584,13 @@
         <v>2968</v>
       </c>
       <c r="F1345" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1345" s="2">
         <v>0</v>
       </c>
       <c r="H1345" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1346" spans="1:8" x14ac:dyDescent="0.25">
@@ -46092,13 +46092,13 @@
         <v>2996</v>
       </c>
       <c r="F1403" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1403" s="2">
         <v>0</v>
       </c>
       <c r="H1403" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1404" spans="1:8" x14ac:dyDescent="0.25">
@@ -47002,13 +47002,13 @@
         <v>2354</v>
       </c>
       <c r="F1438" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G1438" s="2">
         <v>0</v>
       </c>
       <c r="H1438" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1439" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK SRB.xlsx
+++ b/STOK DEALER/STOK SRB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DCF8E2E-9F59-4AE4-B268-3A93247BE913}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C427FEE-3F11-46F7-8AA0-A529E552AD3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{46E7093F-A843-4D56-8D6E-D290D3117D3B}"/>
   </bookViews>
@@ -9756,10 +9756,10 @@
         <v>1627</v>
       </c>
       <c r="F5" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G5" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" s="2">
         <v>2</v>
@@ -9808,13 +9808,13 @@
         <v>1627</v>
       </c>
       <c r="F7" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G7" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H7" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -9860,13 +9860,13 @@
         <v>1628</v>
       </c>
       <c r="F9" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G9" s="2">
         <v>0</v>
       </c>
       <c r="H9" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -10900,10 +10900,10 @@
         <v>1068</v>
       </c>
       <c r="F49" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G49" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H49" s="2">
         <v>9</v>
@@ -11290,10 +11290,10 @@
         <v>1260</v>
       </c>
       <c r="F64" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G64" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H64" s="2">
         <v>17</v>
@@ -11371,10 +11371,10 @@
         <v>12</v>
       </c>
       <c r="G67" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H67" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
@@ -13262,13 +13262,13 @@
         <v>1629</v>
       </c>
       <c r="F140" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G140" s="2">
         <v>1</v>
       </c>
       <c r="H140" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
@@ -13470,13 +13470,13 @@
         <v>1791</v>
       </c>
       <c r="F148" s="2">
-        <v>156</v>
+        <v>151</v>
       </c>
       <c r="G148" s="2">
         <v>6</v>
       </c>
       <c r="H148" s="2">
-        <v>150</v>
+        <v>145</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
@@ -13730,13 +13730,13 @@
         <v>1782</v>
       </c>
       <c r="F158" s="2">
-        <v>131</v>
+        <v>128</v>
       </c>
       <c r="G158" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H158" s="2">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
@@ -13756,13 +13756,13 @@
         <v>1791</v>
       </c>
       <c r="F159" s="2">
-        <v>640</v>
+        <v>633</v>
       </c>
       <c r="G159" s="2">
         <v>9</v>
       </c>
       <c r="H159" s="2">
-        <v>631</v>
+        <v>624</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
@@ -13912,13 +13912,13 @@
         <v>207</v>
       </c>
       <c r="F165" s="2">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="G165" s="2">
         <v>9</v>
       </c>
       <c r="H165" s="2">
-        <v>85</v>
+        <v>82</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
@@ -14071,10 +14071,10 @@
         <v>6</v>
       </c>
       <c r="G171" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H171" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
@@ -14718,13 +14718,13 @@
         <v>1817</v>
       </c>
       <c r="F196" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G196" s="2">
         <v>1</v>
       </c>
       <c r="H196" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.25">
@@ -15082,13 +15082,13 @@
         <v>1856</v>
       </c>
       <c r="F210" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G210" s="2">
         <v>0</v>
       </c>
       <c r="H210" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.25">
@@ -16642,13 +16642,13 @@
         <v>1958</v>
       </c>
       <c r="F270" s="2">
-        <v>1</v>
+        <v>16</v>
       </c>
       <c r="G270" s="2">
         <v>0</v>
       </c>
       <c r="H270" s="2">
-        <v>1</v>
+        <v>16</v>
       </c>
     </row>
     <row r="271" spans="1:8" x14ac:dyDescent="0.25">
@@ -20022,13 +20022,13 @@
         <v>1814</v>
       </c>
       <c r="F400" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G400" s="2">
         <v>0</v>
       </c>
       <c r="H400" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="401" spans="1:8" x14ac:dyDescent="0.25">
@@ -20230,13 +20230,13 @@
         <v>2170</v>
       </c>
       <c r="F408" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G408" s="2">
         <v>1</v>
       </c>
       <c r="H408" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="409" spans="1:8" x14ac:dyDescent="0.25">
@@ -20256,13 +20256,13 @@
         <v>926</v>
       </c>
       <c r="F409" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G409" s="2">
         <v>0</v>
       </c>
       <c r="H409" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="410" spans="1:8" x14ac:dyDescent="0.25">
@@ -20282,13 +20282,13 @@
         <v>2171</v>
       </c>
       <c r="F410" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G410" s="2">
         <v>1</v>
       </c>
       <c r="H410" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="411" spans="1:8" x14ac:dyDescent="0.25">
@@ -20672,13 +20672,13 @@
         <v>2175</v>
       </c>
       <c r="F425" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G425" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H425" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="426" spans="1:8" x14ac:dyDescent="0.25">
@@ -21892,13 +21892,13 @@
         <v>1905</v>
       </c>
       <c r="F472" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G472" s="2">
         <v>0</v>
       </c>
       <c r="H472" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="473" spans="1:8" x14ac:dyDescent="0.25">
@@ -22022,13 +22022,13 @@
         <v>610</v>
       </c>
       <c r="F477" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G477" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H477" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="478" spans="1:8" x14ac:dyDescent="0.25">
@@ -22152,10 +22152,10 @@
         <v>303</v>
       </c>
       <c r="F482" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G482" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H482" s="2">
         <v>5</v>
@@ -22412,10 +22412,10 @@
         <v>2244</v>
       </c>
       <c r="F492" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G492" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H492" s="2">
         <v>4</v>
@@ -22568,10 +22568,10 @@
         <v>919</v>
       </c>
       <c r="F498" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G498" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H498" s="2">
         <v>5</v>
@@ -23088,10 +23088,10 @@
         <v>2254</v>
       </c>
       <c r="F518" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G518" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H518" s="2">
         <v>1</v>
@@ -23864,10 +23864,10 @@
         <v>2277</v>
       </c>
       <c r="F548" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G548" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H548" s="2">
         <v>15</v>
@@ -23968,13 +23968,13 @@
         <v>2280</v>
       </c>
       <c r="F552" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G552" s="2">
         <v>1</v>
       </c>
       <c r="H552" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="553" spans="1:8" x14ac:dyDescent="0.25">
@@ -24852,10 +24852,10 @@
         <v>40</v>
       </c>
       <c r="F586" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G586" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H586" s="2">
         <v>0</v>
@@ -24904,10 +24904,10 @@
         <v>40</v>
       </c>
       <c r="F588" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G588" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H588" s="2">
         <v>0</v>
@@ -24956,10 +24956,10 @@
         <v>40</v>
       </c>
       <c r="F590" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G590" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H590" s="2">
         <v>0</v>
@@ -25710,13 +25710,13 @@
         <v>440</v>
       </c>
       <c r="F619" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G619" s="2">
         <v>2</v>
       </c>
       <c r="H619" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="620" spans="1:8" x14ac:dyDescent="0.25">
@@ -26386,13 +26386,13 @@
         <v>430</v>
       </c>
       <c r="F645" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G645" s="2">
         <v>0</v>
       </c>
       <c r="H645" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="646" spans="1:8" x14ac:dyDescent="0.25">
@@ -26464,13 +26464,13 @@
         <v>402</v>
       </c>
       <c r="F648" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G648" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H648" s="2">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="649" spans="1:8" x14ac:dyDescent="0.25">
@@ -26490,13 +26490,13 @@
         <v>430</v>
       </c>
       <c r="F649" s="2">
-        <v>16</v>
+        <v>45</v>
       </c>
       <c r="G649" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H649" s="2">
-        <v>14</v>
+        <v>44</v>
       </c>
     </row>
     <row r="650" spans="1:8" x14ac:dyDescent="0.25">
@@ -26516,13 +26516,13 @@
         <v>430</v>
       </c>
       <c r="F650" s="2">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G650" s="2">
         <v>4</v>
       </c>
       <c r="H650" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="651" spans="1:8" x14ac:dyDescent="0.25">
@@ -29636,13 +29636,13 @@
         <v>2527</v>
       </c>
       <c r="F770" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G770" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H770" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="771" spans="1:8" x14ac:dyDescent="0.25">
@@ -31742,13 +31742,13 @@
         <v>548</v>
       </c>
       <c r="F851" s="2">
+        <v>3</v>
+      </c>
+      <c r="G851" s="2">
+        <v>1</v>
+      </c>
+      <c r="H851" s="2">
         <v>2</v>
-      </c>
-      <c r="G851" s="2">
-        <v>1</v>
-      </c>
-      <c r="H851" s="2">
-        <v>1</v>
       </c>
     </row>
     <row r="852" spans="1:8" x14ac:dyDescent="0.25">
@@ -32988,13 +32988,13 @@
         <v>1625</v>
       </c>
       <c r="F899" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="G899" s="2">
         <v>0</v>
       </c>
       <c r="H899" s="2">
-        <v>34</v>
+        <v>32</v>
       </c>
     </row>
     <row r="900" spans="1:8" x14ac:dyDescent="0.25">
@@ -34106,10 +34106,10 @@
         <v>2630</v>
       </c>
       <c r="F942" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G942" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H942" s="2">
         <v>21</v>
@@ -36758,13 +36758,13 @@
         <v>2592</v>
       </c>
       <c r="F1044" s="2">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="G1044" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H1044" s="2">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="1045" spans="1:8" x14ac:dyDescent="0.25">
@@ -38396,13 +38396,13 @@
         <v>2730</v>
       </c>
       <c r="F1107" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1107" s="2">
         <v>0</v>
       </c>
       <c r="H1107" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1108" spans="1:8" x14ac:dyDescent="0.25">
@@ -39254,13 +39254,13 @@
         <v>2730</v>
       </c>
       <c r="F1140" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G1140" s="2">
         <v>0</v>
       </c>
       <c r="H1140" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1141" spans="1:8" x14ac:dyDescent="0.25">
@@ -39280,13 +39280,13 @@
         <v>2719</v>
       </c>
       <c r="F1141" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G1141" s="2">
         <v>0</v>
       </c>
       <c r="H1141" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1142" spans="1:8" x14ac:dyDescent="0.25">
@@ -39384,13 +39384,13 @@
         <v>2730</v>
       </c>
       <c r="F1145" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G1145" s="2">
         <v>0</v>
       </c>
       <c r="H1145" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1146" spans="1:8" x14ac:dyDescent="0.25">
@@ -40658,10 +40658,10 @@
         <v>2806</v>
       </c>
       <c r="F1194" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1194" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1194" s="2">
         <v>1</v>
@@ -40892,13 +40892,13 @@
         <v>1786</v>
       </c>
       <c r="F1203" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1203" s="2">
         <v>0</v>
       </c>
       <c r="H1203" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1204" spans="1:8" x14ac:dyDescent="0.25">
@@ -40970,13 +40970,13 @@
         <v>2812</v>
       </c>
       <c r="F1206" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G1206" s="2">
         <v>0</v>
       </c>
       <c r="H1206" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1207" spans="1:8" x14ac:dyDescent="0.25">
@@ -41048,13 +41048,13 @@
         <v>1786</v>
       </c>
       <c r="F1209" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1209" s="2">
         <v>0</v>
       </c>
       <c r="H1209" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1210" spans="1:8" x14ac:dyDescent="0.25">
@@ -41597,10 +41597,10 @@
         <v>37</v>
       </c>
       <c r="G1230" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H1230" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1231" spans="1:8" x14ac:dyDescent="0.25">
@@ -41828,13 +41828,13 @@
         <v>2825</v>
       </c>
       <c r="F1239" s="2">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="G1239" s="2">
         <v>1</v>
       </c>
       <c r="H1239" s="2">
-        <v>112</v>
+        <v>108</v>
       </c>
     </row>
     <row r="1240" spans="1:8" x14ac:dyDescent="0.25">
@@ -42400,13 +42400,13 @@
         <v>2862</v>
       </c>
       <c r="F1261" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G1261" s="2">
         <v>0</v>
       </c>
       <c r="H1261" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1262" spans="1:8" x14ac:dyDescent="0.25">
@@ -42738,13 +42738,13 @@
         <v>2878</v>
       </c>
       <c r="F1274" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1274" s="2">
         <v>0</v>
       </c>
       <c r="H1274" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1275" spans="1:8" x14ac:dyDescent="0.25">
@@ -43310,13 +43310,13 @@
         <v>2906</v>
       </c>
       <c r="F1296" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1296" s="2">
         <v>0</v>
       </c>
       <c r="H1296" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1297" spans="1:8" x14ac:dyDescent="0.25">
@@ -46823,10 +46823,10 @@
         <v>27</v>
       </c>
       <c r="G1431" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1431" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1432" spans="1:8" x14ac:dyDescent="0.25">
@@ -47028,13 +47028,13 @@
         <v>3058</v>
       </c>
       <c r="F1439" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G1439" s="2">
         <v>0</v>
       </c>
       <c r="H1439" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1440" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK SRB.xlsx
+++ b/STOK DEALER/STOK SRB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C427FEE-3F11-46F7-8AA0-A529E552AD3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD600E4F-E745-478D-871F-CC0D89AC23C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{46E7093F-A843-4D56-8D6E-D290D3117D3B}"/>
   </bookViews>
@@ -9860,13 +9860,13 @@
         <v>1628</v>
       </c>
       <c r="F9" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G9" s="2">
         <v>0</v>
       </c>
       <c r="H9" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -11290,13 +11290,13 @@
         <v>1260</v>
       </c>
       <c r="F64" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G64" s="2">
         <v>5</v>
       </c>
       <c r="H64" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
@@ -11368,10 +11368,10 @@
         <v>1682</v>
       </c>
       <c r="F67" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G67" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H67" s="2">
         <v>9</v>
@@ -13288,13 +13288,13 @@
         <v>1782</v>
       </c>
       <c r="F141" s="2">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="G141" s="2">
         <v>2</v>
       </c>
       <c r="H141" s="2">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
@@ -13314,13 +13314,13 @@
         <v>1783</v>
       </c>
       <c r="F142" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G142" s="2">
         <v>2</v>
       </c>
       <c r="H142" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
@@ -13340,13 +13340,13 @@
         <v>1783</v>
       </c>
       <c r="F143" s="2">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="G143" s="2">
         <v>1</v>
       </c>
       <c r="H143" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
@@ -13470,13 +13470,13 @@
         <v>1791</v>
       </c>
       <c r="F148" s="2">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="G148" s="2">
         <v>6</v>
       </c>
       <c r="H148" s="2">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
@@ -13730,13 +13730,13 @@
         <v>1782</v>
       </c>
       <c r="F158" s="2">
-        <v>128</v>
+        <v>125</v>
       </c>
       <c r="G158" s="2">
         <v>8</v>
       </c>
       <c r="H158" s="2">
-        <v>120</v>
+        <v>117</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
@@ -13756,13 +13756,13 @@
         <v>1791</v>
       </c>
       <c r="F159" s="2">
-        <v>633</v>
+        <v>620</v>
       </c>
       <c r="G159" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H159" s="2">
-        <v>624</v>
+        <v>612</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
@@ -13834,13 +13834,13 @@
         <v>207</v>
       </c>
       <c r="F162" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G162" s="2">
         <v>3</v>
       </c>
       <c r="H162" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
@@ -13912,13 +13912,13 @@
         <v>207</v>
       </c>
       <c r="F165" s="2">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="G165" s="2">
         <v>9</v>
       </c>
       <c r="H165" s="2">
-        <v>82</v>
+        <v>77</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
@@ -14068,10 +14068,10 @@
         <v>939</v>
       </c>
       <c r="F171" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G171" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H171" s="2">
         <v>4</v>
@@ -15082,13 +15082,13 @@
         <v>1856</v>
       </c>
       <c r="F210" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G210" s="2">
         <v>0</v>
       </c>
       <c r="H210" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.25">
@@ -15108,13 +15108,13 @@
         <v>1857</v>
       </c>
       <c r="F211" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G211" s="2">
         <v>0</v>
       </c>
       <c r="H211" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.25">
@@ -20022,13 +20022,13 @@
         <v>1814</v>
       </c>
       <c r="F400" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G400" s="2">
         <v>0</v>
       </c>
       <c r="H400" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="401" spans="1:8" x14ac:dyDescent="0.25">
@@ -20230,13 +20230,13 @@
         <v>2170</v>
       </c>
       <c r="F408" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G408" s="2">
         <v>1</v>
       </c>
       <c r="H408" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="409" spans="1:8" x14ac:dyDescent="0.25">
@@ -20256,13 +20256,13 @@
         <v>926</v>
       </c>
       <c r="F409" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G409" s="2">
         <v>0</v>
       </c>
       <c r="H409" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="410" spans="1:8" x14ac:dyDescent="0.25">
@@ -20672,10 +20672,10 @@
         <v>2175</v>
       </c>
       <c r="F425" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G425" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H425" s="2">
         <v>15</v>
@@ -22022,13 +22022,13 @@
         <v>610</v>
       </c>
       <c r="F477" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G477" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H477" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="478" spans="1:8" x14ac:dyDescent="0.25">
@@ -22152,10 +22152,10 @@
         <v>303</v>
       </c>
       <c r="F482" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G482" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H482" s="2">
         <v>5</v>
@@ -23968,13 +23968,13 @@
         <v>2280</v>
       </c>
       <c r="F552" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G552" s="2">
         <v>1</v>
       </c>
       <c r="H552" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="553" spans="1:8" x14ac:dyDescent="0.25">
@@ -24228,13 +24228,13 @@
         <v>483</v>
       </c>
       <c r="F562" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G562" s="2">
         <v>1</v>
       </c>
       <c r="H562" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="563" spans="1:8" x14ac:dyDescent="0.25">
@@ -26464,10 +26464,10 @@
         <v>402</v>
       </c>
       <c r="F648" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G648" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H648" s="2">
         <v>29</v>
@@ -26490,13 +26490,13 @@
         <v>430</v>
       </c>
       <c r="F649" s="2">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="G649" s="2">
         <v>1</v>
       </c>
       <c r="H649" s="2">
-        <v>44</v>
+        <v>41</v>
       </c>
     </row>
     <row r="650" spans="1:8" x14ac:dyDescent="0.25">
@@ -26802,10 +26802,10 @@
         <v>2408</v>
       </c>
       <c r="F661" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G661" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H661" s="2">
         <v>1</v>
@@ -29483,10 +29483,10 @@
         <v>3</v>
       </c>
       <c r="G764" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H764" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="765" spans="1:8" x14ac:dyDescent="0.25">
@@ -30078,13 +30078,13 @@
         <v>1110</v>
       </c>
       <c r="F787" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G787" s="2">
         <v>3</v>
       </c>
       <c r="H787" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="788" spans="1:8" x14ac:dyDescent="0.25">
@@ -32158,13 +32158,13 @@
         <v>2167</v>
       </c>
       <c r="F867" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G867" s="2">
         <v>0</v>
       </c>
       <c r="H867" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="868" spans="1:8" x14ac:dyDescent="0.25">
@@ -34054,13 +34054,13 @@
         <v>2626</v>
       </c>
       <c r="F940" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G940" s="2">
         <v>0</v>
       </c>
       <c r="H940" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="941" spans="1:8" x14ac:dyDescent="0.25">
@@ -34496,10 +34496,10 @@
         <v>2610</v>
       </c>
       <c r="F957" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G957" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H957" s="2">
         <v>0</v>
@@ -35302,13 +35302,13 @@
         <v>2649</v>
       </c>
       <c r="F988" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G988" s="2">
         <v>0</v>
       </c>
       <c r="H988" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="989" spans="1:8" x14ac:dyDescent="0.25">
@@ -36758,13 +36758,13 @@
         <v>2592</v>
       </c>
       <c r="F1044" s="2">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="G1044" s="2">
         <v>1</v>
       </c>
       <c r="H1044" s="2">
-        <v>58</v>
+        <v>53</v>
       </c>
     </row>
     <row r="1045" spans="1:8" x14ac:dyDescent="0.25">
@@ -36784,10 +36784,10 @@
         <v>2682</v>
       </c>
       <c r="F1045" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1045" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1045" s="2">
         <v>0</v>
@@ -36992,10 +36992,10 @@
         <v>2683</v>
       </c>
       <c r="F1053" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1053" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1053" s="2">
         <v>1</v>
@@ -39124,13 +39124,13 @@
         <v>2719</v>
       </c>
       <c r="F1135" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1135" s="2">
         <v>0</v>
       </c>
       <c r="H1135" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1136" spans="1:8" x14ac:dyDescent="0.25">
@@ -39176,13 +39176,13 @@
         <v>2729</v>
       </c>
       <c r="F1137" s="2">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="G1137" s="2">
         <v>0</v>
       </c>
       <c r="H1137" s="2">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1138" spans="1:8" x14ac:dyDescent="0.25">
@@ -39254,13 +39254,13 @@
         <v>2730</v>
       </c>
       <c r="F1140" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G1140" s="2">
         <v>0</v>
       </c>
       <c r="H1140" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1141" spans="1:8" x14ac:dyDescent="0.25">
@@ -40713,10 +40713,10 @@
         <v>2</v>
       </c>
       <c r="G1196" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1196" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1197" spans="1:8" x14ac:dyDescent="0.25">
@@ -40817,10 +40817,10 @@
         <v>6</v>
       </c>
       <c r="G1200" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1200" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1201" spans="1:8" x14ac:dyDescent="0.25">
@@ -41594,10 +41594,10 @@
         <v>2306</v>
       </c>
       <c r="F1230" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G1230" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1230" s="2">
         <v>33</v>
@@ -41649,10 +41649,10 @@
         <v>29</v>
       </c>
       <c r="G1232" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1232" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1233" spans="1:8" x14ac:dyDescent="0.25">
@@ -41776,13 +41776,13 @@
         <v>2827</v>
       </c>
       <c r="F1237" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1237" s="2">
         <v>0</v>
       </c>
       <c r="H1237" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1238" spans="1:8" x14ac:dyDescent="0.25">
@@ -41828,13 +41828,13 @@
         <v>2825</v>
       </c>
       <c r="F1239" s="2">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="G1239" s="2">
         <v>1</v>
       </c>
       <c r="H1239" s="2">
-        <v>108</v>
+        <v>102</v>
       </c>
     </row>
     <row r="1240" spans="1:8" x14ac:dyDescent="0.25">
@@ -42530,13 +42530,13 @@
         <v>2853</v>
       </c>
       <c r="F1266" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1266" s="2">
         <v>0</v>
       </c>
       <c r="H1266" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1267" spans="1:8" x14ac:dyDescent="0.25">
@@ -42686,13 +42686,13 @@
         <v>2835</v>
       </c>
       <c r="F1272" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1272" s="2">
         <v>0</v>
       </c>
       <c r="H1272" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1273" spans="1:8" x14ac:dyDescent="0.25">
@@ -42738,13 +42738,13 @@
         <v>2878</v>
       </c>
       <c r="F1274" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1274" s="2">
         <v>0</v>
       </c>
       <c r="H1274" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1275" spans="1:8" x14ac:dyDescent="0.25">
@@ -44064,13 +44064,13 @@
         <v>2826</v>
       </c>
       <c r="F1325" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G1325" s="2">
         <v>0</v>
       </c>
       <c r="H1325" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1326" spans="1:8" x14ac:dyDescent="0.25">
@@ -46719,10 +46719,10 @@
         <v>20</v>
       </c>
       <c r="G1427" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1427" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1428" spans="1:8" x14ac:dyDescent="0.25">
@@ -46820,10 +46820,10 @@
         <v>207</v>
       </c>
       <c r="F1431" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G1431" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1431" s="2">
         <v>26</v>
@@ -47002,13 +47002,13 @@
         <v>2354</v>
       </c>
       <c r="F1438" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G1438" s="2">
         <v>0</v>
       </c>
       <c r="H1438" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1439" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK SRB.xlsx
+++ b/STOK DEALER/STOK SRB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A39B2EA0-217D-4B93-84A5-DE3CC46520CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D6543B9-C68F-4390-B5DC-3E7CC4A8C13E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{46E7093F-A843-4D56-8D6E-D290D3117D3B}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5814" uniqueCount="3078">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5818" uniqueCount="3080">
   <si>
     <t>No</t>
   </si>
@@ -9270,6 +9270,12 @@
   </si>
   <si>
     <t>MARK,HONDA 100MM TYPE 1</t>
+  </si>
+  <si>
+    <t>MCSMPK1ZVCA</t>
+  </si>
+  <si>
+    <t>SPDMTR PRTECTOR PCX 160 C/A</t>
   </si>
 </sst>
 </file>
@@ -9670,7 +9676,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2BB8C35-92DF-4C27-A2CF-D1CDC7F4FE42}">
-  <dimension ref="A1:H1462"/>
+  <dimension ref="A1:H1463"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -9778,13 +9784,13 @@
         <v>1626</v>
       </c>
       <c r="F4" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G4" s="2">
         <v>0</v>
       </c>
       <c r="H4" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -9804,13 +9810,13 @@
         <v>1627</v>
       </c>
       <c r="F5" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G5" s="2">
         <v>0</v>
       </c>
       <c r="H5" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -9830,13 +9836,13 @@
         <v>1627</v>
       </c>
       <c r="F6" s="2">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
       </c>
       <c r="H6" s="2">
-        <v>57</v>
+        <v>56</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -10246,10 +10252,10 @@
         <v>1648</v>
       </c>
       <c r="F22" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G22" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H22" s="2">
         <v>2</v>
@@ -10428,10 +10434,10 @@
         <v>1653</v>
       </c>
       <c r="F29" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G29" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H29" s="2">
         <v>4</v>
@@ -10818,10 +10824,10 @@
         <v>1672</v>
       </c>
       <c r="F44" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G44" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H44" s="2">
         <v>16</v>
@@ -11338,10 +11344,10 @@
         <v>1260</v>
       </c>
       <c r="F64" s="2">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="G64" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H64" s="2">
         <v>31</v>
@@ -11416,10 +11422,10 @@
         <v>1682</v>
       </c>
       <c r="F67" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G67" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H67" s="2">
         <v>9</v>
@@ -13336,10 +13342,10 @@
         <v>1782</v>
       </c>
       <c r="F141" s="2">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="G141" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H141" s="2">
         <v>64</v>
@@ -13362,10 +13368,10 @@
         <v>1783</v>
       </c>
       <c r="F142" s="2">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G142" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H142" s="2">
         <v>178</v>
@@ -13388,10 +13394,10 @@
         <v>1783</v>
       </c>
       <c r="F143" s="2">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="G143" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H143" s="2">
         <v>256</v>
@@ -13518,13 +13524,13 @@
         <v>1791</v>
       </c>
       <c r="F148" s="2">
-        <v>143</v>
+        <v>136</v>
       </c>
       <c r="G148" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H148" s="2">
-        <v>136</v>
+        <v>130</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
@@ -13726,10 +13732,10 @@
         <v>1794</v>
       </c>
       <c r="F156" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G156" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H156" s="2">
         <v>0</v>
@@ -13778,13 +13784,13 @@
         <v>1782</v>
       </c>
       <c r="F158" s="2">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="G158" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="H158" s="2">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
@@ -13804,13 +13810,13 @@
         <v>1791</v>
       </c>
       <c r="F159" s="2">
-        <v>604</v>
+        <v>591</v>
       </c>
       <c r="G159" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H159" s="2">
-        <v>596</v>
+        <v>587</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
@@ -13882,13 +13888,13 @@
         <v>207</v>
       </c>
       <c r="F162" s="2">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G162" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H162" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
@@ -13960,13 +13966,13 @@
         <v>207</v>
       </c>
       <c r="F165" s="2">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="G165" s="2">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="H165" s="2">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
@@ -14116,10 +14122,10 @@
         <v>939</v>
       </c>
       <c r="F171" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G171" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H171" s="2">
         <v>46</v>
@@ -14896,13 +14902,13 @@
         <v>1829</v>
       </c>
       <c r="F201" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G201" s="2">
         <v>0</v>
       </c>
       <c r="H201" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.25">
@@ -15130,13 +15136,13 @@
         <v>1856</v>
       </c>
       <c r="F210" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G210" s="2">
         <v>0</v>
       </c>
       <c r="H210" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.25">
@@ -17054,10 +17060,10 @@
         <v>1952</v>
       </c>
       <c r="F284" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G284" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H284" s="2">
         <v>1</v>
@@ -17678,10 +17684,10 @@
         <v>2016</v>
       </c>
       <c r="F308" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G308" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H308" s="2">
         <v>0</v>
@@ -18094,10 +18100,10 @@
         <v>2030</v>
       </c>
       <c r="F324" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G324" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H324" s="2">
         <v>1</v>
@@ -18120,10 +18126,10 @@
         <v>2036</v>
       </c>
       <c r="F325" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G325" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H325" s="2">
         <v>0</v>
@@ -18822,10 +18828,10 @@
         <v>1954</v>
       </c>
       <c r="F352" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G352" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H352" s="2">
         <v>2</v>
@@ -19030,10 +19036,10 @@
         <v>2097</v>
       </c>
       <c r="F360" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G360" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H360" s="2">
         <v>1</v>
@@ -19056,10 +19062,10 @@
         <v>2097</v>
       </c>
       <c r="F361" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G361" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H361" s="2">
         <v>0</v>
@@ -19108,10 +19114,10 @@
         <v>2084</v>
       </c>
       <c r="F363" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G363" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H363" s="2">
         <v>0</v>
@@ -19420,10 +19426,10 @@
         <v>2126</v>
       </c>
       <c r="F375" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G375" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H375" s="2">
         <v>0</v>
@@ -19498,10 +19504,10 @@
         <v>2129</v>
       </c>
       <c r="F378" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G378" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H378" s="2">
         <v>1</v>
@@ -19940,10 +19946,10 @@
         <v>2155</v>
       </c>
       <c r="F395" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G395" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H395" s="2">
         <v>0</v>
@@ -20096,13 +20102,13 @@
         <v>1814</v>
       </c>
       <c r="F401" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G401" s="2">
         <v>0</v>
       </c>
       <c r="H401" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="402" spans="1:8" x14ac:dyDescent="0.25">
@@ -20304,10 +20310,10 @@
         <v>2170</v>
       </c>
       <c r="F409" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G409" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H409" s="2">
         <v>33</v>
@@ -20356,13 +20362,13 @@
         <v>2171</v>
       </c>
       <c r="F411" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G411" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H411" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="412" spans="1:8" x14ac:dyDescent="0.25">
@@ -22096,13 +22102,13 @@
         <v>610</v>
       </c>
       <c r="F478" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G478" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H478" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="479" spans="1:8" x14ac:dyDescent="0.25">
@@ -22122,10 +22128,10 @@
         <v>587</v>
       </c>
       <c r="F479" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G479" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H479" s="2">
         <v>11</v>
@@ -22359,10 +22365,10 @@
         <v>4</v>
       </c>
       <c r="G488" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H488" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="489" spans="1:8" x14ac:dyDescent="0.25">
@@ -22801,10 +22807,10 @@
         <v>9</v>
       </c>
       <c r="G505" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H505" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="506" spans="1:8" x14ac:dyDescent="0.25">
@@ -22824,13 +22830,13 @@
         <v>2248</v>
       </c>
       <c r="F506" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G506" s="2">
         <v>0</v>
       </c>
       <c r="H506" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="507" spans="1:8" x14ac:dyDescent="0.25">
@@ -23652,10 +23658,10 @@
         <v>538</v>
       </c>
       <c r="F538" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G538" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H538" s="2">
         <v>2</v>
@@ -23678,13 +23684,13 @@
         <v>647</v>
       </c>
       <c r="F539" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G539" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H539" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="540" spans="1:8" x14ac:dyDescent="0.25">
@@ -23808,10 +23814,10 @@
         <v>236</v>
       </c>
       <c r="F544" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G544" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H544" s="2">
         <v>5</v>
@@ -24068,10 +24074,10 @@
         <v>2280</v>
       </c>
       <c r="F554" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G554" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H554" s="2">
         <v>17</v>
@@ -24146,10 +24152,10 @@
         <v>351</v>
       </c>
       <c r="F557" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G557" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H557" s="2">
         <v>1</v>
@@ -24614,10 +24620,10 @@
         <v>2293</v>
       </c>
       <c r="F575" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G575" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H575" s="2">
         <v>12</v>
@@ -25654,10 +25660,10 @@
         <v>440</v>
       </c>
       <c r="F615" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G615" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H615" s="2">
         <v>0</v>
@@ -25862,10 +25868,10 @@
         <v>440</v>
       </c>
       <c r="F623" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G623" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H623" s="2">
         <v>4</v>
@@ -26304,10 +26310,10 @@
         <v>292</v>
       </c>
       <c r="F640" s="2">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G640" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H640" s="2">
         <v>22</v>
@@ -26694,13 +26700,13 @@
         <v>402</v>
       </c>
       <c r="F655" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G655" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H655" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="656" spans="1:8" x14ac:dyDescent="0.25">
@@ -26746,10 +26752,10 @@
         <v>430</v>
       </c>
       <c r="F657" s="2">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G657" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H657" s="2">
         <v>32</v>
@@ -27968,13 +27974,13 @@
         <v>2457</v>
       </c>
       <c r="F704" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G704" s="2">
         <v>0</v>
       </c>
       <c r="H704" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="705" spans="1:8" x14ac:dyDescent="0.25">
@@ -27994,10 +28000,10 @@
         <v>2463</v>
       </c>
       <c r="F705" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G705" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H705" s="2">
         <v>1</v>
@@ -28150,10 +28156,10 @@
         <v>696</v>
       </c>
       <c r="F711" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G711" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H711" s="2">
         <v>3</v>
@@ -28384,10 +28390,10 @@
         <v>696</v>
       </c>
       <c r="F720" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G720" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H720" s="2">
         <v>9</v>
@@ -28774,10 +28780,10 @@
         <v>2478</v>
       </c>
       <c r="F735" s="2">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="G735" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H735" s="2">
         <v>40</v>
@@ -29086,10 +29092,10 @@
         <v>2055</v>
       </c>
       <c r="F747" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G747" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H747" s="2">
         <v>0</v>
@@ -29944,13 +29950,13 @@
         <v>2529</v>
       </c>
       <c r="F780" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G780" s="2">
         <v>0</v>
       </c>
       <c r="H780" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="781" spans="1:8" x14ac:dyDescent="0.25">
@@ -30334,10 +30340,10 @@
         <v>1110</v>
       </c>
       <c r="F795" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G795" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H795" s="2">
         <v>19</v>
@@ -30675,10 +30681,10 @@
         <v>1</v>
       </c>
       <c r="G808" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H808" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="809" spans="1:8" x14ac:dyDescent="0.25">
@@ -30805,10 +30811,10 @@
         <v>8</v>
       </c>
       <c r="G813" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H813" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="814" spans="1:8" x14ac:dyDescent="0.25">
@@ -30984,13 +30990,13 @@
         <v>2557</v>
       </c>
       <c r="F820" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G820" s="2">
         <v>1</v>
       </c>
       <c r="H820" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="821" spans="1:8" x14ac:dyDescent="0.25">
@@ -31322,10 +31328,10 @@
         <v>2479</v>
       </c>
       <c r="F833" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G833" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H833" s="2">
         <v>0</v>
@@ -31400,10 +31406,10 @@
         <v>59</v>
       </c>
       <c r="F836" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G836" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H836" s="2">
         <v>1</v>
@@ -31764,10 +31770,10 @@
         <v>2575</v>
       </c>
       <c r="F850" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G850" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H850" s="2">
         <v>0</v>
@@ -31842,10 +31848,10 @@
         <v>2579</v>
       </c>
       <c r="F853" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G853" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H853" s="2">
         <v>0</v>
@@ -31998,10 +32004,10 @@
         <v>548</v>
       </c>
       <c r="F859" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G859" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H859" s="2">
         <v>2</v>
@@ -32206,10 +32212,10 @@
         <v>2565</v>
       </c>
       <c r="F867" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G867" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H867" s="2">
         <v>2</v>
@@ -32414,13 +32420,13 @@
         <v>2167</v>
       </c>
       <c r="F875" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G875" s="2">
         <v>0</v>
       </c>
       <c r="H875" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="876" spans="1:8" x14ac:dyDescent="0.25">
@@ -32568,10 +32574,10 @@
         <v>2589</v>
       </c>
       <c r="F881" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G881" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H881" s="2">
         <v>2</v>
@@ -32672,10 +32678,10 @@
         <v>56</v>
       </c>
       <c r="F885" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G885" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H885" s="2">
         <v>0</v>
@@ -33244,13 +33250,13 @@
         <v>1625</v>
       </c>
       <c r="F907" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G907" s="2">
         <v>0</v>
       </c>
       <c r="H907" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="908" spans="1:8" x14ac:dyDescent="0.25">
@@ -34232,13 +34238,13 @@
         <v>2516</v>
       </c>
       <c r="F945" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G945" s="2">
         <v>0</v>
       </c>
       <c r="H945" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="946" spans="1:8" x14ac:dyDescent="0.25">
@@ -34310,13 +34316,13 @@
         <v>2628</v>
       </c>
       <c r="F948" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G948" s="2">
         <v>0</v>
       </c>
       <c r="H948" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="949" spans="1:8" x14ac:dyDescent="0.25">
@@ -34336,13 +34342,13 @@
         <v>2626</v>
       </c>
       <c r="F949" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G949" s="2">
         <v>0</v>
       </c>
       <c r="H949" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="950" spans="1:8" x14ac:dyDescent="0.25">
@@ -37066,13 +37072,13 @@
         <v>2592</v>
       </c>
       <c r="F1054" s="2">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="G1054" s="2">
         <v>1</v>
       </c>
       <c r="H1054" s="2">
-        <v>139</v>
+        <v>133</v>
       </c>
     </row>
     <row r="1055" spans="1:8" x14ac:dyDescent="0.25">
@@ -37378,10 +37384,10 @@
         <v>2683</v>
       </c>
       <c r="F1066" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1066" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1066" s="2">
         <v>0</v>
@@ -38704,13 +38710,13 @@
         <v>2734</v>
       </c>
       <c r="F1117" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1117" s="2">
         <v>0</v>
       </c>
       <c r="H1117" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1118" spans="1:8" x14ac:dyDescent="0.25">
@@ -39510,13 +39516,13 @@
         <v>2729</v>
       </c>
       <c r="F1148" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1148" s="2">
         <v>0</v>
       </c>
       <c r="H1148" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1149" spans="1:8" x14ac:dyDescent="0.25">
@@ -40784,10 +40790,10 @@
         <v>2457</v>
       </c>
       <c r="F1197" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1197" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1197" s="2">
         <v>0</v>
@@ -40862,13 +40868,13 @@
         <v>1671</v>
       </c>
       <c r="F1200" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1200" s="2">
         <v>0</v>
       </c>
       <c r="H1200" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1201" spans="1:8" x14ac:dyDescent="0.25">
@@ -41070,10 +41076,10 @@
         <v>2806</v>
       </c>
       <c r="F1208" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1208" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1208" s="2">
         <v>0</v>
@@ -41174,13 +41180,13 @@
         <v>2811</v>
       </c>
       <c r="F1212" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1212" s="2">
         <v>2</v>
       </c>
       <c r="H1212" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1213" spans="1:8" x14ac:dyDescent="0.25">
@@ -41226,10 +41232,10 @@
         <v>2795</v>
       </c>
       <c r="F1214" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1214" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1214" s="2">
         <v>6</v>
@@ -41252,13 +41258,13 @@
         <v>1786</v>
       </c>
       <c r="F1215" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1215" s="2">
         <v>0</v>
       </c>
       <c r="H1215" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1216" spans="1:8" x14ac:dyDescent="0.25">
@@ -41278,10 +41284,10 @@
         <v>2812</v>
       </c>
       <c r="F1216" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G1216" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H1216" s="2">
         <v>4</v>
@@ -42188,13 +42194,13 @@
         <v>2825</v>
       </c>
       <c r="F1251" s="2">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="G1251" s="2">
         <v>1</v>
       </c>
       <c r="H1251" s="2">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="1252" spans="1:8" x14ac:dyDescent="0.25">
@@ -44294,13 +44300,13 @@
         <v>2948</v>
       </c>
       <c r="F1332" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G1332" s="2">
         <v>0</v>
       </c>
       <c r="H1332" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1333" spans="1:8" x14ac:dyDescent="0.25">
@@ -47232,10 +47238,10 @@
         <v>565</v>
       </c>
       <c r="F1445" s="2">
-        <v>36</v>
+        <v>28</v>
       </c>
       <c r="G1445" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="H1445" s="2">
         <v>28</v>
@@ -47362,13 +47368,13 @@
         <v>2354</v>
       </c>
       <c r="F1450" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G1450" s="2">
         <v>0</v>
       </c>
       <c r="H1450" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1451" spans="1:8" x14ac:dyDescent="0.25">
@@ -47388,13 +47394,13 @@
         <v>3058</v>
       </c>
       <c r="F1451" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G1451" s="2">
         <v>0</v>
       </c>
       <c r="H1451" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1452" spans="1:8" x14ac:dyDescent="0.25">
@@ -47506,25 +47512,25 @@
         <v>1455</v>
       </c>
       <c r="B1456" s="2" t="s">
-        <v>1246</v>
+        <v>3078</v>
       </c>
       <c r="C1456" s="2" t="s">
-        <v>1247</v>
+        <v>3079</v>
       </c>
       <c r="D1456" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1456" s="2" t="s">
-        <v>1665</v>
+        <v>1663</v>
       </c>
       <c r="F1456" s="2">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="G1456" s="2">
         <v>0</v>
       </c>
       <c r="H1456" s="2">
-        <v>32</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1457" spans="1:8" x14ac:dyDescent="0.25">
@@ -47532,25 +47538,25 @@
         <v>1456</v>
       </c>
       <c r="B1457" s="2" t="s">
-        <v>1621</v>
+        <v>1246</v>
       </c>
       <c r="C1457" s="2" t="s">
-        <v>1622</v>
+        <v>1247</v>
       </c>
       <c r="D1457" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1457" s="2" t="s">
-        <v>2242</v>
+        <v>1665</v>
       </c>
       <c r="F1457" s="2">
-        <v>18</v>
+        <v>32</v>
       </c>
       <c r="G1457" s="2">
         <v>0</v>
       </c>
       <c r="H1457" s="2">
-        <v>18</v>
+        <v>32</v>
       </c>
     </row>
     <row r="1458" spans="1:8" x14ac:dyDescent="0.25">
@@ -47558,25 +47564,25 @@
         <v>1457</v>
       </c>
       <c r="B1458" s="2" t="s">
-        <v>1248</v>
+        <v>1621</v>
       </c>
       <c r="C1458" s="2" t="s">
-        <v>1249</v>
+        <v>1622</v>
       </c>
       <c r="D1458" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1458" s="2" t="s">
-        <v>1665</v>
+        <v>2242</v>
       </c>
       <c r="F1458" s="2">
-        <v>4</v>
+        <v>18</v>
       </c>
       <c r="G1458" s="2">
         <v>0</v>
       </c>
       <c r="H1458" s="2">
-        <v>4</v>
+        <v>18</v>
       </c>
     </row>
     <row r="1459" spans="1:8" x14ac:dyDescent="0.25">
@@ -47584,10 +47590,10 @@
         <v>1458</v>
       </c>
       <c r="B1459" s="2" t="s">
-        <v>1250</v>
+        <v>1248</v>
       </c>
       <c r="C1459" s="2" t="s">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="D1459" s="2" t="s">
         <v>1623</v>
@@ -47596,13 +47602,13 @@
         <v>1665</v>
       </c>
       <c r="F1459" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1459" s="2">
         <v>0</v>
       </c>
       <c r="H1459" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1460" spans="1:8" x14ac:dyDescent="0.25">
@@ -47610,25 +47616,25 @@
         <v>1459</v>
       </c>
       <c r="B1460" s="2" t="s">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="C1460" s="2" t="s">
-        <v>1253</v>
+        <v>1251</v>
       </c>
       <c r="D1460" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1460" s="2" t="s">
-        <v>3061</v>
+        <v>1665</v>
       </c>
       <c r="F1460" s="2">
-        <v>37</v>
+        <v>5</v>
       </c>
       <c r="G1460" s="2">
         <v>0</v>
       </c>
       <c r="H1460" s="2">
-        <v>37</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1461" spans="1:8" x14ac:dyDescent="0.25">
@@ -47636,25 +47642,25 @@
         <v>1460</v>
       </c>
       <c r="B1461" s="2" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="C1461" s="2" t="s">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="D1461" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1461" s="2" t="s">
-        <v>939</v>
+        <v>3061</v>
       </c>
       <c r="F1461" s="2">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="G1461" s="2">
         <v>0</v>
       </c>
       <c r="H1461" s="2">
-        <v>29</v>
+        <v>37</v>
       </c>
     </row>
     <row r="1462" spans="1:8" x14ac:dyDescent="0.25">
@@ -47662,24 +47668,50 @@
         <v>1461</v>
       </c>
       <c r="B1462" s="2" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C1462" s="2" t="s">
+        <v>1255</v>
+      </c>
+      <c r="D1462" s="2" t="s">
+        <v>1623</v>
+      </c>
+      <c r="E1462" s="2" t="s">
+        <v>939</v>
+      </c>
+      <c r="F1462" s="2">
+        <v>29</v>
+      </c>
+      <c r="G1462" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1462" s="2">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="1463" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1463" s="2">
+        <v>1462</v>
+      </c>
+      <c r="B1463" s="2" t="s">
         <v>1256</v>
       </c>
-      <c r="C1462" s="2" t="s">
+      <c r="C1463" s="2" t="s">
         <v>1257</v>
       </c>
-      <c r="D1462" s="2" t="s">
-        <v>1623</v>
-      </c>
-      <c r="E1462" s="2" t="s">
+      <c r="D1463" s="2" t="s">
+        <v>1623</v>
+      </c>
+      <c r="E1463" s="2" t="s">
         <v>565</v>
       </c>
-      <c r="F1462" s="2">
-        <v>0</v>
-      </c>
-      <c r="G1462" s="2">
-        <v>0</v>
-      </c>
-      <c r="H1462" s="2">
+      <c r="F1463" s="2">
+        <v>0</v>
+      </c>
+      <c r="G1463" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1463" s="2">
         <v>0</v>
       </c>
     </row>

--- a/STOK DEALER/STOK SRB.xlsx
+++ b/STOK DEALER/STOK SRB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D6543B9-C68F-4390-B5DC-3E7CC4A8C13E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFB4BCFE-420D-46A8-9713-6C7EE40C02F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{46E7093F-A843-4D56-8D6E-D290D3117D3B}"/>
   </bookViews>
@@ -9836,13 +9836,13 @@
         <v>1627</v>
       </c>
       <c r="F6" s="2">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
       </c>
       <c r="H6" s="2">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -9862,13 +9862,13 @@
         <v>1627</v>
       </c>
       <c r="F7" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G7" s="2">
         <v>0</v>
       </c>
       <c r="H7" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -10824,13 +10824,13 @@
         <v>1672</v>
       </c>
       <c r="F44" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G44" s="2">
         <v>1</v>
       </c>
       <c r="H44" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
@@ -11344,13 +11344,13 @@
         <v>1260</v>
       </c>
       <c r="F64" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G64" s="2">
         <v>3</v>
       </c>
       <c r="H64" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
@@ -13342,13 +13342,13 @@
         <v>1782</v>
       </c>
       <c r="F141" s="2">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G141" s="2">
         <v>1</v>
       </c>
       <c r="H141" s="2">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
@@ -13368,13 +13368,13 @@
         <v>1783</v>
       </c>
       <c r="F142" s="2">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="G142" s="2">
         <v>1</v>
       </c>
       <c r="H142" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
@@ -13524,13 +13524,13 @@
         <v>1791</v>
       </c>
       <c r="F148" s="2">
-        <v>136</v>
+        <v>131</v>
       </c>
       <c r="G148" s="2">
         <v>6</v>
       </c>
       <c r="H148" s="2">
-        <v>130</v>
+        <v>125</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
@@ -13784,13 +13784,13 @@
         <v>1782</v>
       </c>
       <c r="F158" s="2">
-        <v>115</v>
+        <v>108</v>
       </c>
       <c r="G158" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H158" s="2">
-        <v>111</v>
+        <v>103</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
@@ -13810,13 +13810,13 @@
         <v>1791</v>
       </c>
       <c r="F159" s="2">
-        <v>591</v>
+        <v>582</v>
       </c>
       <c r="G159" s="2">
         <v>4</v>
       </c>
       <c r="H159" s="2">
-        <v>587</v>
+        <v>578</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
@@ -13888,13 +13888,13 @@
         <v>207</v>
       </c>
       <c r="F162" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G162" s="2">
         <v>0</v>
       </c>
       <c r="H162" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
@@ -13966,13 +13966,13 @@
         <v>207</v>
       </c>
       <c r="F165" s="2">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="G165" s="2">
         <v>3</v>
       </c>
       <c r="H165" s="2">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
@@ -15422,13 +15422,13 @@
         <v>1871</v>
       </c>
       <c r="F221" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G221" s="2">
         <v>0</v>
       </c>
       <c r="H221" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.25">
@@ -19507,10 +19507,10 @@
         <v>1</v>
       </c>
       <c r="G378" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H378" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="379" spans="1:8" x14ac:dyDescent="0.25">
@@ -20336,13 +20336,13 @@
         <v>926</v>
       </c>
       <c r="F410" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G410" s="2">
         <v>0</v>
       </c>
       <c r="H410" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="411" spans="1:8" x14ac:dyDescent="0.25">
@@ -20362,13 +20362,13 @@
         <v>2171</v>
       </c>
       <c r="F411" s="2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G411" s="2">
         <v>0</v>
       </c>
       <c r="H411" s="2">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="412" spans="1:8" x14ac:dyDescent="0.25">
@@ -20833,10 +20833,10 @@
         <v>4</v>
       </c>
       <c r="G429" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H429" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="430" spans="1:8" x14ac:dyDescent="0.25">
@@ -22102,13 +22102,13 @@
         <v>610</v>
       </c>
       <c r="F478" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G478" s="2">
         <v>1</v>
       </c>
       <c r="H478" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="479" spans="1:8" x14ac:dyDescent="0.25">
@@ -26310,13 +26310,13 @@
         <v>292</v>
       </c>
       <c r="F640" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G640" s="2">
         <v>0</v>
       </c>
       <c r="H640" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="641" spans="1:8" x14ac:dyDescent="0.25">
@@ -26703,10 +26703,10 @@
         <v>25</v>
       </c>
       <c r="G655" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H655" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="656" spans="1:8" x14ac:dyDescent="0.25">
@@ -27350,13 +27350,13 @@
         <v>1828</v>
       </c>
       <c r="F680" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G680" s="2">
         <v>0</v>
       </c>
       <c r="H680" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="681" spans="1:8" x14ac:dyDescent="0.25">
@@ -27974,13 +27974,13 @@
         <v>2457</v>
       </c>
       <c r="F704" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G704" s="2">
         <v>0</v>
       </c>
       <c r="H704" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="705" spans="1:8" x14ac:dyDescent="0.25">
@@ -28390,13 +28390,13 @@
         <v>696</v>
       </c>
       <c r="F720" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G720" s="2">
         <v>0</v>
       </c>
       <c r="H720" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="721" spans="1:8" x14ac:dyDescent="0.25">
@@ -28783,10 +28783,10 @@
         <v>40</v>
       </c>
       <c r="G735" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H735" s="2">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="736" spans="1:8" x14ac:dyDescent="0.25">
@@ -29742,13 +29742,13 @@
         <v>2517</v>
       </c>
       <c r="F772" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G772" s="2">
         <v>1</v>
       </c>
       <c r="H772" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="773" spans="1:8" x14ac:dyDescent="0.25">
@@ -32707,10 +32707,10 @@
         <v>1</v>
       </c>
       <c r="G886" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H886" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="887" spans="1:8" x14ac:dyDescent="0.25">
@@ -33250,13 +33250,13 @@
         <v>1625</v>
       </c>
       <c r="F907" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G907" s="2">
         <v>0</v>
       </c>
       <c r="H907" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="908" spans="1:8" x14ac:dyDescent="0.25">
@@ -34342,13 +34342,13 @@
         <v>2626</v>
       </c>
       <c r="F949" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G949" s="2">
         <v>0</v>
       </c>
       <c r="H949" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="950" spans="1:8" x14ac:dyDescent="0.25">
@@ -35044,13 +35044,13 @@
         <v>2645</v>
       </c>
       <c r="F976" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G976" s="2">
         <v>0</v>
       </c>
       <c r="H976" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="977" spans="1:8" x14ac:dyDescent="0.25">
@@ -37072,13 +37072,13 @@
         <v>2592</v>
       </c>
       <c r="F1054" s="2">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="G1054" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1054" s="2">
-        <v>133</v>
+        <v>128</v>
       </c>
     </row>
     <row r="1055" spans="1:8" x14ac:dyDescent="0.25">
@@ -38294,13 +38294,13 @@
         <v>1829</v>
       </c>
       <c r="F1101" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G1101" s="2">
         <v>0</v>
       </c>
       <c r="H1101" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1102" spans="1:8" x14ac:dyDescent="0.25">
@@ -38840,13 +38840,13 @@
         <v>2719</v>
       </c>
       <c r="F1122" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1122" s="2">
         <v>0</v>
       </c>
       <c r="H1122" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1123" spans="1:8" x14ac:dyDescent="0.25">
@@ -39542,13 +39542,13 @@
         <v>2729</v>
       </c>
       <c r="F1149" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G1149" s="2">
         <v>0</v>
       </c>
       <c r="H1149" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1150" spans="1:8" x14ac:dyDescent="0.25">
@@ -41258,13 +41258,13 @@
         <v>1786</v>
       </c>
       <c r="F1215" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1215" s="2">
         <v>0</v>
       </c>
       <c r="H1215" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1216" spans="1:8" x14ac:dyDescent="0.25">
@@ -42194,13 +42194,13 @@
         <v>2825</v>
       </c>
       <c r="F1251" s="2">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="G1251" s="2">
         <v>1</v>
       </c>
       <c r="H1251" s="2">
-        <v>85</v>
+        <v>83</v>
       </c>
     </row>
     <row r="1252" spans="1:8" x14ac:dyDescent="0.25">
@@ -42870,13 +42870,13 @@
         <v>2869</v>
       </c>
       <c r="F1277" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1277" s="2">
         <v>0</v>
       </c>
       <c r="H1277" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1278" spans="1:8" x14ac:dyDescent="0.25">
@@ -47241,10 +47241,10 @@
         <v>28</v>
       </c>
       <c r="G1445" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H1445" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1446" spans="1:8" x14ac:dyDescent="0.25">
@@ -47394,13 +47394,13 @@
         <v>3058</v>
       </c>
       <c r="F1451" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G1451" s="2">
         <v>0</v>
       </c>
       <c r="H1451" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1452" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK SRB.xlsx
+++ b/STOK DEALER/STOK SRB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CFB4BCFE-420D-46A8-9713-6C7EE40C02F0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46296151-5DAF-4EF9-8980-66F33A923300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{46E7093F-A843-4D56-8D6E-D290D3117D3B}"/>
   </bookViews>
@@ -13342,13 +13342,13 @@
         <v>1782</v>
       </c>
       <c r="F141" s="2">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="G141" s="2">
         <v>1</v>
       </c>
       <c r="H141" s="2">
-        <v>62</v>
+        <v>60</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
@@ -13524,13 +13524,13 @@
         <v>1791</v>
       </c>
       <c r="F148" s="2">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="G148" s="2">
         <v>6</v>
       </c>
       <c r="H148" s="2">
-        <v>125</v>
+        <v>118</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
@@ -13784,13 +13784,13 @@
         <v>1782</v>
       </c>
       <c r="F158" s="2">
-        <v>108</v>
+        <v>247</v>
       </c>
       <c r="G158" s="2">
         <v>5</v>
       </c>
       <c r="H158" s="2">
-        <v>103</v>
+        <v>242</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
@@ -13810,13 +13810,13 @@
         <v>1791</v>
       </c>
       <c r="F159" s="2">
-        <v>582</v>
+        <v>821</v>
       </c>
       <c r="G159" s="2">
         <v>4</v>
       </c>
       <c r="H159" s="2">
-        <v>578</v>
+        <v>817</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
@@ -13966,13 +13966,13 @@
         <v>207</v>
       </c>
       <c r="F165" s="2">
-        <v>69</v>
+        <v>119</v>
       </c>
       <c r="G165" s="2">
         <v>3</v>
       </c>
       <c r="H165" s="2">
-        <v>66</v>
+        <v>116</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
@@ -18103,10 +18103,10 @@
         <v>1</v>
       </c>
       <c r="G324" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H324" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="325" spans="1:8" x14ac:dyDescent="0.25">
@@ -20310,13 +20310,13 @@
         <v>2170</v>
       </c>
       <c r="F409" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G409" s="2">
         <v>0</v>
       </c>
       <c r="H409" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="410" spans="1:8" x14ac:dyDescent="0.25">
@@ -22102,13 +22102,13 @@
         <v>610</v>
       </c>
       <c r="F478" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G478" s="2">
         <v>1</v>
       </c>
       <c r="H478" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="479" spans="1:8" x14ac:dyDescent="0.25">
@@ -23687,10 +23687,10 @@
         <v>3</v>
       </c>
       <c r="G539" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H539" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="540" spans="1:8" x14ac:dyDescent="0.25">
@@ -24074,13 +24074,13 @@
         <v>2280</v>
       </c>
       <c r="F554" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G554" s="2">
         <v>0</v>
       </c>
       <c r="H554" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="555" spans="1:8" x14ac:dyDescent="0.25">
@@ -26700,13 +26700,13 @@
         <v>402</v>
       </c>
       <c r="F655" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G655" s="2">
         <v>2</v>
       </c>
       <c r="H655" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="656" spans="1:8" x14ac:dyDescent="0.25">
@@ -31484,13 +31484,13 @@
         <v>1958</v>
       </c>
       <c r="F839" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G839" s="2">
         <v>0</v>
       </c>
       <c r="H839" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="840" spans="1:8" x14ac:dyDescent="0.25">
@@ -31744,13 +31744,13 @@
         <v>2575</v>
       </c>
       <c r="F849" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G849" s="2">
         <v>0</v>
       </c>
       <c r="H849" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="850" spans="1:8" x14ac:dyDescent="0.25">
@@ -32033,10 +32033,10 @@
         <v>1</v>
       </c>
       <c r="G860" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H860" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="861" spans="1:8" x14ac:dyDescent="0.25">
@@ -32420,13 +32420,13 @@
         <v>2167</v>
       </c>
       <c r="F875" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G875" s="2">
         <v>0</v>
       </c>
       <c r="H875" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="876" spans="1:8" x14ac:dyDescent="0.25">
@@ -34238,13 +34238,13 @@
         <v>2516</v>
       </c>
       <c r="F945" s="2">
-        <v>1</v>
+        <v>48</v>
       </c>
       <c r="G945" s="2">
         <v>0</v>
       </c>
       <c r="H945" s="2">
-        <v>1</v>
+        <v>48</v>
       </c>
     </row>
     <row r="946" spans="1:8" x14ac:dyDescent="0.25">
@@ -34342,13 +34342,13 @@
         <v>2626</v>
       </c>
       <c r="F949" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="G949" s="2">
         <v>0</v>
       </c>
       <c r="H949" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="950" spans="1:8" x14ac:dyDescent="0.25">
@@ -37072,13 +37072,13 @@
         <v>2592</v>
       </c>
       <c r="F1054" s="2">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="G1054" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1054" s="2">
-        <v>128</v>
+        <v>125</v>
       </c>
     </row>
     <row r="1055" spans="1:8" x14ac:dyDescent="0.25">
@@ -38580,13 +38580,13 @@
         <v>2730</v>
       </c>
       <c r="F1112" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G1112" s="2">
         <v>0</v>
       </c>
       <c r="H1112" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1113" spans="1:8" x14ac:dyDescent="0.25">
@@ -38710,13 +38710,13 @@
         <v>2734</v>
       </c>
       <c r="F1117" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="G1117" s="2">
         <v>0</v>
       </c>
       <c r="H1117" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1118" spans="1:8" x14ac:dyDescent="0.25">
@@ -38788,13 +38788,13 @@
         <v>2735</v>
       </c>
       <c r="F1120" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G1120" s="2">
         <v>0</v>
       </c>
       <c r="H1120" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1121" spans="1:8" x14ac:dyDescent="0.25">
@@ -38814,13 +38814,13 @@
         <v>2719</v>
       </c>
       <c r="F1121" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1121" s="2">
         <v>0</v>
       </c>
       <c r="H1121" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1122" spans="1:8" x14ac:dyDescent="0.25">
@@ -38970,13 +38970,13 @@
         <v>2735</v>
       </c>
       <c r="F1127" s="2">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G1127" s="2">
         <v>0</v>
       </c>
       <c r="H1127" s="2">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1128" spans="1:8" x14ac:dyDescent="0.25">
@@ -39490,13 +39490,13 @@
         <v>2719</v>
       </c>
       <c r="F1147" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G1147" s="2">
         <v>0</v>
       </c>
       <c r="H1147" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1148" spans="1:8" x14ac:dyDescent="0.25">
@@ -39516,13 +39516,13 @@
         <v>2729</v>
       </c>
       <c r="F1148" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G1148" s="2">
         <v>0</v>
       </c>
       <c r="H1148" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1149" spans="1:8" x14ac:dyDescent="0.25">
@@ -39542,13 +39542,13 @@
         <v>2729</v>
       </c>
       <c r="F1149" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G1149" s="2">
         <v>0</v>
       </c>
       <c r="H1149" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1150" spans="1:8" x14ac:dyDescent="0.25">
@@ -39568,13 +39568,13 @@
         <v>2731</v>
       </c>
       <c r="F1150" s="2">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G1150" s="2">
         <v>0</v>
       </c>
       <c r="H1150" s="2">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1151" spans="1:8" x14ac:dyDescent="0.25">
@@ -39594,13 +39594,13 @@
         <v>2729</v>
       </c>
       <c r="F1151" s="2">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="G1151" s="2">
         <v>0</v>
       </c>
       <c r="H1151" s="2">
-        <v>4</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1152" spans="1:8" x14ac:dyDescent="0.25">
@@ -39620,13 +39620,13 @@
         <v>2730</v>
       </c>
       <c r="F1152" s="2">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="G1152" s="2">
         <v>0</v>
       </c>
       <c r="H1152" s="2">
-        <v>28</v>
+        <v>38</v>
       </c>
     </row>
     <row r="1153" spans="1:8" x14ac:dyDescent="0.25">
@@ -39646,13 +39646,13 @@
         <v>2719</v>
       </c>
       <c r="F1153" s="2">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="G1153" s="2">
         <v>0</v>
       </c>
       <c r="H1153" s="2">
-        <v>19</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1154" spans="1:8" x14ac:dyDescent="0.25">
@@ -39672,13 +39672,13 @@
         <v>2730</v>
       </c>
       <c r="F1154" s="2">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="G1154" s="2">
         <v>0</v>
       </c>
       <c r="H1154" s="2">
-        <v>19</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1155" spans="1:8" x14ac:dyDescent="0.25">
@@ -39698,13 +39698,13 @@
         <v>2730</v>
       </c>
       <c r="F1155" s="2">
-        <v>16</v>
+        <v>26</v>
       </c>
       <c r="G1155" s="2">
         <v>0</v>
       </c>
       <c r="H1155" s="2">
-        <v>16</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1156" spans="1:8" x14ac:dyDescent="0.25">
@@ -39724,13 +39724,13 @@
         <v>2686</v>
       </c>
       <c r="F1156" s="2">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G1156" s="2">
         <v>0</v>
       </c>
       <c r="H1156" s="2">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1157" spans="1:8" x14ac:dyDescent="0.25">
@@ -39750,13 +39750,13 @@
         <v>2730</v>
       </c>
       <c r="F1157" s="2">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="G1157" s="2">
         <v>0</v>
       </c>
       <c r="H1157" s="2">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1158" spans="1:8" x14ac:dyDescent="0.25">
@@ -42688,13 +42688,13 @@
         <v>2853</v>
       </c>
       <c r="F1270" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G1270" s="2">
         <v>0</v>
       </c>
       <c r="H1270" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1271" spans="1:8" x14ac:dyDescent="0.25">
@@ -42974,13 +42974,13 @@
         <v>2871</v>
       </c>
       <c r="F1281" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G1281" s="2">
         <v>0</v>
       </c>
       <c r="H1281" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1282" spans="1:8" x14ac:dyDescent="0.25">
@@ -43000,13 +43000,13 @@
         <v>2853</v>
       </c>
       <c r="F1282" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="G1282" s="2">
         <v>0</v>
       </c>
       <c r="H1282" s="2">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1283" spans="1:8" x14ac:dyDescent="0.25">
@@ -43052,13 +43052,13 @@
         <v>2835</v>
       </c>
       <c r="F1284" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1284" s="2">
         <v>0</v>
       </c>
       <c r="H1284" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1285" spans="1:8" x14ac:dyDescent="0.25">
@@ -44066,13 +44066,13 @@
         <v>2903</v>
       </c>
       <c r="F1323" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G1323" s="2">
         <v>0</v>
       </c>
       <c r="H1323" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1324" spans="1:8" x14ac:dyDescent="0.25">
@@ -44092,13 +44092,13 @@
         <v>2934</v>
       </c>
       <c r="F1324" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G1324" s="2">
         <v>0</v>
       </c>
       <c r="H1324" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1325" spans="1:8" x14ac:dyDescent="0.25">
@@ -44300,13 +44300,13 @@
         <v>2948</v>
       </c>
       <c r="F1332" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="G1332" s="2">
         <v>0</v>
       </c>
       <c r="H1332" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1333" spans="1:8" x14ac:dyDescent="0.25">
@@ -44326,13 +44326,13 @@
         <v>2947</v>
       </c>
       <c r="F1333" s="2">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="G1333" s="2">
         <v>0</v>
       </c>
       <c r="H1333" s="2">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1334" spans="1:8" x14ac:dyDescent="0.25">
@@ -44482,13 +44482,13 @@
         <v>2827</v>
       </c>
       <c r="F1339" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G1339" s="2">
         <v>0</v>
       </c>
       <c r="H1339" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1340" spans="1:8" x14ac:dyDescent="0.25">
@@ -44508,13 +44508,13 @@
         <v>2827</v>
       </c>
       <c r="F1340" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G1340" s="2">
         <v>0</v>
       </c>
       <c r="H1340" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1341" spans="1:8" x14ac:dyDescent="0.25">
@@ -44534,13 +44534,13 @@
         <v>2842</v>
       </c>
       <c r="F1341" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1341" s="2">
         <v>0</v>
       </c>
       <c r="H1341" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1342" spans="1:8" x14ac:dyDescent="0.25">
@@ -44638,13 +44638,13 @@
         <v>2955</v>
       </c>
       <c r="F1345" s="2">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="G1345" s="2">
         <v>0</v>
       </c>
       <c r="H1345" s="2">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1346" spans="1:8" x14ac:dyDescent="0.25">
@@ -44690,13 +44690,13 @@
         <v>2948</v>
       </c>
       <c r="F1347" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G1347" s="2">
         <v>0</v>
       </c>
       <c r="H1347" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1348" spans="1:8" x14ac:dyDescent="0.25">
@@ -44716,13 +44716,13 @@
         <v>2934</v>
       </c>
       <c r="F1348" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G1348" s="2">
         <v>0</v>
       </c>
       <c r="H1348" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1349" spans="1:8" x14ac:dyDescent="0.25">
@@ -45054,13 +45054,13 @@
         <v>2968</v>
       </c>
       <c r="F1361" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G1361" s="2">
         <v>0</v>
       </c>
       <c r="H1361" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1362" spans="1:8" x14ac:dyDescent="0.25">
@@ -45106,13 +45106,13 @@
         <v>2948</v>
       </c>
       <c r="F1363" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="G1363" s="2">
         <v>0</v>
       </c>
       <c r="H1363" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1364" spans="1:8" x14ac:dyDescent="0.25">
@@ -45132,13 +45132,13 @@
         <v>2869</v>
       </c>
       <c r="F1364" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G1364" s="2">
         <v>0</v>
       </c>
       <c r="H1364" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1365" spans="1:8" x14ac:dyDescent="0.25">
@@ -45340,13 +45340,13 @@
         <v>2916</v>
       </c>
       <c r="F1372" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G1372" s="2">
         <v>0</v>
       </c>
       <c r="H1372" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1373" spans="1:8" x14ac:dyDescent="0.25">
@@ -45366,13 +45366,13 @@
         <v>2951</v>
       </c>
       <c r="F1373" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G1373" s="2">
         <v>0</v>
       </c>
       <c r="H1373" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1374" spans="1:8" x14ac:dyDescent="0.25">
@@ -45392,13 +45392,13 @@
         <v>2870</v>
       </c>
       <c r="F1374" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G1374" s="2">
         <v>0</v>
       </c>
       <c r="H1374" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1375" spans="1:8" x14ac:dyDescent="0.25">
@@ -45444,13 +45444,13 @@
         <v>2996</v>
       </c>
       <c r="F1376" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G1376" s="2">
         <v>0</v>
       </c>
       <c r="H1376" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1377" spans="1:8" x14ac:dyDescent="0.25">
@@ -45470,13 +45470,13 @@
         <v>2856</v>
       </c>
       <c r="F1377" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G1377" s="2">
         <v>0</v>
       </c>
       <c r="H1377" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1378" spans="1:8" x14ac:dyDescent="0.25">
@@ -45678,13 +45678,13 @@
         <v>3014</v>
       </c>
       <c r="F1385" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G1385" s="2">
         <v>0</v>
       </c>
       <c r="H1385" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1386" spans="1:8" x14ac:dyDescent="0.25">
@@ -45782,13 +45782,13 @@
         <v>2870</v>
       </c>
       <c r="F1389" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G1389" s="2">
         <v>0</v>
       </c>
       <c r="H1389" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1390" spans="1:8" x14ac:dyDescent="0.25">
@@ -45808,13 +45808,13 @@
         <v>3017</v>
       </c>
       <c r="F1390" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G1390" s="2">
         <v>0</v>
       </c>
       <c r="H1390" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1391" spans="1:8" x14ac:dyDescent="0.25">
@@ -45834,13 +45834,13 @@
         <v>2847</v>
       </c>
       <c r="F1391" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="G1391" s="2">
         <v>0</v>
       </c>
       <c r="H1391" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1392" spans="1:8" x14ac:dyDescent="0.25">
@@ -45860,13 +45860,13 @@
         <v>2996</v>
       </c>
       <c r="F1392" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G1392" s="2">
         <v>0</v>
       </c>
       <c r="H1392" s="2">
-        <v>2</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1393" spans="1:8" x14ac:dyDescent="0.25">
@@ -45990,13 +45990,13 @@
         <v>3014</v>
       </c>
       <c r="F1397" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G1397" s="2">
         <v>0</v>
       </c>
       <c r="H1397" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1398" spans="1:8" x14ac:dyDescent="0.25">
@@ -46094,13 +46094,13 @@
         <v>3014</v>
       </c>
       <c r="F1401" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G1401" s="2">
         <v>0</v>
       </c>
       <c r="H1401" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1402" spans="1:8" x14ac:dyDescent="0.25">
@@ -46120,13 +46120,13 @@
         <v>2903</v>
       </c>
       <c r="F1402" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G1402" s="2">
         <v>0</v>
       </c>
       <c r="H1402" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1403" spans="1:8" x14ac:dyDescent="0.25">
@@ -46146,13 +46146,13 @@
         <v>2968</v>
       </c>
       <c r="F1403" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G1403" s="2">
         <v>0</v>
       </c>
       <c r="H1403" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1404" spans="1:8" x14ac:dyDescent="0.25">
@@ -46172,13 +46172,13 @@
         <v>2996</v>
       </c>
       <c r="F1404" s="2">
-        <v>3</v>
+        <v>11</v>
       </c>
       <c r="G1404" s="2">
         <v>0</v>
       </c>
       <c r="H1404" s="2">
-        <v>3</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1405" spans="1:8" x14ac:dyDescent="0.25">
@@ -46328,13 +46328,13 @@
         <v>2934</v>
       </c>
       <c r="F1410" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1410" s="2">
         <v>0</v>
       </c>
       <c r="H1410" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1411" spans="1:8" x14ac:dyDescent="0.25">
@@ -46380,13 +46380,13 @@
         <v>2870</v>
       </c>
       <c r="F1412" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G1412" s="2">
         <v>0</v>
       </c>
       <c r="H1412" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1413" spans="1:8" x14ac:dyDescent="0.25">
@@ -46406,13 +46406,13 @@
         <v>2847</v>
       </c>
       <c r="F1413" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G1413" s="2">
         <v>0</v>
       </c>
       <c r="H1413" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1414" spans="1:8" x14ac:dyDescent="0.25">
@@ -46432,13 +46432,13 @@
         <v>2917</v>
       </c>
       <c r="F1414" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1414" s="2">
         <v>0</v>
       </c>
       <c r="H1414" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1415" spans="1:8" x14ac:dyDescent="0.25">
@@ -46458,13 +46458,13 @@
         <v>2996</v>
       </c>
       <c r="F1415" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G1415" s="2">
         <v>0</v>
       </c>
       <c r="H1415" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1416" spans="1:8" x14ac:dyDescent="0.25">
@@ -47524,13 +47524,13 @@
         <v>1663</v>
       </c>
       <c r="F1456" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1456" s="2">
         <v>0</v>
       </c>
       <c r="H1456" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1457" spans="1:8" x14ac:dyDescent="0.25">
@@ -47680,13 +47680,13 @@
         <v>939</v>
       </c>
       <c r="F1462" s="2">
-        <v>29</v>
+        <v>40</v>
       </c>
       <c r="G1462" s="2">
         <v>0</v>
       </c>
       <c r="H1462" s="2">
-        <v>29</v>
+        <v>40</v>
       </c>
     </row>
     <row r="1463" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK SRB.xlsx
+++ b/STOK DEALER/STOK SRB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46296151-5DAF-4EF9-8980-66F33A923300}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8BFA5272-8445-4A70-989E-E06D0206E9F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{46E7093F-A843-4D56-8D6E-D290D3117D3B}"/>
   </bookViews>
@@ -10957,10 +10957,10 @@
         <v>10</v>
       </c>
       <c r="G49" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H49" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
@@ -11373,10 +11373,10 @@
         <v>1</v>
       </c>
       <c r="G65" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H65" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
@@ -13342,13 +13342,13 @@
         <v>1782</v>
       </c>
       <c r="F141" s="2">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="G141" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H141" s="2">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
@@ -13368,13 +13368,13 @@
         <v>1783</v>
       </c>
       <c r="F142" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G142" s="2">
         <v>1</v>
       </c>
       <c r="H142" s="2">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
@@ -13524,13 +13524,13 @@
         <v>1791</v>
       </c>
       <c r="F148" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G148" s="2">
         <v>6</v>
       </c>
       <c r="H148" s="2">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
@@ -13787,10 +13787,10 @@
         <v>247</v>
       </c>
       <c r="G158" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H158" s="2">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
@@ -13810,13 +13810,13 @@
         <v>1791</v>
       </c>
       <c r="F159" s="2">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="G159" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H159" s="2">
-        <v>817</v>
+        <v>815</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
@@ -13891,10 +13891,10 @@
         <v>27</v>
       </c>
       <c r="G162" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H162" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
@@ -22833,10 +22833,10 @@
         <v>1</v>
       </c>
       <c r="G506" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H506" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="507" spans="1:8" x14ac:dyDescent="0.25">
@@ -28783,10 +28783,10 @@
         <v>40</v>
       </c>
       <c r="G735" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H735" s="2">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="736" spans="1:8" x14ac:dyDescent="0.25">
@@ -30811,10 +30811,10 @@
         <v>8</v>
       </c>
       <c r="G813" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H813" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="814" spans="1:8" x14ac:dyDescent="0.25">
@@ -31747,10 +31747,10 @@
         <v>3</v>
       </c>
       <c r="G849" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H849" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="850" spans="1:8" x14ac:dyDescent="0.25">
@@ -32215,10 +32215,10 @@
         <v>2</v>
       </c>
       <c r="G867" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H867" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="868" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK SRB.xlsx
+++ b/STOK DEALER/STOK SRB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HPM-DESCO-PSD\Downloads\UPADTE TOOLS BUNDLING\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0351D37-B6F0-4727-BA42-F064E466DDD6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E62574BC-3E40-444B-BADE-9AF84988F7B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{46E7093F-A843-4D56-8D6E-D290D3117D3B}"/>
   </bookViews>
@@ -13893,10 +13893,10 @@
         <v>815</v>
       </c>
       <c r="G159" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H159" s="2">
-        <v>806</v>
+        <v>805</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
@@ -26887,10 +26887,10 @@
         <v>25</v>
       </c>
       <c r="G659" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H659" s="2">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
     <row r="660" spans="1:8" x14ac:dyDescent="0.25">
@@ -37152,10 +37152,10 @@
         <v>2592</v>
       </c>
       <c r="F1054" s="2">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G1054" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1054" s="2">
         <v>122</v>

--- a/STOK DEALER/STOK SRB.xlsx
+++ b/STOK DEALER/STOK SRB.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HPM-DESCO-PSD\Downloads\UPADTE TOOLS BUNDLING SRB\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data D\2025\UPADTE TOOLS BUNDLING SRB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7C4604D-D422-41B6-B765-A868DE720B2F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7141F43A-363F-437F-9EF0-22F46ABCA357}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{46E7093F-A843-4D56-8D6E-D290D3117D3B}"/>
   </bookViews>
@@ -9948,13 +9948,13 @@
         <v>1627</v>
       </c>
       <c r="F7" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G7" s="2">
         <v>0</v>
       </c>
       <c r="H7" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -9974,13 +9974,13 @@
         <v>1627</v>
       </c>
       <c r="F8" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
       </c>
       <c r="H8" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -13428,10 +13428,10 @@
         <v>1782</v>
       </c>
       <c r="F141" s="2">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G141" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H141" s="2">
         <v>52</v>
@@ -13480,13 +13480,13 @@
         <v>1783</v>
       </c>
       <c r="F143" s="2">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="G143" s="2">
         <v>2</v>
       </c>
       <c r="H143" s="2">
-        <v>253</v>
+        <v>252</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
@@ -13610,13 +13610,13 @@
         <v>1791</v>
       </c>
       <c r="F148" s="2">
-        <v>111</v>
+        <v>105</v>
       </c>
       <c r="G148" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H148" s="2">
-        <v>104</v>
+        <v>97</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
@@ -13873,10 +13873,10 @@
         <v>244</v>
       </c>
       <c r="G158" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H158" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
@@ -13896,13 +13896,13 @@
         <v>1791</v>
       </c>
       <c r="F159" s="2">
-        <v>796</v>
+        <v>791</v>
       </c>
       <c r="G159" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H159" s="2">
-        <v>790</v>
+        <v>786</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
@@ -13977,10 +13977,10 @@
         <v>27</v>
       </c>
       <c r="G162" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H162" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
@@ -14052,13 +14052,13 @@
         <v>207</v>
       </c>
       <c r="F165" s="2">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="G165" s="2">
         <v>3</v>
       </c>
       <c r="H165" s="2">
-        <v>114</v>
+        <v>112</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
@@ -14211,10 +14211,10 @@
         <v>46</v>
       </c>
       <c r="G171" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H171" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
@@ -14988,13 +14988,13 @@
         <v>1829</v>
       </c>
       <c r="F201" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G201" s="2">
         <v>0</v>
       </c>
       <c r="H201" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.25">
@@ -22214,13 +22214,13 @@
         <v>587</v>
       </c>
       <c r="F479" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G479" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H479" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="480" spans="1:8" x14ac:dyDescent="0.25">
@@ -22578,13 +22578,13 @@
         <v>2244</v>
       </c>
       <c r="F493" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G493" s="2">
         <v>0</v>
       </c>
       <c r="H493" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="494" spans="1:8" x14ac:dyDescent="0.25">
@@ -22734,13 +22734,13 @@
         <v>919</v>
       </c>
       <c r="F499" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G499" s="2">
         <v>0</v>
       </c>
       <c r="H499" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="500" spans="1:8" x14ac:dyDescent="0.25">
@@ -24160,13 +24160,13 @@
         <v>2280</v>
       </c>
       <c r="F554" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G554" s="2">
         <v>0</v>
       </c>
       <c r="H554" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="555" spans="1:8" x14ac:dyDescent="0.25">
@@ -24553,10 +24553,10 @@
         <v>3</v>
       </c>
       <c r="G569" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H569" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="570" spans="1:8" x14ac:dyDescent="0.25">
@@ -26396,13 +26396,13 @@
         <v>292</v>
       </c>
       <c r="F640" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G640" s="2">
         <v>0</v>
       </c>
       <c r="H640" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="641" spans="1:8" x14ac:dyDescent="0.25">
@@ -26552,13 +26552,13 @@
         <v>292</v>
       </c>
       <c r="F646" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G646" s="2">
         <v>4</v>
       </c>
       <c r="H646" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="647" spans="1:8" x14ac:dyDescent="0.25">
@@ -26838,13 +26838,13 @@
         <v>430</v>
       </c>
       <c r="F657" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G657" s="2">
         <v>1</v>
       </c>
       <c r="H657" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="658" spans="1:8" x14ac:dyDescent="0.25">
@@ -31573,10 +31573,10 @@
         <v>18</v>
       </c>
       <c r="G839" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H839" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="840" spans="1:8" x14ac:dyDescent="0.25">
@@ -34324,13 +34324,13 @@
         <v>2516</v>
       </c>
       <c r="F945" s="2">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="G945" s="2">
         <v>0</v>
       </c>
       <c r="H945" s="2">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="946" spans="1:8" x14ac:dyDescent="0.25">
@@ -34428,13 +34428,13 @@
         <v>2626</v>
       </c>
       <c r="F949" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G949" s="2">
         <v>0</v>
       </c>
       <c r="H949" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="950" spans="1:8" x14ac:dyDescent="0.25">
@@ -37158,13 +37158,13 @@
         <v>2592</v>
       </c>
       <c r="F1054" s="2">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="G1054" s="2">
         <v>1</v>
       </c>
       <c r="H1054" s="2">
-        <v>97</v>
+        <v>92</v>
       </c>
     </row>
     <row r="1055" spans="1:8" x14ac:dyDescent="0.25">
@@ -38900,13 +38900,13 @@
         <v>2735</v>
       </c>
       <c r="F1121" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1121" s="2">
         <v>0</v>
       </c>
       <c r="H1121" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1122" spans="1:8" x14ac:dyDescent="0.25">
@@ -39706,13 +39706,13 @@
         <v>2729</v>
       </c>
       <c r="F1152" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G1152" s="2">
         <v>0</v>
       </c>
       <c r="H1152" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1153" spans="1:8" x14ac:dyDescent="0.25">
@@ -39758,13 +39758,13 @@
         <v>2719</v>
       </c>
       <c r="F1154" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G1154" s="2">
         <v>0</v>
       </c>
       <c r="H1154" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1155" spans="1:8" x14ac:dyDescent="0.25">
@@ -39836,13 +39836,13 @@
         <v>2686</v>
       </c>
       <c r="F1157" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G1157" s="2">
         <v>0</v>
       </c>
       <c r="H1157" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1158" spans="1:8" x14ac:dyDescent="0.25">
@@ -41867,10 +41867,10 @@
         <v>3</v>
       </c>
       <c r="G1235" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1235" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1236" spans="1:8" x14ac:dyDescent="0.25">
@@ -42306,13 +42306,13 @@
         <v>2825</v>
       </c>
       <c r="F1252" s="2">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="G1252" s="2">
         <v>1</v>
       </c>
       <c r="H1252" s="2">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="1253" spans="1:8" x14ac:dyDescent="0.25">
@@ -42800,13 +42800,13 @@
         <v>2853</v>
       </c>
       <c r="F1271" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G1271" s="2">
         <v>0</v>
       </c>
       <c r="H1271" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1272" spans="1:8" x14ac:dyDescent="0.25">
@@ -43086,13 +43086,13 @@
         <v>2871</v>
       </c>
       <c r="F1282" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G1282" s="2">
         <v>0</v>
       </c>
       <c r="H1282" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1283" spans="1:8" x14ac:dyDescent="0.25">
@@ -43216,13 +43216,13 @@
         <v>2878</v>
       </c>
       <c r="F1287" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1287" s="2">
         <v>0</v>
       </c>
       <c r="H1287" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1288" spans="1:8" x14ac:dyDescent="0.25">
@@ -44412,13 +44412,13 @@
         <v>2948</v>
       </c>
       <c r="F1333" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1333" s="2">
         <v>0</v>
       </c>
       <c r="H1333" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1334" spans="1:8" x14ac:dyDescent="0.25">
@@ -44594,13 +44594,13 @@
         <v>2827</v>
       </c>
       <c r="F1340" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1340" s="2">
         <v>0</v>
       </c>
       <c r="H1340" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1341" spans="1:8" x14ac:dyDescent="0.25">
@@ -46102,13 +46102,13 @@
         <v>3014</v>
       </c>
       <c r="F1398" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1398" s="2">
         <v>0</v>
       </c>
       <c r="H1398" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1399" spans="1:8" x14ac:dyDescent="0.25">
@@ -46258,13 +46258,13 @@
         <v>2968</v>
       </c>
       <c r="F1404" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1404" s="2">
         <v>0</v>
       </c>
       <c r="H1404" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1405" spans="1:8" x14ac:dyDescent="0.25">
@@ -47795,10 +47795,10 @@
         <v>40</v>
       </c>
       <c r="G1463" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1463" s="2">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="1464" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK SRB.xlsx
+++ b/STOK DEALER/STOK SRB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07429346-BE2B-4776-90AB-5C1F06A642D4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0408604-1903-438D-88B0-48CBA7C5D336}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{46E7093F-A843-4D56-8D6E-D290D3117D3B}"/>
   </bookViews>
@@ -11298,13 +11298,13 @@
         <v>1678</v>
       </c>
       <c r="F62" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G62" s="2">
         <v>0</v>
       </c>
       <c r="H62" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
@@ -13348,10 +13348,10 @@
         <v>1782</v>
       </c>
       <c r="F141" s="2">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="G141" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H141" s="2">
         <v>50</v>
@@ -13374,10 +13374,10 @@
         <v>1783</v>
       </c>
       <c r="F142" s="2">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="G142" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H142" s="2">
         <v>172</v>
@@ -13400,10 +13400,10 @@
         <v>1783</v>
       </c>
       <c r="F143" s="2">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="G143" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H143" s="2">
         <v>252</v>
@@ -13530,10 +13530,10 @@
         <v>1791</v>
       </c>
       <c r="F148" s="2">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G148" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H148" s="2">
         <v>92</v>
@@ -13790,13 +13790,13 @@
         <v>1782</v>
       </c>
       <c r="F158" s="2">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="G158" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H158" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
@@ -13816,13 +13816,13 @@
         <v>1791</v>
       </c>
       <c r="F159" s="2">
-        <v>777</v>
+        <v>765</v>
       </c>
       <c r="G159" s="2">
         <v>4</v>
       </c>
       <c r="H159" s="2">
-        <v>773</v>
+        <v>761</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
@@ -13894,10 +13894,10 @@
         <v>207</v>
       </c>
       <c r="F162" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G162" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H162" s="2">
         <v>25</v>
@@ -13972,13 +13972,13 @@
         <v>207</v>
       </c>
       <c r="F165" s="2">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="G165" s="2">
         <v>3</v>
       </c>
       <c r="H165" s="2">
-        <v>109</v>
+        <v>104</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
@@ -18106,10 +18106,10 @@
         <v>2030</v>
       </c>
       <c r="F324" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G324" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H324" s="2">
         <v>0</v>
@@ -19822,10 +19822,10 @@
         <v>2147</v>
       </c>
       <c r="F390" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G390" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H390" s="2">
         <v>0</v>
@@ -20706,10 +20706,10 @@
         <v>2177</v>
       </c>
       <c r="F424" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G424" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H424" s="2">
         <v>8</v>
@@ -20758,10 +20758,10 @@
         <v>2175</v>
       </c>
       <c r="F426" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G426" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H426" s="2">
         <v>14</v>
@@ -22368,10 +22368,10 @@
         <v>359</v>
       </c>
       <c r="F488" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G488" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H488" s="2">
         <v>3</v>
@@ -22810,10 +22810,10 @@
         <v>571</v>
       </c>
       <c r="F505" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G505" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H505" s="2">
         <v>8</v>
@@ -22836,10 +22836,10 @@
         <v>2248</v>
       </c>
       <c r="F506" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G506" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H506" s="2">
         <v>0</v>
@@ -23664,10 +23664,10 @@
         <v>538</v>
       </c>
       <c r="F538" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G538" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H538" s="2">
         <v>1</v>
@@ -23690,10 +23690,10 @@
         <v>647</v>
       </c>
       <c r="F539" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G539" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H539" s="2">
         <v>0</v>
@@ -26810,10 +26810,10 @@
         <v>402</v>
       </c>
       <c r="F659" s="2">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G659" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H659" s="2">
         <v>15</v>
@@ -27044,10 +27044,10 @@
         <v>2408</v>
       </c>
       <c r="F668" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G668" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H668" s="2">
         <v>0</v>
@@ -28786,10 +28786,10 @@
         <v>2478</v>
       </c>
       <c r="F735" s="2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G735" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H735" s="2">
         <v>38</v>
@@ -29878,10 +29878,10 @@
         <v>2526</v>
       </c>
       <c r="F777" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G777" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H777" s="2">
         <v>9</v>
@@ -30814,10 +30814,10 @@
         <v>2553</v>
       </c>
       <c r="F813" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G813" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H813" s="2">
         <v>6</v>
@@ -30996,10 +30996,10 @@
         <v>2557</v>
       </c>
       <c r="F820" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G820" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H820" s="2">
         <v>4</v>
@@ -31490,13 +31490,13 @@
         <v>1958</v>
       </c>
       <c r="F839" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G839" s="2">
         <v>0</v>
       </c>
       <c r="H839" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="840" spans="1:8" x14ac:dyDescent="0.25">
@@ -31750,10 +31750,10 @@
         <v>2575</v>
       </c>
       <c r="F849" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G849" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H849" s="2">
         <v>1</v>
@@ -32036,10 +32036,10 @@
         <v>379</v>
       </c>
       <c r="F860" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G860" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H860" s="2">
         <v>0</v>
@@ -32218,10 +32218,10 @@
         <v>2565</v>
       </c>
       <c r="F867" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G867" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H867" s="2">
         <v>0</v>
@@ -32580,10 +32580,10 @@
         <v>2589</v>
       </c>
       <c r="F881" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G881" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H881" s="2">
         <v>1</v>
@@ -32710,10 +32710,10 @@
         <v>2495</v>
       </c>
       <c r="F886" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G886" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H886" s="2">
         <v>0</v>
@@ -40900,10 +40900,10 @@
         <v>1671</v>
       </c>
       <c r="F1201" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1201" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1201" s="2">
         <v>1</v>
@@ -41212,10 +41212,10 @@
         <v>2811</v>
       </c>
       <c r="F1213" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1213" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1213" s="2">
         <v>1</v>
@@ -47270,10 +47270,10 @@
         <v>565</v>
       </c>
       <c r="F1446" s="2">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G1446" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H1446" s="2">
         <v>26</v>
@@ -47712,13 +47712,13 @@
         <v>939</v>
       </c>
       <c r="F1463" s="2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G1463" s="2">
         <v>0</v>
       </c>
       <c r="H1463" s="2">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="1464" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK SRB.xlsx
+++ b/STOK DEALER/STOK SRB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0408604-1903-438D-88B0-48CBA7C5D336}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81241A5E-D74C-458C-A95B-D8732CB3B390}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{46E7093F-A843-4D56-8D6E-D290D3117D3B}"/>
   </bookViews>
@@ -9894,13 +9894,13 @@
         <v>1627</v>
       </c>
       <c r="F8" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
       </c>
       <c r="H8" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -10258,10 +10258,10 @@
         <v>1648</v>
       </c>
       <c r="F22" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G22" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H22" s="2">
         <v>2</v>
@@ -10830,13 +10830,13 @@
         <v>1672</v>
       </c>
       <c r="F44" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G44" s="2">
         <v>0</v>
       </c>
       <c r="H44" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
@@ -10882,10 +10882,10 @@
         <v>451</v>
       </c>
       <c r="F46" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G46" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H46" s="2">
         <v>1</v>
@@ -11350,13 +11350,13 @@
         <v>1260</v>
       </c>
       <c r="F64" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G64" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H64" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
@@ -13348,13 +13348,13 @@
         <v>1782</v>
       </c>
       <c r="F141" s="2">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G141" s="2">
         <v>1</v>
       </c>
       <c r="H141" s="2">
-        <v>50</v>
+        <v>47</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
@@ -13374,10 +13374,10 @@
         <v>1783</v>
       </c>
       <c r="F142" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="G142" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H142" s="2">
         <v>172</v>
@@ -13530,13 +13530,13 @@
         <v>1791</v>
       </c>
       <c r="F148" s="2">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G148" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H148" s="2">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
@@ -13790,13 +13790,13 @@
         <v>1782</v>
       </c>
       <c r="F158" s="2">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G158" s="2">
         <v>4</v>
       </c>
       <c r="H158" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
@@ -13816,13 +13816,13 @@
         <v>1791</v>
       </c>
       <c r="F159" s="2">
-        <v>765</v>
+        <v>759</v>
       </c>
       <c r="G159" s="2">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H159" s="2">
-        <v>761</v>
+        <v>752</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
@@ -13894,13 +13894,13 @@
         <v>207</v>
       </c>
       <c r="F162" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G162" s="2">
         <v>0</v>
       </c>
       <c r="H162" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
@@ -13972,13 +13972,13 @@
         <v>207</v>
       </c>
       <c r="F165" s="2">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="G165" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H165" s="2">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
@@ -16705,10 +16705,10 @@
         <v>26</v>
       </c>
       <c r="G270" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H270" s="2">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="271" spans="1:8" x14ac:dyDescent="0.25">
@@ -16809,10 +16809,10 @@
         <v>1</v>
       </c>
       <c r="G274" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H274" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="275" spans="1:8" x14ac:dyDescent="0.25">
@@ -18993,10 +18993,10 @@
         <v>1</v>
       </c>
       <c r="G358" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H358" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="359" spans="1:8" x14ac:dyDescent="0.25">
@@ -20319,10 +20319,10 @@
         <v>32</v>
       </c>
       <c r="G409" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H409" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="410" spans="1:8" x14ac:dyDescent="0.25">
@@ -20345,10 +20345,10 @@
         <v>27</v>
       </c>
       <c r="G410" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H410" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="411" spans="1:8" x14ac:dyDescent="0.25">
@@ -20368,13 +20368,13 @@
         <v>2171</v>
       </c>
       <c r="F411" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G411" s="2">
         <v>0</v>
       </c>
       <c r="H411" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="412" spans="1:8" x14ac:dyDescent="0.25">
@@ -22030,10 +22030,10 @@
         <v>1099</v>
       </c>
       <c r="F475" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G475" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H475" s="2">
         <v>1</v>
@@ -22134,13 +22134,13 @@
         <v>587</v>
       </c>
       <c r="F479" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G479" s="2">
         <v>2</v>
       </c>
       <c r="H479" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="480" spans="1:8" x14ac:dyDescent="0.25">
@@ -24080,13 +24080,13 @@
         <v>2280</v>
       </c>
       <c r="F554" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G554" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H554" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="555" spans="1:8" x14ac:dyDescent="0.25">
@@ -26758,13 +26758,13 @@
         <v>430</v>
       </c>
       <c r="F657" s="2">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G657" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H657" s="2">
-        <v>27</v>
+        <v>23</v>
       </c>
     </row>
     <row r="658" spans="1:8" x14ac:dyDescent="0.25">
@@ -28789,10 +28789,10 @@
         <v>38</v>
       </c>
       <c r="G735" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H735" s="2">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="736" spans="1:8" x14ac:dyDescent="0.25">
@@ -29959,10 +29959,10 @@
         <v>5</v>
       </c>
       <c r="G780" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H780" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="781" spans="1:8" x14ac:dyDescent="0.25">
@@ -30346,10 +30346,10 @@
         <v>1110</v>
       </c>
       <c r="F795" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G795" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H795" s="2">
         <v>18</v>
@@ -31753,10 +31753,10 @@
         <v>1</v>
       </c>
       <c r="G849" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H849" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="850" spans="1:8" x14ac:dyDescent="0.25">
@@ -32013,10 +32013,10 @@
         <v>2</v>
       </c>
       <c r="G859" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H859" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="860" spans="1:8" x14ac:dyDescent="0.25">
@@ -37078,13 +37078,13 @@
         <v>2592</v>
       </c>
       <c r="F1054" s="2">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="G1054" s="2">
         <v>1</v>
       </c>
       <c r="H1054" s="2">
-        <v>88</v>
+        <v>85</v>
       </c>
     </row>
     <row r="1055" spans="1:8" x14ac:dyDescent="0.25">
@@ -38846,13 +38846,13 @@
         <v>2719</v>
       </c>
       <c r="F1122" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1122" s="2">
         <v>0</v>
       </c>
       <c r="H1122" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1123" spans="1:8" x14ac:dyDescent="0.25">
@@ -39704,13 +39704,13 @@
         <v>2730</v>
       </c>
       <c r="F1155" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G1155" s="2">
         <v>0</v>
       </c>
       <c r="H1155" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1156" spans="1:8" x14ac:dyDescent="0.25">
@@ -41212,10 +41212,10 @@
         <v>2811</v>
       </c>
       <c r="F1213" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1213" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1213" s="2">
         <v>1</v>
@@ -41680,13 +41680,13 @@
         <v>586</v>
       </c>
       <c r="F1231" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G1231" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1231" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1232" spans="1:8" x14ac:dyDescent="0.25">
@@ -42226,13 +42226,13 @@
         <v>2825</v>
       </c>
       <c r="F1252" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G1252" s="2">
         <v>2</v>
       </c>
       <c r="H1252" s="2">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="1253" spans="1:8" x14ac:dyDescent="0.25">
@@ -45424,13 +45424,13 @@
         <v>2870</v>
       </c>
       <c r="F1375" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1375" s="2">
         <v>0</v>
       </c>
       <c r="H1375" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1376" spans="1:8" x14ac:dyDescent="0.25">
@@ -45710,13 +45710,13 @@
         <v>3014</v>
       </c>
       <c r="F1386" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G1386" s="2">
         <v>0</v>
       </c>
       <c r="H1386" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1387" spans="1:8" x14ac:dyDescent="0.25">
@@ -45814,13 +45814,13 @@
         <v>2870</v>
       </c>
       <c r="F1390" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1390" s="2">
         <v>0</v>
       </c>
       <c r="H1390" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1391" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK SRB.xlsx
+++ b/STOK DEALER/STOK SRB.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\STOK DEALER\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data D\2025\UPADTE TOOLS BUNDLING SRB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{81241A5E-D74C-458C-A95B-D8732CB3B390}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1CCFE1D-B7DD-486A-B131-BDB40F303B5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{46E7093F-A843-4D56-8D6E-D290D3117D3B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{46E7093F-A843-4D56-8D6E-D290D3117D3B}"/>
   </bookViews>
   <sheets>
     <sheet name="STOK DEALER" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5822" uniqueCount="3082">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5823" uniqueCount="3083">
   <si>
     <t>No</t>
   </si>
@@ -9276,6 +9276,9 @@
   </si>
   <si>
     <t>SPDMTR PRTECTOR PCX 160 C/A</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
   </si>
   <si>
     <t>86836K2FN90ZA</t>
@@ -9313,7 +9316,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -9336,17 +9339,69 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -9682,7 +9737,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2BB8C35-92DF-4C27-A2CF-D1CDC7F4FE42}">
-  <dimension ref="A1:H1464"/>
+  <dimension ref="A1:H1465"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -9816,13 +9871,13 @@
         <v>1627</v>
       </c>
       <c r="F5" s="2">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="G5" s="2">
         <v>0</v>
       </c>
       <c r="H5" s="2">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -9894,13 +9949,13 @@
         <v>1627</v>
       </c>
       <c r="F8" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
       </c>
       <c r="H8" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -9920,13 +9975,13 @@
         <v>1628</v>
       </c>
       <c r="F9" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G9" s="2">
         <v>0</v>
       </c>
       <c r="H9" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -10391,10 +10446,10 @@
         <v>2</v>
       </c>
       <c r="G27" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H27" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.25">
@@ -13530,13 +13585,13 @@
         <v>1791</v>
       </c>
       <c r="F148" s="2">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="G148" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H148" s="2">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
@@ -13790,13 +13845,13 @@
         <v>1782</v>
       </c>
       <c r="F158" s="2">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G158" s="2">
         <v>4</v>
       </c>
       <c r="H158" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
@@ -13816,13 +13871,13 @@
         <v>1791</v>
       </c>
       <c r="F159" s="2">
-        <v>759</v>
+        <v>751</v>
       </c>
       <c r="G159" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H159" s="2">
-        <v>752</v>
+        <v>745</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
@@ -13972,13 +14027,13 @@
         <v>207</v>
       </c>
       <c r="F165" s="2">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G165" s="2">
         <v>2</v>
       </c>
       <c r="H165" s="2">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
@@ -26758,10 +26813,10 @@
         <v>430</v>
       </c>
       <c r="F657" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G657" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H657" s="2">
         <v>23</v>
@@ -28789,10 +28844,10 @@
         <v>38</v>
       </c>
       <c r="G735" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H735" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="736" spans="1:8" x14ac:dyDescent="0.25">
@@ -34244,13 +34299,13 @@
         <v>2516</v>
       </c>
       <c r="F945" s="2">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="G945" s="2">
         <v>0</v>
       </c>
       <c r="H945" s="2">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="946" spans="1:8" x14ac:dyDescent="0.25">
@@ -34348,13 +34403,13 @@
         <v>2626</v>
       </c>
       <c r="F949" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G949" s="2">
         <v>0</v>
       </c>
       <c r="H949" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="950" spans="1:8" x14ac:dyDescent="0.25">
@@ -34426,13 +34481,13 @@
         <v>2631</v>
       </c>
       <c r="F952" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G952" s="2">
         <v>0</v>
       </c>
       <c r="H952" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="953" spans="1:8" x14ac:dyDescent="0.25">
@@ -37078,13 +37133,13 @@
         <v>2592</v>
       </c>
       <c r="F1054" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
       <c r="G1054" s="2">
         <v>1</v>
       </c>
       <c r="H1054" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
     </row>
     <row r="1055" spans="1:8" x14ac:dyDescent="0.25">
@@ -38548,10 +38603,10 @@
         <v>1110</v>
       </c>
       <c r="B1111" s="2" t="s">
-        <v>3080</v>
+        <v>3081</v>
       </c>
       <c r="C1111" s="2" t="s">
-        <v>3081</v>
+        <v>3082</v>
       </c>
       <c r="D1111" s="2" t="s">
         <v>1623</v>
@@ -38690,13 +38745,13 @@
         <v>2734</v>
       </c>
       <c r="F1116" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1116" s="2">
         <v>0</v>
       </c>
       <c r="H1116" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1117" spans="1:8" x14ac:dyDescent="0.25">
@@ -38742,13 +38797,13 @@
         <v>2734</v>
       </c>
       <c r="F1118" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1118" s="2">
         <v>0</v>
       </c>
       <c r="H1118" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1119" spans="1:8" x14ac:dyDescent="0.25">
@@ -39626,13 +39681,13 @@
         <v>2729</v>
       </c>
       <c r="F1152" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G1152" s="2">
         <v>0</v>
       </c>
       <c r="H1152" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1153" spans="1:8" x14ac:dyDescent="0.25">
@@ -39652,13 +39707,13 @@
         <v>2730</v>
       </c>
       <c r="F1153" s="2">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="G1153" s="2">
         <v>0</v>
       </c>
       <c r="H1153" s="2">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1154" spans="1:8" x14ac:dyDescent="0.25">
@@ -39704,13 +39759,13 @@
         <v>2730</v>
       </c>
       <c r="F1155" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G1155" s="2">
         <v>0</v>
       </c>
       <c r="H1155" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1156" spans="1:8" x14ac:dyDescent="0.25">
@@ -39782,13 +39837,13 @@
         <v>2730</v>
       </c>
       <c r="F1158" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G1158" s="2">
         <v>0</v>
       </c>
       <c r="H1158" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1159" spans="1:8" x14ac:dyDescent="0.25">
@@ -42226,13 +42281,13 @@
         <v>2825</v>
       </c>
       <c r="F1252" s="2">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="G1252" s="2">
         <v>2</v>
       </c>
       <c r="H1252" s="2">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="1253" spans="1:8" x14ac:dyDescent="0.25">
@@ -42720,13 +42775,13 @@
         <v>2853</v>
       </c>
       <c r="F1271" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G1271" s="2">
         <v>0</v>
       </c>
       <c r="H1271" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1272" spans="1:8" x14ac:dyDescent="0.25">
@@ -45866,13 +45921,13 @@
         <v>2847</v>
       </c>
       <c r="F1392" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G1392" s="2">
         <v>0</v>
       </c>
       <c r="H1392" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1393" spans="1:8" x14ac:dyDescent="0.25">
@@ -45892,13 +45947,13 @@
         <v>2996</v>
       </c>
       <c r="F1393" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G1393" s="2">
         <v>0</v>
       </c>
       <c r="H1393" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1394" spans="1:8" x14ac:dyDescent="0.25">
@@ -46022,13 +46077,13 @@
         <v>3014</v>
       </c>
       <c r="F1398" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1398" s="2">
         <v>0</v>
       </c>
       <c r="H1398" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1399" spans="1:8" x14ac:dyDescent="0.25">
@@ -46178,13 +46233,13 @@
         <v>2968</v>
       </c>
       <c r="F1404" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1404" s="2">
         <v>0</v>
       </c>
       <c r="H1404" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1405" spans="1:8" x14ac:dyDescent="0.25">
@@ -46438,13 +46493,13 @@
         <v>2847</v>
       </c>
       <c r="F1414" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1414" s="2">
         <v>0</v>
       </c>
       <c r="H1414" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1415" spans="1:8" x14ac:dyDescent="0.25">
@@ -46490,13 +46545,13 @@
         <v>2996</v>
       </c>
       <c r="F1416" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G1416" s="2">
         <v>0</v>
       </c>
       <c r="H1416" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1417" spans="1:8" x14ac:dyDescent="0.25">
@@ -47221,10 +47276,10 @@
         <v>25</v>
       </c>
       <c r="G1444" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1444" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1445" spans="1:8" x14ac:dyDescent="0.25">
@@ -47400,13 +47455,13 @@
         <v>2354</v>
       </c>
       <c r="F1451" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1451" s="2">
         <v>0</v>
       </c>
       <c r="H1451" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1452" spans="1:8" x14ac:dyDescent="0.25">
@@ -47721,7 +47776,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="1464" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1464" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1464" s="2">
         <v>1463</v>
       </c>
@@ -47747,7 +47802,28 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1465" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1465" s="5" t="s">
+        <v>3080</v>
+      </c>
+      <c r="B1465" s="6"/>
+      <c r="C1465" s="6"/>
+      <c r="D1465" s="6"/>
+      <c r="E1465" s="7"/>
+      <c r="F1465" s="3">
+        <v>5968</v>
+      </c>
+      <c r="G1465" s="4">
+        <v>144</v>
+      </c>
+      <c r="H1465" s="3">
+        <v>5824</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1465:E1465"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/STOK DEALER/STOK SRB.xlsx
+++ b/STOK DEALER/STOK SRB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data D\2025\UPADTE TOOLS BUNDLING SRB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1CCFE1D-B7DD-486A-B131-BDB40F303B5A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA5CE7F9-6C76-4542-8EF3-71AFE2A757BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{46E7093F-A843-4D56-8D6E-D290D3117D3B}"/>
   </bookViews>
@@ -9793,13 +9793,13 @@
         <v>1624</v>
       </c>
       <c r="F2" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G2" s="2">
         <v>0</v>
       </c>
       <c r="H2" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -9871,13 +9871,13 @@
         <v>1627</v>
       </c>
       <c r="F5" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G5" s="2">
         <v>0</v>
       </c>
       <c r="H5" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -9923,13 +9923,13 @@
         <v>1627</v>
       </c>
       <c r="F7" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G7" s="2">
         <v>0</v>
       </c>
       <c r="H7" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -10651,13 +10651,13 @@
         <v>1656</v>
       </c>
       <c r="F35" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G35" s="2">
         <v>0</v>
       </c>
       <c r="H35" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
@@ -13403,13 +13403,13 @@
         <v>1782</v>
       </c>
       <c r="F141" s="2">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G141" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H141" s="2">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
@@ -13429,13 +13429,13 @@
         <v>1783</v>
       </c>
       <c r="F142" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="G142" s="2">
         <v>0</v>
       </c>
       <c r="H142" s="2">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
@@ -13845,13 +13845,13 @@
         <v>1782</v>
       </c>
       <c r="F158" s="2">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="G158" s="2">
         <v>4</v>
       </c>
       <c r="H158" s="2">
-        <v>231</v>
+        <v>229</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
@@ -13871,13 +13871,13 @@
         <v>1791</v>
       </c>
       <c r="F159" s="2">
-        <v>751</v>
+        <v>738</v>
       </c>
       <c r="G159" s="2">
         <v>6</v>
       </c>
       <c r="H159" s="2">
-        <v>745</v>
+        <v>732</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
@@ -14027,13 +14027,13 @@
         <v>207</v>
       </c>
       <c r="F165" s="2">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="G165" s="2">
         <v>2</v>
       </c>
       <c r="H165" s="2">
-        <v>102</v>
+        <v>99</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
@@ -15197,10 +15197,10 @@
         <v>1856</v>
       </c>
       <c r="F210" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G210" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H210" s="2">
         <v>10</v>
@@ -18840,10 +18840,10 @@
         <v>1</v>
       </c>
       <c r="G350" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H350" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="351" spans="1:8" x14ac:dyDescent="0.25">
@@ -26527,13 +26527,13 @@
         <v>292</v>
       </c>
       <c r="F646" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G646" s="2">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="H646" s="2">
-        <v>20</v>
+        <v>15</v>
       </c>
     </row>
     <row r="647" spans="1:8" x14ac:dyDescent="0.25">
@@ -26816,10 +26816,10 @@
         <v>24</v>
       </c>
       <c r="G657" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H657" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="658" spans="1:8" x14ac:dyDescent="0.25">
@@ -29936,10 +29936,10 @@
         <v>9</v>
       </c>
       <c r="G777" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H777" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="778" spans="1:8" x14ac:dyDescent="0.25">
@@ -30794,10 +30794,10 @@
         <v>5</v>
       </c>
       <c r="G810" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H810" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="811" spans="1:8" x14ac:dyDescent="0.25">
@@ -30872,10 +30872,10 @@
         <v>6</v>
       </c>
       <c r="G813" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H813" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="814" spans="1:8" x14ac:dyDescent="0.25">
@@ -32612,10 +32612,10 @@
         <v>3</v>
       </c>
       <c r="G880" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H880" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="881" spans="1:8" x14ac:dyDescent="0.25">
@@ -33600,10 +33600,10 @@
         <v>1</v>
       </c>
       <c r="G918" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H918" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="919" spans="1:8" x14ac:dyDescent="0.25">
@@ -33964,10 +33964,10 @@
         <v>1</v>
       </c>
       <c r="G932" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H932" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="933" spans="1:8" x14ac:dyDescent="0.25">
@@ -34351,13 +34351,13 @@
         <v>2627</v>
       </c>
       <c r="F947" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G947" s="2">
         <v>0</v>
       </c>
       <c r="H947" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="948" spans="1:8" x14ac:dyDescent="0.25">
@@ -35056,10 +35056,10 @@
         <v>1</v>
       </c>
       <c r="G974" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H974" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="975" spans="1:8" x14ac:dyDescent="0.25">
@@ -37133,13 +37133,13 @@
         <v>2592</v>
       </c>
       <c r="F1054" s="2">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G1054" s="2">
         <v>1</v>
       </c>
       <c r="H1054" s="2">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="1055" spans="1:8" x14ac:dyDescent="0.25">
@@ -37474,10 +37474,10 @@
         <v>1</v>
       </c>
       <c r="G1067" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1067" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1068" spans="1:8" x14ac:dyDescent="0.25">
@@ -38693,13 +38693,13 @@
         <v>2731</v>
       </c>
       <c r="F1114" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1114" s="2">
         <v>0</v>
       </c>
       <c r="H1114" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1115" spans="1:8" x14ac:dyDescent="0.25">
@@ -38797,13 +38797,13 @@
         <v>2734</v>
       </c>
       <c r="F1118" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1118" s="2">
         <v>0</v>
       </c>
       <c r="H1118" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1119" spans="1:8" x14ac:dyDescent="0.25">
@@ -38875,13 +38875,13 @@
         <v>2735</v>
       </c>
       <c r="F1121" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1121" s="2">
         <v>0</v>
       </c>
       <c r="H1121" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1122" spans="1:8" x14ac:dyDescent="0.25">
@@ -39603,13 +39603,13 @@
         <v>2729</v>
       </c>
       <c r="F1149" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1149" s="2">
         <v>0</v>
       </c>
       <c r="H1149" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1150" spans="1:8" x14ac:dyDescent="0.25">
@@ -39681,13 +39681,13 @@
         <v>2729</v>
       </c>
       <c r="F1152" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1152" s="2">
         <v>0</v>
       </c>
       <c r="H1152" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1153" spans="1:8" x14ac:dyDescent="0.25">
@@ -40721,13 +40721,13 @@
         <v>2795</v>
       </c>
       <c r="F1192" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G1192" s="2">
         <v>0</v>
       </c>
       <c r="H1192" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1193" spans="1:8" x14ac:dyDescent="0.25">
@@ -41088,10 +41088,10 @@
         <v>1</v>
       </c>
       <c r="G1206" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1206" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1207" spans="1:8" x14ac:dyDescent="0.25">
@@ -41192,10 +41192,10 @@
         <v>1</v>
       </c>
       <c r="G1210" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1210" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1211" spans="1:8" x14ac:dyDescent="0.25">
@@ -42281,13 +42281,13 @@
         <v>2825</v>
       </c>
       <c r="F1252" s="2">
-        <v>56</v>
+        <v>51</v>
       </c>
       <c r="G1252" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1252" s="2">
-        <v>54</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1253" spans="1:8" x14ac:dyDescent="0.25">
@@ -44725,13 +44725,13 @@
         <v>2955</v>
       </c>
       <c r="F1346" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G1346" s="2">
         <v>0</v>
       </c>
       <c r="H1346" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1347" spans="1:8" x14ac:dyDescent="0.25">
@@ -45921,13 +45921,13 @@
         <v>2847</v>
       </c>
       <c r="F1392" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G1392" s="2">
         <v>0</v>
       </c>
       <c r="H1392" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1393" spans="1:8" x14ac:dyDescent="0.25">
@@ -46077,13 +46077,13 @@
         <v>3014</v>
       </c>
       <c r="F1398" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G1398" s="2">
         <v>0</v>
       </c>
       <c r="H1398" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1399" spans="1:8" x14ac:dyDescent="0.25">
@@ -46779,13 +46779,13 @@
         <v>1626</v>
       </c>
       <c r="F1425" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1425" s="2">
         <v>0</v>
       </c>
       <c r="H1425" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1426" spans="1:8" x14ac:dyDescent="0.25">
@@ -47039,13 +47039,13 @@
         <v>3044</v>
       </c>
       <c r="F1435" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1435" s="2">
         <v>0</v>
       </c>
       <c r="H1435" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1436" spans="1:8" x14ac:dyDescent="0.25">
@@ -47273,10 +47273,10 @@
         <v>207</v>
       </c>
       <c r="F1444" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G1444" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1444" s="2">
         <v>24</v>

--- a/STOK DEALER/STOK SRB.xlsx
+++ b/STOK DEALER/STOK SRB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data D\2025\UPADTE TOOLS BUNDLING SRB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA5CE7F9-6C76-4542-8EF3-71AFE2A757BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{016EAE4C-9957-40EE-B0C8-9A998F416F7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{46E7093F-A843-4D56-8D6E-D290D3117D3B}"/>
   </bookViews>
@@ -10888,10 +10888,10 @@
         <v>14</v>
       </c>
       <c r="G44" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H44" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
@@ -11408,10 +11408,10 @@
         <v>29</v>
       </c>
       <c r="G64" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H64" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
@@ -13403,10 +13403,10 @@
         <v>1782</v>
       </c>
       <c r="F141" s="2">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="G141" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H141" s="2">
         <v>45</v>
@@ -13432,10 +13432,10 @@
         <v>171</v>
       </c>
       <c r="G142" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H142" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
@@ -13585,13 +13585,13 @@
         <v>1791</v>
       </c>
       <c r="F148" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="G148" s="2">
         <v>1</v>
       </c>
       <c r="H148" s="2">
-        <v>86</v>
+        <v>79</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
@@ -13845,13 +13845,13 @@
         <v>1782</v>
       </c>
       <c r="F158" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G158" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H158" s="2">
-        <v>229</v>
+        <v>226</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
@@ -13871,13 +13871,13 @@
         <v>1791</v>
       </c>
       <c r="F159" s="2">
-        <v>738</v>
+        <v>733</v>
       </c>
       <c r="G159" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H159" s="2">
-        <v>732</v>
+        <v>726</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
@@ -14027,13 +14027,13 @@
         <v>207</v>
       </c>
       <c r="F165" s="2">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G165" s="2">
         <v>2</v>
       </c>
       <c r="H165" s="2">
-        <v>99</v>
+        <v>97</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
@@ -16760,10 +16760,10 @@
         <v>26</v>
       </c>
       <c r="G270" s="2">
-        <v>2</v>
+        <v>18</v>
       </c>
       <c r="H270" s="2">
-        <v>24</v>
+        <v>8</v>
       </c>
     </row>
     <row r="271" spans="1:8" x14ac:dyDescent="0.25">
@@ -18837,10 +18837,10 @@
         <v>2084</v>
       </c>
       <c r="F350" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G350" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H350" s="2">
         <v>0</v>
@@ -20426,10 +20426,10 @@
         <v>20</v>
       </c>
       <c r="G411" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H411" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="412" spans="1:8" x14ac:dyDescent="0.25">
@@ -20816,10 +20816,10 @@
         <v>14</v>
       </c>
       <c r="G426" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H426" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="427" spans="1:8" x14ac:dyDescent="0.25">
@@ -26371,13 +26371,13 @@
         <v>292</v>
       </c>
       <c r="F640" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G640" s="2">
         <v>0</v>
       </c>
       <c r="H640" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="641" spans="1:8" x14ac:dyDescent="0.25">
@@ -26527,13 +26527,13 @@
         <v>292</v>
       </c>
       <c r="F646" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G646" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H646" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="647" spans="1:8" x14ac:dyDescent="0.25">
@@ -26790,10 +26790,10 @@
         <v>41</v>
       </c>
       <c r="G656" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H656" s="2">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="657" spans="1:8" x14ac:dyDescent="0.25">
@@ -26813,13 +26813,13 @@
         <v>430</v>
       </c>
       <c r="F657" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G657" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H657" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="658" spans="1:8" x14ac:dyDescent="0.25">
@@ -26868,10 +26868,10 @@
         <v>15</v>
       </c>
       <c r="G659" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H659" s="2">
-        <v>15</v>
+        <v>5</v>
       </c>
     </row>
     <row r="660" spans="1:8" x14ac:dyDescent="0.25">
@@ -28064,10 +28064,10 @@
         <v>1</v>
       </c>
       <c r="G705" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H705" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="706" spans="1:8" x14ac:dyDescent="0.25">
@@ -30011,13 +30011,13 @@
         <v>2529</v>
       </c>
       <c r="F780" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G780" s="2">
         <v>1</v>
       </c>
       <c r="H780" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="781" spans="1:8" x14ac:dyDescent="0.25">
@@ -30947,13 +30947,13 @@
         <v>2554</v>
       </c>
       <c r="F816" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G816" s="2">
         <v>0</v>
       </c>
       <c r="H816" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="817" spans="1:8" x14ac:dyDescent="0.25">
@@ -32716,10 +32716,10 @@
         <v>2</v>
       </c>
       <c r="G884" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H884" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="885" spans="1:8" x14ac:dyDescent="0.25">
@@ -34299,13 +34299,13 @@
         <v>2516</v>
       </c>
       <c r="F945" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G945" s="2">
         <v>0</v>
       </c>
       <c r="H945" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="946" spans="1:8" x14ac:dyDescent="0.25">
@@ -36044,10 +36044,10 @@
         <v>1</v>
       </c>
       <c r="G1012" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1012" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1013" spans="1:8" x14ac:dyDescent="0.25">
@@ -37133,13 +37133,13 @@
         <v>2592</v>
       </c>
       <c r="F1054" s="2">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="G1054" s="2">
         <v>1</v>
       </c>
       <c r="H1054" s="2">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="1055" spans="1:8" x14ac:dyDescent="0.25">
@@ -39733,13 +39733,13 @@
         <v>2719</v>
       </c>
       <c r="F1154" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G1154" s="2">
         <v>0</v>
       </c>
       <c r="H1154" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1155" spans="1:8" x14ac:dyDescent="0.25">
@@ -39759,13 +39759,13 @@
         <v>2730</v>
       </c>
       <c r="F1155" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G1155" s="2">
         <v>0</v>
       </c>
       <c r="H1155" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1156" spans="1:8" x14ac:dyDescent="0.25">
@@ -42102,10 +42102,10 @@
         <v>28</v>
       </c>
       <c r="G1245" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1245" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1246" spans="1:8" x14ac:dyDescent="0.25">
@@ -42281,13 +42281,13 @@
         <v>2825</v>
       </c>
       <c r="F1252" s="2">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G1252" s="2">
         <v>1</v>
       </c>
       <c r="H1252" s="2">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1253" spans="1:8" x14ac:dyDescent="0.25">
@@ -44387,13 +44387,13 @@
         <v>2948</v>
       </c>
       <c r="F1333" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1333" s="2">
         <v>0</v>
       </c>
       <c r="H1333" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1334" spans="1:8" x14ac:dyDescent="0.25">
@@ -45895,13 +45895,13 @@
         <v>3017</v>
       </c>
       <c r="F1391" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G1391" s="2">
         <v>0</v>
       </c>
       <c r="H1391" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1392" spans="1:8" x14ac:dyDescent="0.25">
@@ -46519,13 +46519,13 @@
         <v>2917</v>
       </c>
       <c r="F1415" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1415" s="2">
         <v>0</v>
       </c>
       <c r="H1415" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1416" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK SRB.xlsx
+++ b/STOK DEALER/STOK SRB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data D\2025\UPADTE TOOLS BUNDLING SRB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{016EAE4C-9957-40EE-B0C8-9A998F416F7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{873F944D-265E-42C2-A43A-E77B2534EAE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{46E7093F-A843-4D56-8D6E-D290D3117D3B}"/>
   </bookViews>
@@ -9897,13 +9897,13 @@
         <v>1627</v>
       </c>
       <c r="F6" s="2">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
       </c>
       <c r="H6" s="2">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -9923,13 +9923,13 @@
         <v>1627</v>
       </c>
       <c r="F7" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G7" s="2">
         <v>0</v>
       </c>
       <c r="H7" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -9975,13 +9975,13 @@
         <v>1628</v>
       </c>
       <c r="F9" s="2">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="G9" s="2">
         <v>0</v>
       </c>
       <c r="H9" s="2">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -11405,13 +11405,13 @@
         <v>1260</v>
       </c>
       <c r="F64" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G64" s="2">
         <v>4</v>
       </c>
       <c r="H64" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
@@ -13403,13 +13403,13 @@
         <v>1782</v>
       </c>
       <c r="F141" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G141" s="2">
         <v>1</v>
       </c>
       <c r="H141" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
@@ -13429,13 +13429,13 @@
         <v>1783</v>
       </c>
       <c r="F142" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="G142" s="2">
         <v>2</v>
       </c>
       <c r="H142" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
@@ -13585,13 +13585,13 @@
         <v>1791</v>
       </c>
       <c r="F148" s="2">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="G148" s="2">
         <v>1</v>
       </c>
       <c r="H148" s="2">
-        <v>79</v>
+        <v>65</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
@@ -13845,13 +13845,13 @@
         <v>1782</v>
       </c>
       <c r="F158" s="2">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="G158" s="2">
         <v>6</v>
       </c>
       <c r="H158" s="2">
-        <v>226</v>
+        <v>223</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
@@ -13871,13 +13871,13 @@
         <v>1791</v>
       </c>
       <c r="F159" s="2">
-        <v>733</v>
+        <v>717</v>
       </c>
       <c r="G159" s="2">
         <v>7</v>
       </c>
       <c r="H159" s="2">
-        <v>726</v>
+        <v>710</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
@@ -14027,13 +14027,13 @@
         <v>207</v>
       </c>
       <c r="F165" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G165" s="2">
         <v>2</v>
       </c>
       <c r="H165" s="2">
-        <v>97</v>
+        <v>96</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
@@ -14755,13 +14755,13 @@
         <v>1624</v>
       </c>
       <c r="F193" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G193" s="2">
         <v>0</v>
       </c>
       <c r="H193" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.25">
@@ -15405,13 +15405,13 @@
         <v>1865</v>
       </c>
       <c r="F218" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G218" s="2">
         <v>0</v>
       </c>
       <c r="H218" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.25">
@@ -18892,10 +18892,10 @@
         <v>2</v>
       </c>
       <c r="G352" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H352" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="353" spans="1:8" x14ac:dyDescent="0.25">
@@ -20163,13 +20163,13 @@
         <v>1814</v>
       </c>
       <c r="F401" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G401" s="2">
         <v>0</v>
       </c>
       <c r="H401" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="402" spans="1:8" x14ac:dyDescent="0.25">
@@ -20761,13 +20761,13 @@
         <v>2177</v>
       </c>
       <c r="F424" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G424" s="2">
         <v>0</v>
       </c>
       <c r="H424" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="425" spans="1:8" x14ac:dyDescent="0.25">
@@ -24239,13 +24239,13 @@
         <v>2282</v>
       </c>
       <c r="F558" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G558" s="2">
         <v>0</v>
       </c>
       <c r="H558" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="559" spans="1:8" x14ac:dyDescent="0.25">
@@ -26813,13 +26813,13 @@
         <v>430</v>
       </c>
       <c r="F657" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G657" s="2">
         <v>2</v>
       </c>
       <c r="H657" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="658" spans="1:8" x14ac:dyDescent="0.25">
@@ -29829,13 +29829,13 @@
         <v>2518</v>
       </c>
       <c r="F773" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G773" s="2">
         <v>0</v>
       </c>
       <c r="H773" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="774" spans="1:8" x14ac:dyDescent="0.25">
@@ -30011,13 +30011,13 @@
         <v>2529</v>
       </c>
       <c r="F780" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G780" s="2">
         <v>1</v>
       </c>
       <c r="H780" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="781" spans="1:8" x14ac:dyDescent="0.25">
@@ -30791,13 +30791,13 @@
         <v>2525</v>
       </c>
       <c r="F810" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G810" s="2">
         <v>1</v>
       </c>
       <c r="H810" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="811" spans="1:8" x14ac:dyDescent="0.25">
@@ -31025,13 +31025,13 @@
         <v>2556</v>
       </c>
       <c r="F819" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G819" s="2">
         <v>0</v>
       </c>
       <c r="H819" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="820" spans="1:8" x14ac:dyDescent="0.25">
@@ -33730,10 +33730,10 @@
         <v>1</v>
       </c>
       <c r="G923" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H923" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="924" spans="1:8" x14ac:dyDescent="0.25">
@@ -34299,13 +34299,13 @@
         <v>2516</v>
       </c>
       <c r="F945" s="2">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G945" s="2">
         <v>0</v>
       </c>
       <c r="H945" s="2">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="946" spans="1:8" x14ac:dyDescent="0.25">
@@ -34351,13 +34351,13 @@
         <v>2627</v>
       </c>
       <c r="F947" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G947" s="2">
         <v>0</v>
       </c>
       <c r="H947" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="948" spans="1:8" x14ac:dyDescent="0.25">
@@ -34481,13 +34481,13 @@
         <v>2631</v>
       </c>
       <c r="F952" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G952" s="2">
         <v>0</v>
       </c>
       <c r="H952" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="953" spans="1:8" x14ac:dyDescent="0.25">
@@ -37133,13 +37133,13 @@
         <v>2592</v>
       </c>
       <c r="F1054" s="2">
-        <v>71</v>
+        <v>62</v>
       </c>
       <c r="G1054" s="2">
         <v>1</v>
       </c>
       <c r="H1054" s="2">
-        <v>70</v>
+        <v>61</v>
       </c>
     </row>
     <row r="1055" spans="1:8" x14ac:dyDescent="0.25">
@@ -38667,13 +38667,13 @@
         <v>2730</v>
       </c>
       <c r="F1113" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1113" s="2">
         <v>0</v>
       </c>
       <c r="H1113" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1114" spans="1:8" x14ac:dyDescent="0.25">
@@ -38797,13 +38797,13 @@
         <v>2734</v>
       </c>
       <c r="F1118" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1118" s="2">
         <v>0</v>
       </c>
       <c r="H1118" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1119" spans="1:8" x14ac:dyDescent="0.25">
@@ -38875,13 +38875,13 @@
         <v>2735</v>
       </c>
       <c r="F1121" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1121" s="2">
         <v>0</v>
       </c>
       <c r="H1121" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1122" spans="1:8" x14ac:dyDescent="0.25">
@@ -39629,13 +39629,13 @@
         <v>2729</v>
       </c>
       <c r="F1150" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G1150" s="2">
         <v>0</v>
       </c>
       <c r="H1150" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1151" spans="1:8" x14ac:dyDescent="0.25">
@@ -39681,13 +39681,13 @@
         <v>2729</v>
       </c>
       <c r="F1152" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1152" s="2">
         <v>0</v>
       </c>
       <c r="H1152" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1153" spans="1:8" x14ac:dyDescent="0.25">
@@ -39785,13 +39785,13 @@
         <v>2730</v>
       </c>
       <c r="F1156" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G1156" s="2">
         <v>0</v>
       </c>
       <c r="H1156" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1157" spans="1:8" x14ac:dyDescent="0.25">
@@ -42281,13 +42281,13 @@
         <v>2825</v>
       </c>
       <c r="F1252" s="2">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="G1252" s="2">
         <v>1</v>
       </c>
       <c r="H1252" s="2">
-        <v>49</v>
+        <v>45</v>
       </c>
     </row>
     <row r="1253" spans="1:8" x14ac:dyDescent="0.25">
@@ -42775,13 +42775,13 @@
         <v>2853</v>
       </c>
       <c r="F1271" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="G1271" s="2">
         <v>0</v>
       </c>
       <c r="H1271" s="2">
-        <v>11</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1272" spans="1:8" x14ac:dyDescent="0.25">
@@ -42957,13 +42957,13 @@
         <v>2869</v>
       </c>
       <c r="F1278" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1278" s="2">
         <v>0</v>
       </c>
       <c r="H1278" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1279" spans="1:8" x14ac:dyDescent="0.25">
@@ -45765,13 +45765,13 @@
         <v>3014</v>
       </c>
       <c r="F1386" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G1386" s="2">
         <v>0</v>
       </c>
       <c r="H1386" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1387" spans="1:8" x14ac:dyDescent="0.25">
@@ -46181,13 +46181,13 @@
         <v>3014</v>
       </c>
       <c r="F1402" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G1402" s="2">
         <v>0</v>
       </c>
       <c r="H1402" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1403" spans="1:8" x14ac:dyDescent="0.25">
@@ -47455,13 +47455,13 @@
         <v>2354</v>
       </c>
       <c r="F1451" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1451" s="2">
         <v>0</v>
       </c>
       <c r="H1451" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1452" spans="1:8" x14ac:dyDescent="0.25">
@@ -47715,13 +47715,13 @@
         <v>1665</v>
       </c>
       <c r="F1461" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1461" s="2">
         <v>0</v>
       </c>
       <c r="H1461" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1462" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK SRB.xlsx
+++ b/STOK DEALER/STOK SRB.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data D\2025\UPADTE TOOLS BUNDLING SRB\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{873F944D-265E-42C2-A43A-E77B2534EAE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{745D82DE-8819-41BF-88B3-98ECE2BEF406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{46E7093F-A843-4D56-8D6E-D290D3117D3B}"/>
+    <workbookView xWindow="7200" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{46E7093F-A843-4D56-8D6E-D290D3117D3B}"/>
   </bookViews>
   <sheets>
     <sheet name="STOK DEALER" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5823" uniqueCount="3083">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5822" uniqueCount="3082">
   <si>
     <t>No</t>
   </si>
@@ -9276,9 +9276,6 @@
   </si>
   <si>
     <t>SPDMTR PRTECTOR PCX 160 C/A</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
   </si>
   <si>
     <t>86836K2FN90ZA</t>
@@ -9316,7 +9313,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -9339,69 +9336,17 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -9737,7 +9682,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2BB8C35-92DF-4C27-A2CF-D1CDC7F4FE42}">
-  <dimension ref="A1:H1465"/>
+  <dimension ref="A1:H1464"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -9949,13 +9894,13 @@
         <v>1627</v>
       </c>
       <c r="F8" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
       </c>
       <c r="H8" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -11405,13 +11350,13 @@
         <v>1260</v>
       </c>
       <c r="F64" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G64" s="2">
         <v>4</v>
       </c>
       <c r="H64" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
@@ -13403,13 +13348,13 @@
         <v>1782</v>
       </c>
       <c r="F141" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G141" s="2">
         <v>1</v>
       </c>
       <c r="H141" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
@@ -13845,13 +13790,13 @@
         <v>1782</v>
       </c>
       <c r="F158" s="2">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="G158" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H158" s="2">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
@@ -13871,13 +13816,13 @@
         <v>1791</v>
       </c>
       <c r="F159" s="2">
-        <v>717</v>
+        <v>707</v>
       </c>
       <c r="G159" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H159" s="2">
-        <v>710</v>
+        <v>698</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
@@ -14027,13 +13972,13 @@
         <v>207</v>
       </c>
       <c r="F165" s="2">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G165" s="2">
         <v>2</v>
       </c>
       <c r="H165" s="2">
-        <v>96</v>
+        <v>95</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
@@ -20423,13 +20368,13 @@
         <v>2171</v>
       </c>
       <c r="F411" s="2">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G411" s="2">
         <v>1</v>
       </c>
       <c r="H411" s="2">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="412" spans="1:8" x14ac:dyDescent="0.25">
@@ -22163,13 +22108,13 @@
         <v>610</v>
       </c>
       <c r="F478" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G478" s="2">
         <v>1</v>
       </c>
       <c r="H478" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="479" spans="1:8" x14ac:dyDescent="0.25">
@@ -22920,10 +22865,10 @@
         <v>7</v>
       </c>
       <c r="G507" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H507" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="508" spans="1:8" x14ac:dyDescent="0.25">
@@ -23591,13 +23536,13 @@
         <v>236</v>
       </c>
       <c r="F533" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G533" s="2">
         <v>0</v>
       </c>
       <c r="H533" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="534" spans="1:8" x14ac:dyDescent="0.25">
@@ -24135,13 +24080,13 @@
         <v>2280</v>
       </c>
       <c r="F554" s="2">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="G554" s="2">
         <v>1</v>
       </c>
       <c r="H554" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="555" spans="1:8" x14ac:dyDescent="0.25">
@@ -24580,10 +24525,10 @@
         <v>3</v>
       </c>
       <c r="G571" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H571" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="572" spans="1:8" x14ac:dyDescent="0.25">
@@ -31545,13 +31490,13 @@
         <v>1958</v>
       </c>
       <c r="F839" s="2">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G839" s="2">
         <v>0</v>
       </c>
       <c r="H839" s="2">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="840" spans="1:8" x14ac:dyDescent="0.25">
@@ -33441,13 +33386,13 @@
         <v>1871</v>
       </c>
       <c r="F912" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G912" s="2">
         <v>0</v>
       </c>
       <c r="H912" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="913" spans="1:8" x14ac:dyDescent="0.25">
@@ -34403,13 +34348,13 @@
         <v>2626</v>
       </c>
       <c r="F949" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G949" s="2">
         <v>0</v>
       </c>
       <c r="H949" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="950" spans="1:8" x14ac:dyDescent="0.25">
@@ -37133,13 +37078,13 @@
         <v>2592</v>
       </c>
       <c r="F1054" s="2">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="G1054" s="2">
         <v>1</v>
       </c>
       <c r="H1054" s="2">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="1055" spans="1:8" x14ac:dyDescent="0.25">
@@ -38603,10 +38548,10 @@
         <v>1110</v>
       </c>
       <c r="B1111" s="2" t="s">
+        <v>3080</v>
+      </c>
+      <c r="C1111" s="2" t="s">
         <v>3081</v>
-      </c>
-      <c r="C1111" s="2" t="s">
-        <v>3082</v>
       </c>
       <c r="D1111" s="2" t="s">
         <v>1623</v>
@@ -39681,13 +39626,13 @@
         <v>2729</v>
       </c>
       <c r="F1152" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1152" s="2">
         <v>0</v>
       </c>
       <c r="H1152" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1153" spans="1:8" x14ac:dyDescent="0.25">
@@ -43139,13 +43084,13 @@
         <v>2835</v>
       </c>
       <c r="F1285" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1285" s="2">
         <v>0</v>
       </c>
       <c r="H1285" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1286" spans="1:8" x14ac:dyDescent="0.25">
@@ -47767,16 +47712,16 @@
         <v>939</v>
       </c>
       <c r="F1463" s="2">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G1463" s="2">
         <v>0</v>
       </c>
       <c r="H1463" s="2">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="1464" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="1464" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1464" s="2">
         <v>1463</v>
       </c>
@@ -47802,28 +47747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1465" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1465" s="5" t="s">
-        <v>3080</v>
-      </c>
-      <c r="B1465" s="6"/>
-      <c r="C1465" s="6"/>
-      <c r="D1465" s="6"/>
-      <c r="E1465" s="7"/>
-      <c r="F1465" s="3">
-        <v>5968</v>
-      </c>
-      <c r="G1465" s="4">
-        <v>144</v>
-      </c>
-      <c r="H1465" s="3">
-        <v>5824</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1465:E1465"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/STOK DEALER/STOK SRB.xlsx
+++ b/STOK DEALER/STOK SRB.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{745D82DE-8819-41BF-88B3-98ECE2BEF406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A655C949-85A6-4298-869F-AE89934230FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7200" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{46E7093F-A843-4D56-8D6E-D290D3117D3B}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295" xr2:uid="{46E7093F-A843-4D56-8D6E-D290D3117D3B}"/>
   </bookViews>
   <sheets>
     <sheet name="STOK DEALER" sheetId="1" r:id="rId1"/>

--- a/STOK DEALER/STOK SRB.xlsx
+++ b/STOK DEALER/STOK SRB.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A655C949-85A6-4298-869F-AE89934230FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2495ED8-85A5-42D0-9376-9C20B3EB20E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295" xr2:uid="{46E7093F-A843-4D56-8D6E-D290D3117D3B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{46E7093F-A843-4D56-8D6E-D290D3117D3B}"/>
   </bookViews>
   <sheets>
     <sheet name="STOK DEALER" sheetId="1" r:id="rId1"/>
@@ -13348,13 +13348,13 @@
         <v>1782</v>
       </c>
       <c r="F141" s="2">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="G141" s="2">
         <v>1</v>
       </c>
       <c r="H141" s="2">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
@@ -13790,13 +13790,13 @@
         <v>1782</v>
       </c>
       <c r="F158" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G158" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H158" s="2">
-        <v>219</v>
+        <v>217</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
@@ -13816,13 +13816,13 @@
         <v>1791</v>
       </c>
       <c r="F159" s="2">
-        <v>707</v>
+        <v>702</v>
       </c>
       <c r="G159" s="2">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H159" s="2">
-        <v>698</v>
+        <v>690</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
@@ -13975,10 +13975,10 @@
         <v>97</v>
       </c>
       <c r="G165" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H165" s="2">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
@@ -16705,10 +16705,10 @@
         <v>26</v>
       </c>
       <c r="G270" s="2">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="H270" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="271" spans="1:8" x14ac:dyDescent="0.25">
@@ -18239,10 +18239,10 @@
         <v>2</v>
       </c>
       <c r="G329" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H329" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="330" spans="1:8" x14ac:dyDescent="0.25">
@@ -26472,13 +26472,13 @@
         <v>292</v>
       </c>
       <c r="F646" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G646" s="2">
         <v>7</v>
       </c>
       <c r="H646" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="647" spans="1:8" x14ac:dyDescent="0.25">
@@ -26709,10 +26709,10 @@
         <v>22</v>
       </c>
       <c r="G655" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H655" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="656" spans="1:8" x14ac:dyDescent="0.25">
@@ -29777,10 +29777,10 @@
         <v>1</v>
       </c>
       <c r="G773" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H773" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="774" spans="1:8" x14ac:dyDescent="0.25">
@@ -37078,13 +37078,13 @@
         <v>2592</v>
       </c>
       <c r="F1054" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G1054" s="2">
         <v>1</v>
       </c>
       <c r="H1054" s="2">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="1055" spans="1:8" x14ac:dyDescent="0.25">
@@ -40903,10 +40903,10 @@
         <v>1</v>
       </c>
       <c r="G1201" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1201" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1202" spans="1:8" x14ac:dyDescent="0.25">
@@ -41189,10 +41189,10 @@
         <v>2</v>
       </c>
       <c r="G1212" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H1212" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1213" spans="1:8" x14ac:dyDescent="0.25">
@@ -41215,10 +41215,10 @@
         <v>1</v>
       </c>
       <c r="G1213" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1213" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1214" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK SRB.xlsx
+++ b/STOK DEALER/STOK SRB.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\STOK DEALER\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data D\2025\UPADTE TOOLS BUNDLING SRB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2495ED8-85A5-42D0-9376-9C20B3EB20E8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DAEB350-6A17-49AE-A436-945E2A7FBE4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{46E7093F-A843-4D56-8D6E-D290D3117D3B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{46E7093F-A843-4D56-8D6E-D290D3117D3B}"/>
   </bookViews>
   <sheets>
     <sheet name="STOK DEALER" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5822" uniqueCount="3082">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5823" uniqueCount="3083">
   <si>
     <t>No</t>
   </si>
@@ -9276,6 +9276,9 @@
   </si>
   <si>
     <t>SPDMTR PRTECTOR PCX 160 C/A</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
   </si>
   <si>
     <t>86836K2FN90ZA</t>
@@ -9313,7 +9316,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -9336,17 +9339,69 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -9682,7 +9737,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2BB8C35-92DF-4C27-A2CF-D1CDC7F4FE42}">
-  <dimension ref="A1:H1464"/>
+  <dimension ref="A1:H1465"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -9816,13 +9871,13 @@
         <v>1627</v>
       </c>
       <c r="F5" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G5" s="2">
         <v>0</v>
       </c>
       <c r="H5" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -9842,10 +9897,10 @@
         <v>1627</v>
       </c>
       <c r="F6" s="2">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G6" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" s="2">
         <v>51</v>
@@ -9868,13 +9923,13 @@
         <v>1627</v>
       </c>
       <c r="F7" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G7" s="2">
         <v>0</v>
       </c>
       <c r="H7" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -9894,10 +9949,10 @@
         <v>1627</v>
       </c>
       <c r="F8" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G8" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" s="2">
         <v>7</v>
@@ -9920,13 +9975,13 @@
         <v>1628</v>
       </c>
       <c r="F9" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G9" s="2">
         <v>0</v>
       </c>
       <c r="H9" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -13322,10 +13377,10 @@
         <v>1629</v>
       </c>
       <c r="F140" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G140" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H140" s="2">
         <v>20</v>
@@ -13348,13 +13403,13 @@
         <v>1782</v>
       </c>
       <c r="F141" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="G141" s="2">
         <v>1</v>
       </c>
       <c r="H141" s="2">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
@@ -13790,13 +13845,13 @@
         <v>1782</v>
       </c>
       <c r="F158" s="2">
-        <v>225</v>
+        <v>221</v>
       </c>
       <c r="G158" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="H158" s="2">
-        <v>217</v>
+        <v>214</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
@@ -13816,13 +13871,13 @@
         <v>1791</v>
       </c>
       <c r="F159" s="2">
-        <v>702</v>
+        <v>693</v>
       </c>
       <c r="G159" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H159" s="2">
-        <v>690</v>
+        <v>682</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
@@ -13972,13 +14027,13 @@
         <v>207</v>
       </c>
       <c r="F165" s="2">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="G165" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H165" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
@@ -14131,10 +14186,10 @@
         <v>43</v>
       </c>
       <c r="G171" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H171" s="2">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
@@ -14778,10 +14833,10 @@
         <v>1817</v>
       </c>
       <c r="F196" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G196" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H196" s="2">
         <v>1</v>
@@ -15142,13 +15197,13 @@
         <v>1856</v>
       </c>
       <c r="F210" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G210" s="2">
         <v>0</v>
       </c>
       <c r="H210" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.25">
@@ -20368,13 +20423,13 @@
         <v>2171</v>
       </c>
       <c r="F411" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G411" s="2">
         <v>1</v>
       </c>
       <c r="H411" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="412" spans="1:8" x14ac:dyDescent="0.25">
@@ -24080,13 +24135,13 @@
         <v>2280</v>
       </c>
       <c r="F554" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G554" s="2">
         <v>1</v>
       </c>
       <c r="H554" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="555" spans="1:8" x14ac:dyDescent="0.25">
@@ -28789,10 +28844,10 @@
         <v>38</v>
       </c>
       <c r="G735" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H735" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="736" spans="1:8" x14ac:dyDescent="0.25">
@@ -30346,13 +30401,13 @@
         <v>1110</v>
       </c>
       <c r="F795" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G795" s="2">
         <v>2</v>
       </c>
       <c r="H795" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="796" spans="1:8" x14ac:dyDescent="0.25">
@@ -33230,10 +33285,10 @@
         <v>1625</v>
       </c>
       <c r="F906" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G906" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H906" s="2">
         <v>1</v>
@@ -34244,13 +34299,13 @@
         <v>2516</v>
       </c>
       <c r="F945" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G945" s="2">
         <v>0</v>
       </c>
       <c r="H945" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="946" spans="1:8" x14ac:dyDescent="0.25">
@@ -34348,13 +34403,13 @@
         <v>2626</v>
       </c>
       <c r="F949" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G949" s="2">
         <v>0</v>
       </c>
       <c r="H949" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="950" spans="1:8" x14ac:dyDescent="0.25">
@@ -34400,13 +34455,13 @@
         <v>2630</v>
       </c>
       <c r="F951" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G951" s="2">
         <v>0</v>
       </c>
       <c r="H951" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="952" spans="1:8" x14ac:dyDescent="0.25">
@@ -37078,13 +37133,13 @@
         <v>2592</v>
       </c>
       <c r="F1054" s="2">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="G1054" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1054" s="2">
-        <v>58</v>
+        <v>54</v>
       </c>
     </row>
     <row r="1055" spans="1:8" x14ac:dyDescent="0.25">
@@ -38548,10 +38603,10 @@
         <v>1110</v>
       </c>
       <c r="B1111" s="2" t="s">
-        <v>3080</v>
+        <v>3081</v>
       </c>
       <c r="C1111" s="2" t="s">
-        <v>3081</v>
+        <v>3082</v>
       </c>
       <c r="D1111" s="2" t="s">
         <v>1623</v>
@@ -38742,13 +38797,13 @@
         <v>2734</v>
       </c>
       <c r="F1118" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1118" s="2">
         <v>0</v>
       </c>
       <c r="H1118" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1119" spans="1:8" x14ac:dyDescent="0.25">
@@ -39210,10 +39265,10 @@
         <v>2724</v>
       </c>
       <c r="F1136" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1136" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1136" s="2">
         <v>6</v>
@@ -39288,10 +39343,10 @@
         <v>2724</v>
       </c>
       <c r="F1139" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1139" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1139" s="2">
         <v>2</v>
@@ -39574,13 +39629,13 @@
         <v>2729</v>
       </c>
       <c r="F1150" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G1150" s="2">
         <v>0</v>
       </c>
       <c r="H1150" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1151" spans="1:8" x14ac:dyDescent="0.25">
@@ -39652,13 +39707,13 @@
         <v>2730</v>
       </c>
       <c r="F1153" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G1153" s="2">
         <v>0</v>
       </c>
       <c r="H1153" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="1154" spans="1:8" x14ac:dyDescent="0.25">
@@ -42226,13 +42281,13 @@
         <v>2825</v>
       </c>
       <c r="F1252" s="2">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="G1252" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1252" s="2">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="1253" spans="1:8" x14ac:dyDescent="0.25">
@@ -42720,13 +42775,13 @@
         <v>2853</v>
       </c>
       <c r="F1271" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1271" s="2">
         <v>0</v>
       </c>
       <c r="H1271" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1272" spans="1:8" x14ac:dyDescent="0.25">
@@ -44956,10 +45011,10 @@
         <v>2832</v>
       </c>
       <c r="F1357" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1357" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1357" s="2">
         <v>0</v>
@@ -45294,10 +45349,10 @@
         <v>2954</v>
       </c>
       <c r="F1370" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1370" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1370" s="2">
         <v>1</v>
@@ -45710,13 +45765,13 @@
         <v>3014</v>
       </c>
       <c r="F1386" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1386" s="2">
         <v>0</v>
       </c>
       <c r="H1386" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1387" spans="1:8" x14ac:dyDescent="0.25">
@@ -45996,10 +46051,10 @@
         <v>3024</v>
       </c>
       <c r="F1397" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1397" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1397" s="2">
         <v>0</v>
@@ -47273,10 +47328,10 @@
         <v>26</v>
       </c>
       <c r="G1446" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H1446" s="2">
-        <v>26</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1447" spans="1:8" x14ac:dyDescent="0.25">
@@ -47400,13 +47455,13 @@
         <v>2354</v>
       </c>
       <c r="F1451" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1451" s="2">
         <v>0</v>
       </c>
       <c r="H1451" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1452" spans="1:8" x14ac:dyDescent="0.25">
@@ -47478,10 +47533,10 @@
         <v>1665</v>
       </c>
       <c r="F1454" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1454" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1454" s="2">
         <v>6</v>
@@ -47721,7 +47776,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="1464" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1464" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1464" s="2">
         <v>1463</v>
       </c>
@@ -47747,7 +47802,28 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1465" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1465" s="5" t="s">
+        <v>3080</v>
+      </c>
+      <c r="B1465" s="6"/>
+      <c r="C1465" s="6"/>
+      <c r="D1465" s="6"/>
+      <c r="E1465" s="7"/>
+      <c r="F1465" s="3">
+        <v>5379</v>
+      </c>
+      <c r="G1465" s="4">
+        <v>158</v>
+      </c>
+      <c r="H1465" s="3">
+        <v>5221</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1465:E1465"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/STOK DEALER/STOK SRB.xlsx
+++ b/STOK DEALER/STOK SRB.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data D\2025\UPADTE TOOLS BUNDLING SRB\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DAEB350-6A17-49AE-A436-945E2A7FBE4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F08EF65A-7B3F-4424-8254-D5DB1A01735C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{46E7093F-A843-4D56-8D6E-D290D3117D3B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{46E7093F-A843-4D56-8D6E-D290D3117D3B}"/>
   </bookViews>
   <sheets>
     <sheet name="STOK DEALER" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5823" uniqueCount="3083">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5822" uniqueCount="3082">
   <si>
     <t>No</t>
   </si>
@@ -9276,9 +9276,6 @@
   </si>
   <si>
     <t>SPDMTR PRTECTOR PCX 160 C/A</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
   </si>
   <si>
     <t>86836K2FN90ZA</t>
@@ -9316,7 +9313,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -9339,69 +9336,17 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -9737,7 +9682,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2BB8C35-92DF-4C27-A2CF-D1CDC7F4FE42}">
-  <dimension ref="A1:H1465"/>
+  <dimension ref="A1:H1464"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -9793,13 +9738,13 @@
         <v>1624</v>
       </c>
       <c r="F2" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G2" s="2">
         <v>0</v>
       </c>
       <c r="H2" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -9897,13 +9842,13 @@
         <v>1627</v>
       </c>
       <c r="F6" s="2">
-        <v>51</v>
+        <v>46</v>
       </c>
       <c r="G6" s="2">
         <v>0</v>
       </c>
       <c r="H6" s="2">
-        <v>51</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -9923,13 +9868,13 @@
         <v>1627</v>
       </c>
       <c r="F7" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G7" s="2">
         <v>0</v>
       </c>
       <c r="H7" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -9975,13 +9920,13 @@
         <v>1628</v>
       </c>
       <c r="F9" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G9" s="2">
         <v>0</v>
       </c>
       <c r="H9" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -10628,10 +10573,10 @@
         <v>3</v>
       </c>
       <c r="G34" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H34" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
@@ -11067,13 +11012,13 @@
         <v>1260</v>
       </c>
       <c r="F51" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G51" s="2">
         <v>0</v>
       </c>
       <c r="H51" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
@@ -11382,10 +11327,10 @@
         <v>6</v>
       </c>
       <c r="G63" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H63" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
@@ -11405,13 +11350,13 @@
         <v>1260</v>
       </c>
       <c r="F64" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G64" s="2">
         <v>4</v>
       </c>
       <c r="H64" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
@@ -13403,13 +13348,13 @@
         <v>1782</v>
       </c>
       <c r="F141" s="2">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="G141" s="2">
         <v>1</v>
       </c>
       <c r="H141" s="2">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
@@ -13429,13 +13374,13 @@
         <v>1783</v>
       </c>
       <c r="F142" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="G142" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H142" s="2">
-        <v>167</v>
+        <v>164</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
@@ -13585,13 +13530,13 @@
         <v>1791</v>
       </c>
       <c r="F148" s="2">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="G148" s="2">
         <v>1</v>
       </c>
       <c r="H148" s="2">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
@@ -13845,13 +13790,13 @@
         <v>1782</v>
       </c>
       <c r="F158" s="2">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="G158" s="2">
         <v>7</v>
       </c>
       <c r="H158" s="2">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
@@ -13871,13 +13816,13 @@
         <v>1791</v>
       </c>
       <c r="F159" s="2">
-        <v>693</v>
+        <v>682</v>
       </c>
       <c r="G159" s="2">
         <v>11</v>
       </c>
       <c r="H159" s="2">
-        <v>682</v>
+        <v>671</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
@@ -14027,13 +13972,13 @@
         <v>207</v>
       </c>
       <c r="F165" s="2">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="G165" s="2">
         <v>2</v>
       </c>
       <c r="H165" s="2">
-        <v>93</v>
+        <v>91</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
@@ -14186,10 +14131,10 @@
         <v>43</v>
       </c>
       <c r="G171" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H171" s="2">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
@@ -14209,13 +14154,13 @@
         <v>1811</v>
       </c>
       <c r="F172" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G172" s="2">
         <v>0</v>
       </c>
       <c r="H172" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.25">
@@ -15015,13 +14960,13 @@
         <v>1811</v>
       </c>
       <c r="F203" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G203" s="2">
         <v>0</v>
       </c>
       <c r="H203" s="2">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.25">
@@ -20163,13 +20108,13 @@
         <v>1814</v>
       </c>
       <c r="F401" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G401" s="2">
         <v>0</v>
       </c>
       <c r="H401" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="402" spans="1:8" x14ac:dyDescent="0.25">
@@ -20371,13 +20316,13 @@
         <v>2170</v>
       </c>
       <c r="F409" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G409" s="2">
         <v>1</v>
       </c>
       <c r="H409" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="410" spans="1:8" x14ac:dyDescent="0.25">
@@ -20423,13 +20368,13 @@
         <v>2171</v>
       </c>
       <c r="F411" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G411" s="2">
         <v>1</v>
       </c>
       <c r="H411" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="412" spans="1:8" x14ac:dyDescent="0.25">
@@ -26813,13 +26758,13 @@
         <v>430</v>
       </c>
       <c r="F657" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G657" s="2">
         <v>2</v>
       </c>
       <c r="H657" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="658" spans="1:8" x14ac:dyDescent="0.25">
@@ -29936,10 +29881,10 @@
         <v>9</v>
       </c>
       <c r="G777" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H777" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="778" spans="1:8" x14ac:dyDescent="0.25">
@@ -30401,13 +30346,13 @@
         <v>1110</v>
       </c>
       <c r="F795" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G795" s="2">
         <v>2</v>
       </c>
       <c r="H795" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="796" spans="1:8" x14ac:dyDescent="0.25">
@@ -30872,10 +30817,10 @@
         <v>6</v>
       </c>
       <c r="G813" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H813" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="814" spans="1:8" x14ac:dyDescent="0.25">
@@ -32146,10 +32091,10 @@
         <v>2</v>
       </c>
       <c r="G862" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H862" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="863" spans="1:8" x14ac:dyDescent="0.25">
@@ -34299,13 +34244,13 @@
         <v>2516</v>
       </c>
       <c r="F945" s="2">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="G945" s="2">
         <v>0</v>
       </c>
       <c r="H945" s="2">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="946" spans="1:8" x14ac:dyDescent="0.25">
@@ -34351,13 +34296,13 @@
         <v>2627</v>
       </c>
       <c r="F947" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G947" s="2">
         <v>0</v>
       </c>
       <c r="H947" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="948" spans="1:8" x14ac:dyDescent="0.25">
@@ -34403,13 +34348,13 @@
         <v>2626</v>
       </c>
       <c r="F949" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G949" s="2">
         <v>0</v>
       </c>
       <c r="H949" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="950" spans="1:8" x14ac:dyDescent="0.25">
@@ -34481,13 +34426,13 @@
         <v>2631</v>
       </c>
       <c r="F952" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G952" s="2">
         <v>0</v>
       </c>
       <c r="H952" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
     </row>
     <row r="953" spans="1:8" x14ac:dyDescent="0.25">
@@ -37133,13 +37078,13 @@
         <v>2592</v>
       </c>
       <c r="F1054" s="2">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="G1054" s="2">
         <v>0</v>
       </c>
       <c r="H1054" s="2">
-        <v>54</v>
+        <v>46</v>
       </c>
     </row>
     <row r="1055" spans="1:8" x14ac:dyDescent="0.25">
@@ -38603,10 +38548,10 @@
         <v>1110</v>
       </c>
       <c r="B1111" s="2" t="s">
+        <v>3080</v>
+      </c>
+      <c r="C1111" s="2" t="s">
         <v>3081</v>
-      </c>
-      <c r="C1111" s="2" t="s">
-        <v>3082</v>
       </c>
       <c r="D1111" s="2" t="s">
         <v>1623</v>
@@ -38667,13 +38612,13 @@
         <v>2730</v>
       </c>
       <c r="F1113" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1113" s="2">
         <v>0</v>
       </c>
       <c r="H1113" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1114" spans="1:8" x14ac:dyDescent="0.25">
@@ -38849,13 +38794,13 @@
         <v>2730</v>
       </c>
       <c r="F1120" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1120" s="2">
         <v>0</v>
       </c>
       <c r="H1120" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1121" spans="1:8" x14ac:dyDescent="0.25">
@@ -39629,13 +39574,13 @@
         <v>2729</v>
       </c>
       <c r="F1150" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G1150" s="2">
         <v>0</v>
       </c>
       <c r="H1150" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1151" spans="1:8" x14ac:dyDescent="0.25">
@@ -39707,13 +39652,13 @@
         <v>2730</v>
       </c>
       <c r="F1153" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G1153" s="2">
         <v>0</v>
       </c>
       <c r="H1153" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1154" spans="1:8" x14ac:dyDescent="0.25">
@@ -39785,13 +39730,13 @@
         <v>2730</v>
       </c>
       <c r="F1156" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G1156" s="2">
         <v>0</v>
       </c>
       <c r="H1156" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1157" spans="1:8" x14ac:dyDescent="0.25">
@@ -42281,13 +42226,13 @@
         <v>2825</v>
       </c>
       <c r="F1252" s="2">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="G1252" s="2">
         <v>0</v>
       </c>
       <c r="H1252" s="2">
-        <v>43</v>
+        <v>40</v>
       </c>
     </row>
     <row r="1253" spans="1:8" x14ac:dyDescent="0.25">
@@ -42775,13 +42720,13 @@
         <v>2853</v>
       </c>
       <c r="F1271" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1271" s="2">
         <v>0</v>
       </c>
       <c r="H1271" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1272" spans="1:8" x14ac:dyDescent="0.25">
@@ -44387,13 +44332,13 @@
         <v>2948</v>
       </c>
       <c r="F1333" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1333" s="2">
         <v>0</v>
       </c>
       <c r="H1333" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1334" spans="1:8" x14ac:dyDescent="0.25">
@@ -46181,13 +46126,13 @@
         <v>3014</v>
       </c>
       <c r="F1402" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G1402" s="2">
         <v>0</v>
       </c>
       <c r="H1402" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1403" spans="1:8" x14ac:dyDescent="0.25">
@@ -47481,13 +47426,13 @@
         <v>3058</v>
       </c>
       <c r="F1452" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G1452" s="2">
         <v>0</v>
       </c>
       <c r="H1452" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1453" spans="1:8" x14ac:dyDescent="0.25">
@@ -47776,7 +47721,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="1464" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1464" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1464" s="2">
         <v>1463</v>
       </c>
@@ -47802,28 +47747,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1465" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1465" s="5" t="s">
-        <v>3080</v>
-      </c>
-      <c r="B1465" s="6"/>
-      <c r="C1465" s="6"/>
-      <c r="D1465" s="6"/>
-      <c r="E1465" s="7"/>
-      <c r="F1465" s="3">
-        <v>5379</v>
-      </c>
-      <c r="G1465" s="4">
-        <v>158</v>
-      </c>
-      <c r="H1465" s="3">
-        <v>5221</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1465:E1465"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/STOK DEALER/STOK SRB.xlsx
+++ b/STOK DEALER/STOK SRB.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\STOK DEALER\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data D\2025\UPADTE TOOLS BUNDLING SRB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F08EF65A-7B3F-4424-8254-D5DB1A01735C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DAEB350-6A17-49AE-A436-945E2A7FBE4D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{46E7093F-A843-4D56-8D6E-D290D3117D3B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{46E7093F-A843-4D56-8D6E-D290D3117D3B}"/>
   </bookViews>
   <sheets>
     <sheet name="STOK DEALER" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5822" uniqueCount="3082">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5823" uniqueCount="3083">
   <si>
     <t>No</t>
   </si>
@@ -9276,6 +9276,9 @@
   </si>
   <si>
     <t>SPDMTR PRTECTOR PCX 160 C/A</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
   </si>
   <si>
     <t>86836K2FN90ZA</t>
@@ -9313,7 +9316,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -9336,17 +9339,69 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -9682,7 +9737,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2BB8C35-92DF-4C27-A2CF-D1CDC7F4FE42}">
-  <dimension ref="A1:H1464"/>
+  <dimension ref="A1:H1465"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -9738,13 +9793,13 @@
         <v>1624</v>
       </c>
       <c r="F2" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G2" s="2">
         <v>0</v>
       </c>
       <c r="H2" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -9842,13 +9897,13 @@
         <v>1627</v>
       </c>
       <c r="F6" s="2">
-        <v>46</v>
+        <v>51</v>
       </c>
       <c r="G6" s="2">
         <v>0</v>
       </c>
       <c r="H6" s="2">
-        <v>46</v>
+        <v>51</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -9868,13 +9923,13 @@
         <v>1627</v>
       </c>
       <c r="F7" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G7" s="2">
         <v>0</v>
       </c>
       <c r="H7" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -9920,13 +9975,13 @@
         <v>1628</v>
       </c>
       <c r="F9" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G9" s="2">
         <v>0</v>
       </c>
       <c r="H9" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -10573,10 +10628,10 @@
         <v>3</v>
       </c>
       <c r="G34" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H34" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
@@ -11012,13 +11067,13 @@
         <v>1260</v>
       </c>
       <c r="F51" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G51" s="2">
         <v>0</v>
       </c>
       <c r="H51" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
@@ -11327,10 +11382,10 @@
         <v>6</v>
       </c>
       <c r="G63" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H63" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
@@ -11350,13 +11405,13 @@
         <v>1260</v>
       </c>
       <c r="F64" s="2">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="G64" s="2">
         <v>4</v>
       </c>
       <c r="H64" s="2">
-        <v>21</v>
+        <v>23</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
@@ -13348,13 +13403,13 @@
         <v>1782</v>
       </c>
       <c r="F141" s="2">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="G141" s="2">
         <v>1</v>
       </c>
       <c r="H141" s="2">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
@@ -13374,13 +13429,13 @@
         <v>1783</v>
       </c>
       <c r="F142" s="2">
+        <v>169</v>
+      </c>
+      <c r="G142" s="2">
+        <v>2</v>
+      </c>
+      <c r="H142" s="2">
         <v>167</v>
-      </c>
-      <c r="G142" s="2">
-        <v>3</v>
-      </c>
-      <c r="H142" s="2">
-        <v>164</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
@@ -13530,13 +13585,13 @@
         <v>1791</v>
       </c>
       <c r="F148" s="2">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="G148" s="2">
         <v>1</v>
       </c>
       <c r="H148" s="2">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
@@ -13790,13 +13845,13 @@
         <v>1782</v>
       </c>
       <c r="F158" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="G158" s="2">
         <v>7</v>
       </c>
       <c r="H158" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
@@ -13816,13 +13871,13 @@
         <v>1791</v>
       </c>
       <c r="F159" s="2">
-        <v>682</v>
+        <v>693</v>
       </c>
       <c r="G159" s="2">
         <v>11</v>
       </c>
       <c r="H159" s="2">
-        <v>671</v>
+        <v>682</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
@@ -13972,13 +14027,13 @@
         <v>207</v>
       </c>
       <c r="F165" s="2">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="G165" s="2">
         <v>2</v>
       </c>
       <c r="H165" s="2">
-        <v>91</v>
+        <v>93</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
@@ -14131,10 +14186,10 @@
         <v>43</v>
       </c>
       <c r="G171" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H171" s="2">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
@@ -14154,13 +14209,13 @@
         <v>1811</v>
       </c>
       <c r="F172" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G172" s="2">
         <v>0</v>
       </c>
       <c r="H172" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.25">
@@ -14960,13 +15015,13 @@
         <v>1811</v>
       </c>
       <c r="F203" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="G203" s="2">
         <v>0</v>
       </c>
       <c r="H203" s="2">
-        <v>13</v>
+        <v>15</v>
       </c>
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.25">
@@ -20108,13 +20163,13 @@
         <v>1814</v>
       </c>
       <c r="F401" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G401" s="2">
         <v>0</v>
       </c>
       <c r="H401" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="402" spans="1:8" x14ac:dyDescent="0.25">
@@ -20316,13 +20371,13 @@
         <v>2170</v>
       </c>
       <c r="F409" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G409" s="2">
         <v>1</v>
       </c>
       <c r="H409" s="2">
-        <v>30</v>
+        <v>31</v>
       </c>
     </row>
     <row r="410" spans="1:8" x14ac:dyDescent="0.25">
@@ -20368,13 +20423,13 @@
         <v>2171</v>
       </c>
       <c r="F411" s="2">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G411" s="2">
         <v>1</v>
       </c>
       <c r="H411" s="2">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="412" spans="1:8" x14ac:dyDescent="0.25">
@@ -26758,13 +26813,13 @@
         <v>430</v>
       </c>
       <c r="F657" s="2">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="G657" s="2">
         <v>2</v>
       </c>
       <c r="H657" s="2">
-        <v>17</v>
+        <v>18</v>
       </c>
     </row>
     <row r="658" spans="1:8" x14ac:dyDescent="0.25">
@@ -29881,10 +29936,10 @@
         <v>9</v>
       </c>
       <c r="G777" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H777" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="778" spans="1:8" x14ac:dyDescent="0.25">
@@ -30346,13 +30401,13 @@
         <v>1110</v>
       </c>
       <c r="F795" s="2">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="G795" s="2">
         <v>2</v>
       </c>
       <c r="H795" s="2">
-        <v>15</v>
+        <v>17</v>
       </c>
     </row>
     <row r="796" spans="1:8" x14ac:dyDescent="0.25">
@@ -30817,10 +30872,10 @@
         <v>6</v>
       </c>
       <c r="G813" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H813" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="814" spans="1:8" x14ac:dyDescent="0.25">
@@ -32091,10 +32146,10 @@
         <v>2</v>
       </c>
       <c r="G862" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H862" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="863" spans="1:8" x14ac:dyDescent="0.25">
@@ -34244,13 +34299,13 @@
         <v>2516</v>
       </c>
       <c r="F945" s="2">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="G945" s="2">
         <v>0</v>
       </c>
       <c r="H945" s="2">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="946" spans="1:8" x14ac:dyDescent="0.25">
@@ -34296,13 +34351,13 @@
         <v>2627</v>
       </c>
       <c r="F947" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G947" s="2">
         <v>0</v>
       </c>
       <c r="H947" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="948" spans="1:8" x14ac:dyDescent="0.25">
@@ -34348,13 +34403,13 @@
         <v>2626</v>
       </c>
       <c r="F949" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G949" s="2">
         <v>0</v>
       </c>
       <c r="H949" s="2">
-        <v>15</v>
+        <v>16</v>
       </c>
     </row>
     <row r="950" spans="1:8" x14ac:dyDescent="0.25">
@@ -34426,13 +34481,13 @@
         <v>2631</v>
       </c>
       <c r="F952" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G952" s="2">
         <v>0</v>
       </c>
       <c r="H952" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="953" spans="1:8" x14ac:dyDescent="0.25">
@@ -37078,13 +37133,13 @@
         <v>2592</v>
       </c>
       <c r="F1054" s="2">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="G1054" s="2">
         <v>0</v>
       </c>
       <c r="H1054" s="2">
-        <v>46</v>
+        <v>54</v>
       </c>
     </row>
     <row r="1055" spans="1:8" x14ac:dyDescent="0.25">
@@ -38548,10 +38603,10 @@
         <v>1110</v>
       </c>
       <c r="B1111" s="2" t="s">
-        <v>3080</v>
+        <v>3081</v>
       </c>
       <c r="C1111" s="2" t="s">
-        <v>3081</v>
+        <v>3082</v>
       </c>
       <c r="D1111" s="2" t="s">
         <v>1623</v>
@@ -38612,13 +38667,13 @@
         <v>2730</v>
       </c>
       <c r="F1113" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1113" s="2">
         <v>0</v>
       </c>
       <c r="H1113" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1114" spans="1:8" x14ac:dyDescent="0.25">
@@ -38794,13 +38849,13 @@
         <v>2730</v>
       </c>
       <c r="F1120" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1120" s="2">
         <v>0</v>
       </c>
       <c r="H1120" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1121" spans="1:8" x14ac:dyDescent="0.25">
@@ -39574,13 +39629,13 @@
         <v>2729</v>
       </c>
       <c r="F1150" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G1150" s="2">
         <v>0</v>
       </c>
       <c r="H1150" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1151" spans="1:8" x14ac:dyDescent="0.25">
@@ -39652,13 +39707,13 @@
         <v>2730</v>
       </c>
       <c r="F1153" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="G1153" s="2">
         <v>0</v>
       </c>
       <c r="H1153" s="2">
-        <v>33</v>
+        <v>34</v>
       </c>
     </row>
     <row r="1154" spans="1:8" x14ac:dyDescent="0.25">
@@ -39730,13 +39785,13 @@
         <v>2730</v>
       </c>
       <c r="F1156" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G1156" s="2">
         <v>0</v>
       </c>
       <c r="H1156" s="2">
-        <v>20</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1157" spans="1:8" x14ac:dyDescent="0.25">
@@ -42226,13 +42281,13 @@
         <v>2825</v>
       </c>
       <c r="F1252" s="2">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="G1252" s="2">
         <v>0</v>
       </c>
       <c r="H1252" s="2">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="1253" spans="1:8" x14ac:dyDescent="0.25">
@@ -42720,13 +42775,13 @@
         <v>2853</v>
       </c>
       <c r="F1271" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1271" s="2">
         <v>0</v>
       </c>
       <c r="H1271" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1272" spans="1:8" x14ac:dyDescent="0.25">
@@ -44332,13 +44387,13 @@
         <v>2948</v>
       </c>
       <c r="F1333" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1333" s="2">
         <v>0</v>
       </c>
       <c r="H1333" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1334" spans="1:8" x14ac:dyDescent="0.25">
@@ -46126,13 +46181,13 @@
         <v>3014</v>
       </c>
       <c r="F1402" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="G1402" s="2">
         <v>0</v>
       </c>
       <c r="H1402" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1403" spans="1:8" x14ac:dyDescent="0.25">
@@ -47426,13 +47481,13 @@
         <v>3058</v>
       </c>
       <c r="F1452" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="G1452" s="2">
         <v>0</v>
       </c>
       <c r="H1452" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1453" spans="1:8" x14ac:dyDescent="0.25">
@@ -47721,7 +47776,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="1464" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1464" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1464" s="2">
         <v>1463</v>
       </c>
@@ -47747,7 +47802,28 @@
         <v>0</v>
       </c>
     </row>
+    <row r="1465" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1465" s="5" t="s">
+        <v>3080</v>
+      </c>
+      <c r="B1465" s="6"/>
+      <c r="C1465" s="6"/>
+      <c r="D1465" s="6"/>
+      <c r="E1465" s="7"/>
+      <c r="F1465" s="3">
+        <v>5379</v>
+      </c>
+      <c r="G1465" s="4">
+        <v>158</v>
+      </c>
+      <c r="H1465" s="3">
+        <v>5221</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1465:E1465"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/STOK DEALER/STOK SRB.xlsx
+++ b/STOK DEALER/STOK SRB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{73974B03-03EF-4D82-95DB-93E1F15F6729}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F04D5AD-21F2-4BB7-8A20-F8ACD8A260A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{46E7093F-A843-4D56-8D6E-D290D3117D3B}"/>
   </bookViews>
@@ -9843,13 +9843,13 @@
         <v>1627</v>
       </c>
       <c r="F5" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G5" s="2">
         <v>0</v>
       </c>
       <c r="H5" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -9921,13 +9921,13 @@
         <v>1627</v>
       </c>
       <c r="F8" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G8" s="2">
         <v>0</v>
       </c>
       <c r="H8" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -11172,10 +11172,10 @@
         <v>27</v>
       </c>
       <c r="G56" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H56" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
@@ -11377,13 +11377,13 @@
         <v>1260</v>
       </c>
       <c r="F64" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G64" s="2">
         <v>5</v>
       </c>
       <c r="H64" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
@@ -13375,13 +13375,13 @@
         <v>1782</v>
       </c>
       <c r="F141" s="2">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G141" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H141" s="2">
-        <v>37</v>
+        <v>34</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
@@ -13401,13 +13401,13 @@
         <v>1783</v>
       </c>
       <c r="F142" s="2">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="G142" s="2">
         <v>3</v>
       </c>
       <c r="H142" s="2">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
@@ -13557,13 +13557,13 @@
         <v>1791</v>
       </c>
       <c r="F148" s="2">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="G148" s="2">
         <v>1</v>
       </c>
       <c r="H148" s="2">
-        <v>58</v>
+        <v>48</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
@@ -13817,13 +13817,13 @@
         <v>1782</v>
       </c>
       <c r="F158" s="2">
-        <v>211</v>
+        <v>207</v>
       </c>
       <c r="G158" s="2">
         <v>9</v>
       </c>
       <c r="H158" s="2">
-        <v>202</v>
+        <v>198</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
@@ -13843,13 +13843,13 @@
         <v>1791</v>
       </c>
       <c r="F159" s="2">
-        <v>659</v>
+        <v>632</v>
       </c>
       <c r="G159" s="2">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H159" s="2">
-        <v>649</v>
+        <v>620</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
@@ -13921,13 +13921,13 @@
         <v>207</v>
       </c>
       <c r="F162" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G162" s="2">
         <v>1</v>
       </c>
       <c r="H162" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
@@ -13999,13 +13999,13 @@
         <v>207</v>
       </c>
       <c r="F165" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="G165" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H165" s="2">
-        <v>80</v>
+        <v>68</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
@@ -14155,13 +14155,13 @@
         <v>939</v>
       </c>
       <c r="F171" s="2">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G171" s="2">
         <v>3</v>
       </c>
       <c r="H171" s="2">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
@@ -14337,13 +14337,13 @@
         <v>1818</v>
       </c>
       <c r="F178" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G178" s="2">
         <v>0</v>
       </c>
       <c r="H178" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.25">
@@ -14883,13 +14883,13 @@
         <v>1829</v>
       </c>
       <c r="F199" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G199" s="2">
         <v>0</v>
       </c>
       <c r="H199" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.25">
@@ -20346,10 +20346,10 @@
         <v>36</v>
       </c>
       <c r="G409" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H409" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="410" spans="1:8" x14ac:dyDescent="0.25">
@@ -20369,13 +20369,13 @@
         <v>926</v>
       </c>
       <c r="F410" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G410" s="2">
         <v>1</v>
       </c>
       <c r="H410" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="411" spans="1:8" x14ac:dyDescent="0.25">
@@ -20395,13 +20395,13 @@
         <v>2171</v>
       </c>
       <c r="F411" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G411" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H411" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="412" spans="1:8" x14ac:dyDescent="0.25">
@@ -20424,10 +20424,10 @@
         <v>5</v>
       </c>
       <c r="G412" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H412" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="413" spans="1:8" x14ac:dyDescent="0.25">
@@ -21799,10 +21799,10 @@
         <v>2227</v>
       </c>
       <c r="F465" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G465" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H465" s="2">
         <v>0</v>
@@ -24159,13 +24159,13 @@
         <v>2280</v>
       </c>
       <c r="F556" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G556" s="2">
         <v>1</v>
       </c>
       <c r="H556" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="557" spans="1:8" x14ac:dyDescent="0.25">
@@ -24419,13 +24419,13 @@
         <v>483</v>
       </c>
       <c r="F566" s="2">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="G566" s="2">
         <v>2</v>
       </c>
       <c r="H566" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="567" spans="1:8" x14ac:dyDescent="0.25">
@@ -26785,13 +26785,13 @@
         <v>402</v>
       </c>
       <c r="F657" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G657" s="2">
         <v>1</v>
       </c>
       <c r="H657" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="658" spans="1:8" x14ac:dyDescent="0.25">
@@ -26837,13 +26837,13 @@
         <v>430</v>
       </c>
       <c r="F659" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G659" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H659" s="2">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="660" spans="1:8" x14ac:dyDescent="0.25">
@@ -28345,13 +28345,13 @@
         <v>693</v>
       </c>
       <c r="F717" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G717" s="2">
         <v>1</v>
       </c>
       <c r="H717" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="718" spans="1:8" x14ac:dyDescent="0.25">
@@ -30451,13 +30451,13 @@
         <v>1110</v>
       </c>
       <c r="F798" s="2">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="G798" s="2">
         <v>3</v>
       </c>
       <c r="H798" s="2">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="799" spans="1:8" x14ac:dyDescent="0.25">
@@ -30922,10 +30922,10 @@
         <v>9</v>
       </c>
       <c r="G816" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H816" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="817" spans="1:8" x14ac:dyDescent="0.25">
@@ -32170,10 +32170,10 @@
         <v>1</v>
       </c>
       <c r="G864" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H864" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="865" spans="1:8" x14ac:dyDescent="0.25">
@@ -32662,10 +32662,10 @@
         <v>3</v>
       </c>
       <c r="G883" s="2">
+        <v>2</v>
+      </c>
+      <c r="H883" s="2">
         <v>1</v>
-      </c>
-      <c r="H883" s="2">
-        <v>2</v>
       </c>
     </row>
     <row r="884" spans="1:8" x14ac:dyDescent="0.25">
@@ -33361,13 +33361,13 @@
         <v>1625</v>
       </c>
       <c r="F910" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G910" s="2">
         <v>0</v>
       </c>
       <c r="H910" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="911" spans="1:8" x14ac:dyDescent="0.25">
@@ -34349,13 +34349,13 @@
         <v>2516</v>
       </c>
       <c r="F948" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G948" s="2">
         <v>0</v>
       </c>
       <c r="H948" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="949" spans="1:8" x14ac:dyDescent="0.25">
@@ -34453,13 +34453,13 @@
         <v>2626</v>
       </c>
       <c r="F952" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G952" s="2">
         <v>0</v>
       </c>
       <c r="H952" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="953" spans="1:8" x14ac:dyDescent="0.25">
@@ -37183,13 +37183,13 @@
         <v>2592</v>
       </c>
       <c r="F1057" s="2">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="G1057" s="2">
         <v>0</v>
       </c>
       <c r="H1057" s="2">
-        <v>138</v>
+        <v>130</v>
       </c>
     </row>
     <row r="1058" spans="1:8" x14ac:dyDescent="0.25">
@@ -38899,13 +38899,13 @@
         <v>2730</v>
       </c>
       <c r="F1123" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1123" s="2">
         <v>0</v>
       </c>
       <c r="H1123" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1124" spans="1:8" x14ac:dyDescent="0.25">
@@ -39679,13 +39679,13 @@
         <v>2729</v>
       </c>
       <c r="F1153" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G1153" s="2">
         <v>0</v>
       </c>
       <c r="H1153" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1154" spans="1:8" x14ac:dyDescent="0.25">
@@ -39809,13 +39809,13 @@
         <v>2730</v>
       </c>
       <c r="F1158" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G1158" s="2">
         <v>0</v>
       </c>
       <c r="H1158" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1159" spans="1:8" x14ac:dyDescent="0.25">
@@ -42409,13 +42409,13 @@
         <v>2825</v>
       </c>
       <c r="F1258" s="2">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="G1258" s="2">
         <v>0</v>
       </c>
       <c r="H1258" s="2">
-        <v>40</v>
+        <v>34</v>
       </c>
     </row>
     <row r="1259" spans="1:8" x14ac:dyDescent="0.25">
@@ -42851,13 +42851,13 @@
         <v>2850</v>
       </c>
       <c r="F1275" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G1275" s="2">
         <v>0</v>
       </c>
       <c r="H1275" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1276" spans="1:8" x14ac:dyDescent="0.25">
@@ -42877,13 +42877,13 @@
         <v>2631</v>
       </c>
       <c r="F1276" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G1276" s="2">
         <v>0</v>
       </c>
       <c r="H1276" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1277" spans="1:8" x14ac:dyDescent="0.25">
@@ -45893,13 +45893,13 @@
         <v>3014</v>
       </c>
       <c r="F1392" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1392" s="2">
         <v>0</v>
       </c>
       <c r="H1392" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1393" spans="1:8" x14ac:dyDescent="0.25">
@@ -46023,13 +46023,13 @@
         <v>3017</v>
       </c>
       <c r="F1397" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G1397" s="2">
         <v>0</v>
       </c>
       <c r="H1397" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1398" spans="1:8" x14ac:dyDescent="0.25">
@@ -46049,13 +46049,13 @@
         <v>2847</v>
       </c>
       <c r="F1398" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G1398" s="2">
         <v>0</v>
       </c>
       <c r="H1398" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1399" spans="1:8" x14ac:dyDescent="0.25">
@@ -46205,13 +46205,13 @@
         <v>3014</v>
       </c>
       <c r="F1404" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G1404" s="2">
         <v>0</v>
       </c>
       <c r="H1404" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="1405" spans="1:8" x14ac:dyDescent="0.25">
@@ -46309,13 +46309,13 @@
         <v>3014</v>
       </c>
       <c r="F1408" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G1408" s="2">
         <v>0</v>
       </c>
       <c r="H1408" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1409" spans="1:8" x14ac:dyDescent="0.25">
@@ -47427,13 +47427,13 @@
         <v>47</v>
       </c>
       <c r="F1451" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G1451" s="2">
         <v>0</v>
       </c>
       <c r="H1451" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1452" spans="1:8" x14ac:dyDescent="0.25">
@@ -47456,10 +47456,10 @@
         <v>26</v>
       </c>
       <c r="G1452" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H1452" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1453" spans="1:8" x14ac:dyDescent="0.25">
@@ -47791,13 +47791,13 @@
         <v>2242</v>
       </c>
       <c r="F1465" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G1465" s="2">
         <v>0</v>
       </c>
       <c r="H1465" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1466" spans="1:8" x14ac:dyDescent="0.25">
@@ -47869,13 +47869,13 @@
         <v>3061</v>
       </c>
       <c r="F1468" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G1468" s="2">
         <v>0</v>
       </c>
       <c r="H1468" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="1469" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK SRB.xlsx
+++ b/STOK DEALER/STOK SRB.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\STOK DEALER\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data D\2025\UPADTE TOOLS BUNDLING SRB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1F04D5AD-21F2-4BB7-8A20-F8ACD8A260A9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6169FFA3-FE83-4555-A733-F22697C58E64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{46E7093F-A843-4D56-8D6E-D290D3117D3B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{46E7093F-A843-4D56-8D6E-D290D3117D3B}"/>
   </bookViews>
   <sheets>
     <sheet name="STOK DEALER" sheetId="1" r:id="rId1"/>
@@ -11377,13 +11377,13 @@
         <v>1260</v>
       </c>
       <c r="F64" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G64" s="2">
         <v>5</v>
       </c>
       <c r="H64" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
@@ -13378,10 +13378,10 @@
         <v>36</v>
       </c>
       <c r="G141" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H141" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
@@ -13401,13 +13401,13 @@
         <v>1783</v>
       </c>
       <c r="F142" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="G142" s="2">
         <v>3</v>
       </c>
       <c r="H142" s="2">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
@@ -13557,13 +13557,13 @@
         <v>1791</v>
       </c>
       <c r="F148" s="2">
-        <v>49</v>
+        <v>33</v>
       </c>
       <c r="G148" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="H148" s="2">
-        <v>48</v>
+        <v>22</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
@@ -13817,13 +13817,13 @@
         <v>1782</v>
       </c>
       <c r="F158" s="2">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="G158" s="2">
         <v>9</v>
       </c>
       <c r="H158" s="2">
-        <v>198</v>
+        <v>197</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
@@ -13843,13 +13843,13 @@
         <v>1791</v>
       </c>
       <c r="F159" s="2">
-        <v>632</v>
+        <v>626</v>
       </c>
       <c r="G159" s="2">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="H159" s="2">
-        <v>620</v>
+        <v>606</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
@@ -13999,13 +13999,13 @@
         <v>207</v>
       </c>
       <c r="F165" s="2">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G165" s="2">
         <v>7</v>
       </c>
       <c r="H165" s="2">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
@@ -14158,10 +14158,10 @@
         <v>66</v>
       </c>
       <c r="G171" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H171" s="2">
-        <v>63</v>
+        <v>61</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
@@ -15169,13 +15169,13 @@
         <v>1856</v>
       </c>
       <c r="F210" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G210" s="2">
         <v>0</v>
       </c>
       <c r="H210" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.25">
@@ -20395,13 +20395,13 @@
         <v>2171</v>
       </c>
       <c r="F411" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G411" s="2">
         <v>2</v>
       </c>
       <c r="H411" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="412" spans="1:8" x14ac:dyDescent="0.25">
@@ -24159,13 +24159,13 @@
         <v>2280</v>
       </c>
       <c r="F556" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G556" s="2">
         <v>1</v>
       </c>
       <c r="H556" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="557" spans="1:8" x14ac:dyDescent="0.25">
@@ -26398,10 +26398,10 @@
         <v>20</v>
       </c>
       <c r="G642" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H642" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="643" spans="1:8" x14ac:dyDescent="0.25">
@@ -26554,10 +26554,10 @@
         <v>22</v>
       </c>
       <c r="G648" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H648" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="649" spans="1:8" x14ac:dyDescent="0.25">
@@ -28868,10 +28868,10 @@
         <v>37</v>
       </c>
       <c r="G737" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H737" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="738" spans="1:8" x14ac:dyDescent="0.25">
@@ -37183,13 +37183,13 @@
         <v>2592</v>
       </c>
       <c r="F1057" s="2">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="G1057" s="2">
         <v>0</v>
       </c>
       <c r="H1057" s="2">
-        <v>130</v>
+        <v>125</v>
       </c>
     </row>
     <row r="1058" spans="1:8" x14ac:dyDescent="0.25">
@@ -39679,13 +39679,13 @@
         <v>2729</v>
       </c>
       <c r="F1153" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G1153" s="2">
         <v>0</v>
       </c>
       <c r="H1153" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1154" spans="1:8" x14ac:dyDescent="0.25">
@@ -39835,13 +39835,13 @@
         <v>2730</v>
       </c>
       <c r="F1159" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G1159" s="2">
         <v>0</v>
       </c>
       <c r="H1159" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1160" spans="1:8" x14ac:dyDescent="0.25">
@@ -40748,10 +40748,10 @@
         <v>3</v>
       </c>
       <c r="G1194" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1194" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1195" spans="1:8" x14ac:dyDescent="0.25">
@@ -42409,13 +42409,13 @@
         <v>2825</v>
       </c>
       <c r="F1258" s="2">
-        <v>34</v>
+        <v>27</v>
       </c>
       <c r="G1258" s="2">
         <v>0</v>
       </c>
       <c r="H1258" s="2">
-        <v>34</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1259" spans="1:8" x14ac:dyDescent="0.25">
@@ -42903,13 +42903,13 @@
         <v>2853</v>
       </c>
       <c r="F1277" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1277" s="2">
         <v>0</v>
       </c>
       <c r="H1277" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1278" spans="1:8" x14ac:dyDescent="0.25">
@@ -44645,13 +44645,13 @@
         <v>2826</v>
       </c>
       <c r="F1344" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G1344" s="2">
         <v>0</v>
       </c>
       <c r="H1344" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1345" spans="1:8" x14ac:dyDescent="0.25">
@@ -46023,13 +46023,13 @@
         <v>3017</v>
       </c>
       <c r="F1397" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G1397" s="2">
         <v>0</v>
       </c>
       <c r="H1397" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1398" spans="1:8" x14ac:dyDescent="0.25">
@@ -46806,10 +46806,10 @@
         <v>1</v>
       </c>
       <c r="G1427" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1427" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1428" spans="1:8" x14ac:dyDescent="0.25">
@@ -47748,7 +47748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1464" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1464" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1464" s="2">
         <v>1463</v>
       </c>
@@ -47774,7 +47774,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="1465" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1465" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1465" s="2">
         <v>1464</v>
       </c>

--- a/STOK DEALER/STOK SRB.xlsx
+++ b/STOK DEALER/STOK SRB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data D\2025\UPADTE TOOLS BUNDLING SRB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6169FFA3-FE83-4555-A733-F22697C58E64}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93C1EE41-876E-4561-B221-005C7FD0EA37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{46E7093F-A843-4D56-8D6E-D290D3117D3B}"/>
   </bookViews>
@@ -9843,13 +9843,13 @@
         <v>1627</v>
       </c>
       <c r="F5" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G5" s="2">
         <v>0</v>
       </c>
       <c r="H5" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -9869,13 +9869,13 @@
         <v>1627</v>
       </c>
       <c r="F6" s="2">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="G6" s="2">
         <v>0</v>
       </c>
       <c r="H6" s="2">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -9895,13 +9895,13 @@
         <v>1627</v>
       </c>
       <c r="F7" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G7" s="2">
         <v>0</v>
       </c>
       <c r="H7" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -9947,13 +9947,13 @@
         <v>1628</v>
       </c>
       <c r="F9" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G9" s="2">
         <v>0</v>
       </c>
       <c r="H9" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -13375,13 +13375,13 @@
         <v>1782</v>
       </c>
       <c r="F141" s="2">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="G141" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H141" s="2">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
@@ -13401,13 +13401,13 @@
         <v>1783</v>
       </c>
       <c r="F142" s="2">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="G142" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H142" s="2">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
@@ -13557,13 +13557,13 @@
         <v>1791</v>
       </c>
       <c r="F148" s="2">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="G148" s="2">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H148" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
@@ -13817,13 +13817,13 @@
         <v>1782</v>
       </c>
       <c r="F158" s="2">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="G158" s="2">
         <v>9</v>
       </c>
       <c r="H158" s="2">
-        <v>197</v>
+        <v>194</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
@@ -13843,13 +13843,13 @@
         <v>1791</v>
       </c>
       <c r="F159" s="2">
-        <v>626</v>
+        <v>611</v>
       </c>
       <c r="G159" s="2">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="H159" s="2">
-        <v>606</v>
+        <v>598</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
@@ -13999,13 +13999,13 @@
         <v>207</v>
       </c>
       <c r="F165" s="2">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="G165" s="2">
         <v>7</v>
       </c>
       <c r="H165" s="2">
-        <v>66</v>
+        <v>63</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
@@ -20395,13 +20395,13 @@
         <v>2171</v>
       </c>
       <c r="F411" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G411" s="2">
         <v>2</v>
       </c>
       <c r="H411" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="412" spans="1:8" x14ac:dyDescent="0.25">
@@ -20759,13 +20759,13 @@
         <v>2177</v>
       </c>
       <c r="F425" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G425" s="2">
         <v>0</v>
       </c>
       <c r="H425" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="426" spans="1:8" x14ac:dyDescent="0.25">
@@ -22606,10 +22606,10 @@
         <v>4</v>
       </c>
       <c r="G496" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H496" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="497" spans="1:8" x14ac:dyDescent="0.25">
@@ -23308,10 +23308,10 @@
         <v>4</v>
       </c>
       <c r="G523" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H523" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="524" spans="1:8" x14ac:dyDescent="0.25">
@@ -24159,13 +24159,13 @@
         <v>2280</v>
       </c>
       <c r="F556" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G556" s="2">
         <v>1</v>
       </c>
       <c r="H556" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="557" spans="1:8" x14ac:dyDescent="0.25">
@@ -24344,10 +24344,10 @@
         <v>19</v>
       </c>
       <c r="G563" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H563" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="564" spans="1:8" x14ac:dyDescent="0.25">
@@ -26398,10 +26398,10 @@
         <v>20</v>
       </c>
       <c r="G642" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H642" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="643" spans="1:8" x14ac:dyDescent="0.25">
@@ -27851,13 +27851,13 @@
         <v>2454</v>
       </c>
       <c r="F698" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G698" s="2">
         <v>0</v>
       </c>
       <c r="H698" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="699" spans="1:8" x14ac:dyDescent="0.25">
@@ -28868,10 +28868,10 @@
         <v>37</v>
       </c>
       <c r="G737" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H737" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="738" spans="1:8" x14ac:dyDescent="0.25">
@@ -30061,13 +30061,13 @@
         <v>2529</v>
       </c>
       <c r="F783" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G783" s="2">
         <v>1</v>
       </c>
       <c r="H783" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="784" spans="1:8" x14ac:dyDescent="0.25">
@@ -30451,13 +30451,13 @@
         <v>1110</v>
       </c>
       <c r="F798" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G798" s="2">
         <v>3</v>
       </c>
       <c r="H798" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="799" spans="1:8" x14ac:dyDescent="0.25">
@@ -31858,10 +31858,10 @@
         <v>2</v>
       </c>
       <c r="G852" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H852" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="853" spans="1:8" x14ac:dyDescent="0.25">
@@ -34349,13 +34349,13 @@
         <v>2516</v>
       </c>
       <c r="F948" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G948" s="2">
         <v>0</v>
       </c>
       <c r="H948" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="949" spans="1:8" x14ac:dyDescent="0.25">
@@ -34505,13 +34505,13 @@
         <v>2630</v>
       </c>
       <c r="F954" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G954" s="2">
         <v>0</v>
       </c>
       <c r="H954" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="955" spans="1:8" x14ac:dyDescent="0.25">
@@ -34531,13 +34531,13 @@
         <v>2631</v>
       </c>
       <c r="F955" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G955" s="2">
         <v>0</v>
       </c>
       <c r="H955" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="956" spans="1:8" x14ac:dyDescent="0.25">
@@ -37183,13 +37183,13 @@
         <v>2592</v>
       </c>
       <c r="F1057" s="2">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="G1057" s="2">
         <v>0</v>
       </c>
       <c r="H1057" s="2">
-        <v>125</v>
+        <v>119</v>
       </c>
     </row>
     <row r="1058" spans="1:8" x14ac:dyDescent="0.25">
@@ -38847,13 +38847,13 @@
         <v>2734</v>
       </c>
       <c r="F1121" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1121" s="2">
         <v>0</v>
       </c>
       <c r="H1121" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1122" spans="1:8" x14ac:dyDescent="0.25">
@@ -39055,13 +39055,13 @@
         <v>2729</v>
       </c>
       <c r="F1129" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1129" s="2">
         <v>0</v>
       </c>
       <c r="H1129" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1130" spans="1:8" x14ac:dyDescent="0.25">
@@ -39679,13 +39679,13 @@
         <v>2729</v>
       </c>
       <c r="F1153" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G1153" s="2">
         <v>0</v>
       </c>
       <c r="H1153" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1154" spans="1:8" x14ac:dyDescent="0.25">
@@ -42409,13 +42409,13 @@
         <v>2825</v>
       </c>
       <c r="F1258" s="2">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="G1258" s="2">
         <v>0</v>
       </c>
       <c r="H1258" s="2">
-        <v>27</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1259" spans="1:8" x14ac:dyDescent="0.25">
@@ -43345,13 +43345,13 @@
         <v>2878</v>
       </c>
       <c r="F1294" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1294" s="2">
         <v>0</v>
       </c>
       <c r="H1294" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1295" spans="1:8" x14ac:dyDescent="0.25">
@@ -44645,13 +44645,13 @@
         <v>2826</v>
       </c>
       <c r="F1344" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G1344" s="2">
         <v>0</v>
       </c>
       <c r="H1344" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1345" spans="1:8" x14ac:dyDescent="0.25">
@@ -46049,13 +46049,13 @@
         <v>2847</v>
       </c>
       <c r="F1398" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G1398" s="2">
         <v>0</v>
       </c>
       <c r="H1398" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1399" spans="1:8" x14ac:dyDescent="0.25">
@@ -46205,13 +46205,13 @@
         <v>3014</v>
       </c>
       <c r="F1404" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G1404" s="2">
         <v>0</v>
       </c>
       <c r="H1404" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1405" spans="1:8" x14ac:dyDescent="0.25">
@@ -46387,13 +46387,13 @@
         <v>2996</v>
       </c>
       <c r="F1411" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G1411" s="2">
         <v>0</v>
       </c>
       <c r="H1411" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1412" spans="1:8" x14ac:dyDescent="0.25">
@@ -46491,13 +46491,13 @@
         <v>3014</v>
       </c>
       <c r="F1415" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1415" s="2">
         <v>0</v>
       </c>
       <c r="H1415" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1416" spans="1:8" x14ac:dyDescent="0.25">
@@ -46699,13 +46699,13 @@
         <v>2862</v>
       </c>
       <c r="F1423" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1423" s="2">
         <v>0</v>
       </c>
       <c r="H1423" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1424" spans="1:8" x14ac:dyDescent="0.25">
@@ -46803,10 +46803,10 @@
         <v>2871</v>
       </c>
       <c r="F1427" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1427" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1427" s="2">
         <v>0</v>

--- a/STOK DEALER/STOK SRB.xlsx
+++ b/STOK DEALER/STOK SRB.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data D\2025\UPADTE TOOLS BUNDLING SRB\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93C1EE41-876E-4561-B221-005C7FD0EA37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AF5D46B-E191-4EB9-8372-F022F31453A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{46E7093F-A843-4D56-8D6E-D290D3117D3B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{46E7093F-A843-4D56-8D6E-D290D3117D3B}"/>
   </bookViews>
   <sheets>
     <sheet name="STOK DEALER" sheetId="1" r:id="rId1"/>
@@ -9817,13 +9817,13 @@
         <v>1626</v>
       </c>
       <c r="F4" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G4" s="2">
         <v>0</v>
       </c>
       <c r="H4" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.25">
@@ -9869,13 +9869,13 @@
         <v>1627</v>
       </c>
       <c r="F6" s="2">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="G6" s="2">
         <v>0</v>
       </c>
       <c r="H6" s="2">
-        <v>43</v>
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -9947,13 +9947,13 @@
         <v>1628</v>
       </c>
       <c r="F9" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G9" s="2">
         <v>0</v>
       </c>
       <c r="H9" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -11377,13 +11377,13 @@
         <v>1260</v>
       </c>
       <c r="F64" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G64" s="2">
         <v>5</v>
       </c>
       <c r="H64" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
@@ -13375,13 +13375,13 @@
         <v>1782</v>
       </c>
       <c r="F141" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G141" s="2">
         <v>2</v>
       </c>
       <c r="H141" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
@@ -13404,10 +13404,10 @@
         <v>160</v>
       </c>
       <c r="G142" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H142" s="2">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
@@ -13557,13 +13557,13 @@
         <v>1791</v>
       </c>
       <c r="F148" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G148" s="2">
         <v>1</v>
       </c>
       <c r="H148" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
@@ -13817,13 +13817,13 @@
         <v>1782</v>
       </c>
       <c r="F158" s="2">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="G158" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H158" s="2">
-        <v>194</v>
+        <v>190</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
@@ -13843,13 +13843,13 @@
         <v>1791</v>
       </c>
       <c r="F159" s="2">
-        <v>611</v>
+        <v>596</v>
       </c>
       <c r="G159" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="H159" s="2">
-        <v>598</v>
+        <v>580</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
@@ -13999,13 +13999,13 @@
         <v>207</v>
       </c>
       <c r="F165" s="2">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="G165" s="2">
         <v>7</v>
       </c>
       <c r="H165" s="2">
-        <v>63</v>
+        <v>55</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
@@ -14545,13 +14545,13 @@
         <v>1818</v>
       </c>
       <c r="F186" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G186" s="2">
         <v>0</v>
       </c>
       <c r="H186" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.25">
@@ -14987,13 +14987,13 @@
         <v>1811</v>
       </c>
       <c r="F203" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G203" s="2">
         <v>0</v>
       </c>
       <c r="H203" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.25">
@@ -15169,13 +15169,13 @@
         <v>1856</v>
       </c>
       <c r="F210" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G210" s="2">
         <v>0</v>
       </c>
       <c r="H210" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.25">
@@ -20395,13 +20395,13 @@
         <v>2171</v>
       </c>
       <c r="F411" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G411" s="2">
         <v>2</v>
       </c>
       <c r="H411" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="412" spans="1:8" x14ac:dyDescent="0.25">
@@ -20551,13 +20551,13 @@
         <v>442</v>
       </c>
       <c r="F417" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G417" s="2">
         <v>0</v>
       </c>
       <c r="H417" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="418" spans="1:8" x14ac:dyDescent="0.25">
@@ -22733,13 +22733,13 @@
         <v>919</v>
       </c>
       <c r="F501" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G501" s="2">
         <v>0</v>
       </c>
       <c r="H501" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="502" spans="1:8" x14ac:dyDescent="0.25">
@@ -23071,13 +23071,13 @@
         <v>2251</v>
       </c>
       <c r="F514" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G514" s="2">
         <v>0</v>
       </c>
       <c r="H514" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="515" spans="1:8" x14ac:dyDescent="0.25">
@@ -24159,13 +24159,13 @@
         <v>2280</v>
       </c>
       <c r="F556" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G556" s="2">
         <v>1</v>
       </c>
       <c r="H556" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="557" spans="1:8" x14ac:dyDescent="0.25">
@@ -24471,13 +24471,13 @@
         <v>576</v>
       </c>
       <c r="F568" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G568" s="2">
         <v>0</v>
       </c>
       <c r="H568" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="569" spans="1:8" x14ac:dyDescent="0.25">
@@ -25953,13 +25953,13 @@
         <v>440</v>
       </c>
       <c r="F625" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G625" s="2">
         <v>1</v>
       </c>
       <c r="H625" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="626" spans="1:8" x14ac:dyDescent="0.25">
@@ -26398,10 +26398,10 @@
         <v>20</v>
       </c>
       <c r="G642" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H642" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="643" spans="1:8" x14ac:dyDescent="0.25">
@@ -26785,13 +26785,13 @@
         <v>402</v>
       </c>
       <c r="F657" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G657" s="2">
         <v>1</v>
       </c>
       <c r="H657" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="658" spans="1:8" x14ac:dyDescent="0.25">
@@ -27513,13 +27513,13 @@
         <v>1811</v>
       </c>
       <c r="F685" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G685" s="2">
         <v>0</v>
       </c>
       <c r="H685" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="686" spans="1:8" x14ac:dyDescent="0.25">
@@ -27851,13 +27851,13 @@
         <v>2454</v>
       </c>
       <c r="F698" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G698" s="2">
         <v>0</v>
       </c>
       <c r="H698" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="699" spans="1:8" x14ac:dyDescent="0.25">
@@ -28345,13 +28345,13 @@
         <v>693</v>
       </c>
       <c r="F717" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G717" s="2">
         <v>1</v>
       </c>
       <c r="H717" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="718" spans="1:8" x14ac:dyDescent="0.25">
@@ -28865,13 +28865,13 @@
         <v>2478</v>
       </c>
       <c r="F737" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G737" s="2">
         <v>9</v>
       </c>
       <c r="H737" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="738" spans="1:8" x14ac:dyDescent="0.25">
@@ -33361,13 +33361,13 @@
         <v>1625</v>
       </c>
       <c r="F910" s="2">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="G910" s="2">
         <v>0</v>
       </c>
       <c r="H910" s="2">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="911" spans="1:8" x14ac:dyDescent="0.25">
@@ -33491,13 +33491,13 @@
         <v>1871</v>
       </c>
       <c r="F915" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G915" s="2">
         <v>0</v>
       </c>
       <c r="H915" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="916" spans="1:8" x14ac:dyDescent="0.25">
@@ -34349,13 +34349,13 @@
         <v>2516</v>
       </c>
       <c r="F948" s="2">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="G948" s="2">
         <v>0</v>
       </c>
       <c r="H948" s="2">
-        <v>23</v>
+        <v>19</v>
       </c>
     </row>
     <row r="949" spans="1:8" x14ac:dyDescent="0.25">
@@ -34453,13 +34453,13 @@
         <v>2626</v>
       </c>
       <c r="F952" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G952" s="2">
         <v>0</v>
       </c>
       <c r="H952" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="953" spans="1:8" x14ac:dyDescent="0.25">
@@ -34531,13 +34531,13 @@
         <v>2631</v>
       </c>
       <c r="F955" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G955" s="2">
         <v>0</v>
       </c>
       <c r="H955" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="956" spans="1:8" x14ac:dyDescent="0.25">
@@ -37183,13 +37183,13 @@
         <v>2592</v>
       </c>
       <c r="F1057" s="2">
-        <v>119</v>
+        <v>105</v>
       </c>
       <c r="G1057" s="2">
         <v>0</v>
       </c>
       <c r="H1057" s="2">
-        <v>119</v>
+        <v>105</v>
       </c>
     </row>
     <row r="1058" spans="1:8" x14ac:dyDescent="0.25">
@@ -38275,13 +38275,13 @@
         <v>2454</v>
       </c>
       <c r="F1099" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1099" s="2">
         <v>0</v>
       </c>
       <c r="H1099" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1100" spans="1:8" x14ac:dyDescent="0.25">
@@ -38847,13 +38847,13 @@
         <v>2734</v>
       </c>
       <c r="F1121" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1121" s="2">
         <v>0</v>
       </c>
       <c r="H1121" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1122" spans="1:8" x14ac:dyDescent="0.25">
@@ -39679,13 +39679,13 @@
         <v>2729</v>
       </c>
       <c r="F1153" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G1153" s="2">
         <v>0</v>
       </c>
       <c r="H1153" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1154" spans="1:8" x14ac:dyDescent="0.25">
@@ -39757,13 +39757,13 @@
         <v>2730</v>
       </c>
       <c r="F1156" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G1156" s="2">
         <v>0</v>
       </c>
       <c r="H1156" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="1157" spans="1:8" x14ac:dyDescent="0.25">
@@ -39809,13 +39809,13 @@
         <v>2730</v>
       </c>
       <c r="F1158" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G1158" s="2">
         <v>0</v>
       </c>
       <c r="H1158" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1159" spans="1:8" x14ac:dyDescent="0.25">
@@ -39835,13 +39835,13 @@
         <v>2730</v>
       </c>
       <c r="F1159" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G1159" s="2">
         <v>0</v>
       </c>
       <c r="H1159" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1160" spans="1:8" x14ac:dyDescent="0.25">
@@ -42175,13 +42175,13 @@
         <v>2306</v>
       </c>
       <c r="F1249" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="G1249" s="2">
         <v>3</v>
       </c>
       <c r="H1249" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="1250" spans="1:8" x14ac:dyDescent="0.25">
@@ -42409,13 +42409,13 @@
         <v>2825</v>
       </c>
       <c r="F1258" s="2">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G1258" s="2">
         <v>0</v>
       </c>
       <c r="H1258" s="2">
-        <v>21</v>
+        <v>15</v>
       </c>
     </row>
     <row r="1259" spans="1:8" x14ac:dyDescent="0.25">
@@ -42903,13 +42903,13 @@
         <v>2853</v>
       </c>
       <c r="F1277" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1277" s="2">
         <v>0</v>
       </c>
       <c r="H1277" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1278" spans="1:8" x14ac:dyDescent="0.25">
@@ -43371,13 +43371,13 @@
         <v>2856</v>
       </c>
       <c r="F1295" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1295" s="2">
         <v>0</v>
       </c>
       <c r="H1295" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1296" spans="1:8" x14ac:dyDescent="0.25">
@@ -44723,13 +44723,13 @@
         <v>2827</v>
       </c>
       <c r="F1347" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G1347" s="2">
         <v>0</v>
       </c>
       <c r="H1347" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1348" spans="1:8" x14ac:dyDescent="0.25">
@@ -44905,13 +44905,13 @@
         <v>2948</v>
       </c>
       <c r="F1354" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1354" s="2">
         <v>0</v>
       </c>
       <c r="H1354" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1355" spans="1:8" x14ac:dyDescent="0.25">
@@ -45555,13 +45555,13 @@
         <v>2916</v>
       </c>
       <c r="F1379" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1379" s="2">
         <v>0</v>
       </c>
       <c r="H1379" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1380" spans="1:8" x14ac:dyDescent="0.25">
@@ -46049,13 +46049,13 @@
         <v>2847</v>
       </c>
       <c r="F1398" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G1398" s="2">
         <v>0</v>
       </c>
       <c r="H1398" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1399" spans="1:8" x14ac:dyDescent="0.25">
@@ -46075,13 +46075,13 @@
         <v>2996</v>
       </c>
       <c r="F1399" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G1399" s="2">
         <v>0</v>
       </c>
       <c r="H1399" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1400" spans="1:8" x14ac:dyDescent="0.25">
@@ -46205,13 +46205,13 @@
         <v>3014</v>
       </c>
       <c r="F1404" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G1404" s="2">
         <v>0</v>
       </c>
       <c r="H1404" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1405" spans="1:8" x14ac:dyDescent="0.25">
@@ -46647,13 +46647,13 @@
         <v>2917</v>
       </c>
       <c r="F1421" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G1421" s="2">
         <v>0</v>
       </c>
       <c r="H1421" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1422" spans="1:8" x14ac:dyDescent="0.25">
@@ -47583,13 +47583,13 @@
         <v>2354</v>
       </c>
       <c r="F1457" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1457" s="2">
         <v>0</v>
       </c>
       <c r="H1457" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1458" spans="1:8" x14ac:dyDescent="0.25">
@@ -47609,13 +47609,13 @@
         <v>3058</v>
       </c>
       <c r="F1458" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1458" s="2">
         <v>0</v>
       </c>
       <c r="H1458" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1459" spans="1:8" x14ac:dyDescent="0.25">
@@ -47748,7 +47748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1464" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1464" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1464" s="2">
         <v>1463</v>
       </c>
@@ -47774,7 +47774,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="1465" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1465" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1465" s="2">
         <v>1464</v>
       </c>

--- a/STOK DEALER/STOK SRB.xlsx
+++ b/STOK DEALER/STOK SRB.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\STOK DEALER\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data D\2025\UPADTE TOOLS BUNDLING SRB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7AF5D46B-E191-4EB9-8372-F022F31453A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A08E98FD-C96E-483E-8660-7E976242E0AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{46E7093F-A843-4D56-8D6E-D290D3117D3B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{46E7093F-A843-4D56-8D6E-D290D3117D3B}"/>
   </bookViews>
   <sheets>
     <sheet name="STOK DEALER" sheetId="1" r:id="rId1"/>
@@ -9765,13 +9765,13 @@
         <v>1624</v>
       </c>
       <c r="F2" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G2" s="2">
         <v>0</v>
       </c>
       <c r="H2" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -9843,13 +9843,13 @@
         <v>1627</v>
       </c>
       <c r="F5" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G5" s="2">
         <v>0</v>
       </c>
       <c r="H5" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -9872,10 +9872,10 @@
         <v>37</v>
       </c>
       <c r="G6" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H6" s="2">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -9895,13 +9895,13 @@
         <v>1627</v>
       </c>
       <c r="F7" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G7" s="2">
         <v>0</v>
       </c>
       <c r="H7" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.25">
@@ -11455,13 +11455,13 @@
         <v>1682</v>
       </c>
       <c r="F67" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G67" s="2">
         <v>1</v>
       </c>
       <c r="H67" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
@@ -13378,10 +13378,10 @@
         <v>31</v>
       </c>
       <c r="G141" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H141" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
@@ -13401,13 +13401,13 @@
         <v>1783</v>
       </c>
       <c r="F142" s="2">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G142" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H142" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
@@ -13557,13 +13557,13 @@
         <v>1791</v>
       </c>
       <c r="F148" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G148" s="2">
         <v>1</v>
       </c>
       <c r="H148" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
@@ -13817,13 +13817,13 @@
         <v>1782</v>
       </c>
       <c r="F158" s="2">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="G158" s="2">
         <v>10</v>
       </c>
       <c r="H158" s="2">
-        <v>190</v>
+        <v>185</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
@@ -13843,13 +13843,13 @@
         <v>1791</v>
       </c>
       <c r="F159" s="2">
-        <v>596</v>
+        <v>585</v>
       </c>
       <c r="G159" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="H159" s="2">
-        <v>580</v>
+        <v>572</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
@@ -13924,10 +13924,10 @@
         <v>21</v>
       </c>
       <c r="G162" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H162" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
@@ -13999,13 +13999,13 @@
         <v>207</v>
       </c>
       <c r="F165" s="2">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="G165" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H165" s="2">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
@@ -15172,10 +15172,10 @@
         <v>7</v>
       </c>
       <c r="G210" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H210" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.25">
@@ -24211,13 +24211,13 @@
         <v>351</v>
       </c>
       <c r="F558" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G558" s="2">
         <v>2</v>
       </c>
       <c r="H558" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="559" spans="1:8" x14ac:dyDescent="0.25">
@@ -26814,10 +26814,10 @@
         <v>41</v>
       </c>
       <c r="G658" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H658" s="2">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="659" spans="1:8" x14ac:dyDescent="0.25">
@@ -28345,13 +28345,13 @@
         <v>693</v>
       </c>
       <c r="F717" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G717" s="2">
         <v>1</v>
       </c>
       <c r="H717" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="718" spans="1:8" x14ac:dyDescent="0.25">
@@ -34349,13 +34349,13 @@
         <v>2516</v>
       </c>
       <c r="F948" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G948" s="2">
         <v>0</v>
       </c>
       <c r="H948" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="949" spans="1:8" x14ac:dyDescent="0.25">
@@ -34453,13 +34453,13 @@
         <v>2626</v>
       </c>
       <c r="F952" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G952" s="2">
         <v>0</v>
       </c>
       <c r="H952" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="953" spans="1:8" x14ac:dyDescent="0.25">
@@ -36455,13 +36455,13 @@
         <v>1750</v>
       </c>
       <c r="F1029" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1029" s="2">
         <v>0</v>
       </c>
       <c r="H1029" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1030" spans="1:8" x14ac:dyDescent="0.25">
@@ -37183,13 +37183,13 @@
         <v>2592</v>
       </c>
       <c r="F1057" s="2">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="G1057" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1057" s="2">
-        <v>105</v>
+        <v>98</v>
       </c>
     </row>
     <row r="1058" spans="1:8" x14ac:dyDescent="0.25">
@@ -39341,13 +39341,13 @@
         <v>2735</v>
       </c>
       <c r="F1140" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1140" s="2">
         <v>0</v>
       </c>
       <c r="H1140" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1141" spans="1:8" x14ac:dyDescent="0.25">
@@ -39679,13 +39679,13 @@
         <v>2729</v>
       </c>
       <c r="F1153" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1153" s="2">
         <v>0</v>
       </c>
       <c r="H1153" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1154" spans="1:8" x14ac:dyDescent="0.25">
@@ -39757,13 +39757,13 @@
         <v>2730</v>
       </c>
       <c r="F1156" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G1156" s="2">
         <v>0</v>
       </c>
       <c r="H1156" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="1157" spans="1:8" x14ac:dyDescent="0.25">
@@ -39809,13 +39809,13 @@
         <v>2730</v>
       </c>
       <c r="F1158" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G1158" s="2">
         <v>0</v>
       </c>
       <c r="H1158" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1159" spans="1:8" x14ac:dyDescent="0.25">
@@ -40043,13 +40043,13 @@
         <v>2724</v>
       </c>
       <c r="F1167" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1167" s="2">
         <v>0</v>
       </c>
       <c r="H1167" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1168" spans="1:8" x14ac:dyDescent="0.25">
@@ -42175,13 +42175,13 @@
         <v>2306</v>
       </c>
       <c r="F1249" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G1249" s="2">
         <v>3</v>
       </c>
       <c r="H1249" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="1250" spans="1:8" x14ac:dyDescent="0.25">
@@ -42409,13 +42409,13 @@
         <v>2825</v>
       </c>
       <c r="F1258" s="2">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="G1258" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1258" s="2">
-        <v>15</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1259" spans="1:8" x14ac:dyDescent="0.25">
@@ -42854,10 +42854,10 @@
         <v>7</v>
       </c>
       <c r="G1275" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1275" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1276" spans="1:8" x14ac:dyDescent="0.25">
@@ -43319,13 +43319,13 @@
         <v>2878</v>
       </c>
       <c r="F1293" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1293" s="2">
         <v>0</v>
       </c>
       <c r="H1293" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1294" spans="1:8" x14ac:dyDescent="0.25">
@@ -43371,13 +43371,13 @@
         <v>2856</v>
       </c>
       <c r="F1295" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1295" s="2">
         <v>0</v>
       </c>
       <c r="H1295" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1296" spans="1:8" x14ac:dyDescent="0.25">
@@ -45347,13 +45347,13 @@
         <v>2869</v>
       </c>
       <c r="F1371" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G1371" s="2">
         <v>0</v>
       </c>
       <c r="H1371" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1372" spans="1:8" x14ac:dyDescent="0.25">
@@ -45555,13 +45555,13 @@
         <v>2916</v>
       </c>
       <c r="F1379" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1379" s="2">
         <v>0</v>
       </c>
       <c r="H1379" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1380" spans="1:8" x14ac:dyDescent="0.25">
@@ -46205,13 +46205,13 @@
         <v>3014</v>
       </c>
       <c r="F1404" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G1404" s="2">
         <v>0</v>
       </c>
       <c r="H1404" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1405" spans="1:8" x14ac:dyDescent="0.25">
@@ -46309,13 +46309,13 @@
         <v>3014</v>
       </c>
       <c r="F1408" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G1408" s="2">
         <v>0</v>
       </c>
       <c r="H1408" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1409" spans="1:8" x14ac:dyDescent="0.25">
@@ -46595,13 +46595,13 @@
         <v>2870</v>
       </c>
       <c r="F1419" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G1419" s="2">
         <v>0</v>
       </c>
       <c r="H1419" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1420" spans="1:8" x14ac:dyDescent="0.25">
@@ -46647,13 +46647,13 @@
         <v>2917</v>
       </c>
       <c r="F1421" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G1421" s="2">
         <v>0</v>
       </c>
       <c r="H1421" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1422" spans="1:8" x14ac:dyDescent="0.25">
@@ -46673,13 +46673,13 @@
         <v>2996</v>
       </c>
       <c r="F1422" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G1422" s="2">
         <v>0</v>
       </c>
       <c r="H1422" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1423" spans="1:8" x14ac:dyDescent="0.25">
@@ -47748,7 +47748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="1464" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1464" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1464" s="2">
         <v>1463</v>
       </c>
@@ -47774,7 +47774,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="1465" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1465" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1465" s="2">
         <v>1464</v>
       </c>

--- a/STOK DEALER/STOK SRB.xlsx
+++ b/STOK DEALER/STOK SRB.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0FB991CA-63DC-47AD-A460-35E67D0234B7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0A7589D-C89B-4662-BD98-4E930121E1F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{46E7093F-A843-4D56-8D6E-D290D3117D3B}"/>
+    <workbookView xWindow="3765" yWindow="3765" windowWidth="21600" windowHeight="11295" xr2:uid="{46E7093F-A843-4D56-8D6E-D290D3117D3B}"/>
   </bookViews>
   <sheets>
     <sheet name="STOK DEALER" sheetId="1" r:id="rId1"/>
@@ -9870,13 +9870,13 @@
         <v>1627</v>
       </c>
       <c r="F5" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G5" s="2">
         <v>0</v>
       </c>
       <c r="H5" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -9896,13 +9896,13 @@
         <v>1627</v>
       </c>
       <c r="F6" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G6" s="2">
         <v>0</v>
       </c>
       <c r="H6" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -9948,13 +9948,13 @@
         <v>1627</v>
       </c>
       <c r="F8" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G8" s="2">
         <v>0</v>
       </c>
       <c r="H8" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -9974,13 +9974,13 @@
         <v>1628</v>
       </c>
       <c r="F9" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G9" s="2">
         <v>0</v>
       </c>
       <c r="H9" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -11014,13 +11014,13 @@
         <v>1068</v>
       </c>
       <c r="F49" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G49" s="2">
         <v>1</v>
       </c>
       <c r="H49" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
@@ -13428,13 +13428,13 @@
         <v>1783</v>
       </c>
       <c r="F142" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G142" s="2">
         <v>6</v>
       </c>
       <c r="H142" s="2">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
@@ -13844,13 +13844,13 @@
         <v>1782</v>
       </c>
       <c r="F158" s="2">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="G158" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H158" s="2">
-        <v>177</v>
+        <v>174</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
@@ -13870,13 +13870,13 @@
         <v>1791</v>
       </c>
       <c r="F159" s="2">
-        <v>777</v>
+        <v>771</v>
       </c>
       <c r="G159" s="2">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H159" s="2">
-        <v>761</v>
+        <v>754</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
@@ -20422,13 +20422,13 @@
         <v>926</v>
       </c>
       <c r="F411" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G411" s="2">
         <v>5</v>
       </c>
       <c r="H411" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="412" spans="1:8" x14ac:dyDescent="0.25">
@@ -20474,13 +20474,13 @@
         <v>433</v>
       </c>
       <c r="F413" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G413" s="2">
         <v>3</v>
       </c>
       <c r="H413" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="414" spans="1:8" x14ac:dyDescent="0.25">
@@ -20760,13 +20760,13 @@
         <v>2176</v>
       </c>
       <c r="F424" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G424" s="2">
         <v>0</v>
       </c>
       <c r="H424" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="425" spans="1:8" x14ac:dyDescent="0.25">
@@ -22529,10 +22529,10 @@
         <v>11</v>
       </c>
       <c r="G492" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H492" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="493" spans="1:8" x14ac:dyDescent="0.25">
@@ -24524,13 +24524,13 @@
         <v>483</v>
       </c>
       <c r="F569" s="2">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G569" s="2">
         <v>2</v>
       </c>
       <c r="H569" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="570" spans="1:8" x14ac:dyDescent="0.25">
@@ -26890,13 +26890,13 @@
         <v>402</v>
       </c>
       <c r="F660" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G660" s="2">
         <v>1</v>
       </c>
       <c r="H660" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="661" spans="1:8" x14ac:dyDescent="0.25">
@@ -26916,13 +26916,13 @@
         <v>430</v>
       </c>
       <c r="F661" s="2">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G661" s="2">
         <v>3</v>
       </c>
       <c r="H661" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="662" spans="1:8" x14ac:dyDescent="0.25">
@@ -30244,13 +30244,13 @@
         <v>2532</v>
       </c>
       <c r="F789" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G789" s="2">
         <v>0</v>
       </c>
       <c r="H789" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="790" spans="1:8" x14ac:dyDescent="0.25">
@@ -30556,13 +30556,13 @@
         <v>1110</v>
       </c>
       <c r="F801" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G801" s="2">
         <v>4</v>
       </c>
       <c r="H801" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="802" spans="1:8" x14ac:dyDescent="0.25">
@@ -31024,13 +31024,13 @@
         <v>2553</v>
       </c>
       <c r="F819" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G819" s="2">
         <v>3</v>
       </c>
       <c r="H819" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="820" spans="1:8" x14ac:dyDescent="0.25">
@@ -37314,13 +37314,13 @@
         <v>2592</v>
       </c>
       <c r="F1061" s="2">
-        <v>65</v>
+        <v>59</v>
       </c>
       <c r="G1061" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1061" s="2">
-        <v>65</v>
+        <v>58</v>
       </c>
     </row>
     <row r="1062" spans="1:8" x14ac:dyDescent="0.25">
@@ -39602,13 +39602,13 @@
         <v>2730</v>
       </c>
       <c r="F1149" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1149" s="2">
         <v>0</v>
       </c>
       <c r="H1149" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1150" spans="1:8" x14ac:dyDescent="0.25">
@@ -39891,10 +39891,10 @@
         <v>28</v>
       </c>
       <c r="G1160" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1160" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1161" spans="1:8" x14ac:dyDescent="0.25">
@@ -39940,13 +39940,13 @@
         <v>2730</v>
       </c>
       <c r="F1162" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G1162" s="2">
         <v>0</v>
       </c>
       <c r="H1162" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1163" spans="1:8" x14ac:dyDescent="0.25">
@@ -41396,13 +41396,13 @@
         <v>2386</v>
       </c>
       <c r="F1218" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1218" s="2">
         <v>1</v>
       </c>
       <c r="H1218" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1219" spans="1:8" x14ac:dyDescent="0.25">
@@ -46232,13 +46232,13 @@
         <v>2847</v>
       </c>
       <c r="F1404" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G1404" s="2">
         <v>0</v>
       </c>
       <c r="H1404" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1405" spans="1:8" x14ac:dyDescent="0.25">
@@ -46544,13 +46544,13 @@
         <v>2968</v>
       </c>
       <c r="F1416" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G1416" s="2">
         <v>0</v>
       </c>
       <c r="H1416" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="1417" spans="1:8" x14ac:dyDescent="0.25">
@@ -46674,13 +46674,13 @@
         <v>3014</v>
       </c>
       <c r="F1421" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1421" s="2">
         <v>0</v>
       </c>
       <c r="H1421" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1422" spans="1:8" x14ac:dyDescent="0.25">
@@ -46726,13 +46726,13 @@
         <v>2934</v>
       </c>
       <c r="F1423" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1423" s="2">
         <v>0</v>
       </c>
       <c r="H1423" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1424" spans="1:8" x14ac:dyDescent="0.25">
@@ -46830,13 +46830,13 @@
         <v>2917</v>
       </c>
       <c r="F1427" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1427" s="2">
         <v>0</v>
       </c>
       <c r="H1427" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1428" spans="1:8" x14ac:dyDescent="0.25">
@@ -47142,13 +47142,13 @@
         <v>2955</v>
       </c>
       <c r="F1439" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G1439" s="2">
         <v>0</v>
       </c>
       <c r="H1439" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1440" spans="1:8" x14ac:dyDescent="0.25">
@@ -47584,13 +47584,13 @@
         <v>207</v>
       </c>
       <c r="F1456" s="2">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="G1456" s="2">
         <v>0</v>
       </c>
       <c r="H1456" s="2">
-        <v>24</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1457" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK SRB.xlsx
+++ b/STOK DEALER/STOK SRB.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D0A7589D-C89B-4662-BD98-4E930121E1F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B65FFAA-4D7D-4A75-8E17-C0617753295C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3765" yWindow="3765" windowWidth="21600" windowHeight="11295" xr2:uid="{46E7093F-A843-4D56-8D6E-D290D3117D3B}"/>
+    <workbookView xWindow="1950" yWindow="1725" windowWidth="9870" windowHeight="14475" xr2:uid="{46E7093F-A843-4D56-8D6E-D290D3117D3B}"/>
   </bookViews>
   <sheets>
     <sheet name="STOK DEALER" sheetId="1" r:id="rId1"/>
@@ -9795,10 +9795,10 @@
         <v>11</v>
       </c>
       <c r="G2" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -9896,13 +9896,13 @@
         <v>1627</v>
       </c>
       <c r="F6" s="2">
-        <v>30</v>
+        <v>24</v>
       </c>
       <c r="G6" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H6" s="2">
-        <v>30</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -9951,10 +9951,10 @@
         <v>3</v>
       </c>
       <c r="G8" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H8" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -10026,10 +10026,10 @@
         <v>1631</v>
       </c>
       <c r="F11" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G11" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H11" s="2">
         <v>0</v>
@@ -10289,10 +10289,10 @@
         <v>3</v>
       </c>
       <c r="G21" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H21" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
@@ -10442,10 +10442,10 @@
         <v>1652</v>
       </c>
       <c r="F27" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G27" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H27" s="2">
         <v>1</v>
@@ -10624,10 +10624,10 @@
         <v>1660</v>
       </c>
       <c r="F34" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G34" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H34" s="2">
         <v>1</v>
@@ -10702,10 +10702,10 @@
         <v>1647</v>
       </c>
       <c r="F37" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G37" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H37" s="2">
         <v>0</v>
@@ -10884,10 +10884,10 @@
         <v>1672</v>
       </c>
       <c r="F44" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G44" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H44" s="2">
         <v>12</v>
@@ -10936,10 +10936,10 @@
         <v>451</v>
       </c>
       <c r="F46" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G46" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H46" s="2">
         <v>1</v>
@@ -11014,10 +11014,10 @@
         <v>1068</v>
       </c>
       <c r="F49" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G49" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H49" s="2">
         <v>6</v>
@@ -11196,10 +11196,10 @@
         <v>30</v>
       </c>
       <c r="F56" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G56" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H56" s="2">
         <v>24</v>
@@ -11222,10 +11222,10 @@
         <v>1068</v>
       </c>
       <c r="F57" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G57" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H57" s="2">
         <v>0</v>
@@ -11378,10 +11378,10 @@
         <v>1681</v>
       </c>
       <c r="F63" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G63" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H63" s="2">
         <v>5</v>
@@ -11404,13 +11404,13 @@
         <v>1260</v>
       </c>
       <c r="F64" s="2">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="G64" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H64" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
@@ -11482,10 +11482,10 @@
         <v>1682</v>
       </c>
       <c r="F67" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G67" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H67" s="2">
         <v>8</v>
@@ -11508,10 +11508,10 @@
         <v>1682</v>
       </c>
       <c r="F68" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G68" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H68" s="2">
         <v>7</v>
@@ -13402,13 +13402,13 @@
         <v>1782</v>
       </c>
       <c r="F141" s="2">
-        <v>26</v>
+        <v>49</v>
       </c>
       <c r="G141" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H141" s="2">
-        <v>23</v>
+        <v>49</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
@@ -13428,13 +13428,13 @@
         <v>1783</v>
       </c>
       <c r="F142" s="2">
-        <v>152</v>
+        <v>159</v>
       </c>
       <c r="G142" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H142" s="2">
-        <v>146</v>
+        <v>159</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
@@ -13457,10 +13457,10 @@
         <v>252</v>
       </c>
       <c r="G143" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H143" s="2">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
@@ -13584,13 +13584,13 @@
         <v>1791</v>
       </c>
       <c r="F148" s="2">
-        <v>13</v>
+        <v>290</v>
       </c>
       <c r="G148" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H148" s="2">
-        <v>10</v>
+        <v>289</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
@@ -13844,13 +13844,13 @@
         <v>1782</v>
       </c>
       <c r="F158" s="2">
-        <v>185</v>
+        <v>169</v>
       </c>
       <c r="G158" s="2">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H158" s="2">
-        <v>174</v>
+        <v>168</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
@@ -13870,13 +13870,13 @@
         <v>1791</v>
       </c>
       <c r="F159" s="2">
-        <v>771</v>
+        <v>756</v>
       </c>
       <c r="G159" s="2">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="H159" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
@@ -13922,10 +13922,10 @@
         <v>1783</v>
       </c>
       <c r="F161" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G161" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H161" s="2">
         <v>0</v>
@@ -13948,10 +13948,10 @@
         <v>207</v>
       </c>
       <c r="F162" s="2">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G162" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H162" s="2">
         <v>15</v>
@@ -14026,13 +14026,13 @@
         <v>207</v>
       </c>
       <c r="F165" s="2">
-        <v>54</v>
+        <v>136</v>
       </c>
       <c r="G165" s="2">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="H165" s="2">
-        <v>43</v>
+        <v>135</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
@@ -14182,13 +14182,13 @@
         <v>939</v>
       </c>
       <c r="F171" s="2">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="G171" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H171" s="2">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
@@ -14208,13 +14208,13 @@
         <v>1811</v>
       </c>
       <c r="F172" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G172" s="2">
         <v>0</v>
       </c>
       <c r="H172" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.25">
@@ -14312,13 +14312,13 @@
         <v>1818</v>
       </c>
       <c r="F176" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G176" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H176" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.25">
@@ -14832,13 +14832,13 @@
         <v>1817</v>
       </c>
       <c r="F196" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G196" s="2">
         <v>0</v>
       </c>
       <c r="H196" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.25">
@@ -14910,13 +14910,13 @@
         <v>1829</v>
       </c>
       <c r="F199" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G199" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H199" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.25">
@@ -14988,13 +14988,13 @@
         <v>1843</v>
       </c>
       <c r="F202" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G202" s="2">
         <v>0</v>
       </c>
       <c r="H202" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.25">
@@ -15014,13 +15014,13 @@
         <v>1811</v>
       </c>
       <c r="F203" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G203" s="2">
         <v>0</v>
       </c>
       <c r="H203" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.25">
@@ -15222,13 +15222,13 @@
         <v>1857</v>
       </c>
       <c r="F211" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G211" s="2">
         <v>0</v>
       </c>
       <c r="H211" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.25">
@@ -16756,10 +16756,10 @@
         <v>1958</v>
       </c>
       <c r="F270" s="2">
-        <v>44</v>
+        <v>24</v>
       </c>
       <c r="G270" s="2">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H270" s="2">
         <v>24</v>
@@ -16860,10 +16860,10 @@
         <v>1963</v>
       </c>
       <c r="F274" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G274" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H274" s="2">
         <v>0</v>
@@ -18134,10 +18134,10 @@
         <v>2030</v>
       </c>
       <c r="F323" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G323" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H323" s="2">
         <v>2</v>
@@ -18290,10 +18290,10 @@
         <v>2043</v>
       </c>
       <c r="F329" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G329" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H329" s="2">
         <v>0</v>
@@ -18914,10 +18914,10 @@
         <v>1954</v>
       </c>
       <c r="F353" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G353" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H353" s="2">
         <v>1</v>
@@ -19070,10 +19070,10 @@
         <v>2097</v>
       </c>
       <c r="F359" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G359" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H359" s="2">
         <v>0</v>
@@ -19096,10 +19096,10 @@
         <v>2097</v>
       </c>
       <c r="F360" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G360" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H360" s="2">
         <v>0</v>
@@ -19278,10 +19278,10 @@
         <v>2109</v>
       </c>
       <c r="F367" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G367" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H367" s="2">
         <v>0</v>
@@ -19590,10 +19590,10 @@
         <v>2129</v>
       </c>
       <c r="F379" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G379" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H379" s="2">
         <v>0</v>
@@ -19902,10 +19902,10 @@
         <v>2147</v>
       </c>
       <c r="F391" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G391" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H391" s="2">
         <v>0</v>
@@ -19954,10 +19954,10 @@
         <v>2132</v>
       </c>
       <c r="F393" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G393" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H393" s="2">
         <v>0</v>
@@ -20061,10 +20061,10 @@
         <v>1</v>
       </c>
       <c r="G397" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H397" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="398" spans="1:8" ht="30" x14ac:dyDescent="0.25">
@@ -20318,13 +20318,13 @@
         <v>2167</v>
       </c>
       <c r="F407" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G407" s="2">
         <v>0</v>
       </c>
       <c r="H407" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="408" spans="1:8" x14ac:dyDescent="0.25">
@@ -20370,10 +20370,10 @@
         <v>1095</v>
       </c>
       <c r="F409" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G409" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H409" s="2">
         <v>0</v>
@@ -20396,13 +20396,13 @@
         <v>2170</v>
       </c>
       <c r="F410" s="2">
-        <v>35</v>
+        <v>30</v>
       </c>
       <c r="G410" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H410" s="2">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="411" spans="1:8" x14ac:dyDescent="0.25">
@@ -20422,13 +20422,13 @@
         <v>926</v>
       </c>
       <c r="F411" s="2">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G411" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="H411" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="412" spans="1:8" x14ac:dyDescent="0.25">
@@ -20448,10 +20448,10 @@
         <v>2171</v>
       </c>
       <c r="F412" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G412" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H412" s="2">
         <v>8</v>
@@ -20474,10 +20474,10 @@
         <v>433</v>
       </c>
       <c r="F413" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G413" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H413" s="2">
         <v>1</v>
@@ -20838,10 +20838,10 @@
         <v>2175</v>
       </c>
       <c r="F427" s="2">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G427" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H427" s="2">
         <v>11</v>
@@ -20916,10 +20916,10 @@
         <v>1961</v>
       </c>
       <c r="F430" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G430" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H430" s="2">
         <v>13</v>
@@ -22110,10 +22110,10 @@
         <v>1099</v>
       </c>
       <c r="F476" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G476" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H476" s="2">
         <v>5</v>
@@ -22162,10 +22162,10 @@
         <v>2239</v>
       </c>
       <c r="F478" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G478" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H478" s="2">
         <v>0</v>
@@ -22188,13 +22188,13 @@
         <v>610</v>
       </c>
       <c r="F479" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G479" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H479" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="480" spans="1:8" x14ac:dyDescent="0.25">
@@ -22214,10 +22214,10 @@
         <v>587</v>
       </c>
       <c r="F480" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G480" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H480" s="2">
         <v>2</v>
@@ -22240,10 +22240,10 @@
         <v>610</v>
       </c>
       <c r="F481" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G481" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H481" s="2">
         <v>3</v>
@@ -22500,10 +22500,10 @@
         <v>303</v>
       </c>
       <c r="F491" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G491" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H491" s="2">
         <v>0</v>
@@ -22526,13 +22526,13 @@
         <v>300</v>
       </c>
       <c r="F492" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G492" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H492" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="493" spans="1:8" x14ac:dyDescent="0.25">
@@ -22708,10 +22708,10 @@
         <v>2244</v>
       </c>
       <c r="F499" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G499" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H499" s="2">
         <v>2</v>
@@ -22968,10 +22968,10 @@
         <v>581</v>
       </c>
       <c r="F509" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G509" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H509" s="2">
         <v>7</v>
@@ -23410,10 +23410,10 @@
         <v>2255</v>
       </c>
       <c r="F526" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G526" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H526" s="2">
         <v>3</v>
@@ -23697,10 +23697,10 @@
         <v>4</v>
       </c>
       <c r="G537" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H537" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="538" spans="1:8" x14ac:dyDescent="0.25">
@@ -23720,10 +23720,10 @@
         <v>236</v>
       </c>
       <c r="F538" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G538" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H538" s="2">
         <v>1</v>
@@ -23746,10 +23746,10 @@
         <v>568</v>
       </c>
       <c r="F539" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G539" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H539" s="2">
         <v>4</v>
@@ -23848,10 +23848,10 @@
         <v>538</v>
       </c>
       <c r="F543" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G543" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H543" s="2">
         <v>0</v>
@@ -24160,13 +24160,13 @@
         <v>2277</v>
       </c>
       <c r="F555" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G555" s="2">
         <v>0</v>
       </c>
       <c r="H555" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="556" spans="1:8" x14ac:dyDescent="0.25">
@@ -24264,10 +24264,10 @@
         <v>2280</v>
       </c>
       <c r="F559" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G559" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H559" s="2">
         <v>1</v>
@@ -24316,10 +24316,10 @@
         <v>351</v>
       </c>
       <c r="F561" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G561" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H561" s="2">
         <v>2</v>
@@ -24342,10 +24342,10 @@
         <v>351</v>
       </c>
       <c r="F562" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G562" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H562" s="2">
         <v>0</v>
@@ -24446,13 +24446,13 @@
         <v>408</v>
       </c>
       <c r="F566" s="2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G566" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H566" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="567" spans="1:8" x14ac:dyDescent="0.25">
@@ -24524,10 +24524,10 @@
         <v>483</v>
       </c>
       <c r="F569" s="2">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="G569" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H569" s="2">
         <v>31</v>
@@ -24553,10 +24553,10 @@
         <v>5</v>
       </c>
       <c r="G570" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H570" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="571" spans="1:8" x14ac:dyDescent="0.25">
@@ -25798,13 +25798,13 @@
         <v>440</v>
       </c>
       <c r="F618" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G618" s="2">
         <v>0</v>
       </c>
       <c r="H618" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="619" spans="1:8" x14ac:dyDescent="0.25">
@@ -25850,13 +25850,13 @@
         <v>440</v>
       </c>
       <c r="F620" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G620" s="2">
         <v>0</v>
       </c>
       <c r="H620" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="621" spans="1:8" x14ac:dyDescent="0.25">
@@ -26058,10 +26058,10 @@
         <v>440</v>
       </c>
       <c r="F628" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G628" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H628" s="2">
         <v>1</v>
@@ -26500,13 +26500,13 @@
         <v>292</v>
       </c>
       <c r="F645" s="2">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="G645" s="2">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="H645" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="646" spans="1:8" x14ac:dyDescent="0.25">
@@ -26552,13 +26552,13 @@
         <v>1043</v>
       </c>
       <c r="F647" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G647" s="2">
         <v>0</v>
       </c>
       <c r="H647" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="648" spans="1:8" x14ac:dyDescent="0.25">
@@ -26656,13 +26656,13 @@
         <v>292</v>
       </c>
       <c r="F651" s="2">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G651" s="2">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="H651" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="652" spans="1:8" x14ac:dyDescent="0.25">
@@ -26890,13 +26890,13 @@
         <v>402</v>
       </c>
       <c r="F660" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G660" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H660" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="661" spans="1:8" x14ac:dyDescent="0.25">
@@ -26916,10 +26916,10 @@
         <v>430</v>
       </c>
       <c r="F661" s="2">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="G661" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H661" s="2">
         <v>35</v>
@@ -26942,10 +26942,10 @@
         <v>430</v>
       </c>
       <c r="F662" s="2">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="G662" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="H662" s="2">
         <v>13</v>
@@ -26994,10 +26994,10 @@
         <v>402</v>
       </c>
       <c r="F664" s="2">
-        <v>15</v>
+        <v>5</v>
       </c>
       <c r="G664" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H664" s="2">
         <v>5</v>
@@ -27566,13 +27566,13 @@
         <v>1811</v>
       </c>
       <c r="F686" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G686" s="2">
         <v>0</v>
       </c>
       <c r="H686" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="687" spans="1:8" x14ac:dyDescent="0.25">
@@ -28190,10 +28190,10 @@
         <v>2463</v>
       </c>
       <c r="F710" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G710" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H710" s="2">
         <v>0</v>
@@ -28216,13 +28216,13 @@
         <v>410</v>
       </c>
       <c r="F711" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G711" s="2">
         <v>0</v>
       </c>
       <c r="H711" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="712" spans="1:8" x14ac:dyDescent="0.25">
@@ -28450,10 +28450,10 @@
         <v>693</v>
       </c>
       <c r="F720" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G720" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H720" s="2">
         <v>5</v>
@@ -28944,10 +28944,10 @@
         <v>2477</v>
       </c>
       <c r="F739" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G739" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H739" s="2">
         <v>0</v>
@@ -28970,13 +28970,13 @@
         <v>2478</v>
       </c>
       <c r="F740" s="2">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="G740" s="2">
-        <v>12</v>
+        <v>2</v>
       </c>
       <c r="H740" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="741" spans="1:8" x14ac:dyDescent="0.25">
@@ -29958,10 +29958,10 @@
         <v>2517</v>
       </c>
       <c r="F778" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G778" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H778" s="2">
         <v>0</v>
@@ -30088,10 +30088,10 @@
         <v>2526</v>
       </c>
       <c r="F783" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G783" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H783" s="2">
         <v>9</v>
@@ -30166,10 +30166,10 @@
         <v>2529</v>
       </c>
       <c r="F786" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G786" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H786" s="2">
         <v>0</v>
@@ -30530,10 +30530,10 @@
         <v>1110</v>
       </c>
       <c r="F800" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G800" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H800" s="2">
         <v>2</v>
@@ -30556,10 +30556,10 @@
         <v>1110</v>
       </c>
       <c r="F801" s="2">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="G801" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H801" s="2">
         <v>14</v>
@@ -30894,10 +30894,10 @@
         <v>2549</v>
       </c>
       <c r="F814" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G814" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H814" s="2">
         <v>0</v>
@@ -30946,10 +30946,10 @@
         <v>2525</v>
       </c>
       <c r="F816" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G816" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H816" s="2">
         <v>3</v>
@@ -31024,10 +31024,10 @@
         <v>2553</v>
       </c>
       <c r="F819" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G819" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H819" s="2">
         <v>5</v>
@@ -31544,13 +31544,13 @@
         <v>2479</v>
       </c>
       <c r="F839" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G839" s="2">
         <v>0</v>
       </c>
       <c r="H839" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="840" spans="1:8" x14ac:dyDescent="0.25">
@@ -31960,10 +31960,10 @@
         <v>2575</v>
       </c>
       <c r="F855" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G855" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H855" s="2">
         <v>0</v>
@@ -32220,10 +32220,10 @@
         <v>548</v>
       </c>
       <c r="F865" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G865" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H865" s="2">
         <v>4</v>
@@ -32272,10 +32272,10 @@
         <v>2582</v>
       </c>
       <c r="F867" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G867" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H867" s="2">
         <v>0</v>
@@ -32298,10 +32298,10 @@
         <v>2582</v>
       </c>
       <c r="F868" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G868" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H868" s="2">
         <v>0</v>
@@ -32376,10 +32376,10 @@
         <v>652</v>
       </c>
       <c r="F871" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G871" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H871" s="2">
         <v>2</v>
@@ -32764,10 +32764,10 @@
         <v>2588</v>
       </c>
       <c r="F886" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G886" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H886" s="2">
         <v>1</v>
@@ -32868,10 +32868,10 @@
         <v>2588</v>
       </c>
       <c r="F890" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G890" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H890" s="2">
         <v>0</v>
@@ -33492,13 +33492,13 @@
         <v>1625</v>
       </c>
       <c r="F914" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G914" s="2">
         <v>0</v>
       </c>
       <c r="H914" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="915" spans="1:8" x14ac:dyDescent="0.25">
@@ -33596,13 +33596,13 @@
         <v>1828</v>
       </c>
       <c r="F918" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G918" s="2">
         <v>0</v>
       </c>
       <c r="H918" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="919" spans="1:8" x14ac:dyDescent="0.25">
@@ -33778,10 +33778,10 @@
         <v>2608</v>
       </c>
       <c r="F925" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G925" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H925" s="2">
         <v>0</v>
@@ -33908,10 +33908,10 @@
         <v>2609</v>
       </c>
       <c r="F930" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G930" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H930" s="2">
         <v>0</v>
@@ -34142,10 +34142,10 @@
         <v>2615</v>
       </c>
       <c r="F939" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G939" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H939" s="2">
         <v>0</v>
@@ -34480,13 +34480,13 @@
         <v>2516</v>
       </c>
       <c r="F952" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="G952" s="2">
         <v>0</v>
       </c>
       <c r="H952" s="2">
-        <v>46</v>
+        <v>40</v>
       </c>
     </row>
     <row r="953" spans="1:8" x14ac:dyDescent="0.25">
@@ -34584,13 +34584,13 @@
         <v>2626</v>
       </c>
       <c r="F956" s="2">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="G956" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H956" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
     </row>
     <row r="957" spans="1:8" x14ac:dyDescent="0.25">
@@ -34610,13 +34610,13 @@
         <v>2629</v>
       </c>
       <c r="F957" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G957" s="2">
         <v>0</v>
       </c>
       <c r="H957" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="958" spans="1:8" x14ac:dyDescent="0.25">
@@ -34662,13 +34662,13 @@
         <v>2631</v>
       </c>
       <c r="F959" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G959" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H959" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="960" spans="1:8" x14ac:dyDescent="0.25">
@@ -35234,10 +35234,10 @@
         <v>2613</v>
       </c>
       <c r="F981" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G981" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H981" s="2">
         <v>0</v>
@@ -36222,10 +36222,10 @@
         <v>2655</v>
       </c>
       <c r="F1019" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1019" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1019" s="2">
         <v>0</v>
@@ -36586,13 +36586,13 @@
         <v>1750</v>
       </c>
       <c r="F1033" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G1033" s="2">
         <v>0</v>
       </c>
       <c r="H1033" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1034" spans="1:8" x14ac:dyDescent="0.25">
@@ -37314,13 +37314,13 @@
         <v>2592</v>
       </c>
       <c r="F1061" s="2">
-        <v>59</v>
+        <v>37</v>
       </c>
       <c r="G1061" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1061" s="2">
-        <v>58</v>
+        <v>35</v>
       </c>
     </row>
     <row r="1062" spans="1:8" x14ac:dyDescent="0.25">
@@ -37652,10 +37652,10 @@
         <v>2686</v>
       </c>
       <c r="F1074" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1074" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1074" s="2">
         <v>0</v>
@@ -39056,13 +39056,13 @@
         <v>2735</v>
       </c>
       <c r="F1128" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1128" s="2">
         <v>0</v>
       </c>
       <c r="H1128" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1129" spans="1:8" x14ac:dyDescent="0.25">
@@ -39836,13 +39836,13 @@
         <v>2731</v>
       </c>
       <c r="F1158" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G1158" s="2">
         <v>0</v>
       </c>
       <c r="H1158" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1159" spans="1:8" x14ac:dyDescent="0.25">
@@ -39888,13 +39888,13 @@
         <v>2730</v>
       </c>
       <c r="F1160" s="2">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G1160" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1160" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1161" spans="1:8" x14ac:dyDescent="0.25">
@@ -39940,13 +39940,13 @@
         <v>2730</v>
       </c>
       <c r="F1162" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G1162" s="2">
         <v>0</v>
       </c>
       <c r="H1162" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1163" spans="1:8" x14ac:dyDescent="0.25">
@@ -39966,13 +39966,13 @@
         <v>2730</v>
       </c>
       <c r="F1163" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G1163" s="2">
         <v>0</v>
       </c>
       <c r="H1163" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="1164" spans="1:8" x14ac:dyDescent="0.25">
@@ -40018,13 +40018,13 @@
         <v>2730</v>
       </c>
       <c r="F1165" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G1165" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H1165" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1166" spans="1:8" x14ac:dyDescent="0.25">
@@ -40902,10 +40902,10 @@
         <v>1963</v>
       </c>
       <c r="F1199" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1199" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1199" s="2">
         <v>2</v>
@@ -41396,10 +41396,10 @@
         <v>2386</v>
       </c>
       <c r="F1218" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1218" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1218" s="2">
         <v>4</v>
@@ -41500,10 +41500,10 @@
         <v>2386</v>
       </c>
       <c r="F1222" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1222" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1222" s="2">
         <v>0</v>
@@ -41552,10 +41552,10 @@
         <v>2811</v>
       </c>
       <c r="F1224" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1224" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H1224" s="2">
         <v>0</v>
@@ -41890,10 +41890,10 @@
         <v>1786</v>
       </c>
       <c r="F1237" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1237" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1237" s="2">
         <v>0</v>
@@ -42046,10 +42046,10 @@
         <v>586</v>
       </c>
       <c r="F1243" s="2">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G1243" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1243" s="2">
         <v>55</v>
@@ -42358,10 +42358,10 @@
         <v>2306</v>
       </c>
       <c r="F1255" s="2">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="G1255" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H1255" s="2">
         <v>29</v>
@@ -42410,10 +42410,10 @@
         <v>458</v>
       </c>
       <c r="F1257" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G1257" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1257" s="2">
         <v>27</v>
@@ -42592,13 +42592,13 @@
         <v>2825</v>
       </c>
       <c r="F1264" s="2">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="G1264" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1264" s="2">
-        <v>77</v>
+        <v>71</v>
       </c>
     </row>
     <row r="1265" spans="1:8" x14ac:dyDescent="0.25">
@@ -44880,13 +44880,13 @@
         <v>2827</v>
       </c>
       <c r="F1352" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1352" s="2">
         <v>0</v>
       </c>
       <c r="H1352" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1353" spans="1:8" x14ac:dyDescent="0.25">
@@ -45738,13 +45738,13 @@
         <v>2916</v>
       </c>
       <c r="F1385" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1385" s="2">
         <v>0</v>
       </c>
       <c r="H1385" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1386" spans="1:8" x14ac:dyDescent="0.25">
@@ -46180,13 +46180,13 @@
         <v>2870</v>
       </c>
       <c r="F1402" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G1402" s="2">
         <v>0</v>
       </c>
       <c r="H1402" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1403" spans="1:8" x14ac:dyDescent="0.25">
@@ -46258,13 +46258,13 @@
         <v>2996</v>
       </c>
       <c r="F1405" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G1405" s="2">
         <v>0</v>
       </c>
       <c r="H1405" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1406" spans="1:8" x14ac:dyDescent="0.25">
@@ -46388,13 +46388,13 @@
         <v>3014</v>
       </c>
       <c r="F1410" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G1410" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1410" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1411" spans="1:8" x14ac:dyDescent="0.25">
@@ -46544,13 +46544,13 @@
         <v>2968</v>
       </c>
       <c r="F1416" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G1416" s="2">
         <v>0</v>
       </c>
       <c r="H1416" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1417" spans="1:8" x14ac:dyDescent="0.25">
@@ -46570,13 +46570,13 @@
         <v>2996</v>
       </c>
       <c r="F1417" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G1417" s="2">
         <v>0</v>
       </c>
       <c r="H1417" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1418" spans="1:8" x14ac:dyDescent="0.25">
@@ -46726,13 +46726,13 @@
         <v>2934</v>
       </c>
       <c r="F1423" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1423" s="2">
         <v>0</v>
       </c>
       <c r="H1423" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1424" spans="1:8" x14ac:dyDescent="0.25">
@@ -46830,13 +46830,13 @@
         <v>2917</v>
       </c>
       <c r="F1427" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1427" s="2">
         <v>0</v>
       </c>
       <c r="H1427" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1428" spans="1:8" x14ac:dyDescent="0.25">
@@ -46882,13 +46882,13 @@
         <v>2862</v>
       </c>
       <c r="F1429" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G1429" s="2">
         <v>0</v>
       </c>
       <c r="H1429" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1430" spans="1:8" x14ac:dyDescent="0.25">
@@ -47636,10 +47636,10 @@
         <v>565</v>
       </c>
       <c r="F1458" s="2">
-        <v>26</v>
+        <v>21</v>
       </c>
       <c r="G1458" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H1458" s="2">
         <v>21</v>
@@ -47766,13 +47766,13 @@
         <v>2354</v>
       </c>
       <c r="F1463" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1463" s="2">
         <v>0</v>
       </c>
       <c r="H1463" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1464" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK SRB.xlsx
+++ b/STOK DEALER/STOK SRB.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\STOK DEALER\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data D\2026\UPADTE TOOLS BUNDLING SRB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B65FFAA-4D7D-4A75-8E17-C0617753295C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01CE8AA7-0080-4EEB-8020-BAC8B91E2CAB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1950" yWindow="1725" windowWidth="9870" windowHeight="14475" xr2:uid="{46E7093F-A843-4D56-8D6E-D290D3117D3B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{46E7093F-A843-4D56-8D6E-D290D3117D3B}"/>
   </bookViews>
   <sheets>
     <sheet name="STOK DEALER" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5870" uniqueCount="3100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5871" uniqueCount="3101">
   <si>
     <t>No</t>
   </si>
@@ -9336,6 +9336,9 @@
   </si>
   <si>
     <t>MIRROR COMP., L.</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
   </si>
 </sst>
 </file>
@@ -9367,7 +9370,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -9390,17 +9393,69 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -9736,7 +9791,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2BB8C35-92DF-4C27-A2CF-D1CDC7F4FE42}">
-  <dimension ref="A1:H1476"/>
+  <dimension ref="A1:H1477"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -9792,10 +9847,10 @@
         <v>1624</v>
       </c>
       <c r="F2" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G2" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H2" s="2">
         <v>10</v>
@@ -9870,13 +9925,13 @@
         <v>1627</v>
       </c>
       <c r="F5" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G5" s="2">
         <v>0</v>
       </c>
       <c r="H5" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -9896,13 +9951,13 @@
         <v>1627</v>
       </c>
       <c r="F6" s="2">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="G6" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H6" s="2">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -9948,10 +10003,10 @@
         <v>1627</v>
       </c>
       <c r="F8" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G8" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H8" s="2">
         <v>2</v>
@@ -10286,10 +10341,10 @@
         <v>1647</v>
       </c>
       <c r="F21" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G21" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H21" s="2">
         <v>2</v>
@@ -10494,13 +10549,13 @@
         <v>1653</v>
       </c>
       <c r="F29" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G29" s="2">
         <v>0</v>
       </c>
       <c r="H29" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -11404,13 +11459,13 @@
         <v>1260</v>
       </c>
       <c r="F64" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G64" s="2">
         <v>0</v>
       </c>
       <c r="H64" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
@@ -13402,13 +13457,13 @@
         <v>1782</v>
       </c>
       <c r="F141" s="2">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="G141" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H141" s="2">
-        <v>49</v>
+        <v>46</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
@@ -13428,13 +13483,13 @@
         <v>1783</v>
       </c>
       <c r="F142" s="2">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="G142" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H142" s="2">
-        <v>159</v>
+        <v>156</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
@@ -13454,13 +13509,13 @@
         <v>1783</v>
       </c>
       <c r="F143" s="2">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="G143" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H143" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
@@ -13584,13 +13639,13 @@
         <v>1791</v>
       </c>
       <c r="F148" s="2">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="G148" s="2">
         <v>1</v>
       </c>
       <c r="H148" s="2">
-        <v>289</v>
+        <v>280</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
@@ -13844,13 +13899,13 @@
         <v>1782</v>
       </c>
       <c r="F158" s="2">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="G158" s="2">
         <v>1</v>
       </c>
       <c r="H158" s="2">
-        <v>168</v>
+        <v>165</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
@@ -13870,13 +13925,13 @@
         <v>1791</v>
       </c>
       <c r="F159" s="2">
-        <v>756</v>
+        <v>734</v>
       </c>
       <c r="G159" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H159" s="2">
-        <v>753</v>
+        <v>730</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
@@ -14312,10 +14367,10 @@
         <v>1818</v>
       </c>
       <c r="F176" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G176" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H176" s="2">
         <v>8</v>
@@ -14546,13 +14601,13 @@
         <v>1828</v>
       </c>
       <c r="F185" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G185" s="2">
         <v>0</v>
       </c>
       <c r="H185" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.25">
@@ -14910,10 +14965,10 @@
         <v>1829</v>
       </c>
       <c r="F199" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G199" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H199" s="2">
         <v>16</v>
@@ -15199,10 +15254,10 @@
         <v>10</v>
       </c>
       <c r="G210" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H210" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.25">
@@ -20058,10 +20113,10 @@
         <v>2158</v>
       </c>
       <c r="F397" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G397" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H397" s="2">
         <v>0</v>
@@ -20422,10 +20477,10 @@
         <v>926</v>
       </c>
       <c r="F411" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G411" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H411" s="2">
         <v>23</v>
@@ -20919,10 +20974,10 @@
         <v>13</v>
       </c>
       <c r="G430" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H430" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="431" spans="1:8" x14ac:dyDescent="0.25">
@@ -22243,10 +22298,10 @@
         <v>3</v>
       </c>
       <c r="G481" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H481" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="482" spans="1:8" x14ac:dyDescent="0.25">
@@ -22526,10 +22581,10 @@
         <v>300</v>
       </c>
       <c r="F492" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G492" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H492" s="2">
         <v>7</v>
@@ -23046,10 +23101,10 @@
         <v>2248</v>
       </c>
       <c r="F512" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G512" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H512" s="2">
         <v>6</v>
@@ -23694,10 +23749,10 @@
         <v>590</v>
       </c>
       <c r="F537" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G537" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H537" s="2">
         <v>3</v>
@@ -24550,10 +24605,10 @@
         <v>2286</v>
       </c>
       <c r="F570" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G570" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H570" s="2">
         <v>4</v>
@@ -24706,10 +24761,10 @@
         <v>2289</v>
       </c>
       <c r="F576" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G576" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H576" s="2">
         <v>0</v>
@@ -26500,13 +26555,13 @@
         <v>292</v>
       </c>
       <c r="F645" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G645" s="2">
         <v>1</v>
       </c>
       <c r="H645" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="646" spans="1:8" x14ac:dyDescent="0.25">
@@ -26656,13 +26711,13 @@
         <v>292</v>
       </c>
       <c r="F651" s="2">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G651" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H651" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="652" spans="1:8" x14ac:dyDescent="0.25">
@@ -28216,13 +28271,13 @@
         <v>410</v>
       </c>
       <c r="F711" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G711" s="2">
         <v>0</v>
       </c>
       <c r="H711" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="712" spans="1:8" x14ac:dyDescent="0.25">
@@ -34483,10 +34538,10 @@
         <v>40</v>
       </c>
       <c r="G952" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H952" s="2">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="953" spans="1:8" x14ac:dyDescent="0.25">
@@ -34584,13 +34639,13 @@
         <v>2626</v>
       </c>
       <c r="F956" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G956" s="2">
+        <v>0</v>
+      </c>
+      <c r="H956" s="2">
         <v>1</v>
-      </c>
-      <c r="H956" s="2">
-        <v>2</v>
       </c>
     </row>
     <row r="957" spans="1:8" x14ac:dyDescent="0.25">
@@ -34662,13 +34717,13 @@
         <v>2631</v>
       </c>
       <c r="F959" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G959" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H959" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="960" spans="1:8" x14ac:dyDescent="0.25">
@@ -36586,13 +36641,13 @@
         <v>1750</v>
       </c>
       <c r="F1033" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1033" s="2">
         <v>0</v>
       </c>
       <c r="H1033" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1034" spans="1:8" x14ac:dyDescent="0.25">
@@ -37314,13 +37369,13 @@
         <v>2592</v>
       </c>
       <c r="F1061" s="2">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="G1061" s="2">
         <v>2</v>
       </c>
       <c r="H1061" s="2">
-        <v>35</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1062" spans="1:8" x14ac:dyDescent="0.25">
@@ -39056,13 +39111,13 @@
         <v>2735</v>
       </c>
       <c r="F1128" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1128" s="2">
         <v>0</v>
       </c>
       <c r="H1128" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1129" spans="1:8" x14ac:dyDescent="0.25">
@@ -39836,13 +39891,13 @@
         <v>2731</v>
       </c>
       <c r="F1158" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G1158" s="2">
         <v>0</v>
       </c>
       <c r="H1158" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1159" spans="1:8" x14ac:dyDescent="0.25">
@@ -39891,10 +39946,10 @@
         <v>25</v>
       </c>
       <c r="G1160" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1160" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1161" spans="1:8" x14ac:dyDescent="0.25">
@@ -39940,13 +39995,13 @@
         <v>2730</v>
       </c>
       <c r="F1162" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1162" s="2">
         <v>0</v>
       </c>
       <c r="H1162" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1163" spans="1:8" x14ac:dyDescent="0.25">
@@ -40018,13 +40073,13 @@
         <v>2730</v>
       </c>
       <c r="F1165" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="G1165" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H1165" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1166" spans="1:8" x14ac:dyDescent="0.25">
@@ -41399,10 +41454,10 @@
         <v>4</v>
       </c>
       <c r="G1218" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H1218" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1219" spans="1:8" x14ac:dyDescent="0.25">
@@ -42592,10 +42647,10 @@
         <v>2825</v>
       </c>
       <c r="F1264" s="2">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="G1264" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1264" s="2">
         <v>71</v>
@@ -43060,13 +43115,13 @@
         <v>2631</v>
       </c>
       <c r="F1282" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1282" s="2">
         <v>0</v>
       </c>
       <c r="H1282" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1283" spans="1:8" x14ac:dyDescent="0.25">
@@ -43554,13 +43609,13 @@
         <v>2856</v>
       </c>
       <c r="F1301" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1301" s="2">
         <v>0</v>
       </c>
       <c r="H1301" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1302" spans="1:8" x14ac:dyDescent="0.25">
@@ -43866,13 +43921,13 @@
         <v>2906</v>
       </c>
       <c r="F1313" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1313" s="2">
         <v>0</v>
       </c>
       <c r="H1313" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1314" spans="1:8" x14ac:dyDescent="0.25">
@@ -44464,13 +44519,13 @@
         <v>2903</v>
       </c>
       <c r="F1336" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1336" s="2">
         <v>0</v>
       </c>
       <c r="H1336" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1337" spans="1:8" x14ac:dyDescent="0.25">
@@ -44880,13 +44935,13 @@
         <v>2827</v>
       </c>
       <c r="F1352" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1352" s="2">
         <v>0</v>
       </c>
       <c r="H1352" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1353" spans="1:8" x14ac:dyDescent="0.25">
@@ -46209,10 +46264,10 @@
         <v>18</v>
       </c>
       <c r="G1403" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1403" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1404" spans="1:8" x14ac:dyDescent="0.25">
@@ -46388,13 +46443,13 @@
         <v>3014</v>
       </c>
       <c r="F1410" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1410" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1410" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1411" spans="1:8" x14ac:dyDescent="0.25">
@@ -46492,13 +46547,13 @@
         <v>3014</v>
       </c>
       <c r="F1414" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G1414" s="2">
         <v>0</v>
       </c>
       <c r="H1414" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1415" spans="1:8" x14ac:dyDescent="0.25">
@@ -46544,13 +46599,13 @@
         <v>2968</v>
       </c>
       <c r="F1416" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G1416" s="2">
         <v>0</v>
       </c>
       <c r="H1416" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1417" spans="1:8" x14ac:dyDescent="0.25">
@@ -46570,13 +46625,13 @@
         <v>2996</v>
       </c>
       <c r="F1417" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G1417" s="2">
         <v>0</v>
       </c>
       <c r="H1417" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="1418" spans="1:8" x14ac:dyDescent="0.25">
@@ -46596,13 +46651,13 @@
         <v>2856</v>
       </c>
       <c r="F1418" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G1418" s="2">
         <v>0</v>
       </c>
       <c r="H1418" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1419" spans="1:8" x14ac:dyDescent="0.25">
@@ -46882,13 +46937,13 @@
         <v>2862</v>
       </c>
       <c r="F1429" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G1429" s="2">
         <v>0</v>
       </c>
       <c r="H1429" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1430" spans="1:8" x14ac:dyDescent="0.25">
@@ -47584,13 +47639,13 @@
         <v>207</v>
       </c>
       <c r="F1456" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G1456" s="2">
         <v>0</v>
       </c>
       <c r="H1456" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1457" spans="1:8" x14ac:dyDescent="0.25">
@@ -47775,7 +47830,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1464" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1464" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1464" s="2">
         <v>1463</v>
       </c>
@@ -47801,7 +47856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1465" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1465" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1465" s="2">
         <v>1464</v>
       </c>
@@ -48052,13 +48107,13 @@
         <v>3061</v>
       </c>
       <c r="F1474" s="2">
-        <v>36</v>
+        <v>31</v>
       </c>
       <c r="G1474" s="2">
         <v>0</v>
       </c>
       <c r="H1474" s="2">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="1475" spans="1:8" x14ac:dyDescent="0.25">
@@ -48113,7 +48168,28 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1477" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1477" s="5" t="s">
+        <v>3100</v>
+      </c>
+      <c r="B1477" s="6"/>
+      <c r="C1477" s="6"/>
+      <c r="D1477" s="6"/>
+      <c r="E1477" s="7"/>
+      <c r="F1477" s="3">
+        <v>5583</v>
+      </c>
+      <c r="G1477" s="4">
+        <v>33</v>
+      </c>
+      <c r="H1477" s="3">
+        <v>5550</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1477:E1477"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/STOK DEALER/STOK SRB.xlsx
+++ b/STOK DEALER/STOK SRB.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data D\2026\UPADTE TOOLS BUNDLING SRB\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A46F7631-A651-49DA-AE9E-D5771AE8239D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69609890-742B-489E-9932-7E9EFBC336FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{46E7093F-A843-4D56-8D6E-D290D3117D3B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{46E7093F-A843-4D56-8D6E-D290D3117D3B}"/>
   </bookViews>
   <sheets>
     <sheet name="STOK DEALER" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5871" uniqueCount="3101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5870" uniqueCount="3100">
   <si>
     <t>No</t>
   </si>
@@ -9330,9 +9330,6 @@
   </si>
   <si>
     <t>MIRROR COMP., L.</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
   </si>
   <si>
     <t>ACC KIT SE KU 1</t>
@@ -9370,7 +9367,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -9393,69 +9390,17 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -9791,7 +9736,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2BB8C35-92DF-4C27-A2CF-D1CDC7F4FE42}">
-  <dimension ref="A1:H1477"/>
+  <dimension ref="A1:H1476"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -11459,13 +11404,13 @@
         <v>1260</v>
       </c>
       <c r="F64" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G64" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H64" s="2">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
@@ -13344,7 +13289,7 @@
         <v>1774</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>3099</v>
+        <v>3098</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>1623</v>
@@ -13396,7 +13341,7 @@
         <v>1777</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>3100</v>
+        <v>3099</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>1623</v>
@@ -13457,13 +13402,13 @@
         <v>1780</v>
       </c>
       <c r="F141" s="2">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="G141" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H141" s="2">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
@@ -13483,13 +13428,13 @@
         <v>1781</v>
       </c>
       <c r="F142" s="2">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G142" s="2">
         <v>1</v>
       </c>
       <c r="H142" s="2">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
@@ -13512,10 +13457,10 @@
         <v>247</v>
       </c>
       <c r="G143" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H143" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
@@ -13639,13 +13584,13 @@
         <v>1789</v>
       </c>
       <c r="F148" s="2">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="G148" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H148" s="2">
-        <v>278</v>
+        <v>269</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
@@ -13899,13 +13844,13 @@
         <v>1780</v>
       </c>
       <c r="F158" s="2">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="G158" s="2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="H158" s="2">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
@@ -13925,13 +13870,13 @@
         <v>1789</v>
       </c>
       <c r="F159" s="2">
-        <v>706</v>
+        <v>681</v>
       </c>
       <c r="G159" s="2">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="H159" s="2">
-        <v>692</v>
+        <v>679</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
@@ -14081,13 +14026,13 @@
         <v>207</v>
       </c>
       <c r="F165" s="2">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="G165" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H165" s="2">
-        <v>127</v>
+        <v>122</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
@@ -14237,10 +14182,10 @@
         <v>939</v>
       </c>
       <c r="F171" s="2">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G171" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H171" s="2">
         <v>54</v>
@@ -19905,10 +19850,10 @@
         <v>2142</v>
       </c>
       <c r="F389" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G389" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H389" s="2">
         <v>0</v>
@@ -20451,13 +20396,13 @@
         <v>2168</v>
       </c>
       <c r="F410" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G410" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H410" s="2">
-        <v>30</v>
+        <v>27</v>
       </c>
     </row>
     <row r="411" spans="1:8" x14ac:dyDescent="0.25">
@@ -20971,10 +20916,10 @@
         <v>1959</v>
       </c>
       <c r="F430" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G430" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H430" s="2">
         <v>11</v>
@@ -22243,13 +22188,13 @@
         <v>610</v>
       </c>
       <c r="F479" s="2">
-        <v>7</v>
+        <v>2</v>
       </c>
       <c r="G479" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H479" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="480" spans="1:8" x14ac:dyDescent="0.25">
@@ -26243,10 +26188,10 @@
         <v>2359</v>
       </c>
       <c r="F633" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G633" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H633" s="2">
         <v>0</v>
@@ -26711,13 +26656,13 @@
         <v>292</v>
       </c>
       <c r="F651" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G651" s="2">
         <v>2</v>
       </c>
       <c r="H651" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="652" spans="1:8" x14ac:dyDescent="0.25">
@@ -26945,13 +26890,13 @@
         <v>402</v>
       </c>
       <c r="F660" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G660" s="2">
         <v>0</v>
       </c>
       <c r="H660" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="661" spans="1:8" x14ac:dyDescent="0.25">
@@ -28505,10 +28450,10 @@
         <v>693</v>
       </c>
       <c r="F720" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G720" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H720" s="2">
         <v>3</v>
@@ -29025,10 +28970,10 @@
         <v>2476</v>
       </c>
       <c r="F740" s="2">
-        <v>21</v>
+        <v>8</v>
       </c>
       <c r="G740" s="2">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="H740" s="2">
         <v>6</v>
@@ -30143,10 +30088,10 @@
         <v>2524</v>
       </c>
       <c r="F783" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G783" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H783" s="2">
         <v>8</v>
@@ -31755,13 +31700,13 @@
         <v>1956</v>
       </c>
       <c r="F845" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G845" s="2">
         <v>0</v>
       </c>
       <c r="H845" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="846" spans="1:8" x14ac:dyDescent="0.25">
@@ -32278,10 +32223,10 @@
         <v>4</v>
       </c>
       <c r="G865" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H865" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="866" spans="1:8" x14ac:dyDescent="0.25">
@@ -34665,13 +34610,13 @@
         <v>2627</v>
       </c>
       <c r="F957" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G957" s="2">
         <v>0</v>
       </c>
       <c r="H957" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="958" spans="1:8" x14ac:dyDescent="0.25">
@@ -37369,13 +37314,13 @@
         <v>2590</v>
       </c>
       <c r="F1061" s="2">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="G1061" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1061" s="2">
-        <v>19</v>
+        <v>15</v>
       </c>
     </row>
     <row r="1062" spans="1:8" x14ac:dyDescent="0.25">
@@ -39111,13 +39056,13 @@
         <v>2733</v>
       </c>
       <c r="F1128" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1128" s="2">
         <v>0</v>
       </c>
       <c r="H1128" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1129" spans="1:8" x14ac:dyDescent="0.25">
@@ -39946,10 +39891,10 @@
         <v>21</v>
       </c>
       <c r="G1160" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1160" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1161" spans="1:8" x14ac:dyDescent="0.25">
@@ -40073,13 +40018,13 @@
         <v>2728</v>
       </c>
       <c r="F1165" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G1165" s="2">
         <v>0</v>
       </c>
       <c r="H1165" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1166" spans="1:8" x14ac:dyDescent="0.25">
@@ -41711,10 +41656,10 @@
         <v>1784</v>
       </c>
       <c r="F1228" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G1228" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1228" s="2">
         <v>23</v>
@@ -42465,10 +42410,10 @@
         <v>458</v>
       </c>
       <c r="F1257" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G1257" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1257" s="2">
         <v>26</v>
@@ -43092,10 +43037,10 @@
         <v>6</v>
       </c>
       <c r="G1281" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1281" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1282" spans="1:8" x14ac:dyDescent="0.25">
@@ -45406,10 +45351,10 @@
         <v>33</v>
       </c>
       <c r="G1370" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1370" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="1371" spans="1:8" x14ac:dyDescent="0.25">
@@ -46599,13 +46544,13 @@
         <v>2966</v>
       </c>
       <c r="F1416" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G1416" s="2">
         <v>0</v>
       </c>
       <c r="H1416" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1417" spans="1:8" x14ac:dyDescent="0.25">
@@ -46654,10 +46599,10 @@
         <v>8</v>
       </c>
       <c r="G1418" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1418" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1419" spans="1:8" x14ac:dyDescent="0.25">
@@ -47197,13 +47142,13 @@
         <v>2953</v>
       </c>
       <c r="F1439" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G1439" s="2">
         <v>0</v>
       </c>
       <c r="H1439" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1440" spans="1:8" x14ac:dyDescent="0.25">
@@ -47830,7 +47775,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1464" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1464" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1464" s="2">
         <v>1463</v>
       </c>
@@ -47856,7 +47801,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1465" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1465" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1465" s="2">
         <v>1464</v>
       </c>
@@ -48133,13 +48078,13 @@
         <v>939</v>
       </c>
       <c r="F1475" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G1475" s="2">
         <v>0</v>
       </c>
       <c r="H1475" s="2">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="1476" spans="1:8" x14ac:dyDescent="0.25">
@@ -48168,28 +48113,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="1477" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1477" s="5" t="s">
-        <v>3098</v>
-      </c>
-      <c r="B1477" s="6"/>
-      <c r="C1477" s="6"/>
-      <c r="D1477" s="6"/>
-      <c r="E1477" s="7"/>
-      <c r="F1477" s="3">
-        <v>5583</v>
-      </c>
-      <c r="G1477" s="4">
-        <v>33</v>
-      </c>
-      <c r="H1477" s="3">
-        <v>5550</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1477:E1477"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/STOK DEALER/STOK SRB.xlsx
+++ b/STOK DEALER/STOK SRB.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\STOK DEALER\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data D\2026\UPADTE TOOLS BUNDLING SRB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69609890-742B-489E-9932-7E9EFBC336FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{329CDE3A-DAAD-4D04-829F-1971F07E1305}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{46E7093F-A843-4D56-8D6E-D290D3117D3B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{46E7093F-A843-4D56-8D6E-D290D3117D3B}"/>
   </bookViews>
   <sheets>
     <sheet name="STOK DEALER" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5870" uniqueCount="3100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5871" uniqueCount="3101">
   <si>
     <t>No</t>
   </si>
@@ -9330,6 +9330,9 @@
   </si>
   <si>
     <t>MIRROR COMP., L.</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
   </si>
   <si>
     <t>ACC KIT SE KU 1</t>
@@ -9367,7 +9370,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -9390,17 +9393,69 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -9736,7 +9791,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2BB8C35-92DF-4C27-A2CF-D1CDC7F4FE42}">
-  <dimension ref="A1:H1476"/>
+  <dimension ref="A1:H1477"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -13289,7 +13344,7 @@
         <v>1774</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>3098</v>
+        <v>3099</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>1623</v>
@@ -13341,7 +13396,7 @@
         <v>1777</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>3099</v>
+        <v>3100</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>1623</v>
@@ -13402,10 +13457,10 @@
         <v>1780</v>
       </c>
       <c r="F141" s="2">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="G141" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H141" s="2">
         <v>44</v>
@@ -37314,10 +37369,10 @@
         <v>2590</v>
       </c>
       <c r="F1061" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G1061" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1061" s="2">
         <v>15</v>
@@ -39888,10 +39943,10 @@
         <v>2728</v>
       </c>
       <c r="F1160" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G1160" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1160" s="2">
         <v>20</v>
@@ -43034,10 +43089,10 @@
         <v>2848</v>
       </c>
       <c r="F1281" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1281" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1281" s="2">
         <v>5</v>
@@ -45348,10 +45403,10 @@
         <v>2966</v>
       </c>
       <c r="F1370" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G1370" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1370" s="2">
         <v>32</v>
@@ -46596,10 +46651,10 @@
         <v>2854</v>
       </c>
       <c r="F1418" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G1418" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1418" s="2">
         <v>7</v>
@@ -47775,7 +47830,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1464" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1464" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1464" s="2">
         <v>1463</v>
       </c>
@@ -47801,7 +47856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1465" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1465" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1465" s="2">
         <v>1464</v>
       </c>
@@ -48113,7 +48168,28 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1477" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1477" s="5" t="s">
+        <v>3098</v>
+      </c>
+      <c r="B1477" s="6"/>
+      <c r="C1477" s="6"/>
+      <c r="D1477" s="6"/>
+      <c r="E1477" s="7"/>
+      <c r="F1477" s="3">
+        <v>5583</v>
+      </c>
+      <c r="G1477" s="4">
+        <v>33</v>
+      </c>
+      <c r="H1477" s="3">
+        <v>5550</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1477:E1477"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/STOK DEALER/STOK SRB.xlsx
+++ b/STOK DEALER/STOK SRB.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data D\2026\UPADTE TOOLS BUNDLING SRB\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{329CDE3A-DAAD-4D04-829F-1971F07E1305}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CAAC35C-1090-4AAA-9494-06E5BA27A042}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{46E7093F-A843-4D56-8D6E-D290D3117D3B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{46E7093F-A843-4D56-8D6E-D290D3117D3B}"/>
   </bookViews>
   <sheets>
     <sheet name="STOK DEALER" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5871" uniqueCount="3101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5870" uniqueCount="3100">
   <si>
     <t>No</t>
   </si>
@@ -9330,9 +9330,6 @@
   </si>
   <si>
     <t>MIRROR COMP., L.</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
   </si>
   <si>
     <t>ACC KIT SE KU 1</t>
@@ -9370,7 +9367,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -9393,69 +9390,17 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -9791,7 +9736,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2BB8C35-92DF-4C27-A2CF-D1CDC7F4FE42}">
-  <dimension ref="A1:H1477"/>
+  <dimension ref="A1:H1476"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -9847,13 +9792,13 @@
         <v>1624</v>
       </c>
       <c r="F2" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G2" s="2">
         <v>0</v>
       </c>
       <c r="H2" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -9951,13 +9896,13 @@
         <v>1627</v>
       </c>
       <c r="F6" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="G6" s="2">
         <v>0</v>
       </c>
       <c r="H6" s="2">
-        <v>20</v>
+        <v>18</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -11462,10 +11407,10 @@
         <v>12</v>
       </c>
       <c r="G64" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H64" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
@@ -13344,7 +13289,7 @@
         <v>1774</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>3099</v>
+        <v>3098</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>1623</v>
@@ -13396,7 +13341,7 @@
         <v>1777</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>3100</v>
+        <v>3099</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>1623</v>
@@ -13457,13 +13402,13 @@
         <v>1780</v>
       </c>
       <c r="F141" s="2">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="G141" s="2">
         <v>0</v>
       </c>
       <c r="H141" s="2">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
@@ -13483,13 +13428,13 @@
         <v>1781</v>
       </c>
       <c r="F142" s="2">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G142" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H142" s="2">
-        <v>153</v>
+        <v>149</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
@@ -13509,13 +13454,13 @@
         <v>1781</v>
       </c>
       <c r="F143" s="2">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="G143" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H143" s="2">
-        <v>247</v>
+        <v>245</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
@@ -13639,13 +13584,13 @@
         <v>1789</v>
       </c>
       <c r="F148" s="2">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="G148" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H148" s="2">
-        <v>269</v>
+        <v>261</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
@@ -13899,13 +13844,13 @@
         <v>1780</v>
       </c>
       <c r="F158" s="2">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G158" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H158" s="2">
-        <v>147</v>
+        <v>142</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
@@ -13925,13 +13870,13 @@
         <v>1789</v>
       </c>
       <c r="F159" s="2">
-        <v>681</v>
+        <v>668</v>
       </c>
       <c r="G159" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H159" s="2">
-        <v>679</v>
+        <v>664</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
@@ -14003,13 +13948,13 @@
         <v>207</v>
       </c>
       <c r="F162" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G162" s="2">
         <v>0</v>
       </c>
       <c r="H162" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
@@ -14081,13 +14026,13 @@
         <v>207</v>
       </c>
       <c r="F165" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G165" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H165" s="2">
-        <v>122</v>
+        <v>120</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
@@ -14237,13 +14182,13 @@
         <v>939</v>
       </c>
       <c r="F171" s="2">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="G171" s="2">
         <v>1</v>
       </c>
       <c r="H171" s="2">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
@@ -14887,13 +14832,13 @@
         <v>1815</v>
       </c>
       <c r="F196" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G196" s="2">
         <v>0</v>
       </c>
       <c r="H196" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.25">
@@ -15043,13 +14988,13 @@
         <v>1841</v>
       </c>
       <c r="F202" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G202" s="2">
         <v>0</v>
       </c>
       <c r="H202" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.25">
@@ -15251,13 +15196,13 @@
         <v>1854</v>
       </c>
       <c r="F210" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G210" s="2">
         <v>0</v>
       </c>
       <c r="H210" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.25">
@@ -16814,10 +16759,10 @@
         <v>24</v>
       </c>
       <c r="G270" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H270" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="271" spans="1:8" x14ac:dyDescent="0.25">
@@ -20451,13 +20396,13 @@
         <v>2168</v>
       </c>
       <c r="F410" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G410" s="2">
         <v>1</v>
       </c>
       <c r="H410" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="411" spans="1:8" x14ac:dyDescent="0.25">
@@ -20506,10 +20451,10 @@
         <v>7</v>
       </c>
       <c r="G412" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H412" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="413" spans="1:8" x14ac:dyDescent="0.25">
@@ -20662,10 +20607,10 @@
         <v>4</v>
       </c>
       <c r="G418" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H418" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="419" spans="1:8" x14ac:dyDescent="0.25">
@@ -22165,13 +22110,13 @@
         <v>1099</v>
       </c>
       <c r="F476" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G476" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H476" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="477" spans="1:8" x14ac:dyDescent="0.25">
@@ -22246,10 +22191,10 @@
         <v>2</v>
       </c>
       <c r="G479" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H479" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="480" spans="1:8" x14ac:dyDescent="0.25">
@@ -22295,13 +22240,13 @@
         <v>610</v>
       </c>
       <c r="F481" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G481" s="2">
         <v>0</v>
       </c>
       <c r="H481" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="482" spans="1:8" x14ac:dyDescent="0.25">
@@ -24215,13 +24160,13 @@
         <v>2275</v>
       </c>
       <c r="F555" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G555" s="2">
         <v>0</v>
       </c>
       <c r="H555" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="556" spans="1:8" x14ac:dyDescent="0.25">
@@ -24582,10 +24527,10 @@
         <v>31</v>
       </c>
       <c r="G569" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H569" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="570" spans="1:8" x14ac:dyDescent="0.25">
@@ -26555,13 +26500,13 @@
         <v>292</v>
       </c>
       <c r="F645" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G645" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H645" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="646" spans="1:8" x14ac:dyDescent="0.25">
@@ -26711,13 +26656,13 @@
         <v>292</v>
       </c>
       <c r="F651" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G651" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H651" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="652" spans="1:8" x14ac:dyDescent="0.25">
@@ -26948,10 +26893,10 @@
         <v>13</v>
       </c>
       <c r="G660" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H660" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="661" spans="1:8" x14ac:dyDescent="0.25">
@@ -26974,10 +26919,10 @@
         <v>33</v>
       </c>
       <c r="G661" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H661" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="662" spans="1:8" x14ac:dyDescent="0.25">
@@ -28271,13 +28216,13 @@
         <v>410</v>
       </c>
       <c r="F711" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G711" s="2">
         <v>0</v>
       </c>
       <c r="H711" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="712" spans="1:8" x14ac:dyDescent="0.25">
@@ -30143,13 +30088,13 @@
         <v>2524</v>
       </c>
       <c r="F783" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G783" s="2">
         <v>0</v>
       </c>
       <c r="H783" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="784" spans="1:8" x14ac:dyDescent="0.25">
@@ -30585,13 +30530,13 @@
         <v>1110</v>
       </c>
       <c r="F800" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G800" s="2">
         <v>0</v>
       </c>
       <c r="H800" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="801" spans="1:8" x14ac:dyDescent="0.25">
@@ -31079,13 +31024,13 @@
         <v>2551</v>
       </c>
       <c r="F819" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G819" s="2">
         <v>0</v>
       </c>
       <c r="H819" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="820" spans="1:8" x14ac:dyDescent="0.25">
@@ -33547,13 +33492,13 @@
         <v>1625</v>
       </c>
       <c r="F914" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G914" s="2">
         <v>0</v>
       </c>
       <c r="H914" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="915" spans="1:8" x14ac:dyDescent="0.25">
@@ -34535,13 +34480,13 @@
         <v>2514</v>
       </c>
       <c r="F952" s="2">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="G952" s="2">
         <v>0</v>
       </c>
       <c r="H952" s="2">
-        <v>34</v>
+        <v>26</v>
       </c>
     </row>
     <row r="953" spans="1:8" x14ac:dyDescent="0.25">
@@ -34639,13 +34584,13 @@
         <v>2624</v>
       </c>
       <c r="F956" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G956" s="2">
         <v>0</v>
       </c>
       <c r="H956" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="957" spans="1:8" x14ac:dyDescent="0.25">
@@ -34665,13 +34610,13 @@
         <v>2627</v>
       </c>
       <c r="F957" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G957" s="2">
         <v>0</v>
       </c>
       <c r="H957" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="958" spans="1:8" x14ac:dyDescent="0.25">
@@ -37369,13 +37314,13 @@
         <v>2590</v>
       </c>
       <c r="F1061" s="2">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G1061" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1061" s="2">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1062" spans="1:8" x14ac:dyDescent="0.25">
@@ -39033,13 +38978,13 @@
         <v>2732</v>
       </c>
       <c r="F1125" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1125" s="2">
         <v>0</v>
       </c>
       <c r="H1125" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1126" spans="1:8" x14ac:dyDescent="0.25">
@@ -39111,13 +39056,13 @@
         <v>2733</v>
       </c>
       <c r="F1128" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1128" s="2">
         <v>0</v>
       </c>
       <c r="H1128" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1129" spans="1:8" x14ac:dyDescent="0.25">
@@ -39293,13 +39238,13 @@
         <v>2733</v>
       </c>
       <c r="F1135" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G1135" s="2">
         <v>0</v>
       </c>
       <c r="H1135" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="1136" spans="1:8" x14ac:dyDescent="0.25">
@@ -39891,13 +39836,13 @@
         <v>2729</v>
       </c>
       <c r="F1158" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G1158" s="2">
         <v>0</v>
       </c>
       <c r="H1158" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1159" spans="1:8" x14ac:dyDescent="0.25">
@@ -39943,13 +39888,13 @@
         <v>2728</v>
       </c>
       <c r="F1160" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G1160" s="2">
         <v>0</v>
       </c>
       <c r="H1160" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1161" spans="1:8" x14ac:dyDescent="0.25">
@@ -40021,13 +39966,13 @@
         <v>2728</v>
       </c>
       <c r="F1163" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G1163" s="2">
         <v>0</v>
       </c>
       <c r="H1163" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1164" spans="1:8" x14ac:dyDescent="0.25">
@@ -40073,13 +40018,13 @@
         <v>2728</v>
       </c>
       <c r="F1165" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1165" s="2">
         <v>0</v>
       </c>
       <c r="H1165" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1166" spans="1:8" x14ac:dyDescent="0.25">
@@ -41714,10 +41659,10 @@
         <v>23</v>
       </c>
       <c r="G1228" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1228" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1229" spans="1:8" x14ac:dyDescent="0.25">
@@ -42465,13 +42410,13 @@
         <v>458</v>
       </c>
       <c r="F1257" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G1257" s="2">
         <v>0</v>
       </c>
       <c r="H1257" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1258" spans="1:8" x14ac:dyDescent="0.25">
@@ -42647,13 +42592,13 @@
         <v>2823</v>
       </c>
       <c r="F1264" s="2">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="G1264" s="2">
         <v>0</v>
       </c>
       <c r="H1264" s="2">
-        <v>71</v>
+        <v>67</v>
       </c>
     </row>
     <row r="1265" spans="1:8" x14ac:dyDescent="0.25">
@@ -42699,13 +42644,13 @@
         <v>2823</v>
       </c>
       <c r="F1266" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1266" s="2">
         <v>0</v>
       </c>
       <c r="H1266" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1267" spans="1:8" x14ac:dyDescent="0.25">
@@ -44337,13 +44282,13 @@
         <v>2914</v>
       </c>
       <c r="F1329" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1329" s="2">
         <v>0</v>
       </c>
       <c r="H1329" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1330" spans="1:8" x14ac:dyDescent="0.25">
@@ -44883,13 +44828,13 @@
         <v>2824</v>
       </c>
       <c r="F1350" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G1350" s="2">
         <v>0</v>
       </c>
       <c r="H1350" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1351" spans="1:8" x14ac:dyDescent="0.25">
@@ -45013,13 +44958,13 @@
         <v>2945</v>
       </c>
       <c r="F1355" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G1355" s="2">
         <v>0</v>
       </c>
       <c r="H1355" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1356" spans="1:8" x14ac:dyDescent="0.25">
@@ -45143,13 +45088,13 @@
         <v>2946</v>
       </c>
       <c r="F1360" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1360" s="2">
         <v>0</v>
       </c>
       <c r="H1360" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1361" spans="1:8" x14ac:dyDescent="0.25">
@@ -46235,13 +46180,13 @@
         <v>2868</v>
       </c>
       <c r="F1402" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G1402" s="2">
         <v>0</v>
       </c>
       <c r="H1402" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1403" spans="1:8" x14ac:dyDescent="0.25">
@@ -46287,13 +46232,13 @@
         <v>2845</v>
       </c>
       <c r="F1404" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G1404" s="2">
         <v>0</v>
       </c>
       <c r="H1404" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1405" spans="1:8" x14ac:dyDescent="0.25">
@@ -46313,13 +46258,13 @@
         <v>2994</v>
       </c>
       <c r="F1405" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G1405" s="2">
         <v>0</v>
       </c>
       <c r="H1405" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1406" spans="1:8" x14ac:dyDescent="0.25">
@@ -46573,13 +46518,13 @@
         <v>2901</v>
       </c>
       <c r="F1415" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G1415" s="2">
         <v>0</v>
       </c>
       <c r="H1415" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1416" spans="1:8" x14ac:dyDescent="0.25">
@@ -46599,13 +46544,13 @@
         <v>2966</v>
       </c>
       <c r="F1416" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G1416" s="2">
         <v>0</v>
       </c>
       <c r="H1416" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1417" spans="1:8" x14ac:dyDescent="0.25">
@@ -46651,13 +46596,13 @@
         <v>2854</v>
       </c>
       <c r="F1418" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G1418" s="2">
         <v>0</v>
       </c>
       <c r="H1418" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1419" spans="1:8" x14ac:dyDescent="0.25">
@@ -46911,13 +46856,13 @@
         <v>2994</v>
       </c>
       <c r="F1428" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G1428" s="2">
         <v>0</v>
       </c>
       <c r="H1428" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1429" spans="1:8" x14ac:dyDescent="0.25">
@@ -47197,13 +47142,13 @@
         <v>2953</v>
       </c>
       <c r="F1439" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G1439" s="2">
         <v>0</v>
       </c>
       <c r="H1439" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1440" spans="1:8" x14ac:dyDescent="0.25">
@@ -47694,10 +47639,10 @@
         <v>21</v>
       </c>
       <c r="G1458" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1458" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1459" spans="1:8" x14ac:dyDescent="0.25">
@@ -47830,7 +47775,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1464" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1464" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1464" s="2">
         <v>1463</v>
       </c>
@@ -47856,7 +47801,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1465" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1465" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1465" s="2">
         <v>1464</v>
       </c>
@@ -48110,10 +48055,10 @@
         <v>31</v>
       </c>
       <c r="G1474" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H1474" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1475" spans="1:8" x14ac:dyDescent="0.25">
@@ -48168,28 +48113,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="1477" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1477" s="5" t="s">
-        <v>3098</v>
-      </c>
-      <c r="B1477" s="6"/>
-      <c r="C1477" s="6"/>
-      <c r="D1477" s="6"/>
-      <c r="E1477" s="7"/>
-      <c r="F1477" s="3">
-        <v>5583</v>
-      </c>
-      <c r="G1477" s="4">
-        <v>33</v>
-      </c>
-      <c r="H1477" s="3">
-        <v>5550</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1477:E1477"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/STOK DEALER/STOK SRB.xlsx
+++ b/STOK DEALER/STOK SRB.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\STOK DEALER\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data D\2026\UPADTE TOOLS BUNDLING SRB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CAAC35C-1090-4AAA-9494-06E5BA27A042}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{989F5F49-E390-41EE-B58F-09FED3127C6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{46E7093F-A843-4D56-8D6E-D290D3117D3B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{46E7093F-A843-4D56-8D6E-D290D3117D3B}"/>
   </bookViews>
   <sheets>
     <sheet name="STOK DEALER" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5870" uniqueCount="3100">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5871" uniqueCount="3101">
   <si>
     <t>No</t>
   </si>
@@ -9330,6 +9330,9 @@
   </si>
   <si>
     <t>MIRROR COMP., L.</t>
+  </si>
+  <si>
+    <t>TOTAL</t>
   </si>
   <si>
     <t>ACC KIT SE KU 1</t>
@@ -9367,7 +9370,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -9390,17 +9393,69 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -9736,7 +9791,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2BB8C35-92DF-4C27-A2CF-D1CDC7F4FE42}">
-  <dimension ref="A1:H1476"/>
+  <dimension ref="A1:H1477"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -13289,7 +13344,7 @@
         <v>1774</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>3098</v>
+        <v>3099</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>1623</v>
@@ -13341,7 +13396,7 @@
         <v>1777</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>3099</v>
+        <v>3100</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>1623</v>
@@ -22110,10 +22165,10 @@
         <v>1099</v>
       </c>
       <c r="F476" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G476" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H476" s="2">
         <v>2</v>
@@ -24524,10 +24579,10 @@
         <v>483</v>
       </c>
       <c r="F569" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G569" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H569" s="2">
         <v>30</v>
@@ -37314,10 +37369,10 @@
         <v>2590</v>
       </c>
       <c r="F1061" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1061" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1061" s="2">
         <v>0</v>
@@ -47775,7 +47830,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1464" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1464" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1464" s="2">
         <v>1463</v>
       </c>
@@ -47801,7 +47856,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1465" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="1465" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1465" s="2">
         <v>1464</v>
       </c>
@@ -48113,7 +48168,28 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1477" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1477" s="5" t="s">
+        <v>3098</v>
+      </c>
+      <c r="B1477" s="6"/>
+      <c r="C1477" s="6"/>
+      <c r="D1477" s="6"/>
+      <c r="E1477" s="7"/>
+      <c r="F1477" s="3">
+        <v>5583</v>
+      </c>
+      <c r="G1477" s="4">
+        <v>33</v>
+      </c>
+      <c r="H1477" s="3">
+        <v>5550</v>
+      </c>
+    </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1477:E1477"/>
+  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/STOK DEALER/STOK SRB.xlsx
+++ b/STOK DEALER/STOK SRB.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data D\2026\UPADTE TOOLS BUNDLING SRB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{989F5F49-E390-41EE-B58F-09FED3127C6F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEA7B5DD-0936-4D87-9E83-B0E69059CAAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{46E7093F-A843-4D56-8D6E-D290D3117D3B}"/>
   </bookViews>
   <sheets>
     <sheet name="STOK DEALER" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'STOK DEALER'!$A$1:$H$1477</definedName>
+  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -9951,13 +9954,13 @@
         <v>1627</v>
       </c>
       <c r="F6" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G6" s="2">
         <v>0</v>
       </c>
       <c r="H6" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -11459,13 +11462,13 @@
         <v>1260</v>
       </c>
       <c r="F64" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G64" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H64" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
@@ -13457,13 +13460,13 @@
         <v>1780</v>
       </c>
       <c r="F141" s="2">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="G141" s="2">
         <v>0</v>
       </c>
       <c r="H141" s="2">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
@@ -13483,13 +13486,13 @@
         <v>1781</v>
       </c>
       <c r="F142" s="2">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="G142" s="2">
         <v>3</v>
       </c>
       <c r="H142" s="2">
-        <v>149</v>
+        <v>147</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
@@ -13509,13 +13512,13 @@
         <v>1781</v>
       </c>
       <c r="F143" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G143" s="2">
         <v>1</v>
       </c>
       <c r="H143" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
@@ -13639,13 +13642,13 @@
         <v>1789</v>
       </c>
       <c r="F148" s="2">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="G148" s="2">
         <v>2</v>
       </c>
       <c r="H148" s="2">
-        <v>261</v>
+        <v>258</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
@@ -13899,13 +13902,13 @@
         <v>1780</v>
       </c>
       <c r="F158" s="2">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="G158" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H158" s="2">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
@@ -13925,13 +13928,13 @@
         <v>1789</v>
       </c>
       <c r="F159" s="2">
-        <v>668</v>
+        <v>655</v>
       </c>
       <c r="G159" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H159" s="2">
-        <v>664</v>
+        <v>652</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
@@ -14081,13 +14084,13 @@
         <v>207</v>
       </c>
       <c r="F165" s="2">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="G165" s="2">
         <v>2</v>
       </c>
       <c r="H165" s="2">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
@@ -14237,13 +14240,13 @@
         <v>939</v>
       </c>
       <c r="F171" s="2">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="G171" s="2">
         <v>1</v>
       </c>
       <c r="H171" s="2">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
@@ -14419,13 +14422,13 @@
         <v>1816</v>
       </c>
       <c r="F178" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G178" s="2">
         <v>0</v>
       </c>
       <c r="H178" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.25">
@@ -14627,13 +14630,13 @@
         <v>1816</v>
       </c>
       <c r="F186" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G186" s="2">
         <v>0</v>
       </c>
       <c r="H186" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.25">
@@ -14965,13 +14968,13 @@
         <v>1827</v>
       </c>
       <c r="F199" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G199" s="2">
         <v>0</v>
       </c>
       <c r="H199" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.25">
@@ -15251,13 +15254,13 @@
         <v>1854</v>
       </c>
       <c r="F210" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G210" s="2">
         <v>0</v>
       </c>
       <c r="H210" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.25">
@@ -20503,13 +20506,13 @@
         <v>2169</v>
       </c>
       <c r="F412" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G412" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H412" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="413" spans="1:8" x14ac:dyDescent="0.25">
@@ -22165,13 +22168,13 @@
         <v>1099</v>
       </c>
       <c r="F476" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G476" s="2">
         <v>1</v>
       </c>
       <c r="H476" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="477" spans="1:8" x14ac:dyDescent="0.25">
@@ -22243,10 +22246,10 @@
         <v>610</v>
       </c>
       <c r="F479" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G479" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H479" s="2">
         <v>1</v>
@@ -24215,13 +24218,13 @@
         <v>2275</v>
       </c>
       <c r="F555" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G555" s="2">
         <v>0</v>
       </c>
       <c r="H555" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="556" spans="1:8" x14ac:dyDescent="0.25">
@@ -26945,10 +26948,10 @@
         <v>402</v>
       </c>
       <c r="F660" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G660" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H660" s="2">
         <v>12</v>
@@ -26971,13 +26974,13 @@
         <v>430</v>
       </c>
       <c r="F661" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G661" s="2">
         <v>1</v>
       </c>
       <c r="H661" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="662" spans="1:8" x14ac:dyDescent="0.25">
@@ -27673,13 +27676,13 @@
         <v>1809</v>
       </c>
       <c r="F688" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G688" s="2">
         <v>0</v>
       </c>
       <c r="H688" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="689" spans="1:8" x14ac:dyDescent="0.25">
@@ -28505,13 +28508,13 @@
         <v>693</v>
       </c>
       <c r="F720" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G720" s="2">
         <v>0</v>
       </c>
       <c r="H720" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="721" spans="1:8" x14ac:dyDescent="0.25">
@@ -34717,13 +34720,13 @@
         <v>2629</v>
       </c>
       <c r="F959" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G959" s="2">
         <v>0</v>
       </c>
       <c r="H959" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="960" spans="1:8" x14ac:dyDescent="0.25">
@@ -35994,10 +35997,10 @@
         <v>1</v>
       </c>
       <c r="G1008" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1008" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1009" spans="1:8" x14ac:dyDescent="0.25">
@@ -39943,13 +39946,13 @@
         <v>2728</v>
       </c>
       <c r="F1160" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G1160" s="2">
         <v>0</v>
       </c>
       <c r="H1160" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="1161" spans="1:8" x14ac:dyDescent="0.25">
@@ -41711,13 +41714,13 @@
         <v>1784</v>
       </c>
       <c r="F1228" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G1228" s="2">
         <v>1</v>
       </c>
       <c r="H1228" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1229" spans="1:8" x14ac:dyDescent="0.25">
@@ -42101,13 +42104,13 @@
         <v>586</v>
       </c>
       <c r="F1243" s="2">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="G1243" s="2">
         <v>0</v>
       </c>
       <c r="H1243" s="2">
-        <v>55</v>
+        <v>53</v>
       </c>
     </row>
     <row r="1244" spans="1:8" x14ac:dyDescent="0.25">
@@ -42647,13 +42650,13 @@
         <v>2823</v>
       </c>
       <c r="F1264" s="2">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G1264" s="2">
         <v>0</v>
       </c>
       <c r="H1264" s="2">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="1265" spans="1:8" x14ac:dyDescent="0.25">
@@ -46235,13 +46238,13 @@
         <v>2868</v>
       </c>
       <c r="F1402" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G1402" s="2">
         <v>0</v>
       </c>
       <c r="H1402" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1403" spans="1:8" x14ac:dyDescent="0.25">
@@ -48107,10 +48110,10 @@
         <v>3059</v>
       </c>
       <c r="F1474" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G1474" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H1474" s="2">
         <v>29</v>

--- a/STOK DEALER/STOK SRB.xlsx
+++ b/STOK DEALER/STOK SRB.xlsx
@@ -1,23 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data D\2026\UPADTE TOOLS BUNDLING SRB\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEA7B5DD-0936-4D87-9E83-B0E69059CAAE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A00E1D5B-AED6-4FC0-B118-F5A61B2DF1A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{46E7093F-A843-4D56-8D6E-D290D3117D3B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{46E7093F-A843-4D56-8D6E-D290D3117D3B}"/>
   </bookViews>
   <sheets>
     <sheet name="STOK DEALER" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'STOK DEALER'!$A$1:$H$1477</definedName>
-  </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -39,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5871" uniqueCount="3101">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5870" uniqueCount="3100">
   <si>
     <t>No</t>
   </si>
@@ -9333,9 +9330,6 @@
   </si>
   <si>
     <t>MIRROR COMP., L.</t>
-  </si>
-  <si>
-    <t>TOTAL</t>
   </si>
   <si>
     <t>ACC KIT SE KU 1</t>
@@ -9373,7 +9367,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -9396,69 +9390,17 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -9794,7 +9736,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2BB8C35-92DF-4C27-A2CF-D1CDC7F4FE42}">
-  <dimension ref="A1:H1477"/>
+  <dimension ref="A1:H1476"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -9954,13 +9896,13 @@
         <v>1627</v>
       </c>
       <c r="F6" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G6" s="2">
         <v>0</v>
       </c>
       <c r="H6" s="2">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -10552,13 +10494,13 @@
         <v>1653</v>
       </c>
       <c r="F29" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G29" s="2">
         <v>0</v>
       </c>
       <c r="H29" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -11254,13 +11196,13 @@
         <v>30</v>
       </c>
       <c r="F56" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G56" s="2">
         <v>0</v>
       </c>
       <c r="H56" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
@@ -13347,7 +13289,7 @@
         <v>1774</v>
       </c>
       <c r="C137" s="2" t="s">
-        <v>3099</v>
+        <v>3098</v>
       </c>
       <c r="D137" s="2" t="s">
         <v>1623</v>
@@ -13399,7 +13341,7 @@
         <v>1777</v>
       </c>
       <c r="C139" s="2" t="s">
-        <v>3100</v>
+        <v>3099</v>
       </c>
       <c r="D139" s="2" t="s">
         <v>1623</v>
@@ -13460,13 +13402,13 @@
         <v>1780</v>
       </c>
       <c r="F141" s="2">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G141" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H141" s="2">
-        <v>38</v>
+        <v>35</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
@@ -13486,13 +13428,13 @@
         <v>1781</v>
       </c>
       <c r="F142" s="2">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="G142" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H142" s="2">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
@@ -13512,13 +13454,13 @@
         <v>1781</v>
       </c>
       <c r="F143" s="2">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G143" s="2">
         <v>1</v>
       </c>
       <c r="H143" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
@@ -13642,13 +13584,13 @@
         <v>1789</v>
       </c>
       <c r="F148" s="2">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="G148" s="2">
         <v>2</v>
       </c>
       <c r="H148" s="2">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
@@ -13902,13 +13844,13 @@
         <v>1780</v>
       </c>
       <c r="F158" s="2">
-        <v>141</v>
+        <v>135</v>
       </c>
       <c r="G158" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H158" s="2">
-        <v>141</v>
+        <v>134</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
@@ -13928,13 +13870,13 @@
         <v>1789</v>
       </c>
       <c r="F159" s="2">
-        <v>655</v>
+        <v>642</v>
       </c>
       <c r="G159" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H159" s="2">
-        <v>652</v>
+        <v>638</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
@@ -14084,13 +14026,13 @@
         <v>207</v>
       </c>
       <c r="F165" s="2">
-        <v>118</v>
+        <v>113</v>
       </c>
       <c r="G165" s="2">
         <v>2</v>
       </c>
       <c r="H165" s="2">
-        <v>116</v>
+        <v>111</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
@@ -16661,10 +16603,10 @@
         <v>1</v>
       </c>
       <c r="G264" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H264" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="265" spans="1:8" x14ac:dyDescent="0.25">
@@ -16817,10 +16759,10 @@
         <v>24</v>
       </c>
       <c r="G270" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H270" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="271" spans="1:8" x14ac:dyDescent="0.25">
@@ -18065,10 +18007,10 @@
         <v>1</v>
       </c>
       <c r="G318" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H318" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="319" spans="1:8" x14ac:dyDescent="0.25">
@@ -20454,13 +20396,13 @@
         <v>2168</v>
       </c>
       <c r="F410" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G410" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H410" s="2">
-        <v>26</v>
+        <v>24</v>
       </c>
     </row>
     <row r="411" spans="1:8" x14ac:dyDescent="0.25">
@@ -20480,13 +20422,13 @@
         <v>926</v>
       </c>
       <c r="F411" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G411" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H411" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="412" spans="1:8" x14ac:dyDescent="0.25">
@@ -20714,13 +20656,13 @@
         <v>2172</v>
       </c>
       <c r="F420" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G420" s="2">
         <v>0</v>
       </c>
       <c r="H420" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="421" spans="1:8" x14ac:dyDescent="0.25">
@@ -22298,13 +22240,13 @@
         <v>610</v>
       </c>
       <c r="F481" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G481" s="2">
         <v>0</v>
       </c>
       <c r="H481" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="482" spans="1:8" x14ac:dyDescent="0.25">
@@ -22766,13 +22708,13 @@
         <v>2242</v>
       </c>
       <c r="F499" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G499" s="2">
         <v>0</v>
       </c>
       <c r="H499" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="500" spans="1:8" x14ac:dyDescent="0.25">
@@ -23026,13 +22968,13 @@
         <v>581</v>
       </c>
       <c r="F509" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G509" s="2">
         <v>0</v>
       </c>
       <c r="H509" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="510" spans="1:8" x14ac:dyDescent="0.25">
@@ -23104,13 +23046,13 @@
         <v>2246</v>
       </c>
       <c r="F512" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G512" s="2">
         <v>0</v>
       </c>
       <c r="H512" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="513" spans="1:8" x14ac:dyDescent="0.25">
@@ -24039,10 +23981,10 @@
         <v>2</v>
       </c>
       <c r="G548" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H548" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="549" spans="1:8" x14ac:dyDescent="0.25">
@@ -24062,13 +24004,13 @@
         <v>236</v>
       </c>
       <c r="F549" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G549" s="2">
         <v>0</v>
       </c>
       <c r="H549" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="550" spans="1:8" x14ac:dyDescent="0.25">
@@ -24582,13 +24524,13 @@
         <v>483</v>
       </c>
       <c r="F569" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G569" s="2">
         <v>0</v>
       </c>
       <c r="H569" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="570" spans="1:8" x14ac:dyDescent="0.25">
@@ -26717,10 +26659,10 @@
         <v>8</v>
       </c>
       <c r="G651" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H651" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="652" spans="1:8" x14ac:dyDescent="0.25">
@@ -26948,13 +26890,13 @@
         <v>402</v>
       </c>
       <c r="F660" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="G660" s="2">
         <v>0</v>
       </c>
       <c r="H660" s="2">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="661" spans="1:8" x14ac:dyDescent="0.25">
@@ -26977,10 +26919,10 @@
         <v>32</v>
       </c>
       <c r="G661" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H661" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="662" spans="1:8" x14ac:dyDescent="0.25">
@@ -30614,13 +30556,13 @@
         <v>1110</v>
       </c>
       <c r="F801" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G801" s="2">
         <v>1</v>
       </c>
       <c r="H801" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="802" spans="1:8" x14ac:dyDescent="0.25">
@@ -31420,13 +31362,13 @@
         <v>2557</v>
       </c>
       <c r="F832" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G832" s="2">
         <v>0</v>
       </c>
       <c r="H832" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="833" spans="1:8" x14ac:dyDescent="0.25">
@@ -32281,10 +32223,10 @@
         <v>4</v>
       </c>
       <c r="G865" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H865" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="866" spans="1:8" x14ac:dyDescent="0.25">
@@ -39894,13 +39836,13 @@
         <v>2729</v>
       </c>
       <c r="F1158" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G1158" s="2">
         <v>0</v>
       </c>
       <c r="H1158" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1159" spans="1:8" x14ac:dyDescent="0.25">
@@ -41766,13 +41708,13 @@
         <v>2810</v>
       </c>
       <c r="F1230" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1230" s="2">
         <v>0</v>
       </c>
       <c r="H1230" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1231" spans="1:8" x14ac:dyDescent="0.25">
@@ -41792,13 +41734,13 @@
         <v>2810</v>
       </c>
       <c r="F1231" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1231" s="2">
         <v>0</v>
       </c>
       <c r="H1231" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1232" spans="1:8" x14ac:dyDescent="0.25">
@@ -42104,13 +42046,13 @@
         <v>586</v>
       </c>
       <c r="F1243" s="2">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="G1243" s="2">
         <v>0</v>
       </c>
       <c r="H1243" s="2">
-        <v>53</v>
+        <v>52</v>
       </c>
     </row>
     <row r="1244" spans="1:8" x14ac:dyDescent="0.25">
@@ -46602,13 +46544,13 @@
         <v>2966</v>
       </c>
       <c r="F1416" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1416" s="2">
         <v>0</v>
       </c>
       <c r="H1416" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1417" spans="1:8" x14ac:dyDescent="0.25">
@@ -47697,10 +47639,10 @@
         <v>21</v>
       </c>
       <c r="G1458" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1458" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1459" spans="1:8" x14ac:dyDescent="0.25">
@@ -47833,7 +47775,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="1464" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1464" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1464" s="2">
         <v>1463</v>
       </c>
@@ -47859,7 +47801,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="1465" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1465" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1465" s="2">
         <v>1464</v>
       </c>
@@ -48113,10 +48055,10 @@
         <v>30</v>
       </c>
       <c r="G1474" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1474" s="2">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1475" spans="1:8" x14ac:dyDescent="0.25">
@@ -48171,28 +48113,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="1477" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1477" s="5" t="s">
-        <v>3098</v>
-      </c>
-      <c r="B1477" s="6"/>
-      <c r="C1477" s="6"/>
-      <c r="D1477" s="6"/>
-      <c r="E1477" s="7"/>
-      <c r="F1477" s="3">
-        <v>5583</v>
-      </c>
-      <c r="G1477" s="4">
-        <v>33</v>
-      </c>
-      <c r="H1477" s="3">
-        <v>5550</v>
-      </c>
-    </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1477:E1477"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/STOK DEALER/STOK SRB.xlsx
+++ b/STOK DEALER/STOK SRB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data D\2026\UPADTE TOOLS BUNDLING SRB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5341ECA5-2D11-4A57-9DF6-83C301F185C7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A5EBECB-5EC6-41EC-A05A-BA58347C2CB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{46E7093F-A843-4D56-8D6E-D290D3117D3B}"/>
   </bookViews>
@@ -9810,13 +9810,13 @@
         <v>1624</v>
       </c>
       <c r="F2" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G2" s="2">
         <v>0</v>
       </c>
       <c r="H2" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -9836,13 +9836,13 @@
         <v>1625</v>
       </c>
       <c r="F3" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G3" s="2">
         <v>0</v>
       </c>
       <c r="H3" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -9888,13 +9888,13 @@
         <v>1627</v>
       </c>
       <c r="F5" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G5" s="2">
         <v>0</v>
       </c>
       <c r="H5" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -9914,13 +9914,13 @@
         <v>1627</v>
       </c>
       <c r="F6" s="2">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G6" s="2">
         <v>0</v>
       </c>
       <c r="H6" s="2">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -9966,13 +9966,13 @@
         <v>1627</v>
       </c>
       <c r="F8" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G8" s="2">
         <v>0</v>
       </c>
       <c r="H8" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -10616,13 +10616,13 @@
         <v>1659</v>
       </c>
       <c r="F33" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G33" s="2">
         <v>0</v>
       </c>
       <c r="H33" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -11422,13 +11422,13 @@
         <v>1260</v>
       </c>
       <c r="F64" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G64" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H64" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
@@ -11500,13 +11500,13 @@
         <v>1682</v>
       </c>
       <c r="F67" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G67" s="2">
         <v>0</v>
       </c>
       <c r="H67" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
@@ -13420,13 +13420,13 @@
         <v>1780</v>
       </c>
       <c r="F141" s="2">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="G141" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H141" s="2">
-        <v>32</v>
+        <v>26</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
@@ -13446,13 +13446,13 @@
         <v>1781</v>
       </c>
       <c r="F142" s="2">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="G142" s="2">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="H142" s="2">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
@@ -13472,13 +13472,13 @@
         <v>1781</v>
       </c>
       <c r="F143" s="2">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G143" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H143" s="2">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
@@ -13602,13 +13602,13 @@
         <v>1789</v>
       </c>
       <c r="F148" s="2">
-        <v>259</v>
+        <v>254</v>
       </c>
       <c r="G148" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="H148" s="2">
-        <v>257</v>
+        <v>246</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
@@ -13862,13 +13862,13 @@
         <v>1780</v>
       </c>
       <c r="F158" s="2">
-        <v>132</v>
+        <v>125</v>
       </c>
       <c r="G158" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="H158" s="2">
-        <v>130</v>
+        <v>120</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
@@ -13888,13 +13888,13 @@
         <v>1789</v>
       </c>
       <c r="F159" s="2">
-        <v>636</v>
+        <v>615</v>
       </c>
       <c r="G159" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H159" s="2">
-        <v>632</v>
+        <v>609</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
@@ -13966,13 +13966,13 @@
         <v>207</v>
       </c>
       <c r="F162" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G162" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H162" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.25">
@@ -14044,13 +14044,13 @@
         <v>207</v>
       </c>
       <c r="F165" s="2">
-        <v>112</v>
+        <v>109</v>
       </c>
       <c r="G165" s="2">
         <v>2</v>
       </c>
       <c r="H165" s="2">
-        <v>110</v>
+        <v>107</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
@@ -14200,13 +14200,13 @@
         <v>939</v>
       </c>
       <c r="F171" s="2">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G171" s="2">
         <v>2</v>
       </c>
       <c r="H171" s="2">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.25">
@@ -14330,13 +14330,13 @@
         <v>1816</v>
       </c>
       <c r="F176" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G176" s="2">
         <v>0</v>
       </c>
       <c r="H176" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.25">
@@ -14538,13 +14538,13 @@
         <v>1827</v>
       </c>
       <c r="F184" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G184" s="2">
         <v>0</v>
       </c>
       <c r="H184" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.25">
@@ -14928,13 +14928,13 @@
         <v>1827</v>
       </c>
       <c r="F199" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G199" s="2">
         <v>0</v>
       </c>
       <c r="H199" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.25">
@@ -14980,13 +14980,13 @@
         <v>1827</v>
       </c>
       <c r="F201" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G201" s="2">
         <v>0</v>
       </c>
       <c r="H201" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.25">
@@ -15032,13 +15032,13 @@
         <v>1809</v>
       </c>
       <c r="F203" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G203" s="2">
         <v>0</v>
       </c>
       <c r="H203" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.25">
@@ -16803,10 +16803,10 @@
         <v>10</v>
       </c>
       <c r="G271" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H271" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="272" spans="1:8" x14ac:dyDescent="0.25">
@@ -17869,10 +17869,10 @@
         <v>2</v>
       </c>
       <c r="G312" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H312" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="313" spans="1:8" x14ac:dyDescent="0.25">
@@ -17895,10 +17895,10 @@
         <v>5</v>
       </c>
       <c r="G313" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H313" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="314" spans="1:8" x14ac:dyDescent="0.25">
@@ -19218,13 +19218,13 @@
         <v>2082</v>
       </c>
       <c r="F364" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G364" s="2">
         <v>0</v>
       </c>
       <c r="H364" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="365" spans="1:8" x14ac:dyDescent="0.25">
@@ -20414,13 +20414,13 @@
         <v>2168</v>
       </c>
       <c r="F410" s="2">
-        <v>26</v>
+        <v>22</v>
       </c>
       <c r="G410" s="2">
         <v>2</v>
       </c>
       <c r="H410" s="2">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="411" spans="1:8" x14ac:dyDescent="0.25">
@@ -20466,13 +20466,13 @@
         <v>2169</v>
       </c>
       <c r="F412" s="2">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="G412" s="2">
         <v>0</v>
       </c>
       <c r="H412" s="2">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="413" spans="1:8" x14ac:dyDescent="0.25">
@@ -22856,13 +22856,13 @@
         <v>919</v>
       </c>
       <c r="F504" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G504" s="2">
         <v>0</v>
       </c>
       <c r="H504" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="505" spans="1:8" x14ac:dyDescent="0.25">
@@ -23298,13 +23298,13 @@
         <v>268</v>
       </c>
       <c r="F521" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G521" s="2">
         <v>0</v>
       </c>
       <c r="H521" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="522" spans="1:8" x14ac:dyDescent="0.25">
@@ -24178,13 +24178,13 @@
         <v>2275</v>
       </c>
       <c r="F555" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G555" s="2">
         <v>0</v>
       </c>
       <c r="H555" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="556" spans="1:8" x14ac:dyDescent="0.25">
@@ -24207,10 +24207,10 @@
         <v>8</v>
       </c>
       <c r="G556" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H556" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="557" spans="1:8" x14ac:dyDescent="0.25">
@@ -24386,13 +24386,13 @@
         <v>2280</v>
       </c>
       <c r="F563" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G563" s="2">
         <v>0</v>
       </c>
       <c r="H563" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="564" spans="1:8" x14ac:dyDescent="0.25">
@@ -25868,13 +25868,13 @@
         <v>440</v>
       </c>
       <c r="F620" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G620" s="2">
         <v>0</v>
       </c>
       <c r="H620" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="621" spans="1:8" x14ac:dyDescent="0.25">
@@ -26518,13 +26518,13 @@
         <v>292</v>
       </c>
       <c r="F645" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G645" s="2">
         <v>2</v>
       </c>
       <c r="H645" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="646" spans="1:8" x14ac:dyDescent="0.25">
@@ -26934,13 +26934,13 @@
         <v>430</v>
       </c>
       <c r="F661" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G661" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H661" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="662" spans="1:8" x14ac:dyDescent="0.25">
@@ -26963,10 +26963,10 @@
         <v>12</v>
       </c>
       <c r="G662" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H662" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="663" spans="1:8" x14ac:dyDescent="0.25">
@@ -28471,10 +28471,10 @@
         <v>2</v>
       </c>
       <c r="G720" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H720" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="721" spans="1:8" x14ac:dyDescent="0.25">
@@ -28494,13 +28494,13 @@
         <v>50</v>
       </c>
       <c r="F721" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G721" s="2">
         <v>0</v>
       </c>
       <c r="H721" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="722" spans="1:8" x14ac:dyDescent="0.25">
@@ -28598,13 +28598,13 @@
         <v>696</v>
       </c>
       <c r="F725" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G725" s="2">
         <v>0</v>
       </c>
       <c r="H725" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="726" spans="1:8" x14ac:dyDescent="0.25">
@@ -30574,13 +30574,13 @@
         <v>1110</v>
       </c>
       <c r="F801" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G801" s="2">
         <v>0</v>
       </c>
       <c r="H801" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="802" spans="1:8" x14ac:dyDescent="0.25">
@@ -30600,13 +30600,13 @@
         <v>1110</v>
       </c>
       <c r="F802" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G802" s="2">
         <v>1</v>
       </c>
       <c r="H802" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="803" spans="1:8" x14ac:dyDescent="0.25">
@@ -32004,13 +32004,13 @@
         <v>2573</v>
       </c>
       <c r="F856" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G856" s="2">
         <v>0</v>
       </c>
       <c r="H856" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="857" spans="1:8" x14ac:dyDescent="0.25">
@@ -32267,10 +32267,10 @@
         <v>4</v>
       </c>
       <c r="G866" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H866" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="867" spans="1:8" x14ac:dyDescent="0.25">
@@ -34524,13 +34524,13 @@
         <v>2514</v>
       </c>
       <c r="F953" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G953" s="2">
         <v>0</v>
       </c>
       <c r="H953" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="954" spans="1:8" x14ac:dyDescent="0.25">
@@ -34628,13 +34628,13 @@
         <v>2624</v>
       </c>
       <c r="F957" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G957" s="2">
         <v>0</v>
       </c>
       <c r="H957" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="958" spans="1:8" x14ac:dyDescent="0.25">
@@ -34706,13 +34706,13 @@
         <v>2629</v>
       </c>
       <c r="F960" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G960" s="2">
         <v>0</v>
       </c>
       <c r="H960" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="961" spans="1:8" x14ac:dyDescent="0.25">
@@ -36630,13 +36630,13 @@
         <v>1750</v>
       </c>
       <c r="F1034" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G1034" s="2">
         <v>0</v>
       </c>
       <c r="H1034" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1035" spans="1:8" x14ac:dyDescent="0.25">
@@ -37358,13 +37358,13 @@
         <v>2590</v>
       </c>
       <c r="F1062" s="2">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="G1062" s="2">
         <v>0</v>
       </c>
       <c r="H1062" s="2">
-        <v>137</v>
+        <v>126</v>
       </c>
     </row>
     <row r="1063" spans="1:8" x14ac:dyDescent="0.25">
@@ -39100,13 +39100,13 @@
         <v>2733</v>
       </c>
       <c r="F1129" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1129" s="2">
         <v>0</v>
       </c>
       <c r="H1129" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1130" spans="1:8" x14ac:dyDescent="0.25">
@@ -39282,13 +39282,13 @@
         <v>2733</v>
       </c>
       <c r="F1136" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="G1136" s="2">
         <v>0</v>
       </c>
       <c r="H1136" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1137" spans="1:8" x14ac:dyDescent="0.25">
@@ -39828,13 +39828,13 @@
         <v>2727</v>
       </c>
       <c r="F1157" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1157" s="2">
         <v>0</v>
       </c>
       <c r="H1157" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1158" spans="1:8" x14ac:dyDescent="0.25">
@@ -39880,13 +39880,13 @@
         <v>2729</v>
       </c>
       <c r="F1159" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G1159" s="2">
         <v>0</v>
       </c>
       <c r="H1159" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1160" spans="1:8" x14ac:dyDescent="0.25">
@@ -39958,13 +39958,13 @@
         <v>2717</v>
       </c>
       <c r="F1162" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G1162" s="2">
         <v>0</v>
       </c>
       <c r="H1162" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="1163" spans="1:8" x14ac:dyDescent="0.25">
@@ -40010,13 +40010,13 @@
         <v>2728</v>
       </c>
       <c r="F1164" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G1164" s="2">
         <v>0</v>
       </c>
       <c r="H1164" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1165" spans="1:8" x14ac:dyDescent="0.25">
@@ -40062,13 +40062,13 @@
         <v>2728</v>
       </c>
       <c r="F1166" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1166" s="2">
         <v>0</v>
       </c>
       <c r="H1166" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1167" spans="1:8" x14ac:dyDescent="0.25">
@@ -40949,10 +40949,10 @@
         <v>2</v>
       </c>
       <c r="G1200" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1200" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1201" spans="1:8" x14ac:dyDescent="0.25">
@@ -41729,10 +41729,10 @@
         <v>22</v>
       </c>
       <c r="G1230" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H1230" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1231" spans="1:8" x14ac:dyDescent="0.25">
@@ -42116,13 +42116,13 @@
         <v>586</v>
       </c>
       <c r="F1245" s="2">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="G1245" s="2">
         <v>0</v>
       </c>
       <c r="H1245" s="2">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="1246" spans="1:8" x14ac:dyDescent="0.25">
@@ -42428,13 +42428,13 @@
         <v>2304</v>
       </c>
       <c r="F1257" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G1257" s="2">
         <v>0</v>
       </c>
       <c r="H1257" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1258" spans="1:8" x14ac:dyDescent="0.25">
@@ -42483,10 +42483,10 @@
         <v>25</v>
       </c>
       <c r="G1259" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1259" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1260" spans="1:8" x14ac:dyDescent="0.25">
@@ -42662,13 +42662,13 @@
         <v>2823</v>
       </c>
       <c r="F1266" s="2">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="G1266" s="2">
         <v>0</v>
       </c>
       <c r="H1266" s="2">
-        <v>59</v>
+        <v>51</v>
       </c>
     </row>
     <row r="1267" spans="1:8" x14ac:dyDescent="0.25">
@@ -43130,13 +43130,13 @@
         <v>2629</v>
       </c>
       <c r="F1284" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1284" s="2">
         <v>0</v>
       </c>
       <c r="H1284" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1285" spans="1:8" x14ac:dyDescent="0.25">
@@ -45418,13 +45418,13 @@
         <v>2966</v>
       </c>
       <c r="F1372" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G1372" s="2">
         <v>0</v>
       </c>
       <c r="H1372" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="1373" spans="1:8" x14ac:dyDescent="0.25">
@@ -46250,13 +46250,13 @@
         <v>2868</v>
       </c>
       <c r="F1404" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G1404" s="2">
         <v>0</v>
       </c>
       <c r="H1404" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1405" spans="1:8" x14ac:dyDescent="0.25">
@@ -46354,13 +46354,13 @@
         <v>2854</v>
       </c>
       <c r="F1408" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G1408" s="2">
         <v>0</v>
       </c>
       <c r="H1408" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1409" spans="1:8" x14ac:dyDescent="0.25">
@@ -46562,13 +46562,13 @@
         <v>3012</v>
       </c>
       <c r="F1416" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G1416" s="2">
         <v>0</v>
       </c>
       <c r="H1416" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1417" spans="1:8" x14ac:dyDescent="0.25">
@@ -46666,13 +46666,13 @@
         <v>2854</v>
       </c>
       <c r="F1420" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1420" s="2">
         <v>0</v>
       </c>
       <c r="H1420" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1421" spans="1:8" x14ac:dyDescent="0.25">
@@ -46822,13 +46822,13 @@
         <v>2945</v>
       </c>
       <c r="F1426" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1426" s="2">
         <v>0</v>
       </c>
       <c r="H1426" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1427" spans="1:8" x14ac:dyDescent="0.25">
@@ -46874,13 +46874,13 @@
         <v>2845</v>
       </c>
       <c r="F1428" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G1428" s="2">
         <v>0</v>
       </c>
       <c r="H1428" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1429" spans="1:8" x14ac:dyDescent="0.25">
@@ -46926,13 +46926,13 @@
         <v>2994</v>
       </c>
       <c r="F1430" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G1430" s="2">
         <v>0</v>
       </c>
       <c r="H1430" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1431" spans="1:8" x14ac:dyDescent="0.25">
@@ -46952,13 +46952,13 @@
         <v>2860</v>
       </c>
       <c r="F1431" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G1431" s="2">
         <v>0</v>
       </c>
       <c r="H1431" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1432" spans="1:8" x14ac:dyDescent="0.25">
@@ -46978,13 +46978,13 @@
         <v>2909</v>
       </c>
       <c r="F1432" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1432" s="2">
         <v>0</v>
       </c>
       <c r="H1432" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1433" spans="1:8" x14ac:dyDescent="0.25">
@@ -47709,10 +47709,10 @@
         <v>37</v>
       </c>
       <c r="G1460" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H1460" s="2">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="1461" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK SRB.xlsx
+++ b/STOK DEALER/STOK SRB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data D\2026\UPADTE TOOLS BUNDLING SRB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8A5EBECB-5EC6-41EC-A05A-BA58347C2CB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C262D07-623C-484B-A6EA-5516AB6E1A7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{46E7093F-A843-4D56-8D6E-D290D3117D3B}"/>
   </bookViews>
@@ -9914,13 +9914,13 @@
         <v>1627</v>
       </c>
       <c r="F6" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G6" s="2">
         <v>0</v>
       </c>
       <c r="H6" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -10515,10 +10515,10 @@
         <v>2</v>
       </c>
       <c r="G29" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H29" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -11422,10 +11422,10 @@
         <v>1260</v>
       </c>
       <c r="F64" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G64" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H64" s="2">
         <v>18</v>
@@ -13420,13 +13420,13 @@
         <v>1780</v>
       </c>
       <c r="F141" s="2">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="G141" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H141" s="2">
-        <v>26</v>
+        <v>23</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
@@ -13446,10 +13446,10 @@
         <v>1781</v>
       </c>
       <c r="F142" s="2">
-        <v>146</v>
+        <v>142</v>
       </c>
       <c r="G142" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H142" s="2">
         <v>138</v>
@@ -13472,13 +13472,13 @@
         <v>1781</v>
       </c>
       <c r="F143" s="2">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G143" s="2">
         <v>2</v>
       </c>
       <c r="H143" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
@@ -13602,13 +13602,13 @@
         <v>1789</v>
       </c>
       <c r="F148" s="2">
-        <v>254</v>
+        <v>249</v>
       </c>
       <c r="G148" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="H148" s="2">
-        <v>246</v>
+        <v>245</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
@@ -13862,13 +13862,13 @@
         <v>1780</v>
       </c>
       <c r="F158" s="2">
-        <v>125</v>
+        <v>119</v>
       </c>
       <c r="G158" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H158" s="2">
-        <v>120</v>
+        <v>115</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
@@ -13888,13 +13888,13 @@
         <v>1789</v>
       </c>
       <c r="F159" s="2">
-        <v>615</v>
+        <v>598</v>
       </c>
       <c r="G159" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H159" s="2">
-        <v>609</v>
+        <v>591</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
@@ -14044,13 +14044,13 @@
         <v>207</v>
       </c>
       <c r="F165" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G165" s="2">
         <v>2</v>
       </c>
       <c r="H165" s="2">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
@@ -16618,10 +16618,10 @@
         <v>1921</v>
       </c>
       <c r="F264" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G264" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H264" s="2">
         <v>0</v>
@@ -16774,10 +16774,10 @@
         <v>1956</v>
       </c>
       <c r="F270" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G270" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H270" s="2">
         <v>20</v>
@@ -18022,10 +18022,10 @@
         <v>2025</v>
       </c>
       <c r="F318" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G318" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H318" s="2">
         <v>0</v>
@@ -20466,13 +20466,13 @@
         <v>2169</v>
       </c>
       <c r="F412" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G412" s="2">
         <v>0</v>
       </c>
       <c r="H412" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="413" spans="1:8" x14ac:dyDescent="0.25">
@@ -20726,13 +20726,13 @@
         <v>285</v>
       </c>
       <c r="F422" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G422" s="2">
         <v>0</v>
       </c>
       <c r="H422" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="423" spans="1:8" x14ac:dyDescent="0.25">
@@ -20937,10 +20937,10 @@
         <v>11</v>
       </c>
       <c r="G430" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H430" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="431" spans="1:8" x14ac:dyDescent="0.25">
@@ -22989,10 +22989,10 @@
         <v>6</v>
       </c>
       <c r="G509" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H509" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="510" spans="1:8" x14ac:dyDescent="0.25">
@@ -24204,10 +24204,10 @@
         <v>2276</v>
       </c>
       <c r="F556" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G556" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H556" s="2">
         <v>7</v>
@@ -24545,10 +24545,10 @@
         <v>29</v>
       </c>
       <c r="G569" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H569" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="570" spans="1:8" x14ac:dyDescent="0.25">
@@ -26911,10 +26911,10 @@
         <v>9</v>
       </c>
       <c r="G660" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H660" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="661" spans="1:8" x14ac:dyDescent="0.25">
@@ -26934,13 +26934,13 @@
         <v>430</v>
       </c>
       <c r="F661" s="2">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="G661" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H661" s="2">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="662" spans="1:8" x14ac:dyDescent="0.25">
@@ -28468,13 +28468,13 @@
         <v>693</v>
       </c>
       <c r="F720" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G720" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H720" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="721" spans="1:8" x14ac:dyDescent="0.25">
@@ -31744,13 +31744,13 @@
         <v>1956</v>
       </c>
       <c r="F846" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G846" s="2">
         <v>0</v>
       </c>
       <c r="H846" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="847" spans="1:8" x14ac:dyDescent="0.25">
@@ -34524,13 +34524,13 @@
         <v>2514</v>
       </c>
       <c r="F953" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G953" s="2">
         <v>0</v>
       </c>
       <c r="H953" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="954" spans="1:8" x14ac:dyDescent="0.25">
@@ -34706,13 +34706,13 @@
         <v>2629</v>
       </c>
       <c r="F960" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G960" s="2">
         <v>0</v>
       </c>
       <c r="H960" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="961" spans="1:8" x14ac:dyDescent="0.25">
@@ -37358,13 +37358,13 @@
         <v>2590</v>
       </c>
       <c r="F1062" s="2">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="G1062" s="2">
         <v>0</v>
       </c>
       <c r="H1062" s="2">
-        <v>126</v>
+        <v>122</v>
       </c>
     </row>
     <row r="1063" spans="1:8" x14ac:dyDescent="0.25">
@@ -38398,13 +38398,13 @@
         <v>2452</v>
       </c>
       <c r="F1102" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G1102" s="2">
         <v>0</v>
       </c>
       <c r="H1102" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="1103" spans="1:8" x14ac:dyDescent="0.25">
@@ -41726,13 +41726,13 @@
         <v>1784</v>
       </c>
       <c r="F1230" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G1230" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H1230" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="1231" spans="1:8" x14ac:dyDescent="0.25">
@@ -41752,13 +41752,13 @@
         <v>2810</v>
       </c>
       <c r="F1231" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G1231" s="2">
         <v>0</v>
       </c>
       <c r="H1231" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1232" spans="1:8" x14ac:dyDescent="0.25">
@@ -41807,10 +41807,10 @@
         <v>1</v>
       </c>
       <c r="G1233" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1233" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1234" spans="1:8" x14ac:dyDescent="0.25">
@@ -42662,13 +42662,13 @@
         <v>2823</v>
       </c>
       <c r="F1266" s="2">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G1266" s="2">
         <v>0</v>
       </c>
       <c r="H1266" s="2">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1267" spans="1:8" x14ac:dyDescent="0.25">
@@ -44794,13 +44794,13 @@
         <v>2945</v>
       </c>
       <c r="F1348" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G1348" s="2">
         <v>0</v>
       </c>
       <c r="H1348" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1349" spans="1:8" x14ac:dyDescent="0.25">
@@ -46874,13 +46874,13 @@
         <v>2845</v>
       </c>
       <c r="F1428" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G1428" s="2">
         <v>0</v>
       </c>
       <c r="H1428" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1429" spans="1:8" x14ac:dyDescent="0.25">
@@ -47706,10 +47706,10 @@
         <v>565</v>
       </c>
       <c r="F1460" s="2">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="G1460" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H1460" s="2">
         <v>33</v>
@@ -48172,13 +48172,13 @@
         <v>939</v>
       </c>
       <c r="F1478" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G1478" s="2">
         <v>0</v>
       </c>
       <c r="H1478" s="2">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="1479" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK SRB.xlsx
+++ b/STOK DEALER/STOK SRB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data D\2026\UPADTE TOOLS BUNDLING SRB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C262D07-623C-484B-A6EA-5516AB6E1A7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{39B216B2-BEBC-4DF0-B729-ABDD3E067EB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{46E7093F-A843-4D56-8D6E-D290D3117D3B}"/>
   </bookViews>
@@ -9810,13 +9810,13 @@
         <v>1624</v>
       </c>
       <c r="F2" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G2" s="2">
         <v>0</v>
       </c>
       <c r="H2" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -9888,13 +9888,13 @@
         <v>1627</v>
       </c>
       <c r="F5" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G5" s="2">
         <v>0</v>
       </c>
       <c r="H5" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.25">
@@ -9914,13 +9914,13 @@
         <v>1627</v>
       </c>
       <c r="F6" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G6" s="2">
         <v>0</v>
       </c>
       <c r="H6" s="2">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.25">
@@ -9966,13 +9966,13 @@
         <v>1627</v>
       </c>
       <c r="F8" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G8" s="2">
         <v>0</v>
       </c>
       <c r="H8" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.25">
@@ -11422,13 +11422,13 @@
         <v>1260</v>
       </c>
       <c r="F64" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G64" s="2">
         <v>1</v>
       </c>
       <c r="H64" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.25">
@@ -13420,13 +13420,13 @@
         <v>1780</v>
       </c>
       <c r="F141" s="2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="G141" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H141" s="2">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
@@ -13449,10 +13449,10 @@
         <v>142</v>
       </c>
       <c r="G142" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H142" s="2">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
@@ -13475,10 +13475,10 @@
         <v>242</v>
       </c>
       <c r="G143" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H143" s="2">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
@@ -13862,13 +13862,13 @@
         <v>1780</v>
       </c>
       <c r="F158" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G158" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H158" s="2">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
@@ -13888,13 +13888,13 @@
         <v>1789</v>
       </c>
       <c r="F159" s="2">
-        <v>598</v>
+        <v>589</v>
       </c>
       <c r="G159" s="2">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="H159" s="2">
-        <v>591</v>
+        <v>580</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
@@ -14044,13 +14044,13 @@
         <v>207</v>
       </c>
       <c r="F165" s="2">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="G165" s="2">
         <v>2</v>
       </c>
       <c r="H165" s="2">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
@@ -14850,13 +14850,13 @@
         <v>1815</v>
       </c>
       <c r="F196" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G196" s="2">
         <v>0</v>
       </c>
       <c r="H196" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.25">
@@ -15240,13 +15240,13 @@
         <v>1855</v>
       </c>
       <c r="F211" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G211" s="2">
         <v>0</v>
       </c>
       <c r="H211" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.25">
@@ -18935,10 +18935,10 @@
         <v>1</v>
       </c>
       <c r="G353" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H353" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="354" spans="1:8" x14ac:dyDescent="0.25">
@@ -20440,13 +20440,13 @@
         <v>926</v>
       </c>
       <c r="F411" s="2">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G411" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H411" s="2">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="412" spans="1:8" x14ac:dyDescent="0.25">
@@ -20466,13 +20466,13 @@
         <v>2169</v>
       </c>
       <c r="F412" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G412" s="2">
         <v>0</v>
       </c>
       <c r="H412" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="413" spans="1:8" x14ac:dyDescent="0.25">
@@ -20495,10 +20495,10 @@
         <v>1</v>
       </c>
       <c r="G413" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H413" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="414" spans="1:8" x14ac:dyDescent="0.25">
@@ -20729,10 +20729,10 @@
         <v>3</v>
       </c>
       <c r="G422" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H422" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="423" spans="1:8" x14ac:dyDescent="0.25">
@@ -22833,10 +22833,10 @@
         <v>5</v>
       </c>
       <c r="G503" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H503" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="504" spans="1:8" x14ac:dyDescent="0.25">
@@ -22856,13 +22856,13 @@
         <v>919</v>
       </c>
       <c r="F504" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G504" s="2">
         <v>0</v>
       </c>
       <c r="H504" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="505" spans="1:8" x14ac:dyDescent="0.25">
@@ -24025,10 +24025,10 @@
         <v>4</v>
       </c>
       <c r="G549" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H549" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="550" spans="1:8" x14ac:dyDescent="0.25">
@@ -24178,13 +24178,13 @@
         <v>2275</v>
       </c>
       <c r="F555" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G555" s="2">
         <v>0</v>
       </c>
       <c r="H555" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="556" spans="1:8" x14ac:dyDescent="0.25">
@@ -24542,13 +24542,13 @@
         <v>483</v>
       </c>
       <c r="F569" s="2">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="G569" s="2">
         <v>1</v>
       </c>
       <c r="H569" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="570" spans="1:8" x14ac:dyDescent="0.25">
@@ -26674,13 +26674,13 @@
         <v>292</v>
       </c>
       <c r="F651" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G651" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H651" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="652" spans="1:8" x14ac:dyDescent="0.25">
@@ -26934,13 +26934,13 @@
         <v>430</v>
       </c>
       <c r="F661" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G661" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H661" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="662" spans="1:8" x14ac:dyDescent="0.25">
@@ -26963,10 +26963,10 @@
         <v>12</v>
       </c>
       <c r="G662" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H662" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="663" spans="1:8" x14ac:dyDescent="0.25">
@@ -34524,13 +34524,13 @@
         <v>2514</v>
       </c>
       <c r="F953" s="2">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G953" s="2">
         <v>0</v>
       </c>
       <c r="H953" s="2">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="954" spans="1:8" x14ac:dyDescent="0.25">
@@ -34628,13 +34628,13 @@
         <v>2624</v>
       </c>
       <c r="F957" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G957" s="2">
         <v>0</v>
       </c>
       <c r="H957" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="958" spans="1:8" x14ac:dyDescent="0.25">
@@ -36630,13 +36630,13 @@
         <v>1750</v>
       </c>
       <c r="F1034" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1034" s="2">
         <v>0</v>
       </c>
       <c r="H1034" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1035" spans="1:8" x14ac:dyDescent="0.25">
@@ -37358,13 +37358,13 @@
         <v>2590</v>
       </c>
       <c r="F1062" s="2">
-        <v>122</v>
+        <v>115</v>
       </c>
       <c r="G1062" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1062" s="2">
-        <v>122</v>
+        <v>114</v>
       </c>
     </row>
     <row r="1063" spans="1:8" x14ac:dyDescent="0.25">
@@ -39828,13 +39828,13 @@
         <v>2727</v>
       </c>
       <c r="F1157" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1157" s="2">
         <v>0</v>
       </c>
       <c r="H1157" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1158" spans="1:8" x14ac:dyDescent="0.25">
@@ -39932,13 +39932,13 @@
         <v>2728</v>
       </c>
       <c r="F1161" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="G1161" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1161" s="2">
-        <v>16</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1162" spans="1:8" x14ac:dyDescent="0.25">
@@ -40010,13 +40010,13 @@
         <v>2728</v>
       </c>
       <c r="F1164" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G1164" s="2">
         <v>0</v>
       </c>
       <c r="H1164" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1165" spans="1:8" x14ac:dyDescent="0.25">
@@ -41726,13 +41726,13 @@
         <v>1784</v>
       </c>
       <c r="F1230" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G1230" s="2">
         <v>1</v>
       </c>
       <c r="H1230" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1231" spans="1:8" x14ac:dyDescent="0.25">
@@ -42116,13 +42116,13 @@
         <v>586</v>
       </c>
       <c r="F1245" s="2">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G1245" s="2">
         <v>0</v>
       </c>
       <c r="H1245" s="2">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
     <row r="1246" spans="1:8" x14ac:dyDescent="0.25">
@@ -42480,13 +42480,13 @@
         <v>458</v>
       </c>
       <c r="F1259" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G1259" s="2">
         <v>1</v>
       </c>
       <c r="H1259" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1260" spans="1:8" x14ac:dyDescent="0.25">
@@ -42662,13 +42662,13 @@
         <v>2823</v>
       </c>
       <c r="F1266" s="2">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="G1266" s="2">
         <v>0</v>
       </c>
       <c r="H1266" s="2">
-        <v>50</v>
+        <v>45</v>
       </c>
     </row>
     <row r="1267" spans="1:8" x14ac:dyDescent="0.25">
@@ -44846,13 +44846,13 @@
         <v>2881</v>
       </c>
       <c r="F1350" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1350" s="2">
         <v>0</v>
       </c>
       <c r="H1350" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1351" spans="1:8" x14ac:dyDescent="0.25">
@@ -46562,13 +46562,13 @@
         <v>3012</v>
       </c>
       <c r="F1416" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G1416" s="2">
         <v>0</v>
       </c>
       <c r="H1416" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1417" spans="1:8" x14ac:dyDescent="0.25">
@@ -46614,13 +46614,13 @@
         <v>2966</v>
       </c>
       <c r="F1418" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1418" s="2">
         <v>0</v>
       </c>
       <c r="H1418" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1419" spans="1:8" x14ac:dyDescent="0.25">
@@ -46666,13 +46666,13 @@
         <v>2854</v>
       </c>
       <c r="F1420" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1420" s="2">
         <v>0</v>
       </c>
       <c r="H1420" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1421" spans="1:8" x14ac:dyDescent="0.25">
@@ -46874,13 +46874,13 @@
         <v>2845</v>
       </c>
       <c r="F1428" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G1428" s="2">
         <v>0</v>
       </c>
       <c r="H1428" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1429" spans="1:8" x14ac:dyDescent="0.25">
@@ -46952,13 +46952,13 @@
         <v>2860</v>
       </c>
       <c r="F1431" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1431" s="2">
         <v>0</v>
       </c>
       <c r="H1431" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1432" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK SRB.xlsx
+++ b/STOK DEALER/STOK SRB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data D\2026\UPADTE TOOLS BUNDLING SRB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{76E587BC-8E6B-4850-BFD4-C05BBFBD1E8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AB69D3E-FC08-4703-B19D-9C39DEE75F19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -13467,13 +13467,13 @@
         <v>284</v>
       </c>
       <c r="F141" s="2">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="G141" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H141" s="2">
-        <v>72</v>
+        <v>68</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.15">
@@ -13649,13 +13649,13 @@
         <v>303</v>
       </c>
       <c r="F148" s="2">
-        <v>249</v>
+        <v>237</v>
       </c>
       <c r="G148" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="H148" s="2">
-        <v>243</v>
+        <v>233</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.15">
@@ -13909,13 +13909,13 @@
         <v>284</v>
       </c>
       <c r="F158" s="2">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="G158" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H158" s="2">
-        <v>103</v>
+        <v>101</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.15">
@@ -13935,13 +13935,13 @@
         <v>303</v>
       </c>
       <c r="F159" s="2">
-        <v>557</v>
+        <v>555</v>
       </c>
       <c r="G159" s="2">
-        <v>8</v>
+        <v>20</v>
       </c>
       <c r="H159" s="2">
-        <v>549</v>
+        <v>535</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.15">
@@ -14091,13 +14091,13 @@
         <v>334</v>
       </c>
       <c r="F165" s="2">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="G165" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H165" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.15">
@@ -14247,13 +14247,13 @@
         <v>350</v>
       </c>
       <c r="F171" s="2">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G171" s="2">
         <v>4</v>
       </c>
       <c r="H171" s="2">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.15">
@@ -16850,10 +16850,10 @@
         <v>22</v>
       </c>
       <c r="G271" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="H271" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="272" spans="1:8" x14ac:dyDescent="0.15">
@@ -17032,10 +17032,10 @@
         <v>2</v>
       </c>
       <c r="G278" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H278" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="279" spans="1:8" x14ac:dyDescent="0.15">
@@ -23397,13 +23397,13 @@
         <v>1108</v>
       </c>
       <c r="F523" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G523" s="2">
         <v>0</v>
       </c>
       <c r="H523" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="524" spans="1:8" x14ac:dyDescent="0.15">
@@ -24254,10 +24254,10 @@
         <v>29</v>
       </c>
       <c r="G556" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H556" s="2">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="557" spans="1:8" x14ac:dyDescent="0.15">
@@ -26591,13 +26591,13 @@
         <v>1351</v>
       </c>
       <c r="F646" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G646" s="2">
         <v>3</v>
       </c>
       <c r="H646" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="647" spans="1:8" x14ac:dyDescent="0.15">
@@ -27007,13 +27007,13 @@
         <v>1378</v>
       </c>
       <c r="F662" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G662" s="2">
         <v>6</v>
       </c>
       <c r="H662" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="663" spans="1:8" x14ac:dyDescent="0.15">
@@ -30673,13 +30673,13 @@
         <v>1706</v>
       </c>
       <c r="F803" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G803" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H803" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="804" spans="1:8" x14ac:dyDescent="0.15">
@@ -31820,10 +31820,10 @@
         <v>3</v>
       </c>
       <c r="G847" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H847" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="848" spans="1:8" x14ac:dyDescent="0.15">
@@ -36755,13 +36755,13 @@
         <v>250</v>
       </c>
       <c r="F1037" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1037" s="2">
         <v>0</v>
       </c>
       <c r="H1037" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1038" spans="1:8" x14ac:dyDescent="0.15">
@@ -37509,13 +37509,13 @@
         <v>1893</v>
       </c>
       <c r="F1066" s="2">
-        <v>98</v>
+        <v>93</v>
       </c>
       <c r="G1066" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H1066" s="2">
-        <v>98</v>
+        <v>91</v>
       </c>
     </row>
     <row r="1067" spans="1:8" x14ac:dyDescent="0.15">
@@ -40109,13 +40109,13 @@
         <v>2338</v>
       </c>
       <c r="F1166" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G1166" s="2">
         <v>0</v>
       </c>
       <c r="H1166" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1167" spans="1:8" x14ac:dyDescent="0.15">
@@ -40161,13 +40161,13 @@
         <v>2355</v>
       </c>
       <c r="F1168" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G1168" s="2">
         <v>0</v>
       </c>
       <c r="H1168" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1169" spans="1:8" x14ac:dyDescent="0.15">
@@ -42813,13 +42813,13 @@
         <v>2633</v>
       </c>
       <c r="F1270" s="2">
-        <v>34</v>
+        <v>29</v>
       </c>
       <c r="G1270" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1270" s="2">
-        <v>34</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1271" spans="1:8" x14ac:dyDescent="0.15">
@@ -42839,13 +42839,13 @@
         <v>2633</v>
       </c>
       <c r="F1271" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1271" s="2">
         <v>0</v>
       </c>
       <c r="H1271" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1272" spans="1:8" x14ac:dyDescent="0.15">
@@ -43749,13 +43749,13 @@
         <v>2728</v>
       </c>
       <c r="F1306" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1306" s="2">
         <v>0</v>
       </c>
       <c r="H1306" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1307" spans="1:8" x14ac:dyDescent="0.15">
@@ -46453,13 +46453,13 @@
         <v>2681</v>
       </c>
       <c r="F1410" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1410" s="2">
         <v>0</v>
       </c>
       <c r="H1410" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1411" spans="1:8" x14ac:dyDescent="0.15">

--- a/STOK DEALER/STOK SRB.xlsx
+++ b/STOK DEALER/STOK SRB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data D\2026\UPADTE TOOLS BUNDLING SRB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AB69D3E-FC08-4703-B19D-9C39DEE75F19}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22B54D9A-BF7B-4B9E-ABAC-4FF35B28CFB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9961,13 +9961,13 @@
         <v>20</v>
       </c>
       <c r="F6" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G6" s="2">
         <v>0</v>
       </c>
       <c r="H6" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.15">
@@ -10117,10 +10117,10 @@
         <v>35</v>
       </c>
       <c r="F12" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H12" s="2">
         <v>0</v>
@@ -10559,13 +10559,13 @@
         <v>67</v>
       </c>
       <c r="F29" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G29" s="2">
         <v>1</v>
       </c>
       <c r="H29" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.15">
@@ -11469,13 +11469,13 @@
         <v>114</v>
       </c>
       <c r="F64" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G64" s="2">
         <v>1</v>
       </c>
       <c r="H64" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.15">
@@ -13467,10 +13467,10 @@
         <v>284</v>
       </c>
       <c r="F141" s="2">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="G141" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H141" s="2">
         <v>68</v>
@@ -13493,13 +13493,13 @@
         <v>287</v>
       </c>
       <c r="F142" s="2">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G142" s="2">
         <v>5</v>
       </c>
       <c r="H142" s="2">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.15">
@@ -13649,13 +13649,13 @@
         <v>303</v>
       </c>
       <c r="F148" s="2">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="G148" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H148" s="2">
-        <v>233</v>
+        <v>226</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.15">
@@ -13909,13 +13909,13 @@
         <v>284</v>
       </c>
       <c r="F158" s="2">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="G158" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H158" s="2">
-        <v>101</v>
+        <v>96</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.15">
@@ -13935,13 +13935,13 @@
         <v>303</v>
       </c>
       <c r="F159" s="2">
-        <v>555</v>
+        <v>532</v>
       </c>
       <c r="G159" s="2">
-        <v>20</v>
+        <v>8</v>
       </c>
       <c r="H159" s="2">
-        <v>535</v>
+        <v>524</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.15">
@@ -14016,10 +14016,10 @@
         <v>11</v>
       </c>
       <c r="G162" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H162" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.15">
@@ -14091,13 +14091,13 @@
         <v>334</v>
       </c>
       <c r="F165" s="2">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="G165" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H165" s="2">
-        <v>188</v>
+        <v>179</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.15">
@@ -14247,13 +14247,13 @@
         <v>350</v>
       </c>
       <c r="F171" s="2">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="G171" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H171" s="2">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.15">
@@ -15313,13 +15313,13 @@
         <v>445</v>
       </c>
       <c r="F212" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G212" s="2">
         <v>0</v>
       </c>
       <c r="H212" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.15">
@@ -16847,13 +16847,13 @@
         <v>584</v>
       </c>
       <c r="F271" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G271" s="2">
         <v>8</v>
       </c>
       <c r="H271" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="272" spans="1:8" x14ac:dyDescent="0.15">
@@ -19970,10 +19970,10 @@
         <v>1</v>
       </c>
       <c r="G391" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H391" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="392" spans="1:8" x14ac:dyDescent="0.15">
@@ -20487,13 +20487,13 @@
         <v>878</v>
       </c>
       <c r="F411" s="2">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="G411" s="2">
         <v>2</v>
       </c>
       <c r="H411" s="2">
-        <v>17</v>
+        <v>2</v>
       </c>
     </row>
     <row r="412" spans="1:8" x14ac:dyDescent="0.15">
@@ -20539,13 +20539,13 @@
         <v>883</v>
       </c>
       <c r="F413" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G413" s="2">
         <v>5</v>
       </c>
       <c r="H413" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="414" spans="1:8" x14ac:dyDescent="0.15">
@@ -20929,13 +20929,13 @@
         <v>905</v>
       </c>
       <c r="F428" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G428" s="2">
         <v>0</v>
       </c>
       <c r="H428" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="429" spans="1:8" x14ac:dyDescent="0.15">
@@ -22773,13 +22773,13 @@
         <v>1036</v>
       </c>
       <c r="F499" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G499" s="2">
         <v>0</v>
       </c>
       <c r="H499" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="500" spans="1:8" x14ac:dyDescent="0.15">
@@ -22929,13 +22929,13 @@
         <v>1071</v>
       </c>
       <c r="F505" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G505" s="2">
         <v>0</v>
       </c>
       <c r="H505" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="506" spans="1:8" x14ac:dyDescent="0.15">
@@ -23759,13 +23759,13 @@
         <v>1136</v>
       </c>
       <c r="F537" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G537" s="2">
         <v>0</v>
       </c>
       <c r="H537" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="538" spans="1:8" x14ac:dyDescent="0.15">
@@ -24251,13 +24251,13 @@
         <v>1172</v>
       </c>
       <c r="F556" s="2">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="G556" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H556" s="2">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="557" spans="1:8" x14ac:dyDescent="0.15">
@@ -24537,13 +24537,13 @@
         <v>1196</v>
       </c>
       <c r="F567" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G567" s="2">
         <v>0</v>
       </c>
       <c r="H567" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="568" spans="1:8" x14ac:dyDescent="0.15">
@@ -24745,13 +24745,13 @@
         <v>1210</v>
       </c>
       <c r="F575" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G575" s="2">
         <v>1</v>
       </c>
       <c r="H575" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="576" spans="1:8" x14ac:dyDescent="0.15">
@@ -26981,13 +26981,13 @@
         <v>1299</v>
       </c>
       <c r="F661" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G661" s="2">
         <v>1</v>
       </c>
       <c r="H661" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="662" spans="1:8" x14ac:dyDescent="0.15">
@@ -27007,13 +27007,13 @@
         <v>1378</v>
       </c>
       <c r="F662" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G662" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H662" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="663" spans="1:8" x14ac:dyDescent="0.15">
@@ -28437,13 +28437,13 @@
         <v>1517</v>
       </c>
       <c r="F717" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G717" s="2">
         <v>0</v>
       </c>
       <c r="H717" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="718" spans="1:8" x14ac:dyDescent="0.15">
@@ -28567,13 +28567,13 @@
         <v>1529</v>
       </c>
       <c r="F722" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G722" s="2">
         <v>0</v>
       </c>
       <c r="H722" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="723" spans="1:8" x14ac:dyDescent="0.15">
@@ -28671,13 +28671,13 @@
         <v>1517</v>
       </c>
       <c r="F726" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G726" s="2">
         <v>0</v>
       </c>
       <c r="H726" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="727" spans="1:8" x14ac:dyDescent="0.15">
@@ -30364,10 +30364,10 @@
         <v>4</v>
       </c>
       <c r="G791" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H791" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="792" spans="1:8" x14ac:dyDescent="0.15">
@@ -30673,10 +30673,10 @@
         <v>1706</v>
       </c>
       <c r="F803" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G803" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H803" s="2">
         <v>4</v>
@@ -31141,13 +31141,13 @@
         <v>1743</v>
       </c>
       <c r="F821" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G821" s="2">
         <v>0</v>
       </c>
       <c r="H821" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="822" spans="1:8" x14ac:dyDescent="0.15">
@@ -32493,13 +32493,13 @@
         <v>1844</v>
       </c>
       <c r="F873" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G873" s="2">
         <v>0</v>
       </c>
       <c r="H873" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="874" spans="1:8" x14ac:dyDescent="0.15">
@@ -34649,13 +34649,13 @@
         <v>1647</v>
       </c>
       <c r="F956" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G956" s="2">
         <v>0</v>
       </c>
       <c r="H956" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="957" spans="1:8" x14ac:dyDescent="0.15">
@@ -34805,13 +34805,13 @@
         <v>2025</v>
       </c>
       <c r="F962" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G962" s="2">
         <v>0</v>
       </c>
       <c r="H962" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="963" spans="1:8" x14ac:dyDescent="0.15">
@@ -37509,13 +37509,13 @@
         <v>1893</v>
       </c>
       <c r="F1066" s="2">
-        <v>93</v>
+        <v>87</v>
       </c>
       <c r="G1066" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H1066" s="2">
-        <v>91</v>
+        <v>87</v>
       </c>
     </row>
     <row r="1067" spans="1:8" x14ac:dyDescent="0.15">
@@ -39173,13 +39173,13 @@
         <v>2361</v>
       </c>
       <c r="F1130" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1130" s="2">
         <v>0</v>
       </c>
       <c r="H1130" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1131" spans="1:8" x14ac:dyDescent="0.15">
@@ -39381,13 +39381,13 @@
         <v>2352</v>
       </c>
       <c r="F1138" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1138" s="2">
         <v>0</v>
       </c>
       <c r="H1138" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1139" spans="1:8" x14ac:dyDescent="0.15">
@@ -40083,13 +40083,13 @@
         <v>2355</v>
       </c>
       <c r="F1165" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1165" s="2">
         <v>0</v>
       </c>
       <c r="H1165" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1166" spans="1:8" x14ac:dyDescent="0.15">
@@ -40161,13 +40161,13 @@
         <v>2355</v>
       </c>
       <c r="F1168" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1168" s="2">
         <v>0</v>
       </c>
       <c r="H1168" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1169" spans="1:8" x14ac:dyDescent="0.15">
@@ -41981,13 +41981,13 @@
         <v>2580</v>
       </c>
       <c r="F1238" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1238" s="2">
         <v>0</v>
       </c>
       <c r="H1238" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1239" spans="1:8" x14ac:dyDescent="0.15">
@@ -42267,13 +42267,13 @@
         <v>665</v>
       </c>
       <c r="F1249" s="2">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="G1249" s="2">
         <v>0</v>
       </c>
       <c r="H1249" s="2">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="1250" spans="1:8" x14ac:dyDescent="0.15">
@@ -42579,13 +42579,13 @@
         <v>1237</v>
       </c>
       <c r="F1261" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G1261" s="2">
         <v>0</v>
       </c>
       <c r="H1261" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1262" spans="1:8" x14ac:dyDescent="0.15">
@@ -42813,13 +42813,13 @@
         <v>2633</v>
       </c>
       <c r="F1270" s="2">
-        <v>29</v>
+        <v>24</v>
       </c>
       <c r="G1270" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1270" s="2">
-        <v>28</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1271" spans="1:8" x14ac:dyDescent="0.15">
@@ -45569,13 +45569,13 @@
         <v>2882</v>
       </c>
       <c r="F1376" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G1376" s="2">
         <v>0</v>
       </c>
       <c r="H1376" s="2">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1377" spans="1:8" x14ac:dyDescent="0.15">
@@ -46739,13 +46739,13 @@
         <v>2757</v>
       </c>
       <c r="F1421" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G1421" s="2">
         <v>0</v>
       </c>
       <c r="H1421" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="1422" spans="1:8" x14ac:dyDescent="0.15">
@@ -46765,13 +46765,13 @@
         <v>2882</v>
       </c>
       <c r="F1422" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1422" s="2">
         <v>0</v>
       </c>
       <c r="H1422" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1423" spans="1:8" x14ac:dyDescent="0.15">
@@ -48367,13 +48367,13 @@
       <c r="D1484" s="6"/>
       <c r="E1484" s="7"/>
       <c r="F1484" s="3">
-        <v>5120</v>
+        <v>4955</v>
       </c>
       <c r="G1484" s="4">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="H1484" s="3">
-        <v>4992</v>
+        <v>4828</v>
       </c>
     </row>
   </sheetData>

--- a/STOK DEALER/STOK SRB.xlsx
+++ b/STOK DEALER/STOK SRB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data D\2026\UPADTE TOOLS BUNDLING SRB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{22B54D9A-BF7B-4B9E-ABAC-4FF35B28CFB2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{937D0C68-DE1B-4391-A573-A37AE882C7BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9857,13 +9857,13 @@
         <v>11</v>
       </c>
       <c r="F2" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G2" s="2">
         <v>0</v>
       </c>
       <c r="H2" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.15">
@@ -9883,13 +9883,13 @@
         <v>14</v>
       </c>
       <c r="F3" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G3" s="2">
         <v>0</v>
       </c>
       <c r="H3" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.15">
@@ -10013,13 +10013,13 @@
         <v>20</v>
       </c>
       <c r="F8" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G8" s="2">
         <v>0</v>
       </c>
       <c r="H8" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.15">
@@ -11079,13 +11079,13 @@
         <v>110</v>
       </c>
       <c r="F49" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G49" s="2">
         <v>0</v>
       </c>
       <c r="H49" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.15">
@@ -11469,13 +11469,13 @@
         <v>114</v>
       </c>
       <c r="F64" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G64" s="2">
         <v>1</v>
       </c>
       <c r="H64" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.15">
@@ -13470,10 +13470,10 @@
         <v>70</v>
       </c>
       <c r="G141" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H141" s="2">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.15">
@@ -13496,10 +13496,10 @@
         <v>135</v>
       </c>
       <c r="G142" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H142" s="2">
-        <v>130</v>
+        <v>128</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.15">
@@ -13652,10 +13652,10 @@
         <v>228</v>
       </c>
       <c r="G148" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H148" s="2">
-        <v>226</v>
+        <v>225</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.15">
@@ -13909,13 +13909,13 @@
         <v>284</v>
       </c>
       <c r="F158" s="2">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="G158" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="H158" s="2">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.15">
@@ -13935,13 +13935,13 @@
         <v>303</v>
       </c>
       <c r="F159" s="2">
-        <v>532</v>
+        <v>527</v>
       </c>
       <c r="G159" s="2">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="H159" s="2">
-        <v>524</v>
+        <v>516</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.15">
@@ -14091,13 +14091,13 @@
         <v>334</v>
       </c>
       <c r="F165" s="2">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G165" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H165" s="2">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.15">
@@ -20487,13 +20487,13 @@
         <v>878</v>
       </c>
       <c r="F411" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G411" s="2">
         <v>2</v>
       </c>
       <c r="H411" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="412" spans="1:8" x14ac:dyDescent="0.15">
@@ -20643,13 +20643,13 @@
         <v>892</v>
       </c>
       <c r="F417" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G417" s="2">
         <v>0</v>
       </c>
       <c r="H417" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="418" spans="1:8" x14ac:dyDescent="0.15">
@@ -24251,13 +24251,13 @@
         <v>1172</v>
       </c>
       <c r="F556" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G556" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H556" s="2">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="557" spans="1:8" x14ac:dyDescent="0.15">
@@ -26750,10 +26750,10 @@
         <v>7</v>
       </c>
       <c r="G652" s="2">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H652" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="653" spans="1:8" x14ac:dyDescent="0.15">
@@ -27007,13 +27007,13 @@
         <v>1378</v>
       </c>
       <c r="F662" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G662" s="2">
         <v>5</v>
       </c>
       <c r="H662" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="663" spans="1:8" x14ac:dyDescent="0.15">
@@ -28674,10 +28674,10 @@
         <v>2</v>
       </c>
       <c r="G726" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H726" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="727" spans="1:8" x14ac:dyDescent="0.15">
@@ -31323,13 +31323,13 @@
         <v>1760</v>
       </c>
       <c r="F828" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G828" s="2">
         <v>0</v>
       </c>
       <c r="H828" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="829" spans="1:8" x14ac:dyDescent="0.15">
@@ -34649,13 +34649,13 @@
         <v>1647</v>
       </c>
       <c r="F956" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G956" s="2">
         <v>0</v>
       </c>
       <c r="H956" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="957" spans="1:8" x14ac:dyDescent="0.15">
@@ -34753,13 +34753,13 @@
         <v>2008</v>
       </c>
       <c r="F960" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G960" s="2">
         <v>0</v>
       </c>
       <c r="H960" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="961" spans="1:8" x14ac:dyDescent="0.15">
@@ -34831,13 +34831,13 @@
         <v>2028</v>
       </c>
       <c r="F963" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G963" s="2">
         <v>0</v>
       </c>
       <c r="H963" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="964" spans="1:8" x14ac:dyDescent="0.15">
@@ -37509,13 +37509,13 @@
         <v>1893</v>
       </c>
       <c r="F1066" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
       <c r="G1066" s="2">
         <v>0</v>
       </c>
       <c r="H1066" s="2">
-        <v>87</v>
+        <v>80</v>
       </c>
     </row>
     <row r="1067" spans="1:8" x14ac:dyDescent="0.15">
@@ -38575,13 +38575,13 @@
         <v>1477</v>
       </c>
       <c r="F1107" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G1107" s="2">
         <v>0</v>
       </c>
       <c r="H1107" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1108" spans="1:8" x14ac:dyDescent="0.15">
@@ -39433,13 +39433,13 @@
         <v>2374</v>
       </c>
       <c r="F1140" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G1140" s="2">
         <v>0</v>
       </c>
       <c r="H1140" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="1141" spans="1:8" x14ac:dyDescent="0.15">
@@ -40161,13 +40161,13 @@
         <v>2355</v>
       </c>
       <c r="F1168" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1168" s="2">
         <v>0</v>
       </c>
       <c r="H1168" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1169" spans="1:8" x14ac:dyDescent="0.15">
@@ -40213,13 +40213,13 @@
         <v>2355</v>
       </c>
       <c r="F1170" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1170" s="2">
         <v>0</v>
       </c>
       <c r="H1170" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1171" spans="1:8" x14ac:dyDescent="0.15">
@@ -41022,10 +41022,10 @@
         <v>2</v>
       </c>
       <c r="G1201" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1201" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1202" spans="1:8" x14ac:dyDescent="0.15">
@@ -41100,10 +41100,10 @@
         <v>2</v>
       </c>
       <c r="G1204" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1204" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1205" spans="1:8" x14ac:dyDescent="0.15">
@@ -42634,10 +42634,10 @@
         <v>22</v>
       </c>
       <c r="G1263" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1263" s="2">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1264" spans="1:8" x14ac:dyDescent="0.15">
@@ -42813,13 +42813,13 @@
         <v>2633</v>
       </c>
       <c r="F1270" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G1270" s="2">
         <v>0</v>
       </c>
       <c r="H1270" s="2">
-        <v>24</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1271" spans="1:8" x14ac:dyDescent="0.15">
@@ -44945,13 +44945,13 @@
         <v>2825</v>
       </c>
       <c r="F1352" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G1352" s="2">
         <v>0</v>
       </c>
       <c r="H1352" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1353" spans="1:8" x14ac:dyDescent="0.15">
@@ -46505,13 +46505,13 @@
         <v>2692</v>
       </c>
       <c r="F1412" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G1412" s="2">
         <v>0</v>
       </c>
       <c r="H1412" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1413" spans="1:8" x14ac:dyDescent="0.15">
@@ -47103,13 +47103,13 @@
         <v>2698</v>
       </c>
       <c r="F1435" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1435" s="2">
         <v>0</v>
       </c>
       <c r="H1435" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1436" spans="1:8" x14ac:dyDescent="0.15">
@@ -47288,10 +47288,10 @@
         <v>1</v>
       </c>
       <c r="G1442" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1442" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1443" spans="1:8" x14ac:dyDescent="0.15">
@@ -47860,10 +47860,10 @@
         <v>36</v>
       </c>
       <c r="G1464" s="2">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="H1464" s="2">
-        <v>33</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1465" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">

--- a/STOK DEALER/STOK SRB.xlsx
+++ b/STOK DEALER/STOK SRB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data D\2026\UPADTE TOOLS BUNDLING SRB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{937D0C68-DE1B-4391-A573-A37AE882C7BF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85180E12-21E8-4417-88DB-95105276C4D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9883,13 +9883,13 @@
         <v>14</v>
       </c>
       <c r="F3" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G3" s="2">
         <v>0</v>
       </c>
       <c r="H3" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.15">
@@ -9938,10 +9938,10 @@
         <v>3</v>
       </c>
       <c r="G5" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H5" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.15">
@@ -11079,13 +11079,13 @@
         <v>110</v>
       </c>
       <c r="F49" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G49" s="2">
         <v>0</v>
       </c>
       <c r="H49" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.15">
@@ -11469,13 +11469,13 @@
         <v>114</v>
       </c>
       <c r="F64" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G64" s="2">
         <v>1</v>
       </c>
       <c r="H64" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="65" spans="1:8" x14ac:dyDescent="0.15">
@@ -13467,13 +13467,13 @@
         <v>284</v>
       </c>
       <c r="F141" s="2">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="G141" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="H141" s="2">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.15">
@@ -13493,13 +13493,13 @@
         <v>287</v>
       </c>
       <c r="F142" s="2">
-        <v>135</v>
+        <v>132</v>
       </c>
       <c r="G142" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H142" s="2">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.15">
@@ -13519,13 +13519,13 @@
         <v>287</v>
       </c>
       <c r="F143" s="2">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G143" s="2">
         <v>2</v>
       </c>
       <c r="H143" s="2">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.15">
@@ -13649,13 +13649,13 @@
         <v>303</v>
       </c>
       <c r="F148" s="2">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="G148" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H148" s="2">
-        <v>225</v>
+        <v>224</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.15">
@@ -13909,13 +13909,13 @@
         <v>284</v>
       </c>
       <c r="F158" s="2">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="G158" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="H158" s="2">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.15">
@@ -13935,13 +13935,13 @@
         <v>303</v>
       </c>
       <c r="F159" s="2">
-        <v>527</v>
+        <v>510</v>
       </c>
       <c r="G159" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="H159" s="2">
-        <v>516</v>
+        <v>501</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.15">
@@ -14091,13 +14091,13 @@
         <v>334</v>
       </c>
       <c r="F165" s="2">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="G165" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H165" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.15">
@@ -15391,13 +15391,13 @@
         <v>452</v>
       </c>
       <c r="F215" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G215" s="2">
         <v>0</v>
       </c>
       <c r="H215" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.15">
@@ -20513,13 +20513,13 @@
         <v>881</v>
       </c>
       <c r="F412" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G412" s="2">
         <v>3</v>
       </c>
       <c r="H412" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="413" spans="1:8" x14ac:dyDescent="0.15">
@@ -22516,10 +22516,10 @@
         <v>5</v>
       </c>
       <c r="G489" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H489" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="490" spans="1:8" x14ac:dyDescent="0.15">
@@ -22932,10 +22932,10 @@
         <v>4</v>
       </c>
       <c r="G505" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H505" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="506" spans="1:8" x14ac:dyDescent="0.15">
@@ -24251,10 +24251,10 @@
         <v>1172</v>
       </c>
       <c r="F556" s="2">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G556" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H556" s="2">
         <v>23</v>
@@ -24407,13 +24407,13 @@
         <v>1187</v>
       </c>
       <c r="F562" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G562" s="2">
         <v>1</v>
       </c>
       <c r="H562" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="563" spans="1:8" x14ac:dyDescent="0.15">
@@ -24462,10 +24462,10 @@
         <v>2</v>
       </c>
       <c r="G564" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H564" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="565" spans="1:8" x14ac:dyDescent="0.15">
@@ -24615,13 +24615,13 @@
         <v>1201</v>
       </c>
       <c r="F570" s="2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G570" s="2">
         <v>1</v>
       </c>
       <c r="H570" s="2">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="571" spans="1:8" x14ac:dyDescent="0.15">
@@ -26594,10 +26594,10 @@
         <v>12</v>
       </c>
       <c r="G646" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H646" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="647" spans="1:8" x14ac:dyDescent="0.15">
@@ -26747,13 +26747,13 @@
         <v>1351</v>
       </c>
       <c r="F652" s="2">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="G652" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H652" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="653" spans="1:8" x14ac:dyDescent="0.15">
@@ -27007,13 +27007,13 @@
         <v>1378</v>
       </c>
       <c r="F662" s="2">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G662" s="2">
         <v>5</v>
       </c>
       <c r="H662" s="2">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="663" spans="1:8" x14ac:dyDescent="0.15">
@@ -27712,10 +27712,10 @@
         <v>15</v>
       </c>
       <c r="G689" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H689" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="690" spans="1:8" x14ac:dyDescent="0.15">
@@ -28050,10 +28050,10 @@
         <v>20</v>
       </c>
       <c r="G702" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H702" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="703" spans="1:8" x14ac:dyDescent="0.15">
@@ -32496,10 +32496,10 @@
         <v>1</v>
       </c>
       <c r="G873" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H873" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="874" spans="1:8" x14ac:dyDescent="0.15">
@@ -33739,13 +33739,13 @@
         <v>380</v>
       </c>
       <c r="F921" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G921" s="2">
         <v>0</v>
       </c>
       <c r="H921" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="922" spans="1:8" x14ac:dyDescent="0.15">
@@ -34649,13 +34649,13 @@
         <v>1647</v>
       </c>
       <c r="F956" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G956" s="2">
         <v>0</v>
       </c>
       <c r="H956" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="957" spans="1:8" x14ac:dyDescent="0.15">
@@ -34753,13 +34753,13 @@
         <v>2008</v>
       </c>
       <c r="F960" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G960" s="2">
         <v>0</v>
       </c>
       <c r="H960" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="961" spans="1:8" x14ac:dyDescent="0.15">
@@ -34834,10 +34834,10 @@
         <v>5</v>
       </c>
       <c r="G963" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H963" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="964" spans="1:8" x14ac:dyDescent="0.15">
@@ -36755,13 +36755,13 @@
         <v>250</v>
       </c>
       <c r="F1037" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1037" s="2">
         <v>0</v>
       </c>
       <c r="H1037" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1038" spans="1:8" x14ac:dyDescent="0.15">
@@ -37509,13 +37509,13 @@
         <v>1893</v>
       </c>
       <c r="F1066" s="2">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="G1066" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1066" s="2">
-        <v>80</v>
+        <v>71</v>
       </c>
     </row>
     <row r="1067" spans="1:8" x14ac:dyDescent="0.15">
@@ -38731,13 +38731,13 @@
         <v>383</v>
       </c>
       <c r="F1113" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G1113" s="2">
         <v>0</v>
       </c>
       <c r="H1113" s="2">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1114" spans="1:8" x14ac:dyDescent="0.15">
@@ -39228,10 +39228,10 @@
         <v>4</v>
       </c>
       <c r="G1132" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1132" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1133" spans="1:8" x14ac:dyDescent="0.15">
@@ -40031,13 +40031,13 @@
         <v>2358</v>
       </c>
       <c r="F1163" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1163" s="2">
         <v>0</v>
       </c>
       <c r="H1163" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1164" spans="1:8" x14ac:dyDescent="0.15">
@@ -40187,13 +40187,13 @@
         <v>2251</v>
       </c>
       <c r="F1169" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G1169" s="2">
         <v>0</v>
       </c>
       <c r="H1169" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1170" spans="1:8" x14ac:dyDescent="0.15">
@@ -41591,13 +41591,13 @@
         <v>1372</v>
       </c>
       <c r="F1223" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1223" s="2">
         <v>1</v>
       </c>
       <c r="H1223" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1224" spans="1:8" x14ac:dyDescent="0.15">
@@ -41903,13 +41903,13 @@
         <v>2580</v>
       </c>
       <c r="F1235" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G1235" s="2">
         <v>0</v>
       </c>
       <c r="H1235" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1236" spans="1:8" x14ac:dyDescent="0.15">
@@ -42657,13 +42657,13 @@
         <v>2629</v>
       </c>
       <c r="F1264" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1264" s="2">
         <v>0</v>
       </c>
       <c r="H1264" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1265" spans="1:8" x14ac:dyDescent="0.15">
@@ -42813,13 +42813,13 @@
         <v>2633</v>
       </c>
       <c r="F1270" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G1270" s="2">
         <v>0</v>
       </c>
       <c r="H1270" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1271" spans="1:8" x14ac:dyDescent="0.15">
@@ -44425,13 +44425,13 @@
         <v>2782</v>
       </c>
       <c r="F1332" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1332" s="2">
         <v>0</v>
       </c>
       <c r="H1332" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1333" spans="1:8" x14ac:dyDescent="0.15">
@@ -45959,13 +45959,13 @@
         <v>2782</v>
       </c>
       <c r="F1391" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1391" s="2">
         <v>0</v>
       </c>
       <c r="H1391" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1392" spans="1:8" x14ac:dyDescent="0.15">
@@ -46453,13 +46453,13 @@
         <v>2681</v>
       </c>
       <c r="F1410" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1410" s="2">
         <v>0</v>
       </c>
       <c r="H1410" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1411" spans="1:8" x14ac:dyDescent="0.15">
@@ -46791,13 +46791,13 @@
         <v>2922</v>
       </c>
       <c r="F1423" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G1423" s="2">
         <v>0</v>
       </c>
       <c r="H1423" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="1424" spans="1:8" x14ac:dyDescent="0.15">
@@ -48274,10 +48274,10 @@
         <v>4</v>
       </c>
       <c r="G1480" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1480" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1481" spans="1:8" x14ac:dyDescent="0.15">

--- a/STOK DEALER/STOK SRB.xlsx
+++ b/STOK DEALER/STOK SRB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data D\2026\UPADTE TOOLS BUNDLING SRB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85180E12-21E8-4417-88DB-95105276C4D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8ABD6870-D844-4EBB-B2C7-AE0A2F88251E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -9935,10 +9935,10 @@
         <v>20</v>
       </c>
       <c r="F5" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G5" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H5" s="2">
         <v>2</v>
@@ -10039,13 +10039,13 @@
         <v>29</v>
       </c>
       <c r="F9" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G9" s="2">
         <v>0</v>
       </c>
       <c r="H9" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.15">
@@ -13467,13 +13467,13 @@
         <v>284</v>
       </c>
       <c r="F141" s="2">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="G141" s="2">
         <v>2</v>
       </c>
       <c r="H141" s="2">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.15">
@@ -13493,13 +13493,13 @@
         <v>287</v>
       </c>
       <c r="F142" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G142" s="2">
         <v>5</v>
       </c>
       <c r="H142" s="2">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.15">
@@ -13909,13 +13909,13 @@
         <v>284</v>
       </c>
       <c r="F158" s="2">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G158" s="2">
         <v>6</v>
       </c>
       <c r="H158" s="2">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.15">
@@ -13935,13 +13935,13 @@
         <v>303</v>
       </c>
       <c r="F159" s="2">
-        <v>510</v>
+        <v>494</v>
       </c>
       <c r="G159" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="H159" s="2">
-        <v>501</v>
+        <v>486</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.15">
@@ -14091,13 +14091,13 @@
         <v>334</v>
       </c>
       <c r="F165" s="2">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="G165" s="2">
         <v>3</v>
       </c>
       <c r="H165" s="2">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.15">
@@ -15339,13 +15339,13 @@
         <v>442</v>
       </c>
       <c r="F213" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G213" s="2">
         <v>0</v>
       </c>
       <c r="H213" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.15">
@@ -26591,13 +26591,13 @@
         <v>1351</v>
       </c>
       <c r="F646" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G646" s="2">
         <v>4</v>
       </c>
       <c r="H646" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="647" spans="1:8" x14ac:dyDescent="0.15">
@@ -26903,13 +26903,13 @@
         <v>1378</v>
       </c>
       <c r="F658" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G658" s="2">
         <v>0</v>
       </c>
       <c r="H658" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="659" spans="1:8" x14ac:dyDescent="0.15">
@@ -27709,10 +27709,10 @@
         <v>353</v>
       </c>
       <c r="F689" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G689" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H689" s="2">
         <v>14</v>
@@ -28047,10 +28047,10 @@
         <v>1477</v>
       </c>
       <c r="F702" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G702" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H702" s="2">
         <v>19</v>
@@ -33661,13 +33661,13 @@
         <v>14</v>
       </c>
       <c r="F918" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G918" s="2">
         <v>0</v>
       </c>
       <c r="H918" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="919" spans="1:8" x14ac:dyDescent="0.15">
@@ -34649,13 +34649,13 @@
         <v>1647</v>
       </c>
       <c r="F956" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G956" s="2">
         <v>0</v>
       </c>
       <c r="H956" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="957" spans="1:8" x14ac:dyDescent="0.15">
@@ -34831,13 +34831,13 @@
         <v>2028</v>
       </c>
       <c r="F963" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G963" s="2">
         <v>1</v>
       </c>
       <c r="H963" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="964" spans="1:8" x14ac:dyDescent="0.15">
@@ -37509,13 +37509,13 @@
         <v>1893</v>
       </c>
       <c r="F1066" s="2">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="G1066" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1066" s="2">
-        <v>71</v>
+        <v>69</v>
       </c>
     </row>
     <row r="1067" spans="1:8" x14ac:dyDescent="0.15">
@@ -38578,10 +38578,10 @@
         <v>7</v>
       </c>
       <c r="G1107" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1107" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1108" spans="1:8" x14ac:dyDescent="0.15">
@@ -39043,13 +39043,13 @@
         <v>2355</v>
       </c>
       <c r="F1125" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1125" s="2">
         <v>0</v>
       </c>
       <c r="H1125" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1126" spans="1:8" x14ac:dyDescent="0.15">
@@ -39225,10 +39225,10 @@
         <v>2355</v>
       </c>
       <c r="F1132" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1132" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1132" s="2">
         <v>3</v>
@@ -41877,13 +41877,13 @@
         <v>292</v>
       </c>
       <c r="F1234" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G1234" s="2">
         <v>2</v>
       </c>
       <c r="H1234" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="1235" spans="1:8" x14ac:dyDescent="0.15">
@@ -42267,13 +42267,13 @@
         <v>665</v>
       </c>
       <c r="F1249" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="G1249" s="2">
         <v>0</v>
       </c>
       <c r="H1249" s="2">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="1250" spans="1:8" x14ac:dyDescent="0.15">
@@ -43827,13 +43827,13 @@
         <v>2717</v>
       </c>
       <c r="F1309" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G1309" s="2">
         <v>0</v>
       </c>
       <c r="H1309" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1310" spans="1:8" x14ac:dyDescent="0.15">
@@ -45569,13 +45569,13 @@
         <v>2882</v>
       </c>
       <c r="F1376" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G1376" s="2">
         <v>0</v>
       </c>
       <c r="H1376" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1377" spans="1:8" x14ac:dyDescent="0.15">
@@ -46739,13 +46739,13 @@
         <v>2757</v>
       </c>
       <c r="F1421" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G1421" s="2">
         <v>0</v>
       </c>
       <c r="H1421" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1422" spans="1:8" x14ac:dyDescent="0.15">
@@ -48271,10 +48271,10 @@
         <v>88</v>
       </c>
       <c r="F1480" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1480" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1480" s="2">
         <v>3</v>

--- a/STOK DEALER/STOK SRB.xlsx
+++ b/STOK DEALER/STOK SRB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{90A29844-F688-4F97-BD84-1EAD02F4E3DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6495B427-BC0C-4955-AC98-5436195372E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{46E7093F-A843-4D56-8D6E-D290D3117D3B}"/>
   </bookViews>
@@ -9869,13 +9869,13 @@
         <v>1625</v>
       </c>
       <c r="F3" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G3" s="2">
         <v>0</v>
       </c>
       <c r="H3" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.25">
@@ -10025,13 +10025,13 @@
         <v>1628</v>
       </c>
       <c r="F9" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G9" s="2">
         <v>0</v>
       </c>
       <c r="H9" s="2">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -10051,13 +10051,13 @@
         <v>1629</v>
       </c>
       <c r="F10" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G10" s="2">
         <v>0</v>
       </c>
       <c r="H10" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.25">
@@ -10389,13 +10389,13 @@
         <v>1649</v>
       </c>
       <c r="F23" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G23" s="2">
         <v>0</v>
       </c>
       <c r="H23" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -11562,10 +11562,10 @@
         <v>7</v>
       </c>
       <c r="G68" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H68" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
@@ -13453,13 +13453,13 @@
         <v>1780</v>
       </c>
       <c r="F141" s="2">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="G141" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H141" s="2">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
@@ -13479,13 +13479,13 @@
         <v>1781</v>
       </c>
       <c r="F142" s="2">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="G142" s="2">
         <v>3</v>
       </c>
       <c r="H142" s="2">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
@@ -13505,13 +13505,13 @@
         <v>1781</v>
       </c>
       <c r="F143" s="2">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G143" s="2">
         <v>1</v>
       </c>
       <c r="H143" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
@@ -13635,10 +13635,10 @@
         <v>1789</v>
       </c>
       <c r="F148" s="2">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="G148" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H148" s="2">
         <v>295</v>
@@ -13895,13 +13895,13 @@
         <v>1780</v>
       </c>
       <c r="F158" s="2">
-        <v>183</v>
+        <v>176</v>
       </c>
       <c r="G158" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H158" s="2">
-        <v>174</v>
+        <v>169</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.25">
@@ -13921,13 +13921,13 @@
         <v>1789</v>
       </c>
       <c r="F159" s="2">
-        <v>510</v>
+        <v>503</v>
       </c>
       <c r="G159" s="2">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="H159" s="2">
-        <v>499</v>
+        <v>495</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.25">
@@ -14077,13 +14077,13 @@
         <v>207</v>
       </c>
       <c r="F165" s="2">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="G165" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H165" s="2">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.25">
@@ -14207,13 +14207,13 @@
         <v>1808</v>
       </c>
       <c r="F170" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G170" s="2">
         <v>0</v>
       </c>
       <c r="H170" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.25">
@@ -14389,13 +14389,13 @@
         <v>1816</v>
       </c>
       <c r="F177" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G177" s="2">
         <v>0</v>
       </c>
       <c r="H177" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="178" spans="1:8" x14ac:dyDescent="0.25">
@@ -14987,13 +14987,13 @@
         <v>1827</v>
       </c>
       <c r="F200" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G200" s="2">
         <v>0</v>
       </c>
       <c r="H200" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.25">
@@ -15299,13 +15299,13 @@
         <v>1855</v>
       </c>
       <c r="F212" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G212" s="2">
         <v>0</v>
       </c>
       <c r="H212" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.25">
@@ -15377,13 +15377,13 @@
         <v>1856</v>
       </c>
       <c r="F215" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G215" s="2">
         <v>0</v>
       </c>
       <c r="H215" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.25">
@@ -15949,13 +15949,13 @@
         <v>1897</v>
       </c>
       <c r="F237" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G237" s="2">
         <v>0</v>
       </c>
       <c r="H237" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.25">
@@ -20291,13 +20291,13 @@
         <v>1812</v>
       </c>
       <c r="F404" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G404" s="2">
         <v>0</v>
       </c>
       <c r="H404" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="405" spans="1:8" x14ac:dyDescent="0.25">
@@ -27019,13 +27019,13 @@
         <v>430</v>
       </c>
       <c r="F663" s="2">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="G663" s="2">
         <v>5</v>
       </c>
       <c r="H663" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="664" spans="1:8" x14ac:dyDescent="0.25">
@@ -31335,13 +31335,13 @@
         <v>2554</v>
       </c>
       <c r="F829" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G829" s="2">
         <v>0</v>
       </c>
       <c r="H829" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="830" spans="1:8" x14ac:dyDescent="0.25">
@@ -31517,10 +31517,10 @@
         <v>2557</v>
       </c>
       <c r="F836" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G836" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H836" s="2">
         <v>2</v>
@@ -31936,10 +31936,10 @@
         <v>16</v>
       </c>
       <c r="G852" s="2">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="H852" s="2">
-        <v>14</v>
+        <v>10</v>
       </c>
     </row>
     <row r="853" spans="1:8" x14ac:dyDescent="0.25">
@@ -34739,13 +34739,13 @@
         <v>2625</v>
       </c>
       <c r="F960" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G960" s="2">
         <v>0</v>
       </c>
       <c r="H960" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="961" spans="1:8" x14ac:dyDescent="0.25">
@@ -34791,13 +34791,13 @@
         <v>2624</v>
       </c>
       <c r="F962" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G962" s="2">
         <v>0</v>
       </c>
       <c r="H962" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="963" spans="1:8" x14ac:dyDescent="0.25">
@@ -37547,13 +37547,13 @@
         <v>2590</v>
       </c>
       <c r="F1068" s="2">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="G1068" s="2">
         <v>0</v>
       </c>
       <c r="H1068" s="2">
-        <v>17</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1069" spans="1:8" x14ac:dyDescent="0.25">
@@ -38639,13 +38639,13 @@
         <v>2452</v>
       </c>
       <c r="F1110" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1110" s="2">
         <v>0</v>
       </c>
       <c r="H1110" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1111" spans="1:8" x14ac:dyDescent="0.25">
@@ -39471,13 +39471,13 @@
         <v>2733</v>
       </c>
       <c r="F1142" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G1142" s="2">
         <v>0</v>
       </c>
       <c r="H1142" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1143" spans="1:8" x14ac:dyDescent="0.25">
@@ -40147,13 +40147,13 @@
         <v>2717</v>
       </c>
       <c r="F1168" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G1168" s="2">
         <v>0</v>
       </c>
       <c r="H1168" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="1169" spans="1:8" x14ac:dyDescent="0.25">
@@ -42851,13 +42851,13 @@
         <v>2823</v>
       </c>
       <c r="F1272" s="2">
-        <v>3</v>
+        <v>28</v>
       </c>
       <c r="G1272" s="2">
         <v>1</v>
       </c>
       <c r="H1272" s="2">
-        <v>2</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1273" spans="1:8" x14ac:dyDescent="0.25">
@@ -42877,13 +42877,13 @@
         <v>2823</v>
       </c>
       <c r="F1273" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="G1273" s="2">
         <v>0</v>
       </c>
       <c r="H1273" s="2">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1274" spans="1:8" x14ac:dyDescent="0.25">
@@ -43631,13 +43631,13 @@
         <v>2869</v>
       </c>
       <c r="F1302" s="2">
-        <v>9</v>
+        <v>14</v>
       </c>
       <c r="G1302" s="2">
         <v>0</v>
       </c>
       <c r="H1302" s="2">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1303" spans="1:8" x14ac:dyDescent="0.25">
@@ -45009,13 +45009,13 @@
         <v>2915</v>
       </c>
       <c r="F1355" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G1355" s="2">
         <v>0</v>
       </c>
       <c r="H1355" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1356" spans="1:8" x14ac:dyDescent="0.25">
@@ -45087,13 +45087,13 @@
         <v>2824</v>
       </c>
       <c r="F1358" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G1358" s="2">
         <v>0</v>
       </c>
       <c r="H1358" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="1359" spans="1:8" x14ac:dyDescent="0.25">
@@ -45295,13 +45295,13 @@
         <v>2953</v>
       </c>
       <c r="F1366" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G1366" s="2">
         <v>0</v>
       </c>
       <c r="H1366" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="1367" spans="1:8" x14ac:dyDescent="0.25">
@@ -45399,13 +45399,13 @@
         <v>2868</v>
       </c>
       <c r="F1370" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1370" s="2">
         <v>0</v>
       </c>
       <c r="H1370" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1371" spans="1:8" x14ac:dyDescent="0.25">
@@ -45425,13 +45425,13 @@
         <v>2868</v>
       </c>
       <c r="F1371" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1371" s="2">
         <v>0</v>
       </c>
       <c r="H1371" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1372" spans="1:8" x14ac:dyDescent="0.25">
@@ -45607,13 +45607,13 @@
         <v>2966</v>
       </c>
       <c r="F1378" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G1378" s="2">
         <v>0</v>
       </c>
       <c r="H1378" s="2">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1379" spans="1:8" x14ac:dyDescent="0.25">
@@ -45685,13 +45685,13 @@
         <v>2915</v>
       </c>
       <c r="F1381" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1381" s="2">
         <v>0</v>
       </c>
       <c r="H1381" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1382" spans="1:8" x14ac:dyDescent="0.25">
@@ -46439,13 +46439,13 @@
         <v>2868</v>
       </c>
       <c r="F1410" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G1410" s="2">
         <v>0</v>
       </c>
       <c r="H1410" s="2">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1411" spans="1:8" x14ac:dyDescent="0.25">
@@ -46465,13 +46465,13 @@
         <v>3015</v>
       </c>
       <c r="F1411" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1411" s="2">
         <v>0</v>
       </c>
       <c r="H1411" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1412" spans="1:8" x14ac:dyDescent="0.25">
@@ -46517,13 +46517,13 @@
         <v>2994</v>
       </c>
       <c r="F1413" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G1413" s="2">
         <v>0</v>
       </c>
       <c r="H1413" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1414" spans="1:8" x14ac:dyDescent="0.25">
@@ -46751,13 +46751,13 @@
         <v>3012</v>
       </c>
       <c r="F1422" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G1422" s="2">
         <v>0</v>
       </c>
       <c r="H1422" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1423" spans="1:8" x14ac:dyDescent="0.25">
@@ -46803,13 +46803,13 @@
         <v>2966</v>
       </c>
       <c r="F1424" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G1424" s="2">
         <v>0</v>
       </c>
       <c r="H1424" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1425" spans="1:8" x14ac:dyDescent="0.25">
@@ -47401,13 +47401,13 @@
         <v>2953</v>
       </c>
       <c r="F1447" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="G1447" s="2">
         <v>1</v>
       </c>
       <c r="H1447" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1448" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK SRB.xlsx
+++ b/STOK DEALER/STOK SRB.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9881103E-D565-416D-BD17-202634F152DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C980F9D7-9373-436E-8583-1E681BE649B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1170" yWindow="1170" windowWidth="12690" windowHeight="14475" xr2:uid="{46E7093F-A843-4D56-8D6E-D290D3117D3B}"/>
+    <workbookView xWindow="3120" yWindow="1725" windowWidth="12690" windowHeight="14475" xr2:uid="{46E7093F-A843-4D56-8D6E-D290D3117D3B}"/>
   </bookViews>
   <sheets>
     <sheet name="STOK DEALER" sheetId="1" r:id="rId1"/>
@@ -9912,13 +9912,13 @@
         <v>1624</v>
       </c>
       <c r="F2" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G2" s="2">
         <v>0</v>
       </c>
       <c r="H2" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -11446,13 +11446,13 @@
         <v>30</v>
       </c>
       <c r="F61" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G61" s="2">
         <v>0</v>
       </c>
       <c r="H61" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
@@ -13084,13 +13084,13 @@
         <v>1741</v>
       </c>
       <c r="F124" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G124" s="2">
         <v>0</v>
       </c>
       <c r="H124" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
@@ -13652,13 +13652,13 @@
         <v>1780</v>
       </c>
       <c r="F146" s="2">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="G146" s="2">
         <v>3</v>
       </c>
       <c r="H146" s="2">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
@@ -13678,13 +13678,13 @@
         <v>1781</v>
       </c>
       <c r="F147" s="2">
-        <v>105</v>
+        <v>128</v>
       </c>
       <c r="G147" s="2">
         <v>6</v>
       </c>
       <c r="H147" s="2">
-        <v>99</v>
+        <v>122</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
@@ -13704,13 +13704,13 @@
         <v>1781</v>
       </c>
       <c r="F148" s="2">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G148" s="2">
         <v>2</v>
       </c>
       <c r="H148" s="2">
-        <v>232</v>
+        <v>231</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
@@ -13834,13 +13834,13 @@
         <v>1789</v>
       </c>
       <c r="F153" s="2">
-        <v>268</v>
+        <v>247</v>
       </c>
       <c r="G153" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="H153" s="2">
-        <v>260</v>
+        <v>238</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
@@ -14097,10 +14097,10 @@
         <v>139</v>
       </c>
       <c r="G163" s="2">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H163" s="2">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.25">
@@ -14120,13 +14120,13 @@
         <v>1789</v>
       </c>
       <c r="F164" s="2">
-        <v>441</v>
+        <v>429</v>
       </c>
       <c r="G164" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="H164" s="2">
-        <v>435</v>
+        <v>424</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.25">
@@ -14276,13 +14276,13 @@
         <v>207</v>
       </c>
       <c r="F170" s="2">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="G170" s="2">
         <v>5</v>
       </c>
       <c r="H170" s="2">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.25">
@@ -15290,13 +15290,13 @@
         <v>1809</v>
       </c>
       <c r="F209" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G209" s="2">
         <v>0</v>
       </c>
       <c r="H209" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.25">
@@ -16460,13 +16460,13 @@
         <v>1921</v>
       </c>
       <c r="F254" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G254" s="2">
         <v>0</v>
       </c>
       <c r="H254" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="255" spans="1:8" x14ac:dyDescent="0.25">
@@ -17136,13 +17136,13 @@
         <v>1903</v>
       </c>
       <c r="F280" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G280" s="2">
         <v>0</v>
       </c>
       <c r="H280" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="281" spans="1:8" x14ac:dyDescent="0.25">
@@ -17214,13 +17214,13 @@
         <v>1903</v>
       </c>
       <c r="F283" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G283" s="2">
         <v>0</v>
       </c>
       <c r="H283" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="284" spans="1:8" x14ac:dyDescent="0.25">
@@ -18436,13 +18436,13 @@
         <v>2029</v>
       </c>
       <c r="F330" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G330" s="2">
         <v>0</v>
       </c>
       <c r="H330" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="331" spans="1:8" x14ac:dyDescent="0.25">
@@ -18488,13 +18488,13 @@
         <v>2028</v>
       </c>
       <c r="F332" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G332" s="2">
         <v>0</v>
       </c>
       <c r="H332" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="333" spans="1:8" x14ac:dyDescent="0.25">
@@ -20542,13 +20542,13 @@
         <v>1812</v>
       </c>
       <c r="F411" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G411" s="2">
         <v>0</v>
       </c>
       <c r="H411" s="2">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="412" spans="1:8" x14ac:dyDescent="0.25">
@@ -20750,13 +20750,13 @@
         <v>2168</v>
       </c>
       <c r="F419" s="2">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G419" s="2">
         <v>1</v>
       </c>
       <c r="H419" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="420" spans="1:8" x14ac:dyDescent="0.25">
@@ -20776,13 +20776,13 @@
         <v>926</v>
       </c>
       <c r="F420" s="2">
-        <v>26</v>
+        <v>31</v>
       </c>
       <c r="G420" s="2">
         <v>1</v>
       </c>
       <c r="H420" s="2">
-        <v>25</v>
+        <v>30</v>
       </c>
     </row>
     <row r="421" spans="1:8" x14ac:dyDescent="0.25">
@@ -22412,13 +22412,13 @@
         <v>1903</v>
       </c>
       <c r="F483" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G483" s="2">
         <v>0</v>
       </c>
       <c r="H483" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="484" spans="1:8" x14ac:dyDescent="0.25">
@@ -23036,13 +23036,13 @@
         <v>2242</v>
       </c>
       <c r="F507" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G507" s="2">
         <v>0</v>
       </c>
       <c r="H507" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="508" spans="1:8" x14ac:dyDescent="0.25">
@@ -24725,10 +24725,10 @@
         <v>2</v>
       </c>
       <c r="G572" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H572" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="573" spans="1:8" x14ac:dyDescent="0.25">
@@ -27036,13 +27036,13 @@
         <v>292</v>
       </c>
       <c r="F661" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G661" s="2">
         <v>1</v>
       </c>
       <c r="H661" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="662" spans="1:8" x14ac:dyDescent="0.25">
@@ -28596,13 +28596,13 @@
         <v>410</v>
       </c>
       <c r="F721" s="2">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="G721" s="2">
         <v>0</v>
       </c>
       <c r="H721" s="2">
-        <v>13</v>
+        <v>23</v>
       </c>
     </row>
     <row r="722" spans="1:8" x14ac:dyDescent="0.25">
@@ -28726,13 +28726,13 @@
         <v>696</v>
       </c>
       <c r="F726" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G726" s="2">
         <v>0</v>
       </c>
       <c r="H726" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="727" spans="1:8" x14ac:dyDescent="0.25">
@@ -30338,13 +30338,13 @@
         <v>2511</v>
       </c>
       <c r="F788" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G788" s="2">
         <v>0</v>
       </c>
       <c r="H788" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="789" spans="1:8" x14ac:dyDescent="0.25">
@@ -30520,13 +30520,13 @@
         <v>2524</v>
       </c>
       <c r="F795" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G795" s="2">
         <v>2</v>
       </c>
       <c r="H795" s="2">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="796" spans="1:8" x14ac:dyDescent="0.25">
@@ -31534,13 +31534,13 @@
         <v>2552</v>
       </c>
       <c r="F834" s="2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G834" s="2">
         <v>1</v>
       </c>
       <c r="H834" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="835" spans="1:8" x14ac:dyDescent="0.25">
@@ -35094,13 +35094,13 @@
         <v>2624</v>
       </c>
       <c r="F971" s="2">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="G971" s="2">
         <v>0</v>
       </c>
       <c r="H971" s="2">
-        <v>0</v>
+        <v>20</v>
       </c>
     </row>
     <row r="972" spans="1:8" x14ac:dyDescent="0.25">
@@ -35198,13 +35198,13 @@
         <v>2629</v>
       </c>
       <c r="F975" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G975" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H975" s="2">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="976" spans="1:8" x14ac:dyDescent="0.25">
@@ -37902,13 +37902,13 @@
         <v>2590</v>
       </c>
       <c r="F1079" s="2">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="G1079" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H1079" s="2">
-        <v>61</v>
+        <v>53</v>
       </c>
     </row>
     <row r="1080" spans="1:8" x14ac:dyDescent="0.25">
@@ -39647,10 +39647,10 @@
         <v>4</v>
       </c>
       <c r="G1146" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1146" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1147" spans="1:8" x14ac:dyDescent="0.25">
@@ -39826,13 +39826,13 @@
         <v>2727</v>
       </c>
       <c r="F1153" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G1153" s="2">
         <v>0</v>
       </c>
       <c r="H1153" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1154" spans="1:8" x14ac:dyDescent="0.25">
@@ -40531,10 +40531,10 @@
         <v>9</v>
       </c>
       <c r="G1180" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1180" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1181" spans="1:8" x14ac:dyDescent="0.25">
@@ -42114,13 +42114,13 @@
         <v>2804</v>
       </c>
       <c r="F1241" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G1241" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H1241" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1242" spans="1:8" x14ac:dyDescent="0.25">
@@ -42686,13 +42686,13 @@
         <v>586</v>
       </c>
       <c r="F1263" s="2">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="G1263" s="2">
         <v>0</v>
       </c>
       <c r="H1263" s="2">
-        <v>73</v>
+        <v>70</v>
       </c>
     </row>
     <row r="1264" spans="1:8" x14ac:dyDescent="0.25">
@@ -43053,10 +43053,10 @@
         <v>16</v>
       </c>
       <c r="G1277" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="H1277" s="2">
-        <v>16</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1278" spans="1:8" x14ac:dyDescent="0.25">
@@ -43157,10 +43157,10 @@
         <v>22</v>
       </c>
       <c r="G1281" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1281" s="2">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1282" spans="1:8" x14ac:dyDescent="0.25">
@@ -43232,13 +43232,13 @@
         <v>2823</v>
       </c>
       <c r="F1284" s="2">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="G1284" s="2">
         <v>0</v>
       </c>
       <c r="H1284" s="2">
-        <v>15</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1285" spans="1:8" x14ac:dyDescent="0.25">
@@ -43833,10 +43833,10 @@
         <v>15</v>
       </c>
       <c r="G1307" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1307" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1308" spans="1:8" x14ac:dyDescent="0.25">
@@ -44249,10 +44249,10 @@
         <v>15</v>
       </c>
       <c r="G1323" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1323" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1324" spans="1:8" x14ac:dyDescent="0.25">
@@ -46508,13 +46508,13 @@
         <v>2854</v>
       </c>
       <c r="F1410" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1410" s="2">
         <v>0</v>
       </c>
       <c r="H1410" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1411" spans="1:8" x14ac:dyDescent="0.25">
@@ -47158,13 +47158,13 @@
         <v>2901</v>
       </c>
       <c r="F1435" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G1435" s="2">
         <v>0</v>
       </c>
       <c r="H1435" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1436" spans="1:8" x14ac:dyDescent="0.25">
@@ -47444,13 +47444,13 @@
         <v>2845</v>
       </c>
       <c r="F1446" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G1446" s="2">
         <v>0</v>
       </c>
       <c r="H1446" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1447" spans="1:8" x14ac:dyDescent="0.25">
@@ -47522,13 +47522,13 @@
         <v>2860</v>
       </c>
       <c r="F1449" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1449" s="2">
         <v>0</v>
       </c>
       <c r="H1449" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1450" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK SRB.xlsx
+++ b/STOK DEALER/STOK SRB.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C980F9D7-9373-436E-8583-1E681BE649B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1855FC50-2A9C-4534-B9DA-67BC5164BDF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="1725" windowWidth="12690" windowHeight="14475" xr2:uid="{46E7093F-A843-4D56-8D6E-D290D3117D3B}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{46E7093F-A843-4D56-8D6E-D290D3117D3B}"/>
   </bookViews>
   <sheets>
     <sheet name="STOK DEALER" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5953" uniqueCount="3140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5973" uniqueCount="3152">
   <si>
     <t>No</t>
   </si>
@@ -9456,6 +9456,42 @@
   </si>
   <si>
     <t>FASHION PASTEL BLUE HLMT M</t>
+  </si>
+  <si>
+    <t>AHJK0201035</t>
+  </si>
+  <si>
+    <t>CYBER WIND BREAKER L</t>
+  </si>
+  <si>
+    <t>AHJK0301035</t>
+  </si>
+  <si>
+    <t>CYBER WIND BREAKER XL</t>
+  </si>
+  <si>
+    <t>AHK02003019</t>
+  </si>
+  <si>
+    <t>CYBER SHIRT L</t>
+  </si>
+  <si>
+    <t>B3.06.1.1</t>
+  </si>
+  <si>
+    <t>AHK03003019</t>
+  </si>
+  <si>
+    <t>CYBER SHIRT XL</t>
+  </si>
+  <si>
+    <t>AHTA0001014</t>
+  </si>
+  <si>
+    <t>CYBER 2IN1 TOTEBAG</t>
+  </si>
+  <si>
+    <t>B3.06.1.2</t>
   </si>
 </sst>
 </file>
@@ -9856,7 +9892,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2BB8C35-92DF-4C27-A2CF-D1CDC7F4FE42}">
-  <dimension ref="A1:H1497"/>
+  <dimension ref="A1:H1502"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -10172,13 +10208,13 @@
         <v>1627</v>
       </c>
       <c r="F12" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G12" s="2">
         <v>0</v>
       </c>
       <c r="H12" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -11134,13 +11170,13 @@
         <v>1672</v>
       </c>
       <c r="F49" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G49" s="2">
         <v>1</v>
       </c>
       <c r="H49" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
@@ -13834,13 +13870,13 @@
         <v>1789</v>
       </c>
       <c r="F153" s="2">
-        <v>247</v>
+        <v>232</v>
       </c>
       <c r="G153" s="2">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="H153" s="2">
-        <v>238</v>
+        <v>222</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
@@ -14094,13 +14130,13 @@
         <v>1780</v>
       </c>
       <c r="F163" s="2">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="G163" s="2">
         <v>8</v>
       </c>
       <c r="H163" s="2">
-        <v>131</v>
+        <v>127</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.25">
@@ -14120,13 +14156,13 @@
         <v>1789</v>
       </c>
       <c r="F164" s="2">
-        <v>429</v>
+        <v>417</v>
       </c>
       <c r="G164" s="2">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H164" s="2">
-        <v>424</v>
+        <v>408</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.25">
@@ -14276,13 +14312,13 @@
         <v>207</v>
       </c>
       <c r="F170" s="2">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="G170" s="2">
         <v>5</v>
       </c>
       <c r="H170" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.25">
@@ -15108,13 +15144,13 @@
         <v>1815</v>
       </c>
       <c r="F202" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G202" s="2">
         <v>0</v>
       </c>
       <c r="H202" s="2">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.25">
@@ -20542,13 +20578,13 @@
         <v>1812</v>
       </c>
       <c r="F411" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G411" s="2">
         <v>0</v>
       </c>
       <c r="H411" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="412" spans="1:8" x14ac:dyDescent="0.25">
@@ -20750,13 +20786,13 @@
         <v>2168</v>
       </c>
       <c r="F419" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G419" s="2">
         <v>1</v>
       </c>
       <c r="H419" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="420" spans="1:8" x14ac:dyDescent="0.25">
@@ -24644,13 +24680,13 @@
         <v>2278</v>
       </c>
       <c r="F569" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G569" s="2">
         <v>0</v>
       </c>
       <c r="H569" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="570" spans="1:8" x14ac:dyDescent="0.25">
@@ -27039,10 +27075,10 @@
         <v>5</v>
       </c>
       <c r="G661" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H661" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="662" spans="1:8" x14ac:dyDescent="0.25">
@@ -27270,13 +27306,13 @@
         <v>402</v>
       </c>
       <c r="F670" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G670" s="2">
         <v>0</v>
       </c>
       <c r="H670" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="671" spans="1:8" x14ac:dyDescent="0.25">
@@ -27322,13 +27358,13 @@
         <v>430</v>
       </c>
       <c r="F672" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G672" s="2">
         <v>3</v>
       </c>
       <c r="H672" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="673" spans="1:8" x14ac:dyDescent="0.25">
@@ -30445,10 +30481,10 @@
         <v>1</v>
       </c>
       <c r="G792" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H792" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="793" spans="1:8" x14ac:dyDescent="0.25">
@@ -30780,13 +30816,13 @@
         <v>1812</v>
       </c>
       <c r="F805" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G805" s="2">
         <v>0</v>
       </c>
       <c r="H805" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="806" spans="1:8" x14ac:dyDescent="0.25">
@@ -32236,13 +32272,13 @@
         <v>2566</v>
       </c>
       <c r="F861" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G861" s="2">
         <v>0</v>
       </c>
       <c r="H861" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="862" spans="1:8" x14ac:dyDescent="0.25">
@@ -33976,13 +34012,13 @@
         <v>1625</v>
       </c>
       <c r="F928" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G928" s="2">
         <v>0</v>
       </c>
       <c r="H928" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="929" spans="1:8" x14ac:dyDescent="0.25">
@@ -35146,13 +35182,13 @@
         <v>2628</v>
       </c>
       <c r="F973" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G973" s="2">
         <v>0</v>
       </c>
       <c r="H973" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="974" spans="1:8" x14ac:dyDescent="0.25">
@@ -35198,10 +35234,10 @@
         <v>2629</v>
       </c>
       <c r="F975" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G975" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H975" s="2">
         <v>9</v>
@@ -37902,13 +37938,13 @@
         <v>2590</v>
       </c>
       <c r="F1079" s="2">
-        <v>56</v>
+        <v>46</v>
       </c>
       <c r="G1079" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H1079" s="2">
-        <v>53</v>
+        <v>45</v>
       </c>
     </row>
     <row r="1080" spans="1:8" x14ac:dyDescent="0.25">
@@ -39644,10 +39680,10 @@
         <v>2733</v>
       </c>
       <c r="F1146" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1146" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1146" s="2">
         <v>3</v>
@@ -39800,13 +39836,13 @@
         <v>2727</v>
       </c>
       <c r="F1152" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1152" s="2">
         <v>0</v>
       </c>
       <c r="H1152" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1153" spans="1:8" x14ac:dyDescent="0.25">
@@ -40528,13 +40564,13 @@
         <v>2717</v>
       </c>
       <c r="F1180" s="2">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="G1180" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1180" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1181" spans="1:8" x14ac:dyDescent="0.25">
@@ -42686,13 +42722,13 @@
         <v>586</v>
       </c>
       <c r="F1263" s="2">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="G1263" s="2">
         <v>0</v>
       </c>
       <c r="H1263" s="2">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="1264" spans="1:8" x14ac:dyDescent="0.25">
@@ -43154,13 +43190,13 @@
         <v>2824</v>
       </c>
       <c r="F1281" s="2">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="G1281" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1281" s="2">
-        <v>21</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1282" spans="1:8" x14ac:dyDescent="0.25">
@@ -43232,13 +43268,13 @@
         <v>2823</v>
       </c>
       <c r="F1284" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G1284" s="2">
         <v>0</v>
       </c>
       <c r="H1284" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1285" spans="1:8" x14ac:dyDescent="0.25">
@@ -43258,13 +43294,13 @@
         <v>2823</v>
       </c>
       <c r="F1285" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G1285" s="2">
         <v>0</v>
       </c>
       <c r="H1285" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1286" spans="1:8" x14ac:dyDescent="0.25">
@@ -43830,10 +43866,10 @@
         <v>2851</v>
       </c>
       <c r="F1307" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G1307" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1307" s="2">
         <v>14</v>
@@ -43960,13 +43996,13 @@
         <v>2629</v>
       </c>
       <c r="F1312" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1312" s="2">
         <v>0</v>
       </c>
       <c r="H1312" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1313" spans="1:8" x14ac:dyDescent="0.25">
@@ -44104,25 +44140,25 @@
         <v>1317</v>
       </c>
       <c r="B1318" s="2" t="s">
-        <v>2874</v>
+        <v>3140</v>
       </c>
       <c r="C1318" s="2" t="s">
-        <v>2875</v>
+        <v>3141</v>
       </c>
       <c r="D1318" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1318" s="2" t="s">
-        <v>2668</v>
+        <v>2888</v>
       </c>
       <c r="F1318" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1318" s="2">
         <v>0</v>
       </c>
       <c r="H1318" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1319" spans="1:8" x14ac:dyDescent="0.25">
@@ -44130,25 +44166,25 @@
         <v>1318</v>
       </c>
       <c r="B1319" s="2" t="s">
-        <v>1147</v>
+        <v>2874</v>
       </c>
       <c r="C1319" s="2" t="s">
-        <v>1148</v>
+        <v>2875</v>
       </c>
       <c r="D1319" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1319" s="2" t="s">
-        <v>2876</v>
+        <v>2668</v>
       </c>
       <c r="F1319" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1319" s="2">
         <v>0</v>
       </c>
       <c r="H1319" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1320" spans="1:8" x14ac:dyDescent="0.25">
@@ -44156,10 +44192,10 @@
         <v>1319</v>
       </c>
       <c r="B1320" s="2" t="s">
-        <v>1149</v>
+        <v>1147</v>
       </c>
       <c r="C1320" s="2" t="s">
-        <v>1150</v>
+        <v>1148</v>
       </c>
       <c r="D1320" s="2" t="s">
         <v>1623</v>
@@ -44168,13 +44204,13 @@
         <v>2876</v>
       </c>
       <c r="F1320" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1320" s="2">
         <v>0</v>
       </c>
       <c r="H1320" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1321" spans="1:8" x14ac:dyDescent="0.25">
@@ -44182,25 +44218,25 @@
         <v>1320</v>
       </c>
       <c r="B1321" s="2" t="s">
-        <v>2877</v>
+        <v>1149</v>
       </c>
       <c r="C1321" s="2" t="s">
-        <v>2878</v>
+        <v>1150</v>
       </c>
       <c r="D1321" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1321" s="2" t="s">
-        <v>2854</v>
+        <v>2876</v>
       </c>
       <c r="F1321" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1321" s="2">
         <v>0</v>
       </c>
       <c r="H1321" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1322" spans="1:8" x14ac:dyDescent="0.25">
@@ -44208,16 +44244,16 @@
         <v>1321</v>
       </c>
       <c r="B1322" s="2" t="s">
-        <v>2879</v>
+        <v>2877</v>
       </c>
       <c r="C1322" s="2" t="s">
-        <v>2880</v>
+        <v>2878</v>
       </c>
       <c r="D1322" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1322" s="2" t="s">
-        <v>2881</v>
+        <v>2854</v>
       </c>
       <c r="F1322" s="2">
         <v>1</v>
@@ -44234,25 +44270,25 @@
         <v>1322</v>
       </c>
       <c r="B1323" s="2" t="s">
-        <v>2882</v>
+        <v>2879</v>
       </c>
       <c r="C1323" s="2" t="s">
-        <v>2883</v>
+        <v>2880</v>
       </c>
       <c r="D1323" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1323" s="2" t="s">
-        <v>2869</v>
+        <v>2881</v>
       </c>
       <c r="F1323" s="2">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="G1323" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1323" s="2">
         <v>1</v>
-      </c>
-      <c r="H1323" s="2">
-        <v>14</v>
       </c>
     </row>
     <row r="1324" spans="1:8" x14ac:dyDescent="0.25">
@@ -44260,25 +44296,25 @@
         <v>1323</v>
       </c>
       <c r="B1324" s="2" t="s">
-        <v>2884</v>
+        <v>2882</v>
       </c>
       <c r="C1324" s="2" t="s">
-        <v>2885</v>
+        <v>2883</v>
       </c>
       <c r="D1324" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1324" s="2" t="s">
-        <v>2848</v>
+        <v>2869</v>
       </c>
       <c r="F1324" s="2">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="G1324" s="2">
         <v>0</v>
       </c>
       <c r="H1324" s="2">
-        <v>1</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1325" spans="1:8" x14ac:dyDescent="0.25">
@@ -44286,16 +44322,16 @@
         <v>1324</v>
       </c>
       <c r="B1325" s="2" t="s">
-        <v>2886</v>
+        <v>2884</v>
       </c>
       <c r="C1325" s="2" t="s">
-        <v>2887</v>
+        <v>2885</v>
       </c>
       <c r="D1325" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1325" s="2" t="s">
-        <v>2860</v>
+        <v>2848</v>
       </c>
       <c r="F1325" s="2">
         <v>1</v>
@@ -44312,25 +44348,25 @@
         <v>1325</v>
       </c>
       <c r="B1326" s="2" t="s">
-        <v>1151</v>
+        <v>2886</v>
       </c>
       <c r="C1326" s="2" t="s">
-        <v>1152</v>
+        <v>2887</v>
       </c>
       <c r="D1326" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1326" s="2" t="s">
-        <v>2888</v>
+        <v>2860</v>
       </c>
       <c r="F1326" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1326" s="2">
         <v>0</v>
       </c>
       <c r="H1326" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1327" spans="1:8" x14ac:dyDescent="0.25">
@@ -44338,25 +44374,25 @@
         <v>1326</v>
       </c>
       <c r="B1327" s="2" t="s">
-        <v>2889</v>
+        <v>3142</v>
       </c>
       <c r="C1327" s="2" t="s">
-        <v>2890</v>
+        <v>3143</v>
       </c>
       <c r="D1327" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1327" s="2" t="s">
-        <v>2668</v>
+        <v>2888</v>
       </c>
       <c r="F1327" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1327" s="2">
         <v>0</v>
       </c>
       <c r="H1327" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1328" spans="1:8" x14ac:dyDescent="0.25">
@@ -44364,25 +44400,25 @@
         <v>1327</v>
       </c>
       <c r="B1328" s="2" t="s">
-        <v>2891</v>
+        <v>1151</v>
       </c>
       <c r="C1328" s="2" t="s">
-        <v>2892</v>
+        <v>1152</v>
       </c>
       <c r="D1328" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1328" s="2" t="s">
-        <v>1839</v>
+        <v>2888</v>
       </c>
       <c r="F1328" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1328" s="2">
         <v>0</v>
       </c>
       <c r="H1328" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1329" spans="1:8" x14ac:dyDescent="0.25">
@@ -44390,16 +44426,16 @@
         <v>1328</v>
       </c>
       <c r="B1329" s="2" t="s">
-        <v>2893</v>
+        <v>2889</v>
       </c>
       <c r="C1329" s="2" t="s">
-        <v>2894</v>
+        <v>2890</v>
       </c>
       <c r="D1329" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1329" s="2" t="s">
-        <v>1839</v>
+        <v>2668</v>
       </c>
       <c r="F1329" s="2">
         <v>1</v>
@@ -44416,10 +44452,10 @@
         <v>1329</v>
       </c>
       <c r="B1330" s="2" t="s">
-        <v>2895</v>
+        <v>2891</v>
       </c>
       <c r="C1330" s="2" t="s">
-        <v>2896</v>
+        <v>2892</v>
       </c>
       <c r="D1330" s="2" t="s">
         <v>1623</v>
@@ -44428,13 +44464,13 @@
         <v>1839</v>
       </c>
       <c r="F1330" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1330" s="2">
         <v>0</v>
       </c>
       <c r="H1330" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1331" spans="1:8" x14ac:dyDescent="0.25">
@@ -44442,16 +44478,16 @@
         <v>1330</v>
       </c>
       <c r="B1331" s="2" t="s">
-        <v>2897</v>
+        <v>2893</v>
       </c>
       <c r="C1331" s="2" t="s">
-        <v>2898</v>
+        <v>2894</v>
       </c>
       <c r="D1331" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1331" s="2" t="s">
-        <v>2668</v>
+        <v>1839</v>
       </c>
       <c r="F1331" s="2">
         <v>1</v>
@@ -44468,16 +44504,16 @@
         <v>1331</v>
       </c>
       <c r="B1332" s="2" t="s">
-        <v>2899</v>
+        <v>2895</v>
       </c>
       <c r="C1332" s="2" t="s">
-        <v>2900</v>
+        <v>2896</v>
       </c>
       <c r="D1332" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1332" s="2" t="s">
-        <v>2901</v>
+        <v>1839</v>
       </c>
       <c r="F1332" s="2">
         <v>0</v>
@@ -44494,25 +44530,25 @@
         <v>1332</v>
       </c>
       <c r="B1333" s="2" t="s">
-        <v>2902</v>
+        <v>2897</v>
       </c>
       <c r="C1333" s="2" t="s">
-        <v>2903</v>
+        <v>2898</v>
       </c>
       <c r="D1333" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1333" s="2" t="s">
-        <v>2904</v>
+        <v>2668</v>
       </c>
       <c r="F1333" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1333" s="2">
         <v>0</v>
       </c>
       <c r="H1333" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1334" spans="1:8" x14ac:dyDescent="0.25">
@@ -44520,16 +44556,16 @@
         <v>1333</v>
       </c>
       <c r="B1334" s="2" t="s">
-        <v>2902</v>
+        <v>2899</v>
       </c>
       <c r="C1334" s="2" t="s">
-        <v>2903</v>
+        <v>2900</v>
       </c>
       <c r="D1334" s="2" t="s">
-        <v>2162</v>
+        <v>1623</v>
       </c>
       <c r="E1334" s="2" t="s">
-        <v>2904</v>
+        <v>2901</v>
       </c>
       <c r="F1334" s="2">
         <v>0</v>
@@ -44546,10 +44582,10 @@
         <v>1334</v>
       </c>
       <c r="B1335" s="2" t="s">
-        <v>2905</v>
+        <v>2902</v>
       </c>
       <c r="C1335" s="2" t="s">
-        <v>2906</v>
+        <v>2903</v>
       </c>
       <c r="D1335" s="2" t="s">
         <v>1623</v>
@@ -44572,25 +44608,25 @@
         <v>1335</v>
       </c>
       <c r="B1336" s="2" t="s">
-        <v>2907</v>
+        <v>2902</v>
       </c>
       <c r="C1336" s="2" t="s">
-        <v>2908</v>
+        <v>2903</v>
       </c>
       <c r="D1336" s="2" t="s">
-        <v>1623</v>
+        <v>2162</v>
       </c>
       <c r="E1336" s="2" t="s">
-        <v>2668</v>
+        <v>2904</v>
       </c>
       <c r="F1336" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1336" s="2">
         <v>0</v>
       </c>
       <c r="H1336" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1337" spans="1:8" x14ac:dyDescent="0.25">
@@ -44598,16 +44634,16 @@
         <v>1336</v>
       </c>
       <c r="B1337" s="2" t="s">
-        <v>1153</v>
+        <v>2905</v>
       </c>
       <c r="C1337" s="2" t="s">
-        <v>1154</v>
+        <v>2906</v>
       </c>
       <c r="D1337" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1337" s="2" t="s">
-        <v>2909</v>
+        <v>2904</v>
       </c>
       <c r="F1337" s="2">
         <v>0</v>
@@ -44624,25 +44660,25 @@
         <v>1337</v>
       </c>
       <c r="B1338" s="2" t="s">
-        <v>1155</v>
+        <v>2907</v>
       </c>
       <c r="C1338" s="2" t="s">
-        <v>1156</v>
+        <v>2908</v>
       </c>
       <c r="D1338" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1338" s="2" t="s">
-        <v>2857</v>
+        <v>2668</v>
       </c>
       <c r="F1338" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1338" s="2">
         <v>0</v>
       </c>
       <c r="H1338" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1339" spans="1:8" x14ac:dyDescent="0.25">
@@ -44650,16 +44686,16 @@
         <v>1338</v>
       </c>
       <c r="B1339" s="2" t="s">
-        <v>2910</v>
+        <v>1153</v>
       </c>
       <c r="C1339" s="2" t="s">
-        <v>2911</v>
+        <v>1154</v>
       </c>
       <c r="D1339" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1339" s="2" t="s">
-        <v>2857</v>
+        <v>2909</v>
       </c>
       <c r="F1339" s="2">
         <v>0</v>
@@ -44676,16 +44712,16 @@
         <v>1339</v>
       </c>
       <c r="B1340" s="2" t="s">
-        <v>2912</v>
+        <v>1155</v>
       </c>
       <c r="C1340" s="2" t="s">
-        <v>2913</v>
+        <v>1156</v>
       </c>
       <c r="D1340" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1340" s="2" t="s">
-        <v>2833</v>
+        <v>2857</v>
       </c>
       <c r="F1340" s="2">
         <v>0</v>
@@ -44702,16 +44738,16 @@
         <v>1340</v>
       </c>
       <c r="B1341" s="2" t="s">
-        <v>1326</v>
+        <v>2910</v>
       </c>
       <c r="C1341" s="2" t="s">
-        <v>1327</v>
+        <v>2911</v>
       </c>
       <c r="D1341" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1341" s="2" t="s">
-        <v>2904</v>
+        <v>2857</v>
       </c>
       <c r="F1341" s="2">
         <v>0</v>
@@ -44728,16 +44764,16 @@
         <v>1341</v>
       </c>
       <c r="B1342" s="2" t="s">
-        <v>1281</v>
+        <v>2912</v>
       </c>
       <c r="C1342" s="2" t="s">
-        <v>1282</v>
+        <v>2913</v>
       </c>
       <c r="D1342" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1342" s="2" t="s">
-        <v>2828</v>
+        <v>2833</v>
       </c>
       <c r="F1342" s="2">
         <v>0</v>
@@ -44754,10 +44790,10 @@
         <v>1342</v>
       </c>
       <c r="B1343" s="2" t="s">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="C1343" s="2" t="s">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="D1343" s="2" t="s">
         <v>1623</v>
@@ -44780,16 +44816,16 @@
         <v>1343</v>
       </c>
       <c r="B1344" s="2" t="s">
-        <v>1330</v>
+        <v>1281</v>
       </c>
       <c r="C1344" s="2" t="s">
-        <v>1331</v>
+        <v>1282</v>
       </c>
       <c r="D1344" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1344" s="2" t="s">
-        <v>2914</v>
+        <v>2828</v>
       </c>
       <c r="F1344" s="2">
         <v>0</v>
@@ -44806,16 +44842,16 @@
         <v>1344</v>
       </c>
       <c r="B1345" s="2" t="s">
-        <v>1283</v>
+        <v>1328</v>
       </c>
       <c r="C1345" s="2" t="s">
-        <v>1284</v>
+        <v>1329</v>
       </c>
       <c r="D1345" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1345" s="2" t="s">
-        <v>2828</v>
+        <v>2904</v>
       </c>
       <c r="F1345" s="2">
         <v>0</v>
@@ -44832,10 +44868,10 @@
         <v>1345</v>
       </c>
       <c r="B1346" s="2" t="s">
-        <v>1332</v>
+        <v>1330</v>
       </c>
       <c r="C1346" s="2" t="s">
-        <v>1333</v>
+        <v>1331</v>
       </c>
       <c r="D1346" s="2" t="s">
         <v>1623</v>
@@ -44858,16 +44894,16 @@
         <v>1346</v>
       </c>
       <c r="B1347" s="2" t="s">
-        <v>1334</v>
+        <v>1283</v>
       </c>
       <c r="C1347" s="2" t="s">
-        <v>1335</v>
+        <v>1284</v>
       </c>
       <c r="D1347" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1347" s="2" t="s">
-        <v>2914</v>
+        <v>2828</v>
       </c>
       <c r="F1347" s="2">
         <v>0</v>
@@ -44884,16 +44920,16 @@
         <v>1347</v>
       </c>
       <c r="B1348" s="2" t="s">
-        <v>1285</v>
+        <v>1332</v>
       </c>
       <c r="C1348" s="2" t="s">
-        <v>1286</v>
+        <v>1333</v>
       </c>
       <c r="D1348" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1348" s="2" t="s">
-        <v>2915</v>
+        <v>2914</v>
       </c>
       <c r="F1348" s="2">
         <v>0</v>
@@ -44910,25 +44946,25 @@
         <v>1348</v>
       </c>
       <c r="B1349" s="2" t="s">
-        <v>1336</v>
+        <v>3144</v>
       </c>
       <c r="C1349" s="2" t="s">
-        <v>1337</v>
+        <v>3145</v>
       </c>
       <c r="D1349" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1349" s="2" t="s">
-        <v>2914</v>
+        <v>3146</v>
       </c>
       <c r="F1349" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1349" s="2">
         <v>0</v>
       </c>
       <c r="H1349" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1350" spans="1:8" x14ac:dyDescent="0.25">
@@ -44936,16 +44972,16 @@
         <v>1349</v>
       </c>
       <c r="B1350" s="2" t="s">
-        <v>2916</v>
+        <v>1334</v>
       </c>
       <c r="C1350" s="2" t="s">
-        <v>2917</v>
+        <v>1335</v>
       </c>
       <c r="D1350" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1350" s="2" t="s">
-        <v>1839</v>
+        <v>2914</v>
       </c>
       <c r="F1350" s="2">
         <v>0</v>
@@ -44962,16 +44998,16 @@
         <v>1350</v>
       </c>
       <c r="B1351" s="2" t="s">
-        <v>2918</v>
+        <v>1285</v>
       </c>
       <c r="C1351" s="2" t="s">
-        <v>2919</v>
+        <v>1286</v>
       </c>
       <c r="D1351" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1351" s="2" t="s">
-        <v>1738</v>
+        <v>2915</v>
       </c>
       <c r="F1351" s="2">
         <v>0</v>
@@ -44988,25 +45024,25 @@
         <v>1351</v>
       </c>
       <c r="B1352" s="2" t="s">
-        <v>2920</v>
+        <v>1336</v>
       </c>
       <c r="C1352" s="2" t="s">
-        <v>2921</v>
+        <v>1337</v>
       </c>
       <c r="D1352" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1352" s="2" t="s">
-        <v>2829</v>
+        <v>2914</v>
       </c>
       <c r="F1352" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1352" s="2">
         <v>0</v>
       </c>
       <c r="H1352" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1353" spans="1:8" x14ac:dyDescent="0.25">
@@ -45014,25 +45050,25 @@
         <v>1352</v>
       </c>
       <c r="B1353" s="2" t="s">
-        <v>2922</v>
+        <v>3147</v>
       </c>
       <c r="C1353" s="2" t="s">
-        <v>2923</v>
+        <v>3148</v>
       </c>
       <c r="D1353" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1353" s="2" t="s">
-        <v>2915</v>
+        <v>3146</v>
       </c>
       <c r="F1353" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1353" s="2">
         <v>0</v>
       </c>
       <c r="H1353" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1354" spans="1:8" x14ac:dyDescent="0.25">
@@ -45040,16 +45076,16 @@
         <v>1353</v>
       </c>
       <c r="B1354" s="2" t="s">
-        <v>2924</v>
+        <v>2916</v>
       </c>
       <c r="C1354" s="2" t="s">
-        <v>2925</v>
+        <v>2917</v>
       </c>
       <c r="D1354" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1354" s="2" t="s">
-        <v>2668</v>
+        <v>1839</v>
       </c>
       <c r="F1354" s="2">
         <v>0</v>
@@ -45066,16 +45102,16 @@
         <v>1354</v>
       </c>
       <c r="B1355" s="2" t="s">
-        <v>2926</v>
+        <v>2918</v>
       </c>
       <c r="C1355" s="2" t="s">
-        <v>2927</v>
+        <v>2919</v>
       </c>
       <c r="D1355" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1355" s="2" t="s">
-        <v>2901</v>
+        <v>1738</v>
       </c>
       <c r="F1355" s="2">
         <v>0</v>
@@ -45092,25 +45128,25 @@
         <v>1355</v>
       </c>
       <c r="B1356" s="2" t="s">
-        <v>2928</v>
+        <v>2920</v>
       </c>
       <c r="C1356" s="2" t="s">
-        <v>2929</v>
+        <v>2921</v>
       </c>
       <c r="D1356" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1356" s="2" t="s">
-        <v>2901</v>
+        <v>2829</v>
       </c>
       <c r="F1356" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G1356" s="2">
         <v>0</v>
       </c>
       <c r="H1356" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1357" spans="1:8" x14ac:dyDescent="0.25">
@@ -45118,25 +45154,25 @@
         <v>1356</v>
       </c>
       <c r="B1357" s="2" t="s">
-        <v>2930</v>
+        <v>2922</v>
       </c>
       <c r="C1357" s="2" t="s">
-        <v>2931</v>
+        <v>2923</v>
       </c>
       <c r="D1357" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1357" s="2" t="s">
-        <v>2932</v>
+        <v>2915</v>
       </c>
       <c r="F1357" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G1357" s="2">
         <v>0</v>
       </c>
       <c r="H1357" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1358" spans="1:8" x14ac:dyDescent="0.25">
@@ -45144,16 +45180,16 @@
         <v>1357</v>
       </c>
       <c r="B1358" s="2" t="s">
-        <v>1157</v>
+        <v>2924</v>
       </c>
       <c r="C1358" s="2" t="s">
-        <v>1158</v>
+        <v>2925</v>
       </c>
       <c r="D1358" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1358" s="2" t="s">
-        <v>2828</v>
+        <v>2668</v>
       </c>
       <c r="F1358" s="2">
         <v>0</v>
@@ -45170,16 +45206,16 @@
         <v>1358</v>
       </c>
       <c r="B1359" s="2" t="s">
-        <v>2933</v>
+        <v>2926</v>
       </c>
       <c r="C1359" s="2" t="s">
-        <v>2934</v>
+        <v>2927</v>
       </c>
       <c r="D1359" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1359" s="2" t="s">
-        <v>2828</v>
+        <v>2901</v>
       </c>
       <c r="F1359" s="2">
         <v>0</v>
@@ -45196,25 +45232,25 @@
         <v>1359</v>
       </c>
       <c r="B1360" s="2" t="s">
-        <v>2935</v>
+        <v>2928</v>
       </c>
       <c r="C1360" s="2" t="s">
-        <v>2936</v>
+        <v>2929</v>
       </c>
       <c r="D1360" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1360" s="2" t="s">
-        <v>1839</v>
+        <v>2901</v>
       </c>
       <c r="F1360" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G1360" s="2">
         <v>0</v>
       </c>
       <c r="H1360" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1361" spans="1:8" x14ac:dyDescent="0.25">
@@ -45222,25 +45258,25 @@
         <v>1360</v>
       </c>
       <c r="B1361" s="2" t="s">
-        <v>2937</v>
+        <v>2930</v>
       </c>
       <c r="C1361" s="2" t="s">
-        <v>2938</v>
+        <v>2931</v>
       </c>
       <c r="D1361" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1361" s="2" t="s">
-        <v>2848</v>
+        <v>2932</v>
       </c>
       <c r="F1361" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G1361" s="2">
         <v>0</v>
       </c>
       <c r="H1361" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1362" spans="1:8" x14ac:dyDescent="0.25">
@@ -45248,25 +45284,25 @@
         <v>1361</v>
       </c>
       <c r="B1362" s="2" t="s">
-        <v>2939</v>
+        <v>1157</v>
       </c>
       <c r="C1362" s="2" t="s">
-        <v>2940</v>
+        <v>1158</v>
       </c>
       <c r="D1362" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1362" s="2" t="s">
-        <v>2824</v>
+        <v>2828</v>
       </c>
       <c r="F1362" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1362" s="2">
         <v>0</v>
       </c>
       <c r="H1362" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1363" spans="1:8" x14ac:dyDescent="0.25">
@@ -45274,16 +45310,16 @@
         <v>1362</v>
       </c>
       <c r="B1363" s="2" t="s">
-        <v>2941</v>
+        <v>2933</v>
       </c>
       <c r="C1363" s="2" t="s">
-        <v>2942</v>
+        <v>2934</v>
       </c>
       <c r="D1363" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1363" s="2" t="s">
-        <v>2668</v>
+        <v>2828</v>
       </c>
       <c r="F1363" s="2">
         <v>0</v>
@@ -45300,16 +45336,16 @@
         <v>1363</v>
       </c>
       <c r="B1364" s="2" t="s">
-        <v>2943</v>
+        <v>2935</v>
       </c>
       <c r="C1364" s="2" t="s">
-        <v>2944</v>
+        <v>2936</v>
       </c>
       <c r="D1364" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1364" s="2" t="s">
-        <v>2945</v>
+        <v>1839</v>
       </c>
       <c r="F1364" s="2">
         <v>0</v>
@@ -45326,25 +45362,25 @@
         <v>1364</v>
       </c>
       <c r="B1365" s="2" t="s">
-        <v>1603</v>
+        <v>2937</v>
       </c>
       <c r="C1365" s="2" t="s">
-        <v>1604</v>
+        <v>2938</v>
       </c>
       <c r="D1365" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1365" s="2" t="s">
-        <v>2946</v>
+        <v>2848</v>
       </c>
       <c r="F1365" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1365" s="2">
         <v>0</v>
       </c>
       <c r="H1365" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1366" spans="1:8" x14ac:dyDescent="0.25">
@@ -45352,25 +45388,25 @@
         <v>1365</v>
       </c>
       <c r="B1366" s="2" t="s">
-        <v>1605</v>
+        <v>2939</v>
       </c>
       <c r="C1366" s="2" t="s">
-        <v>1606</v>
+        <v>2940</v>
       </c>
       <c r="D1366" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1366" s="2" t="s">
-        <v>2945</v>
+        <v>2824</v>
       </c>
       <c r="F1366" s="2">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="G1366" s="2">
         <v>0</v>
       </c>
       <c r="H1366" s="2">
-        <v>16</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1367" spans="1:8" x14ac:dyDescent="0.25">
@@ -45378,25 +45414,25 @@
         <v>1366</v>
       </c>
       <c r="B1367" s="2" t="s">
-        <v>1159</v>
+        <v>2941</v>
       </c>
       <c r="C1367" s="2" t="s">
-        <v>1160</v>
+        <v>2942</v>
       </c>
       <c r="D1367" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1367" s="2" t="s">
-        <v>2915</v>
+        <v>2668</v>
       </c>
       <c r="F1367" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G1367" s="2">
         <v>0</v>
       </c>
       <c r="H1367" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1368" spans="1:8" x14ac:dyDescent="0.25">
@@ -45404,25 +45440,25 @@
         <v>1367</v>
       </c>
       <c r="B1368" s="2" t="s">
-        <v>1607</v>
+        <v>2943</v>
       </c>
       <c r="C1368" s="2" t="s">
-        <v>1608</v>
+        <v>2944</v>
       </c>
       <c r="D1368" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1368" s="2" t="s">
-        <v>2881</v>
+        <v>2945</v>
       </c>
       <c r="F1368" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1368" s="2">
         <v>0</v>
       </c>
       <c r="H1368" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1369" spans="1:8" x14ac:dyDescent="0.25">
@@ -45430,25 +45466,25 @@
         <v>1368</v>
       </c>
       <c r="B1369" s="2" t="s">
-        <v>1161</v>
+        <v>1603</v>
       </c>
       <c r="C1369" s="2" t="s">
-        <v>1162</v>
+        <v>1604</v>
       </c>
       <c r="D1369" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1369" s="2" t="s">
-        <v>2848</v>
+        <v>2946</v>
       </c>
       <c r="F1369" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1369" s="2">
         <v>0</v>
       </c>
       <c r="H1369" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1370" spans="1:8" x14ac:dyDescent="0.25">
@@ -45456,25 +45492,25 @@
         <v>1369</v>
       </c>
       <c r="B1370" s="2" t="s">
-        <v>1287</v>
+        <v>1605</v>
       </c>
       <c r="C1370" s="2" t="s">
-        <v>1288</v>
+        <v>1606</v>
       </c>
       <c r="D1370" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1370" s="2" t="s">
-        <v>2824</v>
+        <v>2945</v>
       </c>
       <c r="F1370" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="G1370" s="2">
         <v>0</v>
       </c>
       <c r="H1370" s="2">
-        <v>13</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1371" spans="1:8" x14ac:dyDescent="0.25">
@@ -45482,25 +45518,25 @@
         <v>1370</v>
       </c>
       <c r="B1371" s="2" t="s">
-        <v>2947</v>
+        <v>1159</v>
       </c>
       <c r="C1371" s="2" t="s">
-        <v>2948</v>
+        <v>1160</v>
       </c>
       <c r="D1371" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1371" s="2" t="s">
-        <v>2949</v>
+        <v>2915</v>
       </c>
       <c r="F1371" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G1371" s="2">
         <v>0</v>
       </c>
       <c r="H1371" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1372" spans="1:8" x14ac:dyDescent="0.25">
@@ -45508,25 +45544,25 @@
         <v>1371</v>
       </c>
       <c r="B1372" s="2" t="s">
-        <v>1163</v>
+        <v>1607</v>
       </c>
       <c r="C1372" s="2" t="s">
-        <v>1164</v>
+        <v>1608</v>
       </c>
       <c r="D1372" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1372" s="2" t="s">
-        <v>2825</v>
+        <v>2881</v>
       </c>
       <c r="F1372" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1372" s="2">
         <v>0</v>
       </c>
       <c r="H1372" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1373" spans="1:8" x14ac:dyDescent="0.25">
@@ -45534,25 +45570,25 @@
         <v>1372</v>
       </c>
       <c r="B1373" s="2" t="s">
-        <v>1165</v>
+        <v>1161</v>
       </c>
       <c r="C1373" s="2" t="s">
-        <v>1166</v>
+        <v>1162</v>
       </c>
       <c r="D1373" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1373" s="2" t="s">
-        <v>2825</v>
+        <v>2848</v>
       </c>
       <c r="F1373" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G1373" s="2">
         <v>0</v>
       </c>
       <c r="H1373" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1374" spans="1:8" x14ac:dyDescent="0.25">
@@ -45560,25 +45596,25 @@
         <v>1373</v>
       </c>
       <c r="B1374" s="2" t="s">
-        <v>1167</v>
+        <v>1287</v>
       </c>
       <c r="C1374" s="2" t="s">
-        <v>1168</v>
+        <v>1288</v>
       </c>
       <c r="D1374" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1374" s="2" t="s">
-        <v>2840</v>
+        <v>2824</v>
       </c>
       <c r="F1374" s="2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G1374" s="2">
         <v>0</v>
       </c>
       <c r="H1374" s="2">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1375" spans="1:8" x14ac:dyDescent="0.25">
@@ -45586,25 +45622,25 @@
         <v>1374</v>
       </c>
       <c r="B1375" s="2" t="s">
-        <v>1169</v>
+        <v>2947</v>
       </c>
       <c r="C1375" s="2" t="s">
-        <v>1170</v>
+        <v>2948</v>
       </c>
       <c r="D1375" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1375" s="2" t="s">
-        <v>2945</v>
+        <v>2949</v>
       </c>
       <c r="F1375" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1375" s="2">
         <v>0</v>
       </c>
       <c r="H1375" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1376" spans="1:8" x14ac:dyDescent="0.25">
@@ -45612,25 +45648,25 @@
         <v>1375</v>
       </c>
       <c r="B1376" s="2" t="s">
-        <v>2950</v>
+        <v>1163</v>
       </c>
       <c r="C1376" s="2" t="s">
-        <v>2951</v>
+        <v>1164</v>
       </c>
       <c r="D1376" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1376" s="2" t="s">
-        <v>1839</v>
+        <v>2825</v>
       </c>
       <c r="F1376" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1376" s="2">
         <v>0</v>
       </c>
       <c r="H1376" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1377" spans="1:8" x14ac:dyDescent="0.25">
@@ -45638,25 +45674,25 @@
         <v>1376</v>
       </c>
       <c r="B1377" s="2" t="s">
-        <v>1171</v>
+        <v>1165</v>
       </c>
       <c r="C1377" s="2" t="s">
-        <v>1172</v>
+        <v>1166</v>
       </c>
       <c r="D1377" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1377" s="2" t="s">
-        <v>2952</v>
+        <v>2825</v>
       </c>
       <c r="F1377" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G1377" s="2">
         <v>0</v>
       </c>
       <c r="H1377" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1378" spans="1:8" x14ac:dyDescent="0.25">
@@ -45664,25 +45700,25 @@
         <v>1377</v>
       </c>
       <c r="B1378" s="2" t="s">
-        <v>1609</v>
+        <v>1167</v>
       </c>
       <c r="C1378" s="2" t="s">
-        <v>1610</v>
+        <v>1168</v>
       </c>
       <c r="D1378" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1378" s="2" t="s">
-        <v>2953</v>
+        <v>2840</v>
       </c>
       <c r="F1378" s="2">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="G1378" s="2">
         <v>0</v>
       </c>
       <c r="H1378" s="2">
-        <v>15</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1379" spans="1:8" x14ac:dyDescent="0.25">
@@ -45690,25 +45726,25 @@
         <v>1378</v>
       </c>
       <c r="B1379" s="2" t="s">
-        <v>2954</v>
+        <v>1169</v>
       </c>
       <c r="C1379" s="2" t="s">
-        <v>2955</v>
+        <v>1170</v>
       </c>
       <c r="D1379" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1379" s="2" t="s">
-        <v>2949</v>
+        <v>2945</v>
       </c>
       <c r="F1379" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1379" s="2">
         <v>0</v>
       </c>
       <c r="H1379" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1380" spans="1:8" x14ac:dyDescent="0.25">
@@ -45716,25 +45752,25 @@
         <v>1379</v>
       </c>
       <c r="B1380" s="2" t="s">
-        <v>1173</v>
+        <v>2950</v>
       </c>
       <c r="C1380" s="2" t="s">
-        <v>1174</v>
+        <v>2951</v>
       </c>
       <c r="D1380" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1380" s="2" t="s">
-        <v>2946</v>
+        <v>1839</v>
       </c>
       <c r="F1380" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1380" s="2">
         <v>0</v>
       </c>
       <c r="H1380" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1381" spans="1:8" x14ac:dyDescent="0.25">
@@ -45742,25 +45778,25 @@
         <v>1380</v>
       </c>
       <c r="B1381" s="2" t="s">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="C1381" s="2" t="s">
-        <v>1176</v>
+        <v>1172</v>
       </c>
       <c r="D1381" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1381" s="2" t="s">
-        <v>2932</v>
+        <v>2952</v>
       </c>
       <c r="F1381" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G1381" s="2">
         <v>0</v>
       </c>
       <c r="H1381" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1382" spans="1:8" x14ac:dyDescent="0.25">
@@ -45768,25 +45804,25 @@
         <v>1381</v>
       </c>
       <c r="B1382" s="2" t="s">
-        <v>1177</v>
+        <v>1609</v>
       </c>
       <c r="C1382" s="2" t="s">
-        <v>1178</v>
+        <v>1610</v>
       </c>
       <c r="D1382" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1382" s="2" t="s">
-        <v>2868</v>
+        <v>2953</v>
       </c>
       <c r="F1382" s="2">
-        <v>3</v>
+        <v>15</v>
       </c>
       <c r="G1382" s="2">
         <v>0</v>
       </c>
       <c r="H1382" s="2">
-        <v>3</v>
+        <v>15</v>
       </c>
     </row>
     <row r="1383" spans="1:8" x14ac:dyDescent="0.25">
@@ -45794,25 +45830,25 @@
         <v>1382</v>
       </c>
       <c r="B1383" s="2" t="s">
-        <v>1179</v>
+        <v>2954</v>
       </c>
       <c r="C1383" s="2" t="s">
-        <v>1180</v>
+        <v>2955</v>
       </c>
       <c r="D1383" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1383" s="2" t="s">
-        <v>2868</v>
+        <v>2949</v>
       </c>
       <c r="F1383" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1383" s="2">
         <v>0</v>
       </c>
       <c r="H1383" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1384" spans="1:8" x14ac:dyDescent="0.25">
@@ -45820,16 +45856,16 @@
         <v>1383</v>
       </c>
       <c r="B1384" s="2" t="s">
-        <v>1611</v>
+        <v>1173</v>
       </c>
       <c r="C1384" s="2" t="s">
-        <v>1612</v>
+        <v>1174</v>
       </c>
       <c r="D1384" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1384" s="2" t="s">
-        <v>2953</v>
+        <v>2946</v>
       </c>
       <c r="F1384" s="2">
         <v>1</v>
@@ -45846,25 +45882,25 @@
         <v>1384</v>
       </c>
       <c r="B1385" s="2" t="s">
-        <v>2956</v>
+        <v>1175</v>
       </c>
       <c r="C1385" s="2" t="s">
-        <v>2957</v>
+        <v>1176</v>
       </c>
       <c r="D1385" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1385" s="2" t="s">
-        <v>2901</v>
+        <v>2932</v>
       </c>
       <c r="F1385" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G1385" s="2">
         <v>0</v>
       </c>
       <c r="H1385" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1386" spans="1:8" x14ac:dyDescent="0.25">
@@ -45872,25 +45908,25 @@
         <v>1385</v>
       </c>
       <c r="B1386" s="2" t="s">
-        <v>2958</v>
+        <v>1177</v>
       </c>
       <c r="C1386" s="2" t="s">
-        <v>2959</v>
+        <v>1178</v>
       </c>
       <c r="D1386" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1386" s="2" t="s">
-        <v>1839</v>
+        <v>2868</v>
       </c>
       <c r="F1386" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1386" s="2">
         <v>0</v>
       </c>
       <c r="H1386" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1387" spans="1:8" x14ac:dyDescent="0.25">
@@ -45898,25 +45934,25 @@
         <v>1386</v>
       </c>
       <c r="B1387" s="2" t="s">
-        <v>2960</v>
+        <v>1179</v>
       </c>
       <c r="C1387" s="2" t="s">
-        <v>2961</v>
+        <v>1180</v>
       </c>
       <c r="D1387" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1387" s="2" t="s">
-        <v>1840</v>
+        <v>2868</v>
       </c>
       <c r="F1387" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1387" s="2">
         <v>0</v>
       </c>
       <c r="H1387" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1388" spans="1:8" x14ac:dyDescent="0.25">
@@ -45924,25 +45960,25 @@
         <v>1387</v>
       </c>
       <c r="B1388" s="2" t="s">
-        <v>2962</v>
+        <v>1611</v>
       </c>
       <c r="C1388" s="2" t="s">
-        <v>2963</v>
+        <v>1612</v>
       </c>
       <c r="D1388" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1388" s="2" t="s">
-        <v>2830</v>
+        <v>2953</v>
       </c>
       <c r="F1388" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1388" s="2">
         <v>0</v>
       </c>
       <c r="H1388" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1389" spans="1:8" x14ac:dyDescent="0.25">
@@ -45950,16 +45986,16 @@
         <v>1388</v>
       </c>
       <c r="B1389" s="2" t="s">
-        <v>2964</v>
+        <v>2956</v>
       </c>
       <c r="C1389" s="2" t="s">
-        <v>2965</v>
+        <v>2957</v>
       </c>
       <c r="D1389" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1389" s="2" t="s">
-        <v>2830</v>
+        <v>2901</v>
       </c>
       <c r="F1389" s="2">
         <v>0</v>
@@ -45976,25 +46012,25 @@
         <v>1389</v>
       </c>
       <c r="B1390" s="2" t="s">
-        <v>1619</v>
+        <v>2958</v>
       </c>
       <c r="C1390" s="2" t="s">
-        <v>1620</v>
+        <v>2959</v>
       </c>
       <c r="D1390" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1390" s="2" t="s">
-        <v>2966</v>
+        <v>1839</v>
       </c>
       <c r="F1390" s="2">
-        <v>32</v>
+        <v>2</v>
       </c>
       <c r="G1390" s="2">
         <v>0</v>
       </c>
       <c r="H1390" s="2">
-        <v>32</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1391" spans="1:8" x14ac:dyDescent="0.25">
@@ -46002,16 +46038,16 @@
         <v>1390</v>
       </c>
       <c r="B1391" s="2" t="s">
-        <v>1181</v>
+        <v>2960</v>
       </c>
       <c r="C1391" s="2" t="s">
-        <v>1182</v>
+        <v>2961</v>
       </c>
       <c r="D1391" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1391" s="2" t="s">
-        <v>2967</v>
+        <v>1840</v>
       </c>
       <c r="F1391" s="2">
         <v>0</v>
@@ -46028,16 +46064,16 @@
         <v>1391</v>
       </c>
       <c r="B1392" s="2" t="s">
-        <v>2968</v>
+        <v>2962</v>
       </c>
       <c r="C1392" s="2" t="s">
-        <v>2969</v>
+        <v>2963</v>
       </c>
       <c r="D1392" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1392" s="2" t="s">
-        <v>2967</v>
+        <v>2830</v>
       </c>
       <c r="F1392" s="2">
         <v>0</v>
@@ -46054,25 +46090,25 @@
         <v>1392</v>
       </c>
       <c r="B1393" s="2" t="s">
-        <v>2970</v>
+        <v>2964</v>
       </c>
       <c r="C1393" s="2" t="s">
-        <v>2971</v>
+        <v>2965</v>
       </c>
       <c r="D1393" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1393" s="2" t="s">
-        <v>2915</v>
+        <v>2830</v>
       </c>
       <c r="F1393" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G1393" s="2">
         <v>0</v>
       </c>
       <c r="H1393" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1394" spans="1:8" x14ac:dyDescent="0.25">
@@ -46080,10 +46116,10 @@
         <v>1393</v>
       </c>
       <c r="B1394" s="2" t="s">
-        <v>1289</v>
+        <v>1619</v>
       </c>
       <c r="C1394" s="2" t="s">
-        <v>1290</v>
+        <v>1620</v>
       </c>
       <c r="D1394" s="2" t="s">
         <v>1623</v>
@@ -46092,13 +46128,13 @@
         <v>2966</v>
       </c>
       <c r="F1394" s="2">
-        <v>9</v>
+        <v>32</v>
       </c>
       <c r="G1394" s="2">
         <v>0</v>
       </c>
       <c r="H1394" s="2">
-        <v>9</v>
+        <v>32</v>
       </c>
     </row>
     <row r="1395" spans="1:8" x14ac:dyDescent="0.25">
@@ -46106,25 +46142,25 @@
         <v>1394</v>
       </c>
       <c r="B1395" s="2" t="s">
-        <v>2972</v>
+        <v>3149</v>
       </c>
       <c r="C1395" s="2" t="s">
-        <v>2973</v>
+        <v>3150</v>
       </c>
       <c r="D1395" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1395" s="2" t="s">
-        <v>2952</v>
+        <v>3151</v>
       </c>
       <c r="F1395" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1395" s="2">
         <v>0</v>
       </c>
       <c r="H1395" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1396" spans="1:8" x14ac:dyDescent="0.25">
@@ -46132,25 +46168,25 @@
         <v>1395</v>
       </c>
       <c r="B1396" s="2" t="s">
-        <v>1183</v>
+        <v>1181</v>
       </c>
       <c r="C1396" s="2" t="s">
-        <v>1184</v>
+        <v>1182</v>
       </c>
       <c r="D1396" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1396" s="2" t="s">
-        <v>2946</v>
+        <v>2967</v>
       </c>
       <c r="F1396" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="G1396" s="2">
         <v>0</v>
       </c>
       <c r="H1396" s="2">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1397" spans="1:8" x14ac:dyDescent="0.25">
@@ -46158,25 +46194,25 @@
         <v>1396</v>
       </c>
       <c r="B1397" s="2" t="s">
-        <v>1185</v>
+        <v>2968</v>
       </c>
       <c r="C1397" s="2" t="s">
-        <v>1186</v>
+        <v>2969</v>
       </c>
       <c r="D1397" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1397" s="2" t="s">
-        <v>2867</v>
+        <v>2967</v>
       </c>
       <c r="F1397" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="G1397" s="2">
         <v>0</v>
       </c>
       <c r="H1397" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1398" spans="1:8" x14ac:dyDescent="0.25">
@@ -46184,25 +46220,25 @@
         <v>1397</v>
       </c>
       <c r="B1398" s="2" t="s">
-        <v>2974</v>
+        <v>2970</v>
       </c>
       <c r="C1398" s="2" t="s">
-        <v>2975</v>
+        <v>2971</v>
       </c>
       <c r="D1398" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1398" s="2" t="s">
-        <v>1702</v>
+        <v>2915</v>
       </c>
       <c r="F1398" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G1398" s="2">
         <v>0</v>
       </c>
       <c r="H1398" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1399" spans="1:8" x14ac:dyDescent="0.25">
@@ -46210,25 +46246,25 @@
         <v>1398</v>
       </c>
       <c r="B1399" s="2" t="s">
-        <v>2976</v>
+        <v>1289</v>
       </c>
       <c r="C1399" s="2" t="s">
-        <v>2977</v>
+        <v>1290</v>
       </c>
       <c r="D1399" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1399" s="2" t="s">
-        <v>2914</v>
+        <v>2966</v>
       </c>
       <c r="F1399" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G1399" s="2">
         <v>0</v>
       </c>
       <c r="H1399" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1400" spans="1:8" x14ac:dyDescent="0.25">
@@ -46236,16 +46272,16 @@
         <v>1399</v>
       </c>
       <c r="B1400" s="2" t="s">
-        <v>2978</v>
+        <v>2972</v>
       </c>
       <c r="C1400" s="2" t="s">
-        <v>2979</v>
+        <v>2973</v>
       </c>
       <c r="D1400" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1400" s="2" t="s">
-        <v>2668</v>
+        <v>2952</v>
       </c>
       <c r="F1400" s="2">
         <v>0</v>
@@ -46262,25 +46298,25 @@
         <v>1400</v>
       </c>
       <c r="B1401" s="2" t="s">
-        <v>2980</v>
+        <v>1183</v>
       </c>
       <c r="C1401" s="2" t="s">
-        <v>2981</v>
+        <v>1184</v>
       </c>
       <c r="D1401" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1401" s="2" t="s">
-        <v>1738</v>
+        <v>2946</v>
       </c>
       <c r="F1401" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G1401" s="2">
         <v>0</v>
       </c>
       <c r="H1401" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1402" spans="1:8" x14ac:dyDescent="0.25">
@@ -46288,25 +46324,25 @@
         <v>1401</v>
       </c>
       <c r="B1402" s="2" t="s">
-        <v>2982</v>
+        <v>1185</v>
       </c>
       <c r="C1402" s="2" t="s">
-        <v>2983</v>
+        <v>1186</v>
       </c>
       <c r="D1402" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1402" s="2" t="s">
-        <v>2952</v>
+        <v>2867</v>
       </c>
       <c r="F1402" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
       <c r="G1402" s="2">
         <v>0</v>
       </c>
       <c r="H1402" s="2">
-        <v>1</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1403" spans="1:8" x14ac:dyDescent="0.25">
@@ -46314,16 +46350,16 @@
         <v>1402</v>
       </c>
       <c r="B1403" s="2" t="s">
-        <v>2984</v>
+        <v>2974</v>
       </c>
       <c r="C1403" s="2" t="s">
-        <v>2985</v>
+        <v>2975</v>
       </c>
       <c r="D1403" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1403" s="2" t="s">
-        <v>2833</v>
+        <v>1702</v>
       </c>
       <c r="F1403" s="2">
         <v>0</v>
@@ -46340,16 +46376,16 @@
         <v>1403</v>
       </c>
       <c r="B1404" s="2" t="s">
-        <v>2986</v>
+        <v>2976</v>
       </c>
       <c r="C1404" s="2" t="s">
-        <v>2987</v>
+        <v>2977</v>
       </c>
       <c r="D1404" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1404" s="2" t="s">
-        <v>2932</v>
+        <v>2914</v>
       </c>
       <c r="F1404" s="2">
         <v>0</v>
@@ -46366,25 +46402,25 @@
         <v>1404</v>
       </c>
       <c r="B1405" s="2" t="s">
-        <v>1291</v>
+        <v>2978</v>
       </c>
       <c r="C1405" s="2" t="s">
-        <v>1292</v>
+        <v>2979</v>
       </c>
       <c r="D1405" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1405" s="2" t="s">
-        <v>2914</v>
+        <v>2668</v>
       </c>
       <c r="F1405" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1405" s="2">
         <v>0</v>
       </c>
       <c r="H1405" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1406" spans="1:8" x14ac:dyDescent="0.25">
@@ -46392,25 +46428,25 @@
         <v>1405</v>
       </c>
       <c r="B1406" s="2" t="s">
-        <v>2988</v>
+        <v>2980</v>
       </c>
       <c r="C1406" s="2" t="s">
-        <v>2989</v>
+        <v>2981</v>
       </c>
       <c r="D1406" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1406" s="2" t="s">
-        <v>2949</v>
+        <v>1738</v>
       </c>
       <c r="F1406" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G1406" s="2">
         <v>0</v>
       </c>
       <c r="H1406" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1407" spans="1:8" x14ac:dyDescent="0.25">
@@ -46418,25 +46454,25 @@
         <v>1406</v>
       </c>
       <c r="B1407" s="2" t="s">
-        <v>2990</v>
+        <v>2982</v>
       </c>
       <c r="C1407" s="2" t="s">
-        <v>2991</v>
+        <v>2983</v>
       </c>
       <c r="D1407" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1407" s="2" t="s">
-        <v>2868</v>
+        <v>2952</v>
       </c>
       <c r="F1407" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="G1407" s="2">
         <v>0</v>
       </c>
       <c r="H1407" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1408" spans="1:8" x14ac:dyDescent="0.25">
@@ -46444,16 +46480,16 @@
         <v>1407</v>
       </c>
       <c r="B1408" s="2" t="s">
-        <v>2992</v>
+        <v>2984</v>
       </c>
       <c r="C1408" s="2" t="s">
-        <v>2993</v>
+        <v>2985</v>
       </c>
       <c r="D1408" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1408" s="2" t="s">
-        <v>2840</v>
+        <v>2833</v>
       </c>
       <c r="F1408" s="2">
         <v>0</v>
@@ -46470,25 +46506,25 @@
         <v>1408</v>
       </c>
       <c r="B1409" s="2" t="s">
-        <v>1293</v>
+        <v>2986</v>
       </c>
       <c r="C1409" s="2" t="s">
-        <v>1294</v>
+        <v>2987</v>
       </c>
       <c r="D1409" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1409" s="2" t="s">
-        <v>2994</v>
+        <v>2932</v>
       </c>
       <c r="F1409" s="2">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="G1409" s="2">
         <v>0</v>
       </c>
       <c r="H1409" s="2">
-        <v>11</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1410" spans="1:8" x14ac:dyDescent="0.25">
@@ -46496,25 +46532,25 @@
         <v>1409</v>
       </c>
       <c r="B1410" s="2" t="s">
-        <v>1338</v>
+        <v>1291</v>
       </c>
       <c r="C1410" s="2" t="s">
-        <v>1339</v>
+        <v>1292</v>
       </c>
       <c r="D1410" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1410" s="2" t="s">
-        <v>2854</v>
+        <v>2914</v>
       </c>
       <c r="F1410" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1410" s="2">
         <v>0</v>
       </c>
       <c r="H1410" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1411" spans="1:8" x14ac:dyDescent="0.25">
@@ -46522,25 +46558,25 @@
         <v>1410</v>
       </c>
       <c r="B1411" s="2" t="s">
-        <v>2995</v>
+        <v>2988</v>
       </c>
       <c r="C1411" s="2" t="s">
-        <v>2996</v>
+        <v>2989</v>
       </c>
       <c r="D1411" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1411" s="2" t="s">
-        <v>2997</v>
+        <v>2949</v>
       </c>
       <c r="F1411" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G1411" s="2">
         <v>0</v>
       </c>
       <c r="H1411" s="2">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1412" spans="1:8" x14ac:dyDescent="0.25">
@@ -46548,25 +46584,25 @@
         <v>1411</v>
       </c>
       <c r="B1412" s="2" t="s">
-        <v>2998</v>
+        <v>2990</v>
       </c>
       <c r="C1412" s="2" t="s">
-        <v>2999</v>
+        <v>2991</v>
       </c>
       <c r="D1412" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1412" s="2" t="s">
-        <v>1738</v>
+        <v>2868</v>
       </c>
       <c r="F1412" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="G1412" s="2">
         <v>0</v>
       </c>
       <c r="H1412" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1413" spans="1:8" x14ac:dyDescent="0.25">
@@ -46574,25 +46610,25 @@
         <v>1412</v>
       </c>
       <c r="B1413" s="2" t="s">
-        <v>3000</v>
+        <v>2992</v>
       </c>
       <c r="C1413" s="2" t="s">
-        <v>3001</v>
+        <v>2993</v>
       </c>
       <c r="D1413" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1413" s="2" t="s">
-        <v>1738</v>
+        <v>2840</v>
       </c>
       <c r="F1413" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1413" s="2">
         <v>0</v>
       </c>
       <c r="H1413" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1414" spans="1:8" x14ac:dyDescent="0.25">
@@ -46600,25 +46636,25 @@
         <v>1413</v>
       </c>
       <c r="B1414" s="2" t="s">
-        <v>3002</v>
+        <v>1293</v>
       </c>
       <c r="C1414" s="2" t="s">
-        <v>3003</v>
+        <v>1294</v>
       </c>
       <c r="D1414" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1414" s="2" t="s">
-        <v>1738</v>
+        <v>2994</v>
       </c>
       <c r="F1414" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G1414" s="2">
         <v>0</v>
       </c>
       <c r="H1414" s="2">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1415" spans="1:8" x14ac:dyDescent="0.25">
@@ -46626,25 +46662,25 @@
         <v>1414</v>
       </c>
       <c r="B1415" s="2" t="s">
-        <v>3004</v>
+        <v>1338</v>
       </c>
       <c r="C1415" s="2" t="s">
-        <v>3005</v>
+        <v>1339</v>
       </c>
       <c r="D1415" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1415" s="2" t="s">
-        <v>2668</v>
+        <v>2854</v>
       </c>
       <c r="F1415" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G1415" s="2">
         <v>0</v>
       </c>
       <c r="H1415" s="2">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1416" spans="1:8" x14ac:dyDescent="0.25">
@@ -46652,16 +46688,16 @@
         <v>1415</v>
       </c>
       <c r="B1416" s="2" t="s">
-        <v>3006</v>
+        <v>2995</v>
       </c>
       <c r="C1416" s="2" t="s">
-        <v>3007</v>
+        <v>2996</v>
       </c>
       <c r="D1416" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1416" s="2" t="s">
-        <v>1839</v>
+        <v>2997</v>
       </c>
       <c r="F1416" s="2">
         <v>0</v>
@@ -46678,25 +46714,25 @@
         <v>1416</v>
       </c>
       <c r="B1417" s="2" t="s">
-        <v>3008</v>
+        <v>2998</v>
       </c>
       <c r="C1417" s="2" t="s">
-        <v>3009</v>
+        <v>2999</v>
       </c>
       <c r="D1417" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1417" s="2" t="s">
-        <v>2949</v>
+        <v>1738</v>
       </c>
       <c r="F1417" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1417" s="2">
         <v>0</v>
       </c>
       <c r="H1417" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1418" spans="1:8" x14ac:dyDescent="0.25">
@@ -46704,25 +46740,25 @@
         <v>1417</v>
       </c>
       <c r="B1418" s="2" t="s">
-        <v>3010</v>
+        <v>3000</v>
       </c>
       <c r="C1418" s="2" t="s">
-        <v>3011</v>
+        <v>3001</v>
       </c>
       <c r="D1418" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1418" s="2" t="s">
-        <v>3012</v>
+        <v>1738</v>
       </c>
       <c r="F1418" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1418" s="2">
         <v>0</v>
       </c>
       <c r="H1418" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1419" spans="1:8" x14ac:dyDescent="0.25">
@@ -46730,25 +46766,25 @@
         <v>1418</v>
       </c>
       <c r="B1419" s="2" t="s">
-        <v>1187</v>
+        <v>3002</v>
       </c>
       <c r="C1419" s="2" t="s">
-        <v>1188</v>
+        <v>3003</v>
       </c>
       <c r="D1419" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1419" s="2" t="s">
-        <v>2909</v>
+        <v>1738</v>
       </c>
       <c r="F1419" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1419" s="2">
         <v>0</v>
       </c>
       <c r="H1419" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1420" spans="1:8" x14ac:dyDescent="0.25">
@@ -46756,25 +46792,25 @@
         <v>1419</v>
       </c>
       <c r="B1420" s="2" t="s">
-        <v>1295</v>
+        <v>3004</v>
       </c>
       <c r="C1420" s="2" t="s">
-        <v>1296</v>
+        <v>3005</v>
       </c>
       <c r="D1420" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1420" s="2" t="s">
-        <v>2997</v>
+        <v>2668</v>
       </c>
       <c r="F1420" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1420" s="2">
         <v>0</v>
       </c>
       <c r="H1420" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1421" spans="1:8" x14ac:dyDescent="0.25">
@@ -46782,16 +46818,16 @@
         <v>1420</v>
       </c>
       <c r="B1421" s="2" t="s">
-        <v>3013</v>
+        <v>3006</v>
       </c>
       <c r="C1421" s="2" t="s">
-        <v>3014</v>
+        <v>3007</v>
       </c>
       <c r="D1421" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1421" s="2" t="s">
-        <v>2876</v>
+        <v>1839</v>
       </c>
       <c r="F1421" s="2">
         <v>0</v>
@@ -46808,25 +46844,25 @@
         <v>1421</v>
       </c>
       <c r="B1422" s="2" t="s">
-        <v>1321</v>
+        <v>3008</v>
       </c>
       <c r="C1422" s="2" t="s">
-        <v>1322</v>
+        <v>3009</v>
       </c>
       <c r="D1422" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1422" s="2" t="s">
-        <v>2868</v>
+        <v>2949</v>
       </c>
       <c r="F1422" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="G1422" s="2">
         <v>0</v>
       </c>
       <c r="H1422" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1423" spans="1:8" x14ac:dyDescent="0.25">
@@ -46834,25 +46870,25 @@
         <v>1422</v>
       </c>
       <c r="B1423" s="2" t="s">
-        <v>1613</v>
+        <v>3010</v>
       </c>
       <c r="C1423" s="2" t="s">
-        <v>1614</v>
+        <v>3011</v>
       </c>
       <c r="D1423" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1423" s="2" t="s">
-        <v>3015</v>
+        <v>3012</v>
       </c>
       <c r="F1423" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G1423" s="2">
         <v>0</v>
       </c>
       <c r="H1423" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1424" spans="1:8" x14ac:dyDescent="0.25">
@@ -46860,25 +46896,25 @@
         <v>1423</v>
       </c>
       <c r="B1424" s="2" t="s">
-        <v>3016</v>
+        <v>1187</v>
       </c>
       <c r="C1424" s="2" t="s">
-        <v>3017</v>
+        <v>1188</v>
       </c>
       <c r="D1424" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1424" s="2" t="s">
-        <v>2845</v>
+        <v>2909</v>
       </c>
       <c r="F1424" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1424" s="2">
         <v>0</v>
       </c>
       <c r="H1424" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1425" spans="1:8" x14ac:dyDescent="0.25">
@@ -46886,25 +46922,25 @@
         <v>1424</v>
       </c>
       <c r="B1425" s="2" t="s">
-        <v>1297</v>
+        <v>1295</v>
       </c>
       <c r="C1425" s="2" t="s">
-        <v>1298</v>
+        <v>1296</v>
       </c>
       <c r="D1425" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1425" s="2" t="s">
-        <v>2994</v>
+        <v>2997</v>
       </c>
       <c r="F1425" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G1425" s="2">
         <v>0</v>
       </c>
       <c r="H1425" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1426" spans="1:8" x14ac:dyDescent="0.25">
@@ -46912,16 +46948,16 @@
         <v>1425</v>
       </c>
       <c r="B1426" s="2" t="s">
-        <v>1340</v>
+        <v>3013</v>
       </c>
       <c r="C1426" s="2" t="s">
-        <v>1341</v>
+        <v>3014</v>
       </c>
       <c r="D1426" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1426" s="2" t="s">
-        <v>2854</v>
+        <v>2876</v>
       </c>
       <c r="F1426" s="2">
         <v>0</v>
@@ -46938,25 +46974,25 @@
         <v>1426</v>
       </c>
       <c r="B1427" s="2" t="s">
-        <v>1299</v>
+        <v>1321</v>
       </c>
       <c r="C1427" s="2" t="s">
-        <v>1300</v>
+        <v>1322</v>
       </c>
       <c r="D1427" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1427" s="2" t="s">
-        <v>2909</v>
+        <v>2868</v>
       </c>
       <c r="F1427" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="G1427" s="2">
         <v>0</v>
       </c>
       <c r="H1427" s="2">
-        <v>0</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1428" spans="1:8" x14ac:dyDescent="0.25">
@@ -46964,25 +47000,25 @@
         <v>1427</v>
       </c>
       <c r="B1428" s="2" t="s">
-        <v>3018</v>
+        <v>1613</v>
       </c>
       <c r="C1428" s="2" t="s">
-        <v>3019</v>
+        <v>1614</v>
       </c>
       <c r="D1428" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1428" s="2" t="s">
-        <v>1738</v>
+        <v>3015</v>
       </c>
       <c r="F1428" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G1428" s="2">
         <v>0</v>
       </c>
       <c r="H1428" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1429" spans="1:8" x14ac:dyDescent="0.25">
@@ -46990,25 +47026,25 @@
         <v>1428</v>
       </c>
       <c r="B1429" s="2" t="s">
-        <v>3020</v>
+        <v>3016</v>
       </c>
       <c r="C1429" s="2" t="s">
-        <v>3021</v>
+        <v>3017</v>
       </c>
       <c r="D1429" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1429" s="2" t="s">
-        <v>3022</v>
+        <v>2845</v>
       </c>
       <c r="F1429" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1429" s="2">
         <v>0</v>
       </c>
       <c r="H1429" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1430" spans="1:8" x14ac:dyDescent="0.25">
@@ -47016,25 +47052,25 @@
         <v>1429</v>
       </c>
       <c r="B1430" s="2" t="s">
-        <v>3023</v>
+        <v>1297</v>
       </c>
       <c r="C1430" s="2" t="s">
-        <v>3024</v>
+        <v>1298</v>
       </c>
       <c r="D1430" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1430" s="2" t="s">
-        <v>3012</v>
+        <v>2994</v>
       </c>
       <c r="F1430" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1430" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1430" s="2">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1431" spans="1:8" x14ac:dyDescent="0.25">
@@ -47042,16 +47078,16 @@
         <v>1430</v>
       </c>
       <c r="B1431" s="2" t="s">
-        <v>1189</v>
+        <v>1340</v>
       </c>
       <c r="C1431" s="2" t="s">
-        <v>1190</v>
+        <v>1341</v>
       </c>
       <c r="D1431" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1431" s="2" t="s">
-        <v>2867</v>
+        <v>2854</v>
       </c>
       <c r="F1431" s="2">
         <v>0</v>
@@ -47068,16 +47104,16 @@
         <v>1431</v>
       </c>
       <c r="B1432" s="2" t="s">
-        <v>1191</v>
+        <v>1299</v>
       </c>
       <c r="C1432" s="2" t="s">
-        <v>1192</v>
+        <v>1300</v>
       </c>
       <c r="D1432" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1432" s="2" t="s">
-        <v>2825</v>
+        <v>2909</v>
       </c>
       <c r="F1432" s="2">
         <v>0</v>
@@ -47094,25 +47130,25 @@
         <v>1432</v>
       </c>
       <c r="B1433" s="2" t="s">
-        <v>1193</v>
+        <v>3018</v>
       </c>
       <c r="C1433" s="2" t="s">
-        <v>1194</v>
+        <v>3019</v>
       </c>
       <c r="D1433" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1433" s="2" t="s">
-        <v>2876</v>
+        <v>1738</v>
       </c>
       <c r="F1433" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1433" s="2">
         <v>0</v>
       </c>
       <c r="H1433" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1434" spans="1:8" x14ac:dyDescent="0.25">
@@ -47120,25 +47156,25 @@
         <v>1433</v>
       </c>
       <c r="B1434" s="2" t="s">
-        <v>1195</v>
+        <v>3020</v>
       </c>
       <c r="C1434" s="2" t="s">
-        <v>1196</v>
+        <v>3021</v>
       </c>
       <c r="D1434" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1434" s="2" t="s">
-        <v>3012</v>
+        <v>3022</v>
       </c>
       <c r="F1434" s="2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="G1434" s="2">
         <v>0</v>
       </c>
       <c r="H1434" s="2">
-        <v>9</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1435" spans="1:8" x14ac:dyDescent="0.25">
@@ -47146,25 +47182,25 @@
         <v>1434</v>
       </c>
       <c r="B1435" s="2" t="s">
-        <v>1197</v>
+        <v>3023</v>
       </c>
       <c r="C1435" s="2" t="s">
-        <v>1198</v>
+        <v>3024</v>
       </c>
       <c r="D1435" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1435" s="2" t="s">
-        <v>2901</v>
+        <v>3012</v>
       </c>
       <c r="F1435" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="G1435" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1435" s="2">
-        <v>8</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1436" spans="1:8" x14ac:dyDescent="0.25">
@@ -47172,25 +47208,25 @@
         <v>1435</v>
       </c>
       <c r="B1436" s="2" t="s">
-        <v>1199</v>
+        <v>1189</v>
       </c>
       <c r="C1436" s="2" t="s">
-        <v>1200</v>
+        <v>1190</v>
       </c>
       <c r="D1436" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1436" s="2" t="s">
-        <v>2966</v>
+        <v>2867</v>
       </c>
       <c r="F1436" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="G1436" s="2">
         <v>0</v>
       </c>
       <c r="H1436" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1437" spans="1:8" x14ac:dyDescent="0.25">
@@ -47198,25 +47234,25 @@
         <v>1436</v>
       </c>
       <c r="B1437" s="2" t="s">
-        <v>1301</v>
+        <v>1191</v>
       </c>
       <c r="C1437" s="2" t="s">
-        <v>1302</v>
+        <v>1192</v>
       </c>
       <c r="D1437" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1437" s="2" t="s">
-        <v>2994</v>
+        <v>2825</v>
       </c>
       <c r="F1437" s="2">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="G1437" s="2">
         <v>0</v>
       </c>
       <c r="H1437" s="2">
-        <v>13</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1438" spans="1:8" x14ac:dyDescent="0.25">
@@ -47224,16 +47260,16 @@
         <v>1437</v>
       </c>
       <c r="B1438" s="2" t="s">
-        <v>1352</v>
+        <v>1193</v>
       </c>
       <c r="C1438" s="2" t="s">
-        <v>1353</v>
+        <v>1194</v>
       </c>
       <c r="D1438" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1438" s="2" t="s">
-        <v>2854</v>
+        <v>2876</v>
       </c>
       <c r="F1438" s="2">
         <v>0</v>
@@ -47250,25 +47286,25 @@
         <v>1438</v>
       </c>
       <c r="B1439" s="2" t="s">
-        <v>1303</v>
+        <v>1195</v>
       </c>
       <c r="C1439" s="2" t="s">
-        <v>1304</v>
+        <v>1196</v>
       </c>
       <c r="D1439" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1439" s="2" t="s">
-        <v>2909</v>
+        <v>3012</v>
       </c>
       <c r="F1439" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G1439" s="2">
         <v>0</v>
       </c>
       <c r="H1439" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1440" spans="1:8" x14ac:dyDescent="0.25">
@@ -47276,25 +47312,25 @@
         <v>1439</v>
       </c>
       <c r="B1440" s="2" t="s">
-        <v>1615</v>
+        <v>1197</v>
       </c>
       <c r="C1440" s="2" t="s">
-        <v>1616</v>
+        <v>1198</v>
       </c>
       <c r="D1440" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1440" s="2" t="s">
-        <v>3025</v>
+        <v>2901</v>
       </c>
       <c r="F1440" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="G1440" s="2">
         <v>0</v>
       </c>
       <c r="H1440" s="2">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1441" spans="1:8" x14ac:dyDescent="0.25">
@@ -47302,25 +47338,25 @@
         <v>1440</v>
       </c>
       <c r="B1441" s="2" t="s">
-        <v>1305</v>
+        <v>1199</v>
       </c>
       <c r="C1441" s="2" t="s">
-        <v>1306</v>
+        <v>1200</v>
       </c>
       <c r="D1441" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1441" s="2" t="s">
-        <v>3012</v>
+        <v>2966</v>
       </c>
       <c r="F1441" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G1441" s="2">
         <v>0</v>
       </c>
       <c r="H1441" s="2">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1442" spans="1:8" x14ac:dyDescent="0.25">
@@ -47328,25 +47364,25 @@
         <v>1441</v>
       </c>
       <c r="B1442" s="2" t="s">
-        <v>1201</v>
+        <v>1301</v>
       </c>
       <c r="C1442" s="2" t="s">
-        <v>1202</v>
+        <v>1302</v>
       </c>
       <c r="D1442" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1442" s="2" t="s">
-        <v>2867</v>
+        <v>2994</v>
       </c>
       <c r="F1442" s="2">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="G1442" s="2">
         <v>0</v>
       </c>
       <c r="H1442" s="2">
-        <v>0</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1443" spans="1:8" x14ac:dyDescent="0.25">
@@ -47354,16 +47390,16 @@
         <v>1442</v>
       </c>
       <c r="B1443" s="2" t="s">
-        <v>1203</v>
+        <v>1352</v>
       </c>
       <c r="C1443" s="2" t="s">
-        <v>1204</v>
+        <v>1353</v>
       </c>
       <c r="D1443" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1443" s="2" t="s">
-        <v>2932</v>
+        <v>2854</v>
       </c>
       <c r="F1443" s="2">
         <v>0</v>
@@ -47380,16 +47416,16 @@
         <v>1443</v>
       </c>
       <c r="B1444" s="2" t="s">
-        <v>1205</v>
+        <v>1303</v>
       </c>
       <c r="C1444" s="2" t="s">
-        <v>1206</v>
+        <v>1304</v>
       </c>
       <c r="D1444" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1444" s="2" t="s">
-        <v>2945</v>
+        <v>2909</v>
       </c>
       <c r="F1444" s="2">
         <v>0</v>
@@ -47406,25 +47442,25 @@
         <v>1444</v>
       </c>
       <c r="B1445" s="2" t="s">
-        <v>1207</v>
+        <v>1615</v>
       </c>
       <c r="C1445" s="2" t="s">
-        <v>1208</v>
+        <v>1616</v>
       </c>
       <c r="D1445" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1445" s="2" t="s">
-        <v>2868</v>
+        <v>3025</v>
       </c>
       <c r="F1445" s="2">
-        <v>19</v>
+        <v>3</v>
       </c>
       <c r="G1445" s="2">
         <v>0</v>
       </c>
       <c r="H1445" s="2">
-        <v>19</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1446" spans="1:8" x14ac:dyDescent="0.25">
@@ -47432,25 +47468,25 @@
         <v>1445</v>
       </c>
       <c r="B1446" s="2" t="s">
-        <v>1209</v>
+        <v>1305</v>
       </c>
       <c r="C1446" s="2" t="s">
-        <v>1210</v>
+        <v>1306</v>
       </c>
       <c r="D1446" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1446" s="2" t="s">
-        <v>2845</v>
+        <v>3012</v>
       </c>
       <c r="F1446" s="2">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="G1446" s="2">
         <v>0</v>
       </c>
       <c r="H1446" s="2">
-        <v>12</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1447" spans="1:8" x14ac:dyDescent="0.25">
@@ -47458,25 +47494,25 @@
         <v>1446</v>
       </c>
       <c r="B1447" s="2" t="s">
-        <v>1211</v>
+        <v>1201</v>
       </c>
       <c r="C1447" s="2" t="s">
-        <v>1212</v>
+        <v>1202</v>
       </c>
       <c r="D1447" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1447" s="2" t="s">
-        <v>2915</v>
+        <v>2867</v>
       </c>
       <c r="F1447" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1447" s="2">
         <v>0</v>
       </c>
       <c r="H1447" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1448" spans="1:8" x14ac:dyDescent="0.25">
@@ -47484,25 +47520,25 @@
         <v>1447</v>
       </c>
       <c r="B1448" s="2" t="s">
-        <v>1307</v>
+        <v>1203</v>
       </c>
       <c r="C1448" s="2" t="s">
-        <v>1308</v>
+        <v>1204</v>
       </c>
       <c r="D1448" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1448" s="2" t="s">
-        <v>2994</v>
+        <v>2932</v>
       </c>
       <c r="F1448" s="2">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="G1448" s="2">
         <v>0</v>
       </c>
       <c r="H1448" s="2">
-        <v>16</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1449" spans="1:8" x14ac:dyDescent="0.25">
@@ -47510,25 +47546,25 @@
         <v>1448</v>
       </c>
       <c r="B1449" s="2" t="s">
-        <v>1319</v>
+        <v>1205</v>
       </c>
       <c r="C1449" s="2" t="s">
-        <v>1320</v>
+        <v>1206</v>
       </c>
       <c r="D1449" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1449" s="2" t="s">
-        <v>2860</v>
+        <v>2945</v>
       </c>
       <c r="F1449" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1449" s="2">
         <v>0</v>
       </c>
       <c r="H1449" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1450" spans="1:8" x14ac:dyDescent="0.25">
@@ -47536,25 +47572,25 @@
         <v>1449</v>
       </c>
       <c r="B1450" s="2" t="s">
-        <v>3026</v>
+        <v>1207</v>
       </c>
       <c r="C1450" s="2" t="s">
-        <v>3027</v>
+        <v>1208</v>
       </c>
       <c r="D1450" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1450" s="2" t="s">
-        <v>2909</v>
+        <v>2868</v>
       </c>
       <c r="F1450" s="2">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G1450" s="2">
         <v>0</v>
       </c>
       <c r="H1450" s="2">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1451" spans="1:8" x14ac:dyDescent="0.25">
@@ -47562,25 +47598,25 @@
         <v>1450</v>
       </c>
       <c r="B1451" s="2" t="s">
-        <v>3028</v>
+        <v>1209</v>
       </c>
       <c r="C1451" s="2" t="s">
-        <v>3029</v>
+        <v>1210</v>
       </c>
       <c r="D1451" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1451" s="2" t="s">
-        <v>2668</v>
+        <v>2845</v>
       </c>
       <c r="F1451" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
       <c r="G1451" s="2">
         <v>0</v>
       </c>
       <c r="H1451" s="2">
-        <v>1</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1452" spans="1:8" x14ac:dyDescent="0.25">
@@ -47588,25 +47624,25 @@
         <v>1451</v>
       </c>
       <c r="B1452" s="2" t="s">
-        <v>3030</v>
+        <v>1211</v>
       </c>
       <c r="C1452" s="2" t="s">
-        <v>3031</v>
+        <v>1212</v>
       </c>
       <c r="D1452" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1452" s="2" t="s">
-        <v>3025</v>
+        <v>2915</v>
       </c>
       <c r="F1452" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1452" s="2">
         <v>0</v>
       </c>
       <c r="H1452" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1453" spans="1:8" x14ac:dyDescent="0.25">
@@ -47614,25 +47650,25 @@
         <v>1452</v>
       </c>
       <c r="B1453" s="2" t="s">
-        <v>3032</v>
+        <v>1307</v>
       </c>
       <c r="C1453" s="2" t="s">
-        <v>3033</v>
+        <v>1308</v>
       </c>
       <c r="D1453" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1453" s="2" t="s">
-        <v>2869</v>
+        <v>2994</v>
       </c>
       <c r="F1453" s="2">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="G1453" s="2">
         <v>0</v>
       </c>
       <c r="H1453" s="2">
-        <v>0</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1454" spans="1:8" x14ac:dyDescent="0.25">
@@ -47640,25 +47676,25 @@
         <v>1453</v>
       </c>
       <c r="B1454" s="2" t="s">
-        <v>3034</v>
+        <v>1319</v>
       </c>
       <c r="C1454" s="2" t="s">
-        <v>3035</v>
+        <v>1320</v>
       </c>
       <c r="D1454" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1454" s="2" t="s">
-        <v>2994</v>
+        <v>2860</v>
       </c>
       <c r="F1454" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1454" s="2">
         <v>0</v>
       </c>
       <c r="H1454" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1455" spans="1:8" x14ac:dyDescent="0.25">
@@ -47666,25 +47702,25 @@
         <v>1454</v>
       </c>
       <c r="B1455" s="2" t="s">
-        <v>1342</v>
+        <v>3026</v>
       </c>
       <c r="C1455" s="2" t="s">
-        <v>1343</v>
+        <v>3027</v>
       </c>
       <c r="D1455" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1455" s="2" t="s">
-        <v>2860</v>
+        <v>2909</v>
       </c>
       <c r="F1455" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1455" s="2">
         <v>0</v>
       </c>
       <c r="H1455" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1456" spans="1:8" x14ac:dyDescent="0.25">
@@ -47692,25 +47728,25 @@
         <v>1455</v>
       </c>
       <c r="B1456" s="2" t="s">
-        <v>3036</v>
+        <v>3028</v>
       </c>
       <c r="C1456" s="2" t="s">
-        <v>3037</v>
+        <v>3029</v>
       </c>
       <c r="D1456" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1456" s="2" t="s">
-        <v>2909</v>
+        <v>2668</v>
       </c>
       <c r="F1456" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1456" s="2">
         <v>0</v>
       </c>
       <c r="H1456" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1457" spans="1:8" x14ac:dyDescent="0.25">
@@ -47718,25 +47754,25 @@
         <v>1456</v>
       </c>
       <c r="B1457" s="2" t="s">
-        <v>1309</v>
+        <v>3030</v>
       </c>
       <c r="C1457" s="2" t="s">
-        <v>1310</v>
+        <v>3031</v>
       </c>
       <c r="D1457" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1457" s="2" t="s">
-        <v>1626</v>
+        <v>3025</v>
       </c>
       <c r="F1457" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1457" s="2">
         <v>0</v>
       </c>
       <c r="H1457" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1458" spans="1:8" x14ac:dyDescent="0.25">
@@ -47744,16 +47780,16 @@
         <v>1457</v>
       </c>
       <c r="B1458" s="2" t="s">
-        <v>1311</v>
+        <v>3032</v>
       </c>
       <c r="C1458" s="2" t="s">
-        <v>1312</v>
+        <v>3033</v>
       </c>
       <c r="D1458" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1458" s="2" t="s">
-        <v>1626</v>
+        <v>2869</v>
       </c>
       <c r="F1458" s="2">
         <v>0</v>
@@ -47770,25 +47806,25 @@
         <v>1458</v>
       </c>
       <c r="B1459" s="2" t="s">
-        <v>3038</v>
+        <v>3034</v>
       </c>
       <c r="C1459" s="2" t="s">
-        <v>3039</v>
+        <v>3035</v>
       </c>
       <c r="D1459" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1459" s="2" t="s">
-        <v>2953</v>
+        <v>2994</v>
       </c>
       <c r="F1459" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1459" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1459" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1460" spans="1:8" x14ac:dyDescent="0.25">
@@ -47796,16 +47832,16 @@
         <v>1459</v>
       </c>
       <c r="B1460" s="2" t="s">
-        <v>3040</v>
+        <v>1342</v>
       </c>
       <c r="C1460" s="2" t="s">
-        <v>3041</v>
+        <v>1343</v>
       </c>
       <c r="D1460" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1460" s="2" t="s">
-        <v>3042</v>
+        <v>2860</v>
       </c>
       <c r="F1460" s="2">
         <v>1</v>
@@ -47822,25 +47858,25 @@
         <v>1460</v>
       </c>
       <c r="B1461" s="2" t="s">
-        <v>3043</v>
+        <v>3036</v>
       </c>
       <c r="C1461" s="2" t="s">
-        <v>3044</v>
+        <v>3037</v>
       </c>
       <c r="D1461" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1461" s="2" t="s">
-        <v>2997</v>
+        <v>2909</v>
       </c>
       <c r="F1461" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1461" s="2">
         <v>0</v>
       </c>
       <c r="H1461" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1462" spans="1:8" x14ac:dyDescent="0.25">
@@ -47848,16 +47884,16 @@
         <v>1461</v>
       </c>
       <c r="B1462" s="2" t="s">
-        <v>3045</v>
+        <v>1309</v>
       </c>
       <c r="C1462" s="2" t="s">
-        <v>3046</v>
+        <v>1310</v>
       </c>
       <c r="D1462" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1462" s="2" t="s">
-        <v>2952</v>
+        <v>1626</v>
       </c>
       <c r="F1462" s="2">
         <v>0</v>
@@ -47874,25 +47910,25 @@
         <v>1462</v>
       </c>
       <c r="B1463" s="2" t="s">
-        <v>1313</v>
+        <v>1311</v>
       </c>
       <c r="C1463" s="2" t="s">
-        <v>1314</v>
+        <v>1312</v>
       </c>
       <c r="D1463" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1463" s="2" t="s">
-        <v>2997</v>
+        <v>1626</v>
       </c>
       <c r="F1463" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1463" s="2">
         <v>0</v>
       </c>
       <c r="H1463" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1464" spans="1:8" x14ac:dyDescent="0.25">
@@ -47900,25 +47936,25 @@
         <v>1463</v>
       </c>
       <c r="B1464" s="2" t="s">
-        <v>3047</v>
+        <v>3038</v>
       </c>
       <c r="C1464" s="2" t="s">
-        <v>3048</v>
+        <v>3039</v>
       </c>
       <c r="D1464" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1464" s="2" t="s">
-        <v>3042</v>
+        <v>2953</v>
       </c>
       <c r="F1464" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1464" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1464" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1465" spans="1:8" x14ac:dyDescent="0.25">
@@ -47926,25 +47962,25 @@
         <v>1464</v>
       </c>
       <c r="B1465" s="2" t="s">
-        <v>1315</v>
+        <v>3040</v>
       </c>
       <c r="C1465" s="2" t="s">
-        <v>1316</v>
+        <v>3041</v>
       </c>
       <c r="D1465" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1465" s="2" t="s">
-        <v>2932</v>
+        <v>3042</v>
       </c>
       <c r="F1465" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1465" s="2">
         <v>0</v>
       </c>
       <c r="H1465" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1466" spans="1:8" x14ac:dyDescent="0.25">
@@ -47952,25 +47988,25 @@
         <v>1465</v>
       </c>
       <c r="B1466" s="2" t="s">
-        <v>3049</v>
+        <v>3043</v>
       </c>
       <c r="C1466" s="2" t="s">
-        <v>3050</v>
+        <v>3044</v>
       </c>
       <c r="D1466" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1466" s="2" t="s">
-        <v>3042</v>
+        <v>2997</v>
       </c>
       <c r="F1466" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1466" s="2">
         <v>0</v>
       </c>
       <c r="H1466" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1467" spans="1:8" x14ac:dyDescent="0.25">
@@ -47978,25 +48014,25 @@
         <v>1466</v>
       </c>
       <c r="B1467" s="2" t="s">
-        <v>1317</v>
+        <v>3045</v>
       </c>
       <c r="C1467" s="2" t="s">
-        <v>1318</v>
+        <v>3046</v>
       </c>
       <c r="D1467" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1467" s="2" t="s">
-        <v>3042</v>
+        <v>2952</v>
       </c>
       <c r="F1467" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1467" s="2">
         <v>0</v>
       </c>
       <c r="H1467" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1468" spans="1:8" x14ac:dyDescent="0.25">
@@ -48004,25 +48040,25 @@
         <v>1467</v>
       </c>
       <c r="B1468" s="2" t="s">
-        <v>3051</v>
+        <v>1313</v>
       </c>
       <c r="C1468" s="2" t="s">
-        <v>3052</v>
+        <v>1314</v>
       </c>
       <c r="D1468" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1468" s="2" t="s">
-        <v>2881</v>
+        <v>2997</v>
       </c>
       <c r="F1468" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1468" s="2">
         <v>0</v>
       </c>
       <c r="H1468" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1469" spans="1:8" x14ac:dyDescent="0.25">
@@ -48030,25 +48066,25 @@
         <v>1468</v>
       </c>
       <c r="B1469" s="2" t="s">
-        <v>3053</v>
+        <v>3047</v>
       </c>
       <c r="C1469" s="2" t="s">
-        <v>3054</v>
+        <v>3048</v>
       </c>
       <c r="D1469" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1469" s="2" t="s">
-        <v>2997</v>
+        <v>3042</v>
       </c>
       <c r="F1469" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1469" s="2">
         <v>0</v>
       </c>
       <c r="H1469" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1470" spans="1:8" x14ac:dyDescent="0.25">
@@ -48056,25 +48092,25 @@
         <v>1469</v>
       </c>
       <c r="B1470" s="2" t="s">
-        <v>1213</v>
+        <v>1315</v>
       </c>
       <c r="C1470" s="2" t="s">
-        <v>1109</v>
+        <v>1316</v>
       </c>
       <c r="D1470" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1470" s="2" t="s">
-        <v>455</v>
+        <v>2932</v>
       </c>
       <c r="F1470" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1470" s="2">
         <v>0</v>
       </c>
       <c r="H1470" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1471" spans="1:8" x14ac:dyDescent="0.25">
@@ -48082,16 +48118,16 @@
         <v>1470</v>
       </c>
       <c r="B1471" s="2" t="s">
-        <v>1214</v>
+        <v>3049</v>
       </c>
       <c r="C1471" s="2" t="s">
-        <v>1109</v>
+        <v>3050</v>
       </c>
       <c r="D1471" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1471" s="2" t="s">
-        <v>455</v>
+        <v>3042</v>
       </c>
       <c r="F1471" s="2">
         <v>0</v>
@@ -48108,25 +48144,25 @@
         <v>1471</v>
       </c>
       <c r="B1472" s="2" t="s">
-        <v>1215</v>
+        <v>1317</v>
       </c>
       <c r="C1472" s="2" t="s">
-        <v>1216</v>
+        <v>1318</v>
       </c>
       <c r="D1472" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1472" s="2" t="s">
-        <v>565</v>
+        <v>3042</v>
       </c>
       <c r="F1472" s="2">
-        <v>21</v>
+        <v>1</v>
       </c>
       <c r="G1472" s="2">
         <v>0</v>
       </c>
       <c r="H1472" s="2">
-        <v>21</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1473" spans="1:8" x14ac:dyDescent="0.25">
@@ -48134,25 +48170,25 @@
         <v>1472</v>
       </c>
       <c r="B1473" s="2" t="s">
-        <v>1218</v>
+        <v>3051</v>
       </c>
       <c r="C1473" s="2" t="s">
-        <v>1219</v>
+        <v>3052</v>
       </c>
       <c r="D1473" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1473" s="2" t="s">
-        <v>3055</v>
+        <v>2881</v>
       </c>
       <c r="F1473" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1473" s="2">
         <v>0</v>
       </c>
       <c r="H1473" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1474" spans="1:8" x14ac:dyDescent="0.25">
@@ -48160,25 +48196,25 @@
         <v>1473</v>
       </c>
       <c r="B1474" s="2" t="s">
-        <v>1220</v>
+        <v>3053</v>
       </c>
       <c r="C1474" s="2" t="s">
-        <v>1217</v>
+        <v>3054</v>
       </c>
       <c r="D1474" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1474" s="2" t="s">
-        <v>3055</v>
+        <v>2997</v>
       </c>
       <c r="F1474" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1474" s="2">
         <v>0</v>
       </c>
       <c r="H1474" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1475" spans="1:8" x14ac:dyDescent="0.25">
@@ -48186,16 +48222,16 @@
         <v>1474</v>
       </c>
       <c r="B1475" s="2" t="s">
-        <v>1221</v>
+        <v>1213</v>
       </c>
       <c r="C1475" s="2" t="s">
-        <v>1217</v>
+        <v>1109</v>
       </c>
       <c r="D1475" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1475" s="2" t="s">
-        <v>2809</v>
+        <v>455</v>
       </c>
       <c r="F1475" s="2">
         <v>0</v>
@@ -48212,25 +48248,25 @@
         <v>1475</v>
       </c>
       <c r="B1476" s="2" t="s">
-        <v>1222</v>
+        <v>1214</v>
       </c>
       <c r="C1476" s="2" t="s">
-        <v>1223</v>
+        <v>1109</v>
       </c>
       <c r="D1476" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1476" s="2" t="s">
-        <v>207</v>
+        <v>455</v>
       </c>
       <c r="F1476" s="2">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="G1476" s="2">
         <v>0</v>
       </c>
       <c r="H1476" s="2">
-        <v>19</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1477" spans="1:8" x14ac:dyDescent="0.25">
@@ -48238,25 +48274,25 @@
         <v>1476</v>
       </c>
       <c r="B1477" s="2" t="s">
-        <v>1224</v>
+        <v>1215</v>
       </c>
       <c r="C1477" s="2" t="s">
-        <v>1225</v>
+        <v>1216</v>
       </c>
       <c r="D1477" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1477" s="2" t="s">
-        <v>47</v>
+        <v>565</v>
       </c>
       <c r="F1477" s="2">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="G1477" s="2">
         <v>0</v>
       </c>
       <c r="H1477" s="2">
-        <v>9</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1478" spans="1:8" x14ac:dyDescent="0.25">
@@ -48264,25 +48300,25 @@
         <v>1477</v>
       </c>
       <c r="B1478" s="2" t="s">
-        <v>1226</v>
+        <v>1218</v>
       </c>
       <c r="C1478" s="2" t="s">
-        <v>1227</v>
+        <v>1219</v>
       </c>
       <c r="D1478" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1478" s="2" t="s">
-        <v>565</v>
+        <v>3055</v>
       </c>
       <c r="F1478" s="2">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="G1478" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="H1478" s="2">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1479" spans="1:8" x14ac:dyDescent="0.25">
@@ -48290,14 +48326,16 @@
         <v>1478</v>
       </c>
       <c r="B1479" s="2" t="s">
-        <v>3113</v>
-      </c>
-      <c r="C1479" s="2"/>
+        <v>1220</v>
+      </c>
+      <c r="C1479" s="2" t="s">
+        <v>1217</v>
+      </c>
       <c r="D1479" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1479" s="2" t="s">
-        <v>2384</v>
+        <v>3055</v>
       </c>
       <c r="F1479" s="2">
         <v>0</v>
@@ -48314,16 +48352,16 @@
         <v>1479</v>
       </c>
       <c r="B1480" s="2" t="s">
-        <v>1228</v>
+        <v>1221</v>
       </c>
       <c r="C1480" s="2" t="s">
-        <v>1229</v>
+        <v>1217</v>
       </c>
       <c r="D1480" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1480" s="2" t="s">
-        <v>455</v>
+        <v>2809</v>
       </c>
       <c r="F1480" s="2">
         <v>0</v>
@@ -48340,25 +48378,25 @@
         <v>1480</v>
       </c>
       <c r="B1481" s="2" t="s">
-        <v>1230</v>
+        <v>1222</v>
       </c>
       <c r="C1481" s="2" t="s">
-        <v>1231</v>
+        <v>1223</v>
       </c>
       <c r="D1481" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1481" s="2" t="s">
-        <v>455</v>
+        <v>207</v>
       </c>
       <c r="F1481" s="2">
-        <v>0</v>
+        <v>19</v>
       </c>
       <c r="G1481" s="2">
         <v>0</v>
       </c>
       <c r="H1481" s="2">
-        <v>0</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1482" spans="1:8" x14ac:dyDescent="0.25">
@@ -48366,25 +48404,25 @@
         <v>1481</v>
       </c>
       <c r="B1482" s="2" t="s">
-        <v>1232</v>
+        <v>1224</v>
       </c>
       <c r="C1482" s="2" t="s">
-        <v>1233</v>
+        <v>1225</v>
       </c>
       <c r="D1482" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1482" s="2" t="s">
-        <v>2352</v>
+        <v>47</v>
       </c>
       <c r="F1482" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="G1482" s="2">
         <v>0</v>
       </c>
       <c r="H1482" s="2">
-        <v>4</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1483" spans="1:8" x14ac:dyDescent="0.25">
@@ -48392,25 +48430,25 @@
         <v>1482</v>
       </c>
       <c r="B1483" s="2" t="s">
-        <v>1234</v>
+        <v>1226</v>
       </c>
       <c r="C1483" s="2" t="s">
-        <v>1235</v>
+        <v>1227</v>
       </c>
       <c r="D1483" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1483" s="2" t="s">
-        <v>2352</v>
+        <v>565</v>
       </c>
       <c r="F1483" s="2">
-        <v>8</v>
+        <v>40</v>
       </c>
       <c r="G1483" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H1483" s="2">
-        <v>8</v>
+        <v>30</v>
       </c>
     </row>
     <row r="1484" spans="1:8" x14ac:dyDescent="0.25">
@@ -48418,16 +48456,14 @@
         <v>1483</v>
       </c>
       <c r="B1484" s="2" t="s">
-        <v>1236</v>
-      </c>
-      <c r="C1484" s="2" t="s">
-        <v>1237</v>
-      </c>
+        <v>3113</v>
+      </c>
+      <c r="C1484" s="2"/>
       <c r="D1484" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1484" s="2" t="s">
-        <v>2352</v>
+        <v>2384</v>
       </c>
       <c r="F1484" s="2">
         <v>0</v>
@@ -48444,25 +48480,25 @@
         <v>1484</v>
       </c>
       <c r="B1485" s="2" t="s">
-        <v>1238</v>
+        <v>1228</v>
       </c>
       <c r="C1485" s="2" t="s">
-        <v>1239</v>
+        <v>1229</v>
       </c>
       <c r="D1485" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1485" s="2" t="s">
-        <v>3056</v>
+        <v>455</v>
       </c>
       <c r="F1485" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1485" s="2">
         <v>0</v>
       </c>
       <c r="H1485" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1486" spans="1:8" x14ac:dyDescent="0.25">
@@ -48470,25 +48506,25 @@
         <v>1485</v>
       </c>
       <c r="B1486" s="2" t="s">
-        <v>1240</v>
+        <v>1230</v>
       </c>
       <c r="C1486" s="2" t="s">
-        <v>1241</v>
+        <v>1231</v>
       </c>
       <c r="D1486" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1486" s="2" t="s">
-        <v>2352</v>
+        <v>455</v>
       </c>
       <c r="F1486" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1486" s="2">
         <v>0</v>
       </c>
       <c r="H1486" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1487" spans="1:8" x14ac:dyDescent="0.25">
@@ -48496,25 +48532,25 @@
         <v>1486</v>
       </c>
       <c r="B1487" s="2" t="s">
-        <v>1242</v>
+        <v>1232</v>
       </c>
       <c r="C1487" s="2" t="s">
-        <v>1243</v>
+        <v>1233</v>
       </c>
       <c r="D1487" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1487" s="2" t="s">
-        <v>1665</v>
+        <v>2352</v>
       </c>
       <c r="F1487" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1487" s="2">
         <v>0</v>
       </c>
       <c r="H1487" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1488" spans="1:8" x14ac:dyDescent="0.25">
@@ -48522,25 +48558,25 @@
         <v>1487</v>
       </c>
       <c r="B1488" s="2" t="s">
-        <v>1244</v>
+        <v>1234</v>
       </c>
       <c r="C1488" s="2" t="s">
-        <v>1245</v>
+        <v>1235</v>
       </c>
       <c r="D1488" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1488" s="2" t="s">
-        <v>1665</v>
+        <v>2352</v>
       </c>
       <c r="F1488" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="G1488" s="2">
         <v>0</v>
       </c>
       <c r="H1488" s="2">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1489" spans="1:8" x14ac:dyDescent="0.25">
@@ -48548,25 +48584,25 @@
         <v>1488</v>
       </c>
       <c r="B1489" s="2" t="s">
-        <v>3057</v>
+        <v>1236</v>
       </c>
       <c r="C1489" s="2" t="s">
-        <v>3058</v>
+        <v>1237</v>
       </c>
       <c r="D1489" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1489" s="2" t="s">
-        <v>1663</v>
+        <v>2352</v>
       </c>
       <c r="F1489" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="G1489" s="2">
         <v>0</v>
       </c>
       <c r="H1489" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1490" spans="1:8" x14ac:dyDescent="0.25">
@@ -48574,25 +48610,25 @@
         <v>1489</v>
       </c>
       <c r="B1490" s="2" t="s">
-        <v>3076</v>
+        <v>1238</v>
       </c>
       <c r="C1490" s="2" t="s">
-        <v>3077</v>
+        <v>1239</v>
       </c>
       <c r="D1490" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1490" s="2" t="s">
-        <v>1663</v>
+        <v>3056</v>
       </c>
       <c r="F1490" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1490" s="2">
         <v>0</v>
       </c>
       <c r="H1490" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1491" spans="1:8" x14ac:dyDescent="0.25">
@@ -48600,25 +48636,25 @@
         <v>1490</v>
       </c>
       <c r="B1491" s="2" t="s">
-        <v>1246</v>
+        <v>1240</v>
       </c>
       <c r="C1491" s="2" t="s">
-        <v>1247</v>
+        <v>1241</v>
       </c>
       <c r="D1491" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1491" s="2" t="s">
-        <v>1665</v>
+        <v>2352</v>
       </c>
       <c r="F1491" s="2">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="G1491" s="2">
         <v>0</v>
       </c>
       <c r="H1491" s="2">
-        <v>32</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1492" spans="1:8" x14ac:dyDescent="0.25">
@@ -48626,25 +48662,25 @@
         <v>1491</v>
       </c>
       <c r="B1492" s="2" t="s">
-        <v>1621</v>
+        <v>1242</v>
       </c>
       <c r="C1492" s="2" t="s">
-        <v>1622</v>
+        <v>1243</v>
       </c>
       <c r="D1492" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1492" s="2" t="s">
-        <v>2240</v>
+        <v>1665</v>
       </c>
       <c r="F1492" s="2">
-        <v>13</v>
+        <v>3</v>
       </c>
       <c r="G1492" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1492" s="2">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1493" spans="1:8" x14ac:dyDescent="0.25">
@@ -48652,10 +48688,10 @@
         <v>1492</v>
       </c>
       <c r="B1493" s="2" t="s">
-        <v>1248</v>
+        <v>1244</v>
       </c>
       <c r="C1493" s="2" t="s">
-        <v>1249</v>
+        <v>1245</v>
       </c>
       <c r="D1493" s="2" t="s">
         <v>1623</v>
@@ -48664,13 +48700,13 @@
         <v>1665</v>
       </c>
       <c r="F1493" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="G1493" s="2">
         <v>0</v>
       </c>
       <c r="H1493" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1494" spans="1:8" x14ac:dyDescent="0.25">
@@ -48678,25 +48714,25 @@
         <v>1493</v>
       </c>
       <c r="B1494" s="2" t="s">
-        <v>1250</v>
+        <v>3057</v>
       </c>
       <c r="C1494" s="2" t="s">
-        <v>1251</v>
+        <v>3058</v>
       </c>
       <c r="D1494" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1494" s="2" t="s">
-        <v>1665</v>
+        <v>1663</v>
       </c>
       <c r="F1494" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G1494" s="2">
         <v>0</v>
       </c>
       <c r="H1494" s="2">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1495" spans="1:8" x14ac:dyDescent="0.25">
@@ -48704,25 +48740,25 @@
         <v>1494</v>
       </c>
       <c r="B1495" s="2" t="s">
-        <v>1252</v>
+        <v>3076</v>
       </c>
       <c r="C1495" s="2" t="s">
-        <v>1253</v>
+        <v>3077</v>
       </c>
       <c r="D1495" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1495" s="2" t="s">
-        <v>3059</v>
+        <v>1663</v>
       </c>
       <c r="F1495" s="2">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="G1495" s="2">
         <v>0</v>
       </c>
       <c r="H1495" s="2">
-        <v>30</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1496" spans="1:8" x14ac:dyDescent="0.25">
@@ -48730,25 +48766,25 @@
         <v>1495</v>
       </c>
       <c r="B1496" s="2" t="s">
-        <v>1254</v>
+        <v>1246</v>
       </c>
       <c r="C1496" s="2" t="s">
-        <v>1255</v>
+        <v>1247</v>
       </c>
       <c r="D1496" s="2" t="s">
         <v>1623</v>
       </c>
       <c r="E1496" s="2" t="s">
-        <v>939</v>
+        <v>1665</v>
       </c>
       <c r="F1496" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G1496" s="2">
         <v>0</v>
       </c>
       <c r="H1496" s="2">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
     <row r="1497" spans="1:8" x14ac:dyDescent="0.25">
@@ -48756,24 +48792,154 @@
         <v>1496</v>
       </c>
       <c r="B1497" s="2" t="s">
+        <v>1621</v>
+      </c>
+      <c r="C1497" s="2" t="s">
+        <v>1622</v>
+      </c>
+      <c r="D1497" s="2" t="s">
+        <v>1623</v>
+      </c>
+      <c r="E1497" s="2" t="s">
+        <v>2240</v>
+      </c>
+      <c r="F1497" s="2">
+        <v>13</v>
+      </c>
+      <c r="G1497" s="2">
+        <v>1</v>
+      </c>
+      <c r="H1497" s="2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="1498" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1498" s="2">
+        <v>1497</v>
+      </c>
+      <c r="B1498" s="2" t="s">
+        <v>1248</v>
+      </c>
+      <c r="C1498" s="2" t="s">
+        <v>1249</v>
+      </c>
+      <c r="D1498" s="2" t="s">
+        <v>1623</v>
+      </c>
+      <c r="E1498" s="2" t="s">
+        <v>1665</v>
+      </c>
+      <c r="F1498" s="2">
+        <v>4</v>
+      </c>
+      <c r="G1498" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1498" s="2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="1499" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1499" s="2">
+        <v>1498</v>
+      </c>
+      <c r="B1499" s="2" t="s">
+        <v>1250</v>
+      </c>
+      <c r="C1499" s="2" t="s">
+        <v>1251</v>
+      </c>
+      <c r="D1499" s="2" t="s">
+        <v>1623</v>
+      </c>
+      <c r="E1499" s="2" t="s">
+        <v>1665</v>
+      </c>
+      <c r="F1499" s="2">
+        <v>2</v>
+      </c>
+      <c r="G1499" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1499" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="1500" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1500" s="2">
+        <v>1499</v>
+      </c>
+      <c r="B1500" s="2" t="s">
+        <v>1252</v>
+      </c>
+      <c r="C1500" s="2" t="s">
+        <v>1253</v>
+      </c>
+      <c r="D1500" s="2" t="s">
+        <v>1623</v>
+      </c>
+      <c r="E1500" s="2" t="s">
+        <v>3059</v>
+      </c>
+      <c r="F1500" s="2">
+        <v>30</v>
+      </c>
+      <c r="G1500" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1500" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1501" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1501" s="2">
+        <v>1500</v>
+      </c>
+      <c r="B1501" s="2" t="s">
+        <v>1254</v>
+      </c>
+      <c r="C1501" s="2" t="s">
+        <v>1255</v>
+      </c>
+      <c r="D1501" s="2" t="s">
+        <v>1623</v>
+      </c>
+      <c r="E1501" s="2" t="s">
+        <v>939</v>
+      </c>
+      <c r="F1501" s="2">
+        <v>30</v>
+      </c>
+      <c r="G1501" s="2">
+        <v>0</v>
+      </c>
+      <c r="H1501" s="2">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="1502" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A1502" s="2">
+        <v>1501</v>
+      </c>
+      <c r="B1502" s="2" t="s">
         <v>1256</v>
       </c>
-      <c r="C1497" s="2" t="s">
+      <c r="C1502" s="2" t="s">
         <v>1257</v>
       </c>
-      <c r="D1497" s="2" t="s">
-        <v>1623</v>
-      </c>
-      <c r="E1497" s="2" t="s">
+      <c r="D1502" s="2" t="s">
+        <v>1623</v>
+      </c>
+      <c r="E1502" s="2" t="s">
         <v>565</v>
       </c>
-      <c r="F1497" s="2">
+      <c r="F1502" s="2">
         <v>32</v>
       </c>
-      <c r="G1497" s="2">
+      <c r="G1502" s="2">
         <v>5</v>
       </c>
-      <c r="H1497" s="2">
+      <c r="H1502" s="2">
         <v>27</v>
       </c>
     </row>

--- a/STOK DEALER/STOK SRB.xlsx
+++ b/STOK DEALER/STOK SRB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1855FC50-2A9C-4534-B9DA-67BC5164BDF3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C56C2757-AC54-44B8-8933-5E20B1849918}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{46E7093F-A843-4D56-8D6E-D290D3117D3B}"/>
   </bookViews>
@@ -11170,13 +11170,13 @@
         <v>1672</v>
       </c>
       <c r="F49" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G49" s="2">
         <v>1</v>
       </c>
       <c r="H49" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
@@ -13688,13 +13688,13 @@
         <v>1780</v>
       </c>
       <c r="F146" s="2">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="G146" s="2">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="H146" s="2">
-        <v>42</v>
+        <v>36</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
@@ -13717,10 +13717,10 @@
         <v>128</v>
       </c>
       <c r="G147" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="H147" s="2">
-        <v>122</v>
+        <v>119</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
@@ -13740,13 +13740,13 @@
         <v>1781</v>
       </c>
       <c r="F148" s="2">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G148" s="2">
         <v>2</v>
       </c>
       <c r="H148" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
@@ -13870,13 +13870,13 @@
         <v>1789</v>
       </c>
       <c r="F153" s="2">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="G153" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="H153" s="2">
-        <v>222</v>
+        <v>215</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
@@ -14130,13 +14130,13 @@
         <v>1780</v>
       </c>
       <c r="F163" s="2">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="G163" s="2">
         <v>8</v>
       </c>
       <c r="H163" s="2">
-        <v>127</v>
+        <v>123</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.25">
@@ -14156,13 +14156,13 @@
         <v>1789</v>
       </c>
       <c r="F164" s="2">
-        <v>417</v>
+        <v>402</v>
       </c>
       <c r="G164" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H164" s="2">
-        <v>408</v>
+        <v>397</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.25">
@@ -14312,13 +14312,13 @@
         <v>207</v>
       </c>
       <c r="F170" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="G170" s="2">
         <v>5</v>
       </c>
       <c r="H170" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.25">
@@ -15144,13 +15144,13 @@
         <v>1815</v>
       </c>
       <c r="F202" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G202" s="2">
         <v>0</v>
       </c>
       <c r="H202" s="2">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.25">
@@ -15794,13 +15794,13 @@
         <v>1869</v>
       </c>
       <c r="F227" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G227" s="2">
         <v>0</v>
       </c>
       <c r="H227" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.25">
@@ -20786,13 +20786,13 @@
         <v>2168</v>
       </c>
       <c r="F419" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G419" s="2">
         <v>1</v>
       </c>
       <c r="H419" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="420" spans="1:8" x14ac:dyDescent="0.25">
@@ -21179,10 +21179,10 @@
         <v>2</v>
       </c>
       <c r="G434" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H434" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="435" spans="1:8" x14ac:dyDescent="0.25">
@@ -21309,10 +21309,10 @@
         <v>16</v>
       </c>
       <c r="G439" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H439" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="440" spans="1:8" x14ac:dyDescent="0.25">
@@ -24683,10 +24683,10 @@
         <v>7</v>
       </c>
       <c r="G569" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H569" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="570" spans="1:8" x14ac:dyDescent="0.25">
@@ -27335,10 +27335,10 @@
         <v>13</v>
       </c>
       <c r="G671" s="2">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="H671" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="672" spans="1:8" x14ac:dyDescent="0.25">
@@ -30559,10 +30559,10 @@
         <v>9</v>
       </c>
       <c r="G795" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H795" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="796" spans="1:8" x14ac:dyDescent="0.25">
@@ -31674,13 +31674,13 @@
         <v>2555</v>
       </c>
       <c r="F838" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G838" s="2">
         <v>0</v>
       </c>
       <c r="H838" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="839" spans="1:8" x14ac:dyDescent="0.25">
@@ -32457,10 +32457,10 @@
         <v>2</v>
       </c>
       <c r="G868" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H868" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="869" spans="1:8" x14ac:dyDescent="0.25">
@@ -34142,13 +34142,13 @@
         <v>1869</v>
       </c>
       <c r="F933" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G933" s="2">
         <v>1</v>
       </c>
       <c r="H933" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="934" spans="1:8" x14ac:dyDescent="0.25">
@@ -35130,13 +35130,13 @@
         <v>2624</v>
       </c>
       <c r="F971" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G971" s="2">
         <v>0</v>
       </c>
       <c r="H971" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="972" spans="1:8" x14ac:dyDescent="0.25">
@@ -37938,13 +37938,13 @@
         <v>2590</v>
       </c>
       <c r="F1079" s="2">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="G1079" s="2">
         <v>1</v>
       </c>
       <c r="H1079" s="2">
-        <v>45</v>
+        <v>41</v>
       </c>
     </row>
     <row r="1080" spans="1:8" x14ac:dyDescent="0.25">
@@ -39680,13 +39680,13 @@
         <v>2733</v>
       </c>
       <c r="F1146" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1146" s="2">
         <v>0</v>
       </c>
       <c r="H1146" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1147" spans="1:8" x14ac:dyDescent="0.25">
@@ -40148,13 +40148,13 @@
         <v>2717</v>
       </c>
       <c r="F1164" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1164" s="2">
         <v>0</v>
       </c>
       <c r="H1164" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1165" spans="1:8" x14ac:dyDescent="0.25">
@@ -40408,13 +40408,13 @@
         <v>2717</v>
       </c>
       <c r="F1174" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1174" s="2">
         <v>0</v>
       </c>
       <c r="H1174" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1175" spans="1:8" x14ac:dyDescent="0.25">
@@ -40772,13 +40772,13 @@
         <v>2722</v>
       </c>
       <c r="F1188" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1188" s="2">
         <v>0</v>
       </c>
       <c r="H1188" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1189" spans="1:8" x14ac:dyDescent="0.25">
@@ -40824,13 +40824,13 @@
         <v>2722</v>
       </c>
       <c r="F1190" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1190" s="2">
         <v>0</v>
       </c>
       <c r="H1190" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1191" spans="1:8" x14ac:dyDescent="0.25">
@@ -43190,13 +43190,13 @@
         <v>2824</v>
       </c>
       <c r="F1281" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G1281" s="2">
         <v>0</v>
       </c>
       <c r="H1281" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="1282" spans="1:8" x14ac:dyDescent="0.25">
@@ -43268,13 +43268,13 @@
         <v>2823</v>
       </c>
       <c r="F1284" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G1284" s="2">
         <v>0</v>
       </c>
       <c r="H1284" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1285" spans="1:8" x14ac:dyDescent="0.25">
@@ -43294,13 +43294,13 @@
         <v>2823</v>
       </c>
       <c r="F1285" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G1285" s="2">
         <v>0</v>
       </c>
       <c r="H1285" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1286" spans="1:8" x14ac:dyDescent="0.25">
@@ -43450,13 +43450,13 @@
         <v>2829</v>
       </c>
       <c r="F1291" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1291" s="2">
         <v>0</v>
       </c>
       <c r="H1291" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1292" spans="1:8" x14ac:dyDescent="0.25">
@@ -44958,13 +44958,13 @@
         <v>3146</v>
       </c>
       <c r="F1349" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G1349" s="2">
         <v>0</v>
       </c>
       <c r="H1349" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1350" spans="1:8" x14ac:dyDescent="0.25">
@@ -45530,13 +45530,13 @@
         <v>2915</v>
       </c>
       <c r="F1371" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1371" s="2">
         <v>0</v>
       </c>
       <c r="H1371" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1372" spans="1:8" x14ac:dyDescent="0.25">
@@ -45686,13 +45686,13 @@
         <v>2825</v>
       </c>
       <c r="F1377" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G1377" s="2">
         <v>0</v>
       </c>
       <c r="H1377" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1378" spans="1:8" x14ac:dyDescent="0.25">
@@ -46128,13 +46128,13 @@
         <v>2966</v>
       </c>
       <c r="F1394" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="G1394" s="2">
         <v>0</v>
       </c>
       <c r="H1394" s="2">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="1395" spans="1:8" x14ac:dyDescent="0.25">
@@ -46310,13 +46310,13 @@
         <v>2946</v>
       </c>
       <c r="F1401" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G1401" s="2">
         <v>0</v>
       </c>
       <c r="H1401" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1402" spans="1:8" x14ac:dyDescent="0.25">
@@ -46674,13 +46674,13 @@
         <v>2854</v>
       </c>
       <c r="F1415" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1415" s="2">
         <v>0</v>
       </c>
       <c r="H1415" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1416" spans="1:8" x14ac:dyDescent="0.25">
@@ -47350,13 +47350,13 @@
         <v>2966</v>
       </c>
       <c r="F1441" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1441" s="2">
         <v>0</v>
       </c>
       <c r="H1441" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1442" spans="1:8" x14ac:dyDescent="0.25">
@@ -47376,13 +47376,13 @@
         <v>2994</v>
       </c>
       <c r="F1442" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G1442" s="2">
         <v>0</v>
       </c>
       <c r="H1442" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="1443" spans="1:8" x14ac:dyDescent="0.25">

--- a/STOK DEALER/STOK SRB.xlsx
+++ b/STOK DEALER/STOK SRB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C56C2757-AC54-44B8-8933-5E20B1849918}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44217697-CB31-4267-9B71-EF88AD23B226}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{46E7093F-A843-4D56-8D6E-D290D3117D3B}"/>
   </bookViews>
@@ -10130,13 +10130,13 @@
         <v>1627</v>
       </c>
       <c r="F9" s="2">
-        <v>2</v>
+        <v>28</v>
       </c>
       <c r="G9" s="2">
         <v>0</v>
       </c>
       <c r="H9" s="2">
-        <v>2</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.25">
@@ -10234,13 +10234,13 @@
         <v>1628</v>
       </c>
       <c r="F13" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G13" s="2">
         <v>0</v>
       </c>
       <c r="H13" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.25">
@@ -10702,10 +10702,10 @@
         <v>1648</v>
       </c>
       <c r="F31" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G31" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H31" s="2">
         <v>3</v>
@@ -11170,13 +11170,13 @@
         <v>1672</v>
       </c>
       <c r="F49" s="2">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G49" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H49" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
@@ -11222,13 +11222,13 @@
         <v>451</v>
       </c>
       <c r="F51" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G51" s="2">
         <v>0</v>
       </c>
       <c r="H51" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
@@ -11508,13 +11508,13 @@
         <v>1068</v>
       </c>
       <c r="F62" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G62" s="2">
         <v>0</v>
       </c>
       <c r="H62" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.25">
@@ -11690,10 +11690,10 @@
         <v>1260</v>
       </c>
       <c r="F69" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G69" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H69" s="2">
         <v>5</v>
@@ -11716,10 +11716,10 @@
         <v>1260</v>
       </c>
       <c r="F70" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G70" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H70" s="2">
         <v>2</v>
@@ -11768,13 +11768,13 @@
         <v>1682</v>
       </c>
       <c r="F72" s="2">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G72" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H72" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.25">
@@ -11794,10 +11794,10 @@
         <v>1682</v>
       </c>
       <c r="F73" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G73" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H73" s="2">
         <v>6</v>
@@ -13688,13 +13688,13 @@
         <v>1780</v>
       </c>
       <c r="F146" s="2">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="G146" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H146" s="2">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
@@ -13714,10 +13714,10 @@
         <v>1781</v>
       </c>
       <c r="F147" s="2">
-        <v>128</v>
+        <v>121</v>
       </c>
       <c r="G147" s="2">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="H147" s="2">
         <v>119</v>
@@ -13740,13 +13740,13 @@
         <v>1781</v>
       </c>
       <c r="F148" s="2">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="G148" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H148" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
@@ -13870,13 +13870,13 @@
         <v>1789</v>
       </c>
       <c r="F153" s="2">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="G153" s="2">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="H153" s="2">
-        <v>215</v>
+        <v>211</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
@@ -14130,13 +14130,13 @@
         <v>1780</v>
       </c>
       <c r="F163" s="2">
-        <v>131</v>
+        <v>124</v>
       </c>
       <c r="G163" s="2">
-        <v>8</v>
+        <v>2</v>
       </c>
       <c r="H163" s="2">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.25">
@@ -14156,13 +14156,13 @@
         <v>1789</v>
       </c>
       <c r="F164" s="2">
-        <v>402</v>
+        <v>394</v>
       </c>
       <c r="G164" s="2">
         <v>5</v>
       </c>
       <c r="H164" s="2">
-        <v>397</v>
+        <v>389</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.25">
@@ -14234,10 +14234,10 @@
         <v>207</v>
       </c>
       <c r="F167" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G167" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H167" s="2">
         <v>1</v>
@@ -14312,13 +14312,13 @@
         <v>207</v>
       </c>
       <c r="F170" s="2">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="G170" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="H170" s="2">
-        <v>176</v>
+        <v>173</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.25">
@@ -14468,13 +14468,13 @@
         <v>939</v>
       </c>
       <c r="F176" s="2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="G176" s="2">
         <v>2</v>
       </c>
       <c r="H176" s="2">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.25">
@@ -14676,10 +14676,10 @@
         <v>1816</v>
       </c>
       <c r="F184" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G184" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H184" s="2">
         <v>1</v>
@@ -15144,13 +15144,13 @@
         <v>1815</v>
       </c>
       <c r="F202" s="2">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="G202" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H202" s="2">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.25">
@@ -17120,13 +17120,13 @@
         <v>1956</v>
       </c>
       <c r="F278" s="2">
-        <v>15</v>
+        <v>27</v>
       </c>
       <c r="G278" s="2">
         <v>2</v>
       </c>
       <c r="H278" s="2">
-        <v>13</v>
+        <v>25</v>
       </c>
     </row>
     <row r="279" spans="1:8" x14ac:dyDescent="0.25">
@@ -19928,13 +19928,13 @@
         <v>2125</v>
       </c>
       <c r="F386" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G386" s="2">
         <v>2</v>
       </c>
       <c r="H386" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="387" spans="1:8" x14ac:dyDescent="0.25">
@@ -20656,10 +20656,10 @@
         <v>2165</v>
       </c>
       <c r="F414" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G414" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H414" s="2">
         <v>13</v>
@@ -20786,10 +20786,10 @@
         <v>2168</v>
       </c>
       <c r="F419" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G419" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H419" s="2">
         <v>3</v>
@@ -20838,10 +20838,10 @@
         <v>2169</v>
       </c>
       <c r="F421" s="2">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G421" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H421" s="2">
         <v>2</v>
@@ -20864,13 +20864,13 @@
         <v>433</v>
       </c>
       <c r="F422" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G422" s="2">
         <v>0</v>
       </c>
       <c r="H422" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="423" spans="1:8" x14ac:dyDescent="0.25">
@@ -21150,10 +21150,10 @@
         <v>2174</v>
       </c>
       <c r="F433" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G433" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H433" s="2">
         <v>3</v>
@@ -21176,10 +21176,10 @@
         <v>2175</v>
       </c>
       <c r="F434" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G434" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H434" s="2">
         <v>1</v>
@@ -21228,10 +21228,10 @@
         <v>2173</v>
       </c>
       <c r="F436" s="2">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G436" s="2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H436" s="2">
         <v>2</v>
@@ -21306,10 +21306,10 @@
         <v>1959</v>
       </c>
       <c r="F439" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G439" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H439" s="2">
         <v>14</v>
@@ -22526,13 +22526,13 @@
         <v>1099</v>
       </c>
       <c r="F486" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G486" s="2">
         <v>0</v>
       </c>
       <c r="H486" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="487" spans="1:8" x14ac:dyDescent="0.25">
@@ -22552,13 +22552,13 @@
         <v>2237</v>
       </c>
       <c r="F487" s="2">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G487" s="2">
         <v>1</v>
       </c>
       <c r="H487" s="2">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="488" spans="1:8" x14ac:dyDescent="0.25">
@@ -22578,10 +22578,10 @@
         <v>610</v>
       </c>
       <c r="F488" s="2">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G488" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H488" s="2">
         <v>2</v>
@@ -22630,10 +22630,10 @@
         <v>610</v>
       </c>
       <c r="F490" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G490" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H490" s="2">
         <v>18</v>
@@ -22812,10 +22812,10 @@
         <v>303</v>
       </c>
       <c r="F497" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G497" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H497" s="2">
         <v>3</v>
@@ -22916,10 +22916,10 @@
         <v>300</v>
       </c>
       <c r="F501" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G501" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H501" s="2">
         <v>2</v>
@@ -23384,10 +23384,10 @@
         <v>581</v>
       </c>
       <c r="F519" s="2">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="G519" s="2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="H519" s="2">
         <v>3</v>
@@ -23595,10 +23595,10 @@
         <v>2</v>
       </c>
       <c r="G527" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H527" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="528" spans="1:8" x14ac:dyDescent="0.25">
@@ -24316,13 +24316,13 @@
         <v>240</v>
       </c>
       <c r="F555" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G555" s="2">
         <v>0</v>
       </c>
       <c r="H555" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="556" spans="1:8" x14ac:dyDescent="0.25">
@@ -24576,10 +24576,10 @@
         <v>2275</v>
       </c>
       <c r="F565" s="2">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="G565" s="2">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H565" s="2">
         <v>18</v>
@@ -24680,10 +24680,10 @@
         <v>2278</v>
       </c>
       <c r="F569" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G569" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H569" s="2">
         <v>6</v>
@@ -24758,10 +24758,10 @@
         <v>351</v>
       </c>
       <c r="F572" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G572" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H572" s="2">
         <v>1</v>
@@ -24940,10 +24940,10 @@
         <v>483</v>
       </c>
       <c r="F579" s="2">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="G579" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H579" s="2">
         <v>19</v>
@@ -26217,10 +26217,10 @@
         <v>1</v>
       </c>
       <c r="G628" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H628" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="629" spans="1:8" x14ac:dyDescent="0.25">
@@ -26318,10 +26318,10 @@
         <v>440</v>
       </c>
       <c r="F632" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G632" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H632" s="2">
         <v>3</v>
@@ -27072,10 +27072,10 @@
         <v>292</v>
       </c>
       <c r="F661" s="2">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G661" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H661" s="2">
         <v>2</v>
@@ -27098,10 +27098,10 @@
         <v>2378</v>
       </c>
       <c r="F662" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G662" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H662" s="2">
         <v>7</v>
@@ -27306,13 +27306,13 @@
         <v>402</v>
       </c>
       <c r="F670" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="G670" s="2">
         <v>0</v>
       </c>
       <c r="H670" s="2">
-        <v>1</v>
+        <v>8</v>
       </c>
     </row>
     <row r="671" spans="1:8" x14ac:dyDescent="0.25">
@@ -27332,10 +27332,10 @@
         <v>430</v>
       </c>
       <c r="F671" s="2">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="G671" s="2">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="H671" s="2">
         <v>7</v>
@@ -27358,13 +27358,13 @@
         <v>430</v>
       </c>
       <c r="F672" s="2">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="G672" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H672" s="2">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="673" spans="1:8" x14ac:dyDescent="0.25">
@@ -29386,13 +29386,13 @@
         <v>2476</v>
       </c>
       <c r="F750" s="2">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G750" s="2">
         <v>2</v>
       </c>
       <c r="H750" s="2">
-        <v>0</v>
+        <v>6</v>
       </c>
     </row>
     <row r="751" spans="1:8" x14ac:dyDescent="0.25">
@@ -29906,10 +29906,10 @@
         <v>2378</v>
       </c>
       <c r="F770" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G770" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H770" s="2">
         <v>1</v>
@@ -30478,10 +30478,10 @@
         <v>2519</v>
       </c>
       <c r="F792" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G792" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H792" s="2">
         <v>0</v>
@@ -30556,10 +30556,10 @@
         <v>2524</v>
       </c>
       <c r="F795" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G795" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H795" s="2">
         <v>6</v>
@@ -30712,10 +30712,10 @@
         <v>2530</v>
       </c>
       <c r="F801" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G801" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H801" s="2">
         <v>0</v>
@@ -31648,10 +31648,10 @@
         <v>2554</v>
       </c>
       <c r="F837" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G837" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H837" s="2">
         <v>0</v>
@@ -31830,10 +31830,10 @@
         <v>2557</v>
       </c>
       <c r="F844" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G844" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H844" s="2">
         <v>1</v>
@@ -32142,13 +32142,13 @@
         <v>59</v>
       </c>
       <c r="F856" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G856" s="2">
         <v>0</v>
       </c>
       <c r="H856" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="857" spans="1:8" x14ac:dyDescent="0.25">
@@ -32246,10 +32246,10 @@
         <v>2095</v>
       </c>
       <c r="F860" s="2">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G860" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H860" s="2">
         <v>10</v>
@@ -32275,10 +32275,10 @@
         <v>6</v>
       </c>
       <c r="G861" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H861" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="862" spans="1:8" x14ac:dyDescent="0.25">
@@ -32454,10 +32454,10 @@
         <v>2573</v>
       </c>
       <c r="F868" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G868" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H868" s="2">
         <v>0</v>
@@ -32532,13 +32532,13 @@
         <v>2577</v>
       </c>
       <c r="F871" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G871" s="2">
         <v>0</v>
       </c>
       <c r="H871" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="872" spans="1:8" x14ac:dyDescent="0.25">
@@ -32662,13 +32662,13 @@
         <v>2566</v>
       </c>
       <c r="F876" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G876" s="2">
         <v>0</v>
       </c>
       <c r="H876" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="877" spans="1:8" x14ac:dyDescent="0.25">
@@ -32740,13 +32740,13 @@
         <v>2580</v>
       </c>
       <c r="F879" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G879" s="2">
         <v>0</v>
       </c>
       <c r="H879" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="880" spans="1:8" x14ac:dyDescent="0.25">
@@ -33104,10 +33104,10 @@
         <v>2165</v>
       </c>
       <c r="F893" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G893" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H893" s="2">
         <v>9</v>
@@ -33258,10 +33258,10 @@
         <v>2587</v>
       </c>
       <c r="F899" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G899" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H899" s="2">
         <v>0</v>
@@ -33674,10 +33674,10 @@
         <v>1677</v>
       </c>
       <c r="F915" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G915" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H915" s="2">
         <v>1</v>
@@ -34142,10 +34142,10 @@
         <v>1869</v>
       </c>
       <c r="F933" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G933" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H933" s="2">
         <v>2</v>
@@ -35026,13 +35026,13 @@
         <v>2514</v>
       </c>
       <c r="F967" s="2">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="G967" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H967" s="2">
-        <v>0</v>
+        <v>59</v>
       </c>
     </row>
     <row r="968" spans="1:8" x14ac:dyDescent="0.25">
@@ -35910,10 +35910,10 @@
         <v>2643</v>
       </c>
       <c r="F1001" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1001" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1001" s="2">
         <v>3</v>
@@ -36326,10 +36326,10 @@
         <v>2647</v>
       </c>
       <c r="F1017" s="2">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G1017" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H1017" s="2">
         <v>1</v>
@@ -37912,10 +37912,10 @@
         <v>2679</v>
       </c>
       <c r="F1078" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1078" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1078" s="2">
         <v>1</v>
@@ -37938,13 +37938,13 @@
         <v>2590</v>
       </c>
       <c r="F1079" s="2">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="G1079" s="2">
         <v>1</v>
       </c>
       <c r="H1079" s="2">
-        <v>41</v>
+        <v>37</v>
       </c>
     </row>
     <row r="1080" spans="1:8" x14ac:dyDescent="0.25">
@@ -39212,10 +39212,10 @@
         <v>1827</v>
       </c>
       <c r="F1128" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1128" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1128" s="2">
         <v>2</v>
@@ -40564,13 +40564,13 @@
         <v>2717</v>
       </c>
       <c r="F1180" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1180" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1180" s="2">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1181" spans="1:8" x14ac:dyDescent="0.25">
@@ -42150,10 +42150,10 @@
         <v>2804</v>
       </c>
       <c r="F1241" s="2">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G1241" s="2">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H1241" s="2">
         <v>1</v>
@@ -43060,10 +43060,10 @@
         <v>939</v>
       </c>
       <c r="F1276" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G1276" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1276" s="2">
         <v>12</v>
@@ -43086,10 +43086,10 @@
         <v>458</v>
       </c>
       <c r="F1277" s="2">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="G1277" s="2">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="H1277" s="2">
         <v>10</v>
@@ -43268,13 +43268,13 @@
         <v>2823</v>
       </c>
       <c r="F1284" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G1284" s="2">
         <v>0</v>
       </c>
       <c r="H1284" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1285" spans="1:8" x14ac:dyDescent="0.25">
@@ -43606,13 +43606,13 @@
         <v>2629</v>
       </c>
       <c r="F1297" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1297" s="2">
         <v>0</v>
       </c>
       <c r="H1297" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1298" spans="1:8" x14ac:dyDescent="0.25">
@@ -45530,13 +45530,13 @@
         <v>2915</v>
       </c>
       <c r="F1371" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1371" s="2">
         <v>0</v>
       </c>
       <c r="H1371" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1372" spans="1:8" x14ac:dyDescent="0.25">
@@ -45920,13 +45920,13 @@
         <v>2868</v>
       </c>
       <c r="F1386" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1386" s="2">
         <v>0</v>
       </c>
       <c r="H1386" s="2">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1387" spans="1:8" x14ac:dyDescent="0.25">
@@ -45946,13 +45946,13 @@
         <v>2868</v>
       </c>
       <c r="F1387" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1387" s="2">
         <v>0</v>
       </c>
       <c r="H1387" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1388" spans="1:8" x14ac:dyDescent="0.25">
@@ -46232,13 +46232,13 @@
         <v>2915</v>
       </c>
       <c r="F1398" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="G1398" s="2">
         <v>0</v>
       </c>
       <c r="H1398" s="2">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1399" spans="1:8" x14ac:dyDescent="0.25">
@@ -46674,13 +46674,13 @@
         <v>2854</v>
       </c>
       <c r="F1415" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1415" s="2">
         <v>0</v>
       </c>
       <c r="H1415" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1416" spans="1:8" x14ac:dyDescent="0.25">
@@ -47327,10 +47327,10 @@
         <v>6</v>
       </c>
       <c r="G1440" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1440" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1441" spans="1:8" x14ac:dyDescent="0.25">
@@ -47379,10 +47379,10 @@
         <v>12</v>
       </c>
       <c r="G1442" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1442" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1443" spans="1:8" x14ac:dyDescent="0.25">
@@ -48442,13 +48442,13 @@
         <v>565</v>
       </c>
       <c r="F1483" s="2">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="G1483" s="2">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="H1483" s="2">
-        <v>30</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1484" spans="1:8" x14ac:dyDescent="0.25">
@@ -48804,10 +48804,10 @@
         <v>2240</v>
       </c>
       <c r="F1497" s="2">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G1497" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1497" s="2">
         <v>12</v>
@@ -48911,10 +48911,10 @@
         <v>30</v>
       </c>
       <c r="G1501" s="2">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H1501" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1502" spans="1:8" x14ac:dyDescent="0.25">
@@ -48934,10 +48934,10 @@
         <v>565</v>
       </c>
       <c r="F1502" s="2">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="G1502" s="2">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="H1502" s="2">
         <v>27</v>

--- a/STOK DEALER/STOK SRB.xlsx
+++ b/STOK DEALER/STOK SRB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documents\Wanda - PSD\HIL\HIL 2025\STOK DEALER\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44217697-CB31-4267-9B71-EF88AD23B226}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C5F1FA9-62A1-4589-A29C-87684D9282AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{46E7093F-A843-4D56-8D6E-D290D3117D3B}"/>
   </bookViews>
@@ -10182,13 +10182,13 @@
         <v>1627</v>
       </c>
       <c r="F11" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G11" s="2">
         <v>0</v>
       </c>
       <c r="H11" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.25">
@@ -10208,13 +10208,13 @@
         <v>1627</v>
       </c>
       <c r="F12" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G12" s="2">
         <v>0</v>
       </c>
       <c r="H12" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.25">
@@ -11303,10 +11303,10 @@
         <v>2</v>
       </c>
       <c r="G54" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H54" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.25">
@@ -11326,13 +11326,13 @@
         <v>451</v>
       </c>
       <c r="F55" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G55" s="2">
         <v>0</v>
       </c>
       <c r="H55" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="56" spans="1:8" x14ac:dyDescent="0.25">
@@ -11716,13 +11716,13 @@
         <v>1260</v>
       </c>
       <c r="F70" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G70" s="2">
         <v>0</v>
       </c>
       <c r="H70" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
@@ -13688,13 +13688,13 @@
         <v>1780</v>
       </c>
       <c r="F146" s="2">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="G146" s="2">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H146" s="2">
-        <v>35</v>
+        <v>29</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
@@ -13714,13 +13714,13 @@
         <v>1781</v>
       </c>
       <c r="F147" s="2">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="G147" s="2">
         <v>2</v>
       </c>
       <c r="H147" s="2">
-        <v>119</v>
+        <v>117</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.25">
@@ -13740,10 +13740,10 @@
         <v>1781</v>
       </c>
       <c r="F148" s="2">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G148" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H148" s="2">
         <v>229</v>
@@ -13870,13 +13870,13 @@
         <v>1789</v>
       </c>
       <c r="F153" s="2">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="G153" s="2">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H153" s="2">
-        <v>211</v>
+        <v>207</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.25">
@@ -14130,13 +14130,13 @@
         <v>1780</v>
       </c>
       <c r="F163" s="2">
-        <v>124</v>
+        <v>118</v>
       </c>
       <c r="G163" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H163" s="2">
-        <v>122</v>
+        <v>115</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.25">
@@ -14156,13 +14156,13 @@
         <v>1789</v>
       </c>
       <c r="F164" s="2">
-        <v>394</v>
+        <v>392</v>
       </c>
       <c r="G164" s="2">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="H164" s="2">
-        <v>389</v>
+        <v>386</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.25">
@@ -14312,13 +14312,13 @@
         <v>207</v>
       </c>
       <c r="F170" s="2">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="G170" s="2">
         <v>3</v>
       </c>
       <c r="H170" s="2">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.25">
@@ -14468,10 +14468,10 @@
         <v>939</v>
       </c>
       <c r="F176" s="2">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="G176" s="2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H176" s="2">
         <v>80</v>
@@ -15144,13 +15144,13 @@
         <v>1815</v>
       </c>
       <c r="F202" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G202" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H202" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.25">
@@ -15222,13 +15222,13 @@
         <v>1827</v>
       </c>
       <c r="F205" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G205" s="2">
         <v>0</v>
       </c>
       <c r="H205" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.25">
@@ -15534,13 +15534,13 @@
         <v>1855</v>
       </c>
       <c r="F217" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G217" s="2">
         <v>0</v>
       </c>
       <c r="H217" s="2">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.25">
@@ -15612,13 +15612,13 @@
         <v>1856</v>
       </c>
       <c r="F220" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G220" s="2">
         <v>0</v>
       </c>
       <c r="H220" s="2">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.25">
@@ -20578,13 +20578,13 @@
         <v>1812</v>
       </c>
       <c r="F411" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G411" s="2">
         <v>0</v>
       </c>
       <c r="H411" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="412" spans="1:8" x14ac:dyDescent="0.25">
@@ -20815,10 +20815,10 @@
         <v>31</v>
       </c>
       <c r="G420" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H420" s="2">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
     <row r="421" spans="1:8" x14ac:dyDescent="0.25">
@@ -20864,13 +20864,13 @@
         <v>433</v>
       </c>
       <c r="F422" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G422" s="2">
         <v>0</v>
       </c>
       <c r="H422" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="423" spans="1:8" x14ac:dyDescent="0.25">
@@ -24576,13 +24576,13 @@
         <v>2275</v>
       </c>
       <c r="F565" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G565" s="2">
         <v>1</v>
       </c>
       <c r="H565" s="2">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="566" spans="1:8" x14ac:dyDescent="0.25">
@@ -24943,10 +24943,10 @@
         <v>20</v>
       </c>
       <c r="G579" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H579" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="580" spans="1:8" x14ac:dyDescent="0.25">
@@ -29389,10 +29389,10 @@
         <v>8</v>
       </c>
       <c r="G750" s="2">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H750" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="751" spans="1:8" x14ac:dyDescent="0.25">
@@ -31417,10 +31417,10 @@
         <v>3</v>
       </c>
       <c r="G828" s="2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H828" s="2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="829" spans="1:8" x14ac:dyDescent="0.25">
@@ -32272,10 +32272,10 @@
         <v>2566</v>
       </c>
       <c r="F861" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G861" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H861" s="2">
         <v>5</v>
@@ -35026,10 +35026,10 @@
         <v>2514</v>
       </c>
       <c r="F967" s="2">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="G967" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H967" s="2">
         <v>59</v>
@@ -35234,13 +35234,13 @@
         <v>2629</v>
       </c>
       <c r="F975" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G975" s="2">
         <v>0</v>
       </c>
       <c r="H975" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="976" spans="1:8" x14ac:dyDescent="0.25">
@@ -37938,13 +37938,13 @@
         <v>2590</v>
       </c>
       <c r="F1079" s="2">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="G1079" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1079" s="2">
-        <v>37</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1080" spans="1:8" x14ac:dyDescent="0.25">
@@ -40096,13 +40096,13 @@
         <v>2722</v>
       </c>
       <c r="F1162" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1162" s="2">
         <v>0</v>
       </c>
       <c r="H1162" s="2">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1163" spans="1:8" x14ac:dyDescent="0.25">
@@ -40564,13 +40564,13 @@
         <v>2717</v>
       </c>
       <c r="F1180" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1180" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1180" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1181" spans="1:8" x14ac:dyDescent="0.25">
@@ -42361,10 +42361,10 @@
         <v>11</v>
       </c>
       <c r="G1249" s="2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H1249" s="2">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1250" spans="1:8" x14ac:dyDescent="0.25">
@@ -43190,13 +43190,13 @@
         <v>2824</v>
       </c>
       <c r="F1281" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G1281" s="2">
         <v>0</v>
       </c>
       <c r="H1281" s="2">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1282" spans="1:8" x14ac:dyDescent="0.25">
@@ -43268,13 +43268,13 @@
         <v>2823</v>
       </c>
       <c r="F1284" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G1284" s="2">
         <v>0</v>
       </c>
       <c r="H1284" s="2">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1285" spans="1:8" x14ac:dyDescent="0.25">
@@ -43294,13 +43294,13 @@
         <v>2823</v>
       </c>
       <c r="F1285" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G1285" s="2">
         <v>0</v>
       </c>
       <c r="H1285" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1286" spans="1:8" x14ac:dyDescent="0.25">
@@ -44048,13 +44048,13 @@
         <v>2869</v>
       </c>
       <c r="F1314" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G1314" s="2">
         <v>0</v>
       </c>
       <c r="H1314" s="2">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1315" spans="1:8" x14ac:dyDescent="0.25">
@@ -45504,13 +45504,13 @@
         <v>2945</v>
       </c>
       <c r="F1370" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G1370" s="2">
         <v>0</v>
       </c>
       <c r="H1370" s="2">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="1371" spans="1:8" x14ac:dyDescent="0.25">
@@ -45686,13 +45686,13 @@
         <v>2825</v>
       </c>
       <c r="F1377" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G1377" s="2">
         <v>0</v>
       </c>
       <c r="H1377" s="2">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1378" spans="1:8" x14ac:dyDescent="0.25">
@@ -46128,13 +46128,13 @@
         <v>2966</v>
       </c>
       <c r="F1394" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="G1394" s="2">
         <v>0</v>
       </c>
       <c r="H1394" s="2">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="1395" spans="1:8" x14ac:dyDescent="0.25">
@@ -46232,13 +46232,13 @@
         <v>2915</v>
       </c>
       <c r="F1398" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G1398" s="2">
         <v>0</v>
       </c>
       <c r="H1398" s="2">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1399" spans="1:8" x14ac:dyDescent="0.25">
@@ -46986,13 +46986,13 @@
         <v>2868</v>
       </c>
       <c r="F1427" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1427" s="2">
         <v>0</v>
       </c>
       <c r="H1427" s="2">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1428" spans="1:8" x14ac:dyDescent="0.25">
@@ -47012,13 +47012,13 @@
         <v>3015</v>
       </c>
       <c r="F1428" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1428" s="2">
         <v>0</v>
       </c>
       <c r="H1428" s="2">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1429" spans="1:8" x14ac:dyDescent="0.25">
@@ -47324,13 +47324,13 @@
         <v>2901</v>
       </c>
       <c r="F1440" s="2">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="G1440" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1440" s="2">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1441" spans="1:8" x14ac:dyDescent="0.25">
@@ -47376,13 +47376,13 @@
         <v>2994</v>
       </c>
       <c r="F1442" s="2">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G1442" s="2">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1442" s="2">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1443" spans="1:8" x14ac:dyDescent="0.25">
@@ -47584,13 +47584,13 @@
         <v>2868</v>
       </c>
       <c r="F1450" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G1450" s="2">
         <v>0</v>
       </c>
       <c r="H1450" s="2">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="1451" spans="1:8" x14ac:dyDescent="0.25">
@@ -47662,13 +47662,13 @@
         <v>2994</v>
       </c>
       <c r="F1453" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="G1453" s="2">
         <v>0</v>
       </c>
       <c r="H1453" s="2">
-        <v>16</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1454" spans="1:8" x14ac:dyDescent="0.25">
@@ -48908,10 +48908,10 @@
         <v>939</v>
       </c>
       <c r="F1501" s="2">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="G1501" s="2">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H1501" s="2">
         <v>28</v>

--- a/STOK DEALER/STOK SRB.xlsx
+++ b/STOK DEALER/STOK SRB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data D\2026\UPADTE TOOLS BUNDLING SRB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6215571-E0DC-4F2C-B4C9-32956A614854}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BA4B0A9-5D93-441F-86B8-518DFFC3D0E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10047,13 +10047,13 @@
         <v>17</v>
       </c>
       <c r="F5" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G5" s="1">
         <v>0</v>
       </c>
       <c r="H5" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.15">
@@ -10229,13 +10229,13 @@
         <v>20</v>
       </c>
       <c r="F12" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G12" s="1">
         <v>0</v>
       </c>
       <c r="H12" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.15">
@@ -10593,13 +10593,13 @@
         <v>54</v>
       </c>
       <c r="F26" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G26" s="1">
         <v>0</v>
       </c>
       <c r="H26" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.15">
@@ -10619,13 +10619,13 @@
         <v>56</v>
       </c>
       <c r="F27" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G27" s="1">
         <v>0</v>
       </c>
       <c r="H27" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.15">
@@ -11009,10 +11009,10 @@
         <v>54</v>
       </c>
       <c r="F42" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G42" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H42" s="1">
         <v>0</v>
@@ -11321,10 +11321,10 @@
         <v>110</v>
       </c>
       <c r="F54" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G54" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H54" s="1">
         <v>1</v>
@@ -11711,13 +11711,13 @@
         <v>114</v>
       </c>
       <c r="F69" s="1">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="G69" s="1">
         <v>0</v>
       </c>
       <c r="H69" s="1">
-        <v>5</v>
+        <v>14</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.15">
@@ -13141,13 +13141,13 @@
         <v>241</v>
       </c>
       <c r="F124" s="1">
-        <v>2</v>
+        <v>31</v>
       </c>
       <c r="G124" s="1">
         <v>0</v>
       </c>
       <c r="H124" s="1">
-        <v>2</v>
+        <v>31</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.15">
@@ -13712,10 +13712,10 @@
         <v>28</v>
       </c>
       <c r="G146" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H146" s="1">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.15">
@@ -13735,13 +13735,13 @@
         <v>287</v>
       </c>
       <c r="F147" s="1">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="G147" s="1">
         <v>2</v>
       </c>
       <c r="H147" s="1">
-        <v>117</v>
+        <v>118</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.15">
@@ -13761,13 +13761,13 @@
         <v>287</v>
       </c>
       <c r="F148" s="1">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="G148" s="1">
         <v>0</v>
       </c>
       <c r="H148" s="1">
-        <v>229</v>
+        <v>227</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.15">
@@ -13891,13 +13891,13 @@
         <v>303</v>
       </c>
       <c r="F153" s="1">
-        <v>204</v>
+        <v>383</v>
       </c>
       <c r="G153" s="1">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="H153" s="1">
-        <v>197</v>
+        <v>379</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.15">
@@ -14151,13 +14151,13 @@
         <v>284</v>
       </c>
       <c r="F163" s="1">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="G163" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H163" s="1">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.15">
@@ -14177,13 +14177,13 @@
         <v>303</v>
       </c>
       <c r="F164" s="1">
-        <v>382</v>
+        <v>637</v>
       </c>
       <c r="G164" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H164" s="1">
-        <v>378</v>
+        <v>634</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.15">
@@ -14333,13 +14333,13 @@
         <v>334</v>
       </c>
       <c r="F170" s="1">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="G170" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H170" s="1">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.15">
@@ -14697,13 +14697,13 @@
         <v>364</v>
       </c>
       <c r="F184" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G184" s="1">
         <v>0</v>
       </c>
       <c r="H184" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="185" spans="1:8" ht="27" x14ac:dyDescent="0.15">
@@ -15165,13 +15165,13 @@
         <v>361</v>
       </c>
       <c r="F202" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G202" s="1">
         <v>0</v>
       </c>
       <c r="H202" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.15">
@@ -15295,13 +15295,13 @@
         <v>383</v>
       </c>
       <c r="F207" s="1">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="G207" s="1">
         <v>0</v>
       </c>
       <c r="H207" s="1">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.15">
@@ -15373,13 +15373,13 @@
         <v>377</v>
       </c>
       <c r="F210" s="1">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G210" s="1">
         <v>0</v>
       </c>
       <c r="H210" s="1">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="211" spans="1:8" ht="27" x14ac:dyDescent="0.15">
@@ -15529,13 +15529,13 @@
         <v>442</v>
       </c>
       <c r="F216" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G216" s="1">
         <v>0</v>
       </c>
       <c r="H216" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.15">
@@ -15581,13 +15581,13 @@
         <v>442</v>
       </c>
       <c r="F218" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G218" s="1">
         <v>0</v>
       </c>
       <c r="H218" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.15">
@@ -20599,13 +20599,13 @@
         <v>358</v>
       </c>
       <c r="F411" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G411" s="1">
         <v>0</v>
       </c>
       <c r="H411" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="412" spans="1:8" ht="27" x14ac:dyDescent="0.15">
@@ -20807,10 +20807,10 @@
         <v>878</v>
       </c>
       <c r="F419" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="G419" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H419" s="1">
         <v>1</v>
@@ -20833,13 +20833,13 @@
         <v>881</v>
       </c>
       <c r="F420" s="1">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="G420" s="1">
         <v>2</v>
       </c>
       <c r="H420" s="1">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="421" spans="1:8" x14ac:dyDescent="0.15">
@@ -21327,10 +21327,10 @@
         <v>594</v>
       </c>
       <c r="F439" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G439" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H439" s="1">
         <v>13</v>
@@ -22547,13 +22547,13 @@
         <v>1019</v>
       </c>
       <c r="F486" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G486" s="1">
         <v>0</v>
       </c>
       <c r="H486" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="487" spans="1:8" x14ac:dyDescent="0.15">
@@ -22651,13 +22651,13 @@
         <v>605</v>
       </c>
       <c r="F490" s="1">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G490" s="1">
         <v>0</v>
       </c>
       <c r="H490" s="1">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="491" spans="1:8" x14ac:dyDescent="0.15">
@@ -23275,13 +23275,13 @@
         <v>1071</v>
       </c>
       <c r="F514" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="G514" s="1">
         <v>0</v>
       </c>
       <c r="H514" s="1">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="515" spans="1:8" x14ac:dyDescent="0.15">
@@ -23405,13 +23405,13 @@
         <v>1080</v>
       </c>
       <c r="F519" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G519" s="1">
         <v>1</v>
       </c>
       <c r="H519" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="520" spans="1:8" x14ac:dyDescent="0.15">
@@ -23613,13 +23613,13 @@
         <v>1096</v>
       </c>
       <c r="F527" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G527" s="1">
         <v>0</v>
       </c>
       <c r="H527" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="528" spans="1:8" x14ac:dyDescent="0.15">
@@ -24157,13 +24157,13 @@
         <v>1141</v>
       </c>
       <c r="F548" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G548" s="1">
         <v>0</v>
       </c>
       <c r="H548" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="549" spans="1:8" x14ac:dyDescent="0.15">
@@ -24209,13 +24209,13 @@
         <v>589</v>
       </c>
       <c r="F550" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G550" s="1">
         <v>0</v>
       </c>
       <c r="H550" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="551" spans="1:8" x14ac:dyDescent="0.15">
@@ -24259,13 +24259,13 @@
         <v>1136</v>
       </c>
       <c r="F552" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G552" s="1">
         <v>0</v>
       </c>
       <c r="H552" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="553" spans="1:8" x14ac:dyDescent="0.15">
@@ -24311,13 +24311,13 @@
         <v>1148</v>
       </c>
       <c r="F554" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G554" s="1">
         <v>0</v>
       </c>
       <c r="H554" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="555" spans="1:8" x14ac:dyDescent="0.15">
@@ -25091,10 +25091,10 @@
         <v>1210</v>
       </c>
       <c r="F584" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G584" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H584" s="1">
         <v>0</v>
@@ -25143,10 +25143,10 @@
         <v>1213</v>
       </c>
       <c r="F586" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G586" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H586" s="1">
         <v>0</v>
@@ -26937,10 +26937,10 @@
         <v>1351</v>
       </c>
       <c r="F655" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G655" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H655" s="1">
         <v>8</v>
@@ -27093,13 +27093,13 @@
         <v>1351</v>
       </c>
       <c r="F661" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G661" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H661" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="662" spans="1:8" x14ac:dyDescent="0.15">
@@ -27119,13 +27119,13 @@
         <v>1366</v>
       </c>
       <c r="F662" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G662" s="1">
         <v>0</v>
       </c>
       <c r="H662" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="663" spans="1:8" x14ac:dyDescent="0.15">
@@ -27249,13 +27249,13 @@
         <v>1378</v>
       </c>
       <c r="F667" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G667" s="1">
         <v>0</v>
       </c>
       <c r="H667" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="668" spans="1:8" x14ac:dyDescent="0.15">
@@ -27327,13 +27327,13 @@
         <v>1299</v>
       </c>
       <c r="F670" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G670" s="1">
         <v>0</v>
       </c>
       <c r="H670" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="671" spans="1:8" x14ac:dyDescent="0.15">
@@ -27353,10 +27353,10 @@
         <v>1378</v>
       </c>
       <c r="F671" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G671" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H671" s="1">
         <v>7</v>
@@ -28055,13 +28055,13 @@
         <v>353</v>
       </c>
       <c r="F698" s="1">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G698" s="1">
         <v>0</v>
       </c>
       <c r="H698" s="1">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="699" spans="1:8" x14ac:dyDescent="0.15">
@@ -28393,13 +28393,13 @@
         <v>1477</v>
       </c>
       <c r="F711" s="1">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G711" s="1">
         <v>0</v>
       </c>
       <c r="H711" s="1">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="712" spans="1:8" x14ac:dyDescent="0.15">
@@ -28887,13 +28887,13 @@
         <v>1510</v>
       </c>
       <c r="F730" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="G730" s="1">
         <v>0</v>
       </c>
       <c r="H730" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="731" spans="1:8" x14ac:dyDescent="0.15">
@@ -29407,13 +29407,13 @@
         <v>1564</v>
       </c>
       <c r="F750" s="1">
-        <v>8</v>
+        <v>27</v>
       </c>
       <c r="G750" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H750" s="1">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="751" spans="1:8" x14ac:dyDescent="0.15">
@@ -30395,13 +30395,13 @@
         <v>1644</v>
       </c>
       <c r="F788" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G788" s="1">
         <v>0</v>
       </c>
       <c r="H788" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="789" spans="1:8" x14ac:dyDescent="0.15">
@@ -30577,13 +30577,13 @@
         <v>1664</v>
       </c>
       <c r="F795" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G795" s="1">
         <v>1</v>
       </c>
       <c r="H795" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="796" spans="1:8" x14ac:dyDescent="0.15">
@@ -30655,13 +30655,13 @@
         <v>1673</v>
       </c>
       <c r="F798" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G798" s="1">
         <v>0</v>
       </c>
       <c r="H798" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="799" spans="1:8" x14ac:dyDescent="0.15">
@@ -31019,13 +31019,13 @@
         <v>1706</v>
       </c>
       <c r="F812" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G812" s="1">
         <v>0</v>
       </c>
       <c r="H812" s="1">
-        <v>1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="813" spans="1:8" x14ac:dyDescent="0.15">
@@ -31383,13 +31383,13 @@
         <v>1732</v>
       </c>
       <c r="F826" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G826" s="1">
         <v>0</v>
       </c>
       <c r="H826" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="827" spans="1:8" x14ac:dyDescent="0.15">
@@ -31435,10 +31435,10 @@
         <v>1662</v>
       </c>
       <c r="F828" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G828" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H828" s="1">
         <v>2</v>
@@ -31513,13 +31513,13 @@
         <v>1743</v>
       </c>
       <c r="F831" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="G831" s="1">
         <v>0</v>
       </c>
       <c r="H831" s="1">
-        <v>1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="832" spans="1:8" x14ac:dyDescent="0.15">
@@ -31594,10 +31594,10 @@
         <v>5</v>
       </c>
       <c r="G834" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H834" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="835" spans="1:8" x14ac:dyDescent="0.15">
@@ -32293,13 +32293,13 @@
         <v>1803</v>
       </c>
       <c r="F861" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G861" s="1">
         <v>0</v>
       </c>
       <c r="H861" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="862" spans="1:8" x14ac:dyDescent="0.15">
@@ -32475,13 +32475,13 @@
         <v>1818</v>
       </c>
       <c r="F868" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G868" s="1">
         <v>1</v>
       </c>
       <c r="H868" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="869" spans="1:8" x14ac:dyDescent="0.15">
@@ -35047,13 +35047,13 @@
         <v>1647</v>
       </c>
       <c r="F967" s="1">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="G967" s="1">
         <v>0</v>
       </c>
       <c r="H967" s="1">
-        <v>56</v>
+        <v>54</v>
       </c>
     </row>
     <row r="968" spans="1:8" x14ac:dyDescent="0.15">
@@ -35099,13 +35099,13 @@
         <v>1997</v>
       </c>
       <c r="F969" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G969" s="1">
         <v>0</v>
       </c>
       <c r="H969" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="970" spans="1:8" x14ac:dyDescent="0.15">
@@ -35151,13 +35151,13 @@
         <v>2008</v>
       </c>
       <c r="F971" s="1">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="G971" s="1">
         <v>0</v>
       </c>
       <c r="H971" s="1">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="972" spans="1:8" x14ac:dyDescent="0.15">
@@ -35229,13 +35229,13 @@
         <v>2025</v>
       </c>
       <c r="F974" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G974" s="1">
         <v>0</v>
       </c>
       <c r="H974" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="975" spans="1:8" x14ac:dyDescent="0.15">
@@ -35255,13 +35255,13 @@
         <v>2028</v>
       </c>
       <c r="F975" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G975" s="1">
         <v>0</v>
       </c>
       <c r="H975" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="976" spans="1:8" x14ac:dyDescent="0.15">
@@ -37959,13 +37959,13 @@
         <v>1893</v>
       </c>
       <c r="F1079" s="1">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G1079" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1079" s="1">
-        <v>21</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1080" spans="1:8" x14ac:dyDescent="0.15">
@@ -39623,13 +39623,13 @@
         <v>2361</v>
       </c>
       <c r="F1143" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1143" s="1">
         <v>0</v>
       </c>
       <c r="H1143" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1144" spans="1:8" x14ac:dyDescent="0.15">
@@ -39701,13 +39701,13 @@
         <v>2374</v>
       </c>
       <c r="F1146" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1146" s="1">
         <v>0</v>
       </c>
       <c r="H1146" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1147" spans="1:8" x14ac:dyDescent="0.15">
@@ -39727,13 +39727,13 @@
         <v>2338</v>
       </c>
       <c r="F1147" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1147" s="1">
         <v>0</v>
       </c>
       <c r="H1147" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1148" spans="1:8" x14ac:dyDescent="0.15">
@@ -39753,13 +39753,13 @@
         <v>2338</v>
       </c>
       <c r="F1148" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="G1148" s="1">
         <v>0</v>
       </c>
       <c r="H1148" s="1">
-        <v>0</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1149" spans="1:8" x14ac:dyDescent="0.15">
@@ -40221,13 +40221,13 @@
         <v>2343</v>
       </c>
       <c r="F1166" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G1166" s="1">
         <v>0</v>
       </c>
       <c r="H1166" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1167" spans="1:8" x14ac:dyDescent="0.15">
@@ -40403,13 +40403,13 @@
         <v>2352</v>
       </c>
       <c r="F1173" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="G1173" s="1">
         <v>0</v>
       </c>
       <c r="H1173" s="1">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1174" spans="1:8" x14ac:dyDescent="0.15">
@@ -40429,13 +40429,13 @@
         <v>2338</v>
       </c>
       <c r="F1174" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1174" s="1">
         <v>0</v>
       </c>
       <c r="H1174" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1175" spans="1:8" x14ac:dyDescent="0.15">
@@ -40455,13 +40455,13 @@
         <v>2352</v>
       </c>
       <c r="F1175" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="G1175" s="1">
         <v>0</v>
       </c>
       <c r="H1175" s="1">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1176" spans="1:8" x14ac:dyDescent="0.15">
@@ -40585,13 +40585,13 @@
         <v>2338</v>
       </c>
       <c r="F1180" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1180" s="1">
         <v>0</v>
       </c>
       <c r="H1180" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1181" spans="1:8" x14ac:dyDescent="0.15">
@@ -40637,13 +40637,13 @@
         <v>2355</v>
       </c>
       <c r="F1182" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1182" s="1">
         <v>0</v>
       </c>
       <c r="H1182" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1183" spans="1:8" x14ac:dyDescent="0.15">
@@ -40793,13 +40793,13 @@
         <v>2343</v>
       </c>
       <c r="F1188" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G1188" s="1">
         <v>0</v>
       </c>
       <c r="H1188" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1189" spans="1:8" x14ac:dyDescent="0.15">
@@ -40845,13 +40845,13 @@
         <v>2343</v>
       </c>
       <c r="F1190" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G1190" s="1">
         <v>0</v>
       </c>
       <c r="H1190" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1191" spans="1:8" ht="27" x14ac:dyDescent="0.15">
@@ -42067,13 +42067,13 @@
         <v>1372</v>
       </c>
       <c r="F1237" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1237" s="1">
         <v>0</v>
       </c>
       <c r="H1237" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1238" spans="1:8" x14ac:dyDescent="0.15">
@@ -42509,13 +42509,13 @@
         <v>292</v>
       </c>
       <c r="F1254" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G1254" s="1">
         <v>0</v>
       </c>
       <c r="H1254" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1255" spans="1:8" x14ac:dyDescent="0.15">
@@ -42743,13 +42743,13 @@
         <v>665</v>
       </c>
       <c r="F1263" s="1">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="G1263" s="1">
         <v>0</v>
       </c>
       <c r="H1263" s="1">
-        <v>69</v>
+        <v>67</v>
       </c>
     </row>
     <row r="1264" spans="1:8" x14ac:dyDescent="0.15">
@@ -43055,13 +43055,13 @@
         <v>1237</v>
       </c>
       <c r="F1275" s="1">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G1275" s="1">
         <v>0</v>
       </c>
       <c r="H1275" s="1">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="1276" spans="1:8" x14ac:dyDescent="0.15">
@@ -43081,13 +43081,13 @@
         <v>350</v>
       </c>
       <c r="F1276" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G1276" s="1">
         <v>0</v>
       </c>
       <c r="H1276" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1277" spans="1:8" x14ac:dyDescent="0.15">
@@ -43211,13 +43211,13 @@
         <v>2636</v>
       </c>
       <c r="F1281" s="1">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G1281" s="1">
         <v>0</v>
       </c>
       <c r="H1281" s="1">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1282" spans="1:8" x14ac:dyDescent="0.15">
@@ -43289,13 +43289,13 @@
         <v>2633</v>
       </c>
       <c r="F1284" s="1">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="G1284" s="1">
         <v>0</v>
       </c>
       <c r="H1284" s="1">
-        <v>5</v>
+        <v>28</v>
       </c>
     </row>
     <row r="1285" spans="1:8" x14ac:dyDescent="0.15">
@@ -43315,13 +43315,13 @@
         <v>2633</v>
       </c>
       <c r="F1285" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1285" s="1">
         <v>0</v>
       </c>
       <c r="H1285" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1286" spans="1:8" x14ac:dyDescent="0.15">
@@ -46149,13 +46149,13 @@
         <v>2882</v>
       </c>
       <c r="F1394" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G1394" s="1">
         <v>0</v>
       </c>
       <c r="H1394" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1395" spans="1:8" x14ac:dyDescent="0.15">
@@ -47007,13 +47007,13 @@
         <v>2714</v>
       </c>
       <c r="F1427" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1427" s="1">
         <v>0</v>
       </c>
       <c r="H1427" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1428" spans="1:8" ht="27" x14ac:dyDescent="0.15">
@@ -47319,13 +47319,13 @@
         <v>2942</v>
       </c>
       <c r="F1439" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G1439" s="1">
         <v>0</v>
       </c>
       <c r="H1439" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1440" spans="1:8" x14ac:dyDescent="0.15">
@@ -47371,13 +47371,13 @@
         <v>2882</v>
       </c>
       <c r="F1441" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1441" s="1">
         <v>0</v>
       </c>
       <c r="H1441" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1442" spans="1:8" x14ac:dyDescent="0.15">
@@ -47397,13 +47397,13 @@
         <v>2922</v>
       </c>
       <c r="F1442" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G1442" s="1">
         <v>0</v>
       </c>
       <c r="H1442" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1443" spans="1:8" x14ac:dyDescent="0.15">
@@ -47605,13 +47605,13 @@
         <v>2714</v>
       </c>
       <c r="F1450" s="1">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G1450" s="1">
         <v>0</v>
       </c>
       <c r="H1450" s="1">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1451" spans="1:8" x14ac:dyDescent="0.15">
@@ -47631,13 +47631,13 @@
         <v>2681</v>
       </c>
       <c r="F1451" s="1">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G1451" s="1">
         <v>0</v>
       </c>
       <c r="H1451" s="1">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1452" spans="1:8" x14ac:dyDescent="0.15">
@@ -48929,13 +48929,13 @@
         <v>350</v>
       </c>
       <c r="F1501" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G1501" s="1">
         <v>0</v>
       </c>
       <c r="H1501" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1502" spans="1:8" x14ac:dyDescent="0.15">

--- a/STOK DEALER/STOK SRB.xlsx
+++ b/STOK DEALER/STOK SRB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data D\2026\UPADTE TOOLS BUNDLING SRB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5BA4B0A9-5D93-441F-86B8-518DFFC3D0E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20052F75-AAA3-44F1-A315-272296DD52DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10021,13 +10021,13 @@
         <v>17</v>
       </c>
       <c r="F4" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G4" s="1">
         <v>0</v>
       </c>
       <c r="H4" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.15">
@@ -10151,13 +10151,13 @@
         <v>20</v>
       </c>
       <c r="F9" s="1">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
       </c>
       <c r="H9" s="1">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.15">
@@ -11246,10 +11246,10 @@
         <v>6</v>
       </c>
       <c r="G51" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H51" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.15">
@@ -11506,10 +11506,10 @@
         <v>21</v>
       </c>
       <c r="G61" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H61" s="1">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.15">
@@ -11714,10 +11714,10 @@
         <v>14</v>
       </c>
       <c r="G69" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H69" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.15">
@@ -13712,10 +13712,10 @@
         <v>28</v>
       </c>
       <c r="G146" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H146" s="1">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.15">
@@ -13735,13 +13735,13 @@
         <v>287</v>
       </c>
       <c r="F147" s="1">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="G147" s="1">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="H147" s="1">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.15">
@@ -13764,10 +13764,10 @@
         <v>227</v>
       </c>
       <c r="G148" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H148" s="1">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.15">
@@ -13891,10 +13891,10 @@
         <v>303</v>
       </c>
       <c r="F153" s="1">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="G153" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H153" s="1">
         <v>379</v>
@@ -14151,13 +14151,13 @@
         <v>284</v>
       </c>
       <c r="F163" s="1">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="G163" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H163" s="1">
-        <v>110</v>
+        <v>105</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.15">
@@ -14177,13 +14177,13 @@
         <v>303</v>
       </c>
       <c r="F164" s="1">
-        <v>637</v>
+        <v>629</v>
       </c>
       <c r="G164" s="1">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="H164" s="1">
-        <v>634</v>
+        <v>621</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.15">
@@ -14333,13 +14333,13 @@
         <v>334</v>
       </c>
       <c r="F170" s="1">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="G170" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H170" s="1">
-        <v>170</v>
+        <v>165</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.15">
@@ -20833,13 +20833,13 @@
         <v>881</v>
       </c>
       <c r="F420" s="1">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G420" s="1">
         <v>2</v>
       </c>
       <c r="H420" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="421" spans="1:8" x14ac:dyDescent="0.15">
@@ -20885,13 +20885,13 @@
         <v>885</v>
       </c>
       <c r="F422" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G422" s="1">
         <v>0</v>
       </c>
       <c r="H422" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="423" spans="1:8" x14ac:dyDescent="0.15">
@@ -22550,10 +22550,10 @@
         <v>1</v>
       </c>
       <c r="G486" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H486" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="487" spans="1:8" x14ac:dyDescent="0.15">
@@ -22651,13 +22651,13 @@
         <v>605</v>
       </c>
       <c r="F490" s="1">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G490" s="1">
         <v>0</v>
       </c>
       <c r="H490" s="1">
-        <v>17</v>
+        <v>16</v>
       </c>
     </row>
     <row r="491" spans="1:8" x14ac:dyDescent="0.15">
@@ -24753,13 +24753,13 @@
         <v>1187</v>
       </c>
       <c r="F571" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G571" s="1">
         <v>2</v>
       </c>
       <c r="H571" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="572" spans="1:8" x14ac:dyDescent="0.15">
@@ -24964,10 +24964,10 @@
         <v>20</v>
       </c>
       <c r="G579" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H579" s="1">
-        <v>18</v>
+        <v>17</v>
       </c>
     </row>
     <row r="580" spans="1:8" x14ac:dyDescent="0.15">
@@ -27379,13 +27379,13 @@
         <v>1378</v>
       </c>
       <c r="F672" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G672" s="1">
         <v>1</v>
       </c>
       <c r="H672" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="673" spans="1:8" x14ac:dyDescent="0.15">
@@ -28890,10 +28890,10 @@
         <v>10</v>
       </c>
       <c r="G730" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H730" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="731" spans="1:8" x14ac:dyDescent="0.15">
@@ -29407,10 +29407,10 @@
         <v>1564</v>
       </c>
       <c r="F750" s="1">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="G750" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H750" s="1">
         <v>25</v>
@@ -30577,13 +30577,13 @@
         <v>1664</v>
       </c>
       <c r="F795" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G795" s="1">
         <v>1</v>
       </c>
       <c r="H795" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="796" spans="1:8" x14ac:dyDescent="0.15">
@@ -30788,10 +30788,10 @@
         <v>1</v>
       </c>
       <c r="G803" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H803" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="804" spans="1:8" x14ac:dyDescent="0.15">
@@ -31045,10 +31045,10 @@
         <v>1706</v>
       </c>
       <c r="F813" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G813" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H813" s="1">
         <v>1</v>
@@ -33412,10 +33412,10 @@
         <v>3</v>
       </c>
       <c r="G904" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H904" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="905" spans="1:8" x14ac:dyDescent="0.15">
@@ -35050,10 +35050,10 @@
         <v>54</v>
       </c>
       <c r="G967" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H967" s="1">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="968" spans="1:8" x14ac:dyDescent="0.15">
@@ -35151,13 +35151,13 @@
         <v>2008</v>
       </c>
       <c r="F971" s="1">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G971" s="1">
         <v>0</v>
       </c>
       <c r="H971" s="1">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="972" spans="1:8" x14ac:dyDescent="0.15">
@@ -37959,13 +37959,13 @@
         <v>1893</v>
       </c>
       <c r="F1079" s="1">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G1079" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1079" s="1">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1080" spans="1:8" x14ac:dyDescent="0.15">
@@ -39860,10 +39860,10 @@
         <v>4</v>
       </c>
       <c r="G1152" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1152" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1153" spans="1:8" x14ac:dyDescent="0.15">
@@ -39987,13 +39987,13 @@
         <v>2117</v>
       </c>
       <c r="F1157" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1157" s="1">
         <v>0</v>
       </c>
       <c r="H1157" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1158" spans="1:8" x14ac:dyDescent="0.15">
@@ -43292,10 +43292,10 @@
         <v>28</v>
       </c>
       <c r="G1284" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1284" s="1">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="1285" spans="1:8" x14ac:dyDescent="0.15">
@@ -47319,13 +47319,13 @@
         <v>2942</v>
       </c>
       <c r="F1439" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1439" s="1">
         <v>0</v>
       </c>
       <c r="H1439" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1440" spans="1:8" x14ac:dyDescent="0.15">

--- a/STOK DEALER/STOK SRB.xlsx
+++ b/STOK DEALER/STOK SRB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data D\2026\UPADTE TOOLS BUNDLING SRB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B2F0E27-2A09-48B7-A9DB-8E45A69EAF6B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E9456AD-CF02-40A2-B837-5E33C336AB3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -11186,13 +11186,13 @@
         <v>97</v>
       </c>
       <c r="F49" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G49" s="1">
         <v>0</v>
       </c>
       <c r="H49" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.15">
@@ -11241,10 +11241,10 @@
         <v>4</v>
       </c>
       <c r="G51" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H51" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.15">
@@ -11527,10 +11527,10 @@
         <v>2</v>
       </c>
       <c r="G62" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H62" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="63" spans="1:8" x14ac:dyDescent="0.15">
@@ -11732,13 +11732,13 @@
         <v>114</v>
       </c>
       <c r="F70" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G70" s="1">
         <v>0</v>
       </c>
       <c r="H70" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.15">
@@ -11784,13 +11784,13 @@
         <v>145</v>
       </c>
       <c r="F72" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G72" s="1">
         <v>0</v>
       </c>
       <c r="H72" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.15">
@@ -13139,10 +13139,10 @@
         <v>29</v>
       </c>
       <c r="G124" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H124" s="1">
-        <v>29</v>
+        <v>27</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.15">
@@ -13704,13 +13704,13 @@
         <v>284</v>
       </c>
       <c r="F146" s="1">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="G146" s="1">
         <v>4</v>
       </c>
       <c r="H146" s="1">
-        <v>16</v>
+        <v>13</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.15">
@@ -13756,13 +13756,13 @@
         <v>287</v>
       </c>
       <c r="F148" s="1">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="G148" s="1">
         <v>1</v>
       </c>
       <c r="H148" s="1">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.15">
@@ -13886,13 +13886,13 @@
         <v>303</v>
       </c>
       <c r="F153" s="1">
-        <v>372</v>
+        <v>356</v>
       </c>
       <c r="G153" s="1">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="H153" s="1">
-        <v>362</v>
+        <v>344</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.15">
@@ -14146,13 +14146,13 @@
         <v>284</v>
       </c>
       <c r="F163" s="1">
-        <v>93</v>
+        <v>86</v>
       </c>
       <c r="G163" s="1">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="H163" s="1">
-        <v>91</v>
+        <v>75</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.15">
@@ -14172,13 +14172,13 @@
         <v>303</v>
       </c>
       <c r="F164" s="1">
-        <v>592</v>
+        <v>570</v>
       </c>
       <c r="G164" s="1">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H164" s="1">
-        <v>575</v>
+        <v>552</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.15">
@@ -14328,13 +14328,13 @@
         <v>334</v>
       </c>
       <c r="F170" s="1">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="G170" s="1">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="H170" s="1">
-        <v>152</v>
+        <v>140</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.15">
@@ -14484,13 +14484,13 @@
         <v>350</v>
       </c>
       <c r="F176" s="1">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="G176" s="1">
         <v>1</v>
       </c>
       <c r="H176" s="1">
-        <v>78</v>
+        <v>75</v>
       </c>
     </row>
     <row r="177" spans="1:8" x14ac:dyDescent="0.15">
@@ -14640,13 +14640,13 @@
         <v>364</v>
       </c>
       <c r="F182" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G182" s="1">
         <v>0</v>
       </c>
       <c r="H182" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.15">
@@ -15290,13 +15290,13 @@
         <v>383</v>
       </c>
       <c r="F207" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G207" s="1">
         <v>0</v>
       </c>
       <c r="H207" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.15">
@@ -15550,13 +15550,13 @@
         <v>445</v>
       </c>
       <c r="F217" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G217" s="1">
         <v>0</v>
       </c>
       <c r="H217" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.15">
@@ -19583,10 +19583,10 @@
         <v>1</v>
       </c>
       <c r="G372" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H372" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="373" spans="1:8" x14ac:dyDescent="0.15">
@@ -20698,13 +20698,13 @@
         <v>866</v>
       </c>
       <c r="F415" s="1">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G415" s="1">
         <v>0</v>
       </c>
       <c r="H415" s="1">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="416" spans="1:8" x14ac:dyDescent="0.15">
@@ -20831,10 +20831,10 @@
         <v>28</v>
       </c>
       <c r="G420" s="1">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="H420" s="1">
-        <v>24</v>
+        <v>23</v>
       </c>
     </row>
     <row r="421" spans="1:8" x14ac:dyDescent="0.15">
@@ -21036,13 +21036,13 @@
         <v>900</v>
       </c>
       <c r="F428" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G428" s="1">
         <v>0</v>
       </c>
       <c r="H428" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="429" spans="1:8" x14ac:dyDescent="0.15">
@@ -21244,13 +21244,13 @@
         <v>905</v>
       </c>
       <c r="F436" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G436" s="1">
         <v>0</v>
       </c>
       <c r="H436" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="437" spans="1:8" x14ac:dyDescent="0.15">
@@ -22649,10 +22649,10 @@
         <v>14</v>
       </c>
       <c r="G490" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H490" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="491" spans="1:8" x14ac:dyDescent="0.15">
@@ -23530,13 +23530,13 @@
         <v>1091</v>
       </c>
       <c r="F524" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G524" s="1">
         <v>0</v>
       </c>
       <c r="H524" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="525" spans="1:8" x14ac:dyDescent="0.15">
@@ -24592,13 +24592,13 @@
         <v>1172</v>
       </c>
       <c r="F565" s="1">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G565" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="H565" s="1">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
     <row r="566" spans="1:8" x14ac:dyDescent="0.15">
@@ -24878,13 +24878,13 @@
         <v>1196</v>
       </c>
       <c r="F576" s="1">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G576" s="1">
         <v>0</v>
       </c>
       <c r="H576" s="1">
-        <v>15</v>
+        <v>13</v>
       </c>
     </row>
     <row r="577" spans="1:8" x14ac:dyDescent="0.15">
@@ -24956,13 +24956,13 @@
         <v>1201</v>
       </c>
       <c r="F579" s="1">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G579" s="1">
         <v>3</v>
       </c>
       <c r="H579" s="1">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="580" spans="1:8" x14ac:dyDescent="0.15">
@@ -26935,10 +26935,10 @@
         <v>8</v>
       </c>
       <c r="G655" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H655" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="656" spans="1:8" x14ac:dyDescent="0.15">
@@ -27091,10 +27091,10 @@
         <v>2</v>
       </c>
       <c r="G661" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H661" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="662" spans="1:8" x14ac:dyDescent="0.15">
@@ -27348,13 +27348,13 @@
         <v>1378</v>
       </c>
       <c r="F671" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="G671" s="1">
         <v>1</v>
       </c>
       <c r="H671" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="672" spans="1:8" x14ac:dyDescent="0.15">
@@ -28050,13 +28050,13 @@
         <v>353</v>
       </c>
       <c r="F698" s="1">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G698" s="1">
         <v>0</v>
       </c>
       <c r="H698" s="1">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="699" spans="1:8" x14ac:dyDescent="0.15">
@@ -28388,13 +28388,13 @@
         <v>1477</v>
       </c>
       <c r="F711" s="1">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G711" s="1">
         <v>0</v>
       </c>
       <c r="H711" s="1">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="712" spans="1:8" x14ac:dyDescent="0.15">
@@ -28648,13 +28648,13 @@
         <v>1505</v>
       </c>
       <c r="F721" s="1">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="G721" s="1">
         <v>0</v>
       </c>
       <c r="H721" s="1">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="722" spans="1:8" x14ac:dyDescent="0.15">
@@ -30653,10 +30653,10 @@
         <v>4</v>
       </c>
       <c r="G798" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H798" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="799" spans="1:8" x14ac:dyDescent="0.15">
@@ -31508,13 +31508,13 @@
         <v>1743</v>
       </c>
       <c r="F831" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G831" s="1">
         <v>0</v>
       </c>
       <c r="H831" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="832" spans="1:8" x14ac:dyDescent="0.15">
@@ -31589,10 +31589,10 @@
         <v>5</v>
       </c>
       <c r="G834" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H834" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="835" spans="1:8" x14ac:dyDescent="0.15">
@@ -31976,13 +31976,13 @@
         <v>1567</v>
       </c>
       <c r="F849" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G849" s="1">
         <v>0</v>
       </c>
       <c r="H849" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="850" spans="1:8" x14ac:dyDescent="0.15">
@@ -32733,10 +32733,10 @@
         <v>1</v>
       </c>
       <c r="G878" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H878" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="879" spans="1:8" x14ac:dyDescent="0.15">
@@ -33068,13 +33068,13 @@
         <v>866</v>
       </c>
       <c r="F891" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G891" s="1">
         <v>0</v>
       </c>
       <c r="H891" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="892" spans="1:8" x14ac:dyDescent="0.15">
@@ -35045,10 +35045,10 @@
         <v>48</v>
       </c>
       <c r="G967" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H967" s="1">
-        <v>48</v>
+        <v>45</v>
       </c>
     </row>
     <row r="968" spans="1:8" x14ac:dyDescent="0.15">
@@ -35146,13 +35146,13 @@
         <v>2008</v>
       </c>
       <c r="F971" s="1">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G971" s="1">
         <v>0</v>
       </c>
       <c r="H971" s="1">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="972" spans="1:8" x14ac:dyDescent="0.15">
@@ -35198,13 +35198,13 @@
         <v>2025</v>
       </c>
       <c r="F973" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G973" s="1">
         <v>0</v>
       </c>
       <c r="H973" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="974" spans="1:8" x14ac:dyDescent="0.15">
@@ -35250,13 +35250,13 @@
         <v>2028</v>
       </c>
       <c r="F975" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="G975" s="1">
         <v>0</v>
       </c>
       <c r="H975" s="1">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="976" spans="1:8" x14ac:dyDescent="0.15">
@@ -36527,10 +36527,10 @@
         <v>1</v>
       </c>
       <c r="G1024" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1024" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1025" spans="1:8" x14ac:dyDescent="0.15">
@@ -36631,10 +36631,10 @@
         <v>1</v>
       </c>
       <c r="G1028" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1028" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1029" spans="1:8" x14ac:dyDescent="0.15">
@@ -37954,13 +37954,13 @@
         <v>1893</v>
       </c>
       <c r="F1079" s="1">
-        <v>176</v>
+        <v>169</v>
       </c>
       <c r="G1079" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H1079" s="1">
-        <v>176</v>
+        <v>165</v>
       </c>
     </row>
     <row r="1080" spans="1:8" x14ac:dyDescent="0.15">
@@ -38994,13 +38994,13 @@
         <v>1477</v>
       </c>
       <c r="F1119" s="1">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G1119" s="1">
         <v>0</v>
       </c>
       <c r="H1119" s="1">
-        <v>12</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1120" spans="1:8" x14ac:dyDescent="0.15">
@@ -39670,13 +39670,13 @@
         <v>2355</v>
       </c>
       <c r="F1145" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1145" s="1">
         <v>0</v>
       </c>
       <c r="H1145" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1146" spans="1:8" x14ac:dyDescent="0.15">
@@ -39904,13 +39904,13 @@
         <v>2374</v>
       </c>
       <c r="F1154" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1154" s="1">
         <v>0</v>
       </c>
       <c r="H1154" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1155" spans="1:8" x14ac:dyDescent="0.15">
@@ -40089,10 +40089,10 @@
         <v>3</v>
       </c>
       <c r="G1161" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1161" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1162" spans="1:8" x14ac:dyDescent="0.15">
@@ -40450,13 +40450,13 @@
         <v>2352</v>
       </c>
       <c r="F1175" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1175" s="1">
         <v>0</v>
       </c>
       <c r="H1175" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1176" spans="1:8" x14ac:dyDescent="0.15">
@@ -40791,10 +40791,10 @@
         <v>3</v>
       </c>
       <c r="G1188" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1188" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1189" spans="1:8" x14ac:dyDescent="0.15">
@@ -42374,13 +42374,13 @@
         <v>2580</v>
       </c>
       <c r="F1249" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G1249" s="1">
         <v>2</v>
       </c>
       <c r="H1249" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1250" spans="1:8" x14ac:dyDescent="0.15">
@@ -42738,13 +42738,13 @@
         <v>665</v>
       </c>
       <c r="F1263" s="1">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G1263" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1263" s="1">
-        <v>67</v>
+        <v>65</v>
       </c>
     </row>
     <row r="1264" spans="1:8" x14ac:dyDescent="0.15">
@@ -42842,13 +42842,13 @@
         <v>1381</v>
       </c>
       <c r="F1267" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1267" s="1">
         <v>1</v>
       </c>
       <c r="H1267" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1268" spans="1:8" x14ac:dyDescent="0.15">
@@ -43050,13 +43050,13 @@
         <v>1237</v>
       </c>
       <c r="F1275" s="1">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="G1275" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="H1275" s="1">
-        <v>24</v>
+        <v>20</v>
       </c>
     </row>
     <row r="1276" spans="1:8" x14ac:dyDescent="0.15">
@@ -43206,13 +43206,13 @@
         <v>2636</v>
       </c>
       <c r="F1281" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="G1281" s="1">
         <v>0</v>
       </c>
       <c r="H1281" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1282" spans="1:8" x14ac:dyDescent="0.15">
@@ -43284,13 +43284,13 @@
         <v>2633</v>
       </c>
       <c r="F1284" s="1">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="G1284" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1284" s="1">
-        <v>25</v>
+        <v>21</v>
       </c>
     </row>
     <row r="1285" spans="1:8" x14ac:dyDescent="0.15">
@@ -43313,10 +43313,10 @@
         <v>6</v>
       </c>
       <c r="G1285" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1285" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="1286" spans="1:8" x14ac:dyDescent="0.15">
@@ -44090,13 +44090,13 @@
         <v>2689</v>
       </c>
       <c r="F1315" s="1">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G1315" s="1">
         <v>0</v>
       </c>
       <c r="H1315" s="1">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="1316" spans="1:8" x14ac:dyDescent="0.15">
@@ -45520,13 +45520,13 @@
         <v>2825</v>
       </c>
       <c r="F1370" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G1370" s="1">
         <v>0</v>
       </c>
       <c r="H1370" s="1">
-        <v>15</v>
+        <v>14</v>
       </c>
     </row>
     <row r="1371" spans="1:8" x14ac:dyDescent="0.15">
@@ -45705,10 +45705,10 @@
         <v>7</v>
       </c>
       <c r="G1377" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1377" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1378" spans="1:8" x14ac:dyDescent="0.15">
@@ -46170,13 +46170,13 @@
         <v>3151</v>
       </c>
       <c r="F1395" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1395" s="1">
         <v>0</v>
       </c>
       <c r="H1395" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1396" spans="1:8" x14ac:dyDescent="0.15">
@@ -47080,13 +47080,13 @@
         <v>2922</v>
       </c>
       <c r="F1430" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1430" s="1">
         <v>0</v>
       </c>
       <c r="H1430" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1431" spans="1:8" x14ac:dyDescent="0.15">
@@ -47340,13 +47340,13 @@
         <v>2757</v>
       </c>
       <c r="F1440" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1440" s="1">
         <v>0</v>
       </c>
       <c r="H1440" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1441" spans="1:8" x14ac:dyDescent="0.15">
@@ -47392,13 +47392,13 @@
         <v>2922</v>
       </c>
       <c r="F1442" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1442" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1442" s="1">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1443" spans="1:8" x14ac:dyDescent="0.15">
@@ -47600,13 +47600,13 @@
         <v>2714</v>
       </c>
       <c r="F1450" s="1">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="G1450" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1450" s="1">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1451" spans="1:8" x14ac:dyDescent="0.15">
@@ -47629,10 +47629,10 @@
         <v>7</v>
       </c>
       <c r="G1451" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1451" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1452" spans="1:8" x14ac:dyDescent="0.15">
@@ -47678,13 +47678,13 @@
         <v>2922</v>
       </c>
       <c r="F1453" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G1453" s="1">
         <v>0</v>
       </c>
       <c r="H1453" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1454" spans="1:8" x14ac:dyDescent="0.15">
@@ -48820,13 +48820,13 @@
         <v>1052</v>
       </c>
       <c r="F1497" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G1497" s="1">
         <v>0</v>
       </c>
       <c r="H1497" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1498" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.15">
@@ -48924,13 +48924,13 @@
         <v>350</v>
       </c>
       <c r="F1501" s="1">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="G1501" s="1">
         <v>0</v>
       </c>
       <c r="H1501" s="1">
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="1502" spans="1:8" x14ac:dyDescent="0.15">

--- a/STOK DEALER/STOK SRB.xlsx
+++ b/STOK DEALER/STOK SRB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data D\2026\UPADTE TOOLS BUNDLING SRB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E9456AD-CF02-40A2-B837-5E33C336AB3F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E9FEB6F-B803-4EE1-BE8B-37DD1EFF7D2B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10146,13 +10146,13 @@
         <v>20</v>
       </c>
       <c r="F9" s="1">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
       </c>
       <c r="H9" s="1">
-        <v>23</v>
+        <v>20</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.15">
@@ -10799,10 +10799,10 @@
         <v>1</v>
       </c>
       <c r="G34" s="1">
+        <v>0</v>
+      </c>
+      <c r="H34" s="1">
         <v>1</v>
-      </c>
-      <c r="H34" s="1">
-        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.15">
@@ -11316,13 +11316,13 @@
         <v>110</v>
       </c>
       <c r="F54" s="1">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="G54" s="1">
         <v>0</v>
       </c>
       <c r="H54" s="1">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="55" spans="1:8" x14ac:dyDescent="0.15">
@@ -11706,13 +11706,13 @@
         <v>114</v>
       </c>
       <c r="F69" s="1">
-        <v>13</v>
+        <v>18</v>
       </c>
       <c r="G69" s="1">
         <v>1</v>
       </c>
       <c r="H69" s="1">
-        <v>12</v>
+        <v>17</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.15">
@@ -11732,13 +11732,13 @@
         <v>114</v>
       </c>
       <c r="F70" s="1">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="G70" s="1">
         <v>0</v>
       </c>
       <c r="H70" s="1">
-        <v>0</v>
+        <v>11</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.15">
@@ -11784,13 +11784,13 @@
         <v>145</v>
       </c>
       <c r="F72" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G72" s="1">
         <v>0</v>
       </c>
       <c r="H72" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="73" spans="1:8" x14ac:dyDescent="0.15">
@@ -13136,13 +13136,13 @@
         <v>241</v>
       </c>
       <c r="F124" s="1">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="G124" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H124" s="1">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.15">
@@ -13704,13 +13704,13 @@
         <v>284</v>
       </c>
       <c r="F146" s="1">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G146" s="1">
         <v>4</v>
       </c>
       <c r="H146" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.15">
@@ -13730,13 +13730,13 @@
         <v>287</v>
       </c>
       <c r="F147" s="1">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="G147" s="1">
         <v>2</v>
       </c>
       <c r="H147" s="1">
-        <v>109</v>
+        <v>106</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.15">
@@ -13886,13 +13886,13 @@
         <v>303</v>
       </c>
       <c r="F153" s="1">
-        <v>356</v>
+        <v>425</v>
       </c>
       <c r="G153" s="1">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H153" s="1">
-        <v>344</v>
+        <v>412</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.15">
@@ -14146,13 +14146,13 @@
         <v>284</v>
       </c>
       <c r="F163" s="1">
-        <v>86</v>
+        <v>176</v>
       </c>
       <c r="G163" s="1">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="H163" s="1">
-        <v>75</v>
+        <v>163</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.15">
@@ -14172,13 +14172,13 @@
         <v>303</v>
       </c>
       <c r="F164" s="1">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="G164" s="1">
         <v>18</v>
       </c>
       <c r="H164" s="1">
-        <v>552</v>
+        <v>546</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.15">
@@ -14328,13 +14328,13 @@
         <v>334</v>
       </c>
       <c r="F170" s="1">
-        <v>154</v>
+        <v>150</v>
       </c>
       <c r="G170" s="1">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="H170" s="1">
-        <v>140</v>
+        <v>134</v>
       </c>
     </row>
     <row r="171" spans="1:8" x14ac:dyDescent="0.15">
@@ -15602,13 +15602,13 @@
         <v>445</v>
       </c>
       <c r="F219" s="1">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G219" s="1">
         <v>0</v>
       </c>
       <c r="H219" s="1">
-        <v>22</v>
+        <v>21</v>
       </c>
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.15">
@@ -22542,13 +22542,13 @@
         <v>1019</v>
       </c>
       <c r="F486" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G486" s="1">
         <v>1</v>
       </c>
       <c r="H486" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="487" spans="1:8" x14ac:dyDescent="0.15">
@@ -22646,13 +22646,13 @@
         <v>605</v>
       </c>
       <c r="F490" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G490" s="1">
         <v>1</v>
       </c>
       <c r="H490" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="491" spans="1:8" x14ac:dyDescent="0.15">
@@ -23140,13 +23140,13 @@
         <v>1036</v>
       </c>
       <c r="F509" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G509" s="1">
         <v>0</v>
       </c>
       <c r="H509" s="1">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="510" spans="1:8" x14ac:dyDescent="0.15">
@@ -23400,13 +23400,13 @@
         <v>1080</v>
       </c>
       <c r="F519" s="1">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="G519" s="1">
         <v>1</v>
       </c>
       <c r="H519" s="1">
-        <v>2</v>
+        <v>7</v>
       </c>
     </row>
     <row r="520" spans="1:8" x14ac:dyDescent="0.15">
@@ -24595,10 +24595,10 @@
         <v>15</v>
       </c>
       <c r="G565" s="1">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="H565" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
     </row>
     <row r="566" spans="1:8" x14ac:dyDescent="0.15">
@@ -24748,13 +24748,13 @@
         <v>1187</v>
       </c>
       <c r="F571" s="1">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G571" s="1">
         <v>2</v>
       </c>
       <c r="H571" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
     </row>
     <row r="572" spans="1:8" x14ac:dyDescent="0.15">
@@ -27088,13 +27088,13 @@
         <v>1351</v>
       </c>
       <c r="F661" s="1">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="G661" s="1">
         <v>2</v>
       </c>
       <c r="H661" s="1">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
     <row r="662" spans="1:8" x14ac:dyDescent="0.15">
@@ -27244,13 +27244,13 @@
         <v>1378</v>
       </c>
       <c r="F667" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G667" s="1">
         <v>0</v>
       </c>
       <c r="H667" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="668" spans="1:8" x14ac:dyDescent="0.15">
@@ -27322,13 +27322,13 @@
         <v>1299</v>
       </c>
       <c r="F670" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G670" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H670" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="671" spans="1:8" x14ac:dyDescent="0.15">
@@ -27348,13 +27348,13 @@
         <v>1378</v>
       </c>
       <c r="F671" s="1">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="G671" s="1">
         <v>1</v>
       </c>
       <c r="H671" s="1">
-        <v>3</v>
+        <v>13</v>
       </c>
     </row>
     <row r="672" spans="1:8" x14ac:dyDescent="0.15">
@@ -27374,13 +27374,13 @@
         <v>1378</v>
       </c>
       <c r="F672" s="1">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="G672" s="1">
         <v>2</v>
       </c>
       <c r="H672" s="1">
-        <v>1</v>
+        <v>11</v>
       </c>
     </row>
     <row r="673" spans="1:8" x14ac:dyDescent="0.15">
@@ -28050,13 +28050,13 @@
         <v>353</v>
       </c>
       <c r="F698" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G698" s="1">
         <v>0</v>
       </c>
       <c r="H698" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="699" spans="1:8" x14ac:dyDescent="0.15">
@@ -29402,13 +29402,13 @@
         <v>1564</v>
       </c>
       <c r="F750" s="1">
-        <v>25</v>
+        <v>29</v>
       </c>
       <c r="G750" s="1">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="H750" s="1">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="751" spans="1:8" x14ac:dyDescent="0.15">
@@ -30468,13 +30468,13 @@
         <v>1653</v>
       </c>
       <c r="F791" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="G791" s="1">
         <v>0</v>
       </c>
       <c r="H791" s="1">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="792" spans="1:8" x14ac:dyDescent="0.15">
@@ -31430,13 +31430,13 @@
         <v>1662</v>
       </c>
       <c r="F828" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G828" s="1">
         <v>0</v>
       </c>
       <c r="H828" s="1">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="829" spans="1:8" x14ac:dyDescent="0.15">
@@ -32548,13 +32548,13 @@
         <v>1825</v>
       </c>
       <c r="F871" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="G871" s="1">
         <v>0</v>
       </c>
       <c r="H871" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="872" spans="1:8" x14ac:dyDescent="0.15">
@@ -32707,10 +32707,10 @@
         <v>2</v>
       </c>
       <c r="G877" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H877" s="1">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="878" spans="1:8" x14ac:dyDescent="0.15">
@@ -33378,13 +33378,13 @@
         <v>1882</v>
       </c>
       <c r="F903" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G903" s="1">
         <v>0</v>
       </c>
       <c r="H903" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="904" spans="1:8" x14ac:dyDescent="0.15">
@@ -34028,13 +34028,13 @@
         <v>14</v>
       </c>
       <c r="F928" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G928" s="1">
         <v>0</v>
       </c>
       <c r="H928" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="929" spans="1:8" x14ac:dyDescent="0.15">
@@ -35042,13 +35042,13 @@
         <v>1647</v>
       </c>
       <c r="F967" s="1">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="G967" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H967" s="1">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="968" spans="1:8" x14ac:dyDescent="0.15">
@@ -35146,13 +35146,13 @@
         <v>2008</v>
       </c>
       <c r="F971" s="1">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="G971" s="1">
         <v>0</v>
       </c>
       <c r="H971" s="1">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="972" spans="1:8" x14ac:dyDescent="0.15">
@@ -35250,13 +35250,13 @@
         <v>2028</v>
       </c>
       <c r="F975" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="G975" s="1">
         <v>0</v>
       </c>
       <c r="H975" s="1">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="976" spans="1:8" x14ac:dyDescent="0.15">
@@ -37954,13 +37954,13 @@
         <v>1893</v>
       </c>
       <c r="F1079" s="1">
-        <v>169</v>
+        <v>160</v>
       </c>
       <c r="G1079" s="1">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="H1079" s="1">
-        <v>165</v>
+        <v>160</v>
       </c>
     </row>
     <row r="1080" spans="1:8" x14ac:dyDescent="0.15">
@@ -38994,13 +38994,13 @@
         <v>1477</v>
       </c>
       <c r="F1119" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G1119" s="1">
         <v>0</v>
       </c>
       <c r="H1119" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1120" spans="1:8" x14ac:dyDescent="0.15">
@@ -39904,13 +39904,13 @@
         <v>2374</v>
       </c>
       <c r="F1154" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G1154" s="1">
         <v>0</v>
       </c>
       <c r="H1154" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1155" spans="1:8" x14ac:dyDescent="0.15">
@@ -40086,10 +40086,10 @@
         <v>2352</v>
       </c>
       <c r="F1161" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1161" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1161" s="1">
         <v>2</v>
@@ -40450,13 +40450,13 @@
         <v>2352</v>
       </c>
       <c r="F1175" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1175" s="1">
         <v>0</v>
       </c>
       <c r="H1175" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1176" spans="1:8" x14ac:dyDescent="0.15">
@@ -40658,13 +40658,13 @@
         <v>2251</v>
       </c>
       <c r="F1183" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1183" s="1">
         <v>0</v>
       </c>
       <c r="H1183" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1184" spans="1:8" x14ac:dyDescent="0.15">
@@ -40684,13 +40684,13 @@
         <v>2355</v>
       </c>
       <c r="F1184" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G1184" s="1">
         <v>0</v>
       </c>
       <c r="H1184" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1185" spans="1:8" x14ac:dyDescent="0.15">
@@ -40788,10 +40788,10 @@
         <v>2343</v>
       </c>
       <c r="F1188" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1188" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1188" s="1">
         <v>2</v>
@@ -42348,13 +42348,13 @@
         <v>292</v>
       </c>
       <c r="F1248" s="1">
-        <v>1</v>
+        <v>26</v>
       </c>
       <c r="G1248" s="1">
         <v>0</v>
       </c>
       <c r="H1248" s="1">
-        <v>1</v>
+        <v>26</v>
       </c>
     </row>
     <row r="1249" spans="1:8" x14ac:dyDescent="0.15">
@@ -42426,13 +42426,13 @@
         <v>2580</v>
       </c>
       <c r="F1251" s="1">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G1251" s="1">
         <v>0</v>
       </c>
       <c r="H1251" s="1">
-        <v>0</v>
+        <v>22</v>
       </c>
     </row>
     <row r="1252" spans="1:8" x14ac:dyDescent="0.15">
@@ -43206,13 +43206,13 @@
         <v>2636</v>
       </c>
       <c r="F1281" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1281" s="1">
         <v>0</v>
       </c>
       <c r="H1281" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1282" spans="1:8" x14ac:dyDescent="0.15">
@@ -43284,13 +43284,13 @@
         <v>2633</v>
       </c>
       <c r="F1284" s="1">
-        <v>22</v>
+        <v>36</v>
       </c>
       <c r="G1284" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1284" s="1">
-        <v>21</v>
+        <v>36</v>
       </c>
     </row>
     <row r="1285" spans="1:8" x14ac:dyDescent="0.15">
@@ -43310,10 +43310,10 @@
         <v>2633</v>
       </c>
       <c r="F1285" s="1">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G1285" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1285" s="1">
         <v>5</v>
@@ -43882,13 +43882,13 @@
         <v>2689</v>
       </c>
       <c r="F1307" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G1307" s="1">
         <v>0</v>
       </c>
       <c r="H1307" s="1">
-        <v>14</v>
+        <v>13</v>
       </c>
     </row>
     <row r="1308" spans="1:8" x14ac:dyDescent="0.15">
@@ -45702,10 +45702,10 @@
         <v>2639</v>
       </c>
       <c r="F1377" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1377" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1377" s="1">
         <v>6</v>
@@ -46664,13 +46664,13 @@
         <v>2922</v>
       </c>
       <c r="F1414" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G1414" s="1">
         <v>0</v>
       </c>
       <c r="H1414" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1415" spans="1:8" x14ac:dyDescent="0.15">
@@ -47314,13 +47314,13 @@
         <v>2942</v>
       </c>
       <c r="F1439" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1439" s="1">
         <v>0</v>
       </c>
       <c r="H1439" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1440" spans="1:8" x14ac:dyDescent="0.15">
@@ -47392,13 +47392,13 @@
         <v>2922</v>
       </c>
       <c r="F1442" s="1">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G1442" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1442" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1443" spans="1:8" x14ac:dyDescent="0.15">
@@ -47600,10 +47600,10 @@
         <v>2714</v>
       </c>
       <c r="F1450" s="1">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="G1450" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1450" s="1">
         <v>11</v>
@@ -47626,10 +47626,10 @@
         <v>2681</v>
       </c>
       <c r="F1451" s="1">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G1451" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H1451" s="1">
         <v>6</v>
@@ -47678,13 +47678,13 @@
         <v>2922</v>
       </c>
       <c r="F1453" s="1">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G1453" s="1">
         <v>0</v>
       </c>
       <c r="H1453" s="1">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="1454" spans="1:8" x14ac:dyDescent="0.15">
@@ -48461,10 +48461,10 @@
         <v>27</v>
       </c>
       <c r="G1483" s="1">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="H1483" s="1">
-        <v>22</v>
+        <v>18</v>
       </c>
     </row>
     <row r="1484" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.15">

--- a/STOK DEALER/STOK SRB.xlsx
+++ b/STOK DEALER/STOK SRB.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Data D\2026\UPADTE TOOLS BUNDLING SRB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{441AA113-8475-4F32-9D02-D78C0EB9EDCD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54901702-163F-4826-A41B-09251A65B524}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -10118,13 +10118,13 @@
         <v>20</v>
       </c>
       <c r="F9" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G9" s="1">
         <v>0</v>
       </c>
       <c r="H9" s="1">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.15">
@@ -11109,10 +11109,10 @@
         <v>7</v>
       </c>
       <c r="G47" s="1">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="H47" s="1">
-        <v>7</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.15">
@@ -11135,10 +11135,10 @@
         <v>3</v>
       </c>
       <c r="G48" s="1">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H48" s="1">
-        <v>3</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.15">
@@ -11366,13 +11366,13 @@
         <v>116</v>
       </c>
       <c r="F57" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G57" s="1">
         <v>0</v>
       </c>
       <c r="H57" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.15">
@@ -11678,13 +11678,13 @@
         <v>114</v>
       </c>
       <c r="F69" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G69" s="1">
         <v>0</v>
       </c>
       <c r="H69" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.15">
@@ -13108,13 +13108,13 @@
         <v>241</v>
       </c>
       <c r="F124" s="1">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G124" s="1">
         <v>0</v>
       </c>
       <c r="H124" s="1">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.15">
@@ -13754,13 +13754,13 @@
         <v>284</v>
       </c>
       <c r="F149" s="1">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="G149" s="1">
         <v>0</v>
       </c>
       <c r="H149" s="1">
-        <v>19</v>
+        <v>12</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.15">
@@ -13780,13 +13780,13 @@
         <v>287</v>
       </c>
       <c r="F150" s="1">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="G150" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H150" s="1">
-        <v>69</v>
+        <v>56</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.15">
@@ -13936,13 +13936,13 @@
         <v>303</v>
       </c>
       <c r="F156" s="1">
-        <v>256</v>
+        <v>196</v>
       </c>
       <c r="G156" s="1">
         <v>8</v>
       </c>
       <c r="H156" s="1">
-        <v>248</v>
+        <v>188</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.15">
@@ -14196,13 +14196,13 @@
         <v>284</v>
       </c>
       <c r="F166" s="1">
-        <v>52</v>
+        <v>38</v>
       </c>
       <c r="G166" s="1">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="H166" s="1">
-        <v>46</v>
+        <v>35</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.15">
@@ -14222,13 +14222,13 @@
         <v>303</v>
       </c>
       <c r="F167" s="1">
-        <v>406</v>
+        <v>383</v>
       </c>
       <c r="G167" s="1">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="H167" s="1">
-        <v>396</v>
+        <v>376</v>
       </c>
     </row>
     <row r="168" spans="1:8" x14ac:dyDescent="0.15">
@@ -14378,13 +14378,13 @@
         <v>334</v>
       </c>
       <c r="F173" s="1">
-        <v>35</v>
+        <v>27</v>
       </c>
       <c r="G173" s="1">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="H173" s="1">
-        <v>28</v>
+        <v>22</v>
       </c>
     </row>
     <row r="174" spans="1:8" x14ac:dyDescent="0.15">
@@ -14407,10 +14407,10 @@
         <v>89</v>
       </c>
       <c r="G174" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H174" s="1">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="175" spans="1:8" x14ac:dyDescent="0.15">
@@ -15392,13 +15392,13 @@
         <v>353</v>
       </c>
       <c r="F212" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G212" s="1">
         <v>0</v>
       </c>
       <c r="H212" s="1">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.15">
@@ -15418,13 +15418,13 @@
         <v>377</v>
       </c>
       <c r="F213" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G213" s="1">
         <v>0</v>
       </c>
       <c r="H213" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="214" spans="1:8" ht="27" x14ac:dyDescent="0.15">
@@ -15652,13 +15652,13 @@
         <v>445</v>
       </c>
       <c r="F222" s="1">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="G222" s="1">
         <v>0</v>
       </c>
       <c r="H222" s="1">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.15">
@@ -17215,10 +17215,10 @@
         <v>8</v>
       </c>
       <c r="G282" s="1">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H282" s="1">
-        <v>8</v>
+        <v>4</v>
       </c>
     </row>
     <row r="283" spans="1:8" x14ac:dyDescent="0.15">
@@ -20852,13 +20852,13 @@
         <v>877</v>
       </c>
       <c r="F422" s="1">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="G422" s="1">
         <v>0</v>
       </c>
       <c r="H422" s="1">
-        <v>14</v>
+        <v>11</v>
       </c>
     </row>
     <row r="423" spans="1:8" x14ac:dyDescent="0.15">
@@ -20878,13 +20878,13 @@
         <v>880</v>
       </c>
       <c r="F423" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G423" s="1">
         <v>0</v>
       </c>
       <c r="H423" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="424" spans="1:8" x14ac:dyDescent="0.15">
@@ -20904,13 +20904,13 @@
         <v>882</v>
       </c>
       <c r="F424" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G424" s="1">
         <v>0</v>
       </c>
       <c r="H424" s="1">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="425" spans="1:8" x14ac:dyDescent="0.15">
@@ -22722,13 +22722,13 @@
         <v>1028</v>
       </c>
       <c r="F494" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G494" s="1">
         <v>0</v>
       </c>
       <c r="H494" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="495" spans="1:8" x14ac:dyDescent="0.15">
@@ -22985,10 +22985,10 @@
         <v>2</v>
       </c>
       <c r="G504" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H504" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="505" spans="1:8" x14ac:dyDescent="0.15">
@@ -23450,13 +23450,13 @@
         <v>1079</v>
       </c>
       <c r="F522" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G522" s="1">
         <v>2</v>
       </c>
       <c r="H522" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="523" spans="1:8" x14ac:dyDescent="0.15">
@@ -23658,13 +23658,13 @@
         <v>1095</v>
       </c>
       <c r="F530" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G530" s="1">
         <v>0</v>
       </c>
       <c r="H530" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="531" spans="1:8" x14ac:dyDescent="0.15">
@@ -23710,13 +23710,13 @@
         <v>1095</v>
       </c>
       <c r="F532" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G532" s="1">
         <v>0</v>
       </c>
       <c r="H532" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="533" spans="1:8" x14ac:dyDescent="0.15">
@@ -24254,13 +24254,13 @@
         <v>588</v>
       </c>
       <c r="F553" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G553" s="1">
         <v>3</v>
       </c>
       <c r="H553" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="554" spans="1:8" x14ac:dyDescent="0.15">
@@ -24668,13 +24668,13 @@
         <v>1174</v>
       </c>
       <c r="F569" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G569" s="1">
         <v>1</v>
       </c>
       <c r="H569" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="570" spans="1:8" x14ac:dyDescent="0.15">
@@ -24746,13 +24746,13 @@
         <v>1182</v>
       </c>
       <c r="F572" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="G572" s="1">
         <v>0</v>
       </c>
       <c r="H572" s="1">
-        <v>5</v>
+        <v>1</v>
       </c>
     </row>
     <row r="573" spans="1:8" x14ac:dyDescent="0.15">
@@ -25032,13 +25032,13 @@
         <v>1202</v>
       </c>
       <c r="F583" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G583" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H583" s="1">
-        <v>3</v>
+        <v>1</v>
       </c>
     </row>
     <row r="584" spans="1:8" x14ac:dyDescent="0.15">
@@ -27037,10 +27037,10 @@
         <v>1</v>
       </c>
       <c r="G660" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H660" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="661" spans="1:8" x14ac:dyDescent="0.15">
@@ -27138,13 +27138,13 @@
         <v>1350</v>
       </c>
       <c r="F664" s="1">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G664" s="1">
         <v>2</v>
       </c>
       <c r="H664" s="1">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="665" spans="1:8" x14ac:dyDescent="0.15">
@@ -28932,13 +28932,13 @@
         <v>1509</v>
       </c>
       <c r="F733" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G733" s="1">
         <v>0</v>
       </c>
       <c r="H733" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="734" spans="1:8" x14ac:dyDescent="0.15">
@@ -31090,13 +31090,13 @@
         <v>1705</v>
       </c>
       <c r="F816" s="1">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G816" s="1">
         <v>1</v>
       </c>
       <c r="H816" s="1">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="817" spans="1:8" x14ac:dyDescent="0.15">
@@ -31639,10 +31639,10 @@
         <v>2</v>
       </c>
       <c r="G837" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H837" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="838" spans="1:8" x14ac:dyDescent="0.15">
@@ -33298,13 +33298,13 @@
         <v>1871</v>
       </c>
       <c r="F901" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G901" s="1">
         <v>0</v>
       </c>
       <c r="H901" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="902" spans="1:8" x14ac:dyDescent="0.15">
@@ -35274,13 +35274,13 @@
         <v>2024</v>
       </c>
       <c r="F977" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G977" s="1">
         <v>0</v>
       </c>
       <c r="H977" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="978" spans="1:8" x14ac:dyDescent="0.15">
@@ -35300,13 +35300,13 @@
         <v>2027</v>
       </c>
       <c r="F978" s="1">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="G978" s="1">
         <v>0</v>
       </c>
       <c r="H978" s="1">
-        <v>28</v>
+        <v>25</v>
       </c>
     </row>
     <row r="979" spans="1:8" x14ac:dyDescent="0.15">
@@ -38082,13 +38082,13 @@
         <v>1892</v>
       </c>
       <c r="F1085" s="1">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="G1085" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1085" s="1">
-        <v>57</v>
+        <v>48</v>
       </c>
     </row>
     <row r="1086" spans="1:8" x14ac:dyDescent="0.15">
@@ -39122,13 +39122,13 @@
         <v>1476</v>
       </c>
       <c r="F1125" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="G1125" s="1">
         <v>0</v>
       </c>
       <c r="H1125" s="1">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1126" spans="1:8" x14ac:dyDescent="0.15">
@@ -39746,13 +39746,13 @@
         <v>2360</v>
       </c>
       <c r="F1149" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G1149" s="1">
         <v>0</v>
       </c>
       <c r="H1149" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1150" spans="1:8" x14ac:dyDescent="0.15">
@@ -40578,13 +40578,13 @@
         <v>2351</v>
       </c>
       <c r="F1181" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1181" s="1">
         <v>0</v>
       </c>
       <c r="H1181" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1182" spans="1:8" x14ac:dyDescent="0.15">
@@ -40656,13 +40656,13 @@
         <v>2351</v>
       </c>
       <c r="F1184" s="1">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="G1184" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1184" s="1">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="1185" spans="1:8" x14ac:dyDescent="0.15">
@@ -41647,10 +41647,10 @@
         <v>1</v>
       </c>
       <c r="G1222" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1222" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1223" spans="1:8" x14ac:dyDescent="0.15">
@@ -41725,10 +41725,10 @@
         <v>1</v>
       </c>
       <c r="G1225" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1225" s="1">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="1226" spans="1:8" x14ac:dyDescent="0.15">
@@ -42193,10 +42193,10 @@
         <v>5</v>
       </c>
       <c r="G1243" s="1">
+        <v>3</v>
+      </c>
+      <c r="H1243" s="1">
         <v>2</v>
-      </c>
-      <c r="H1243" s="1">
-        <v>3</v>
       </c>
     </row>
     <row r="1244" spans="1:8" x14ac:dyDescent="0.15">
@@ -42297,10 +42297,10 @@
         <v>2</v>
       </c>
       <c r="G1247" s="1">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H1247" s="1">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="1248" spans="1:8" x14ac:dyDescent="0.15">
@@ -42476,13 +42476,13 @@
         <v>292</v>
       </c>
       <c r="F1254" s="1">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G1254" s="1">
         <v>5</v>
       </c>
       <c r="H1254" s="1">
-        <v>7</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1255" spans="1:8" x14ac:dyDescent="0.15">
@@ -42502,13 +42502,13 @@
         <v>2579</v>
       </c>
       <c r="F1255" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1255" s="1">
         <v>0</v>
       </c>
       <c r="H1255" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1256" spans="1:8" x14ac:dyDescent="0.15">
@@ -43412,13 +43412,13 @@
         <v>2632</v>
       </c>
       <c r="F1290" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G1290" s="1">
         <v>0</v>
       </c>
       <c r="H1290" s="1">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1291" spans="1:8" x14ac:dyDescent="0.15">
@@ -43438,13 +43438,13 @@
         <v>2632</v>
       </c>
       <c r="F1291" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="G1291" s="1">
         <v>0</v>
       </c>
       <c r="H1291" s="1">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="1292" spans="1:8" x14ac:dyDescent="0.15">
@@ -44192,13 +44192,13 @@
         <v>2716</v>
       </c>
       <c r="F1320" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="G1320" s="1">
         <v>0</v>
       </c>
       <c r="H1320" s="1">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="1321" spans="1:8" x14ac:dyDescent="0.15">
@@ -44218,13 +44218,13 @@
         <v>2688</v>
       </c>
       <c r="F1321" s="1">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="G1321" s="1">
         <v>0</v>
       </c>
       <c r="H1321" s="1">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="1322" spans="1:8" x14ac:dyDescent="0.15">
@@ -44452,13 +44452,13 @@
         <v>2716</v>
       </c>
       <c r="F1330" s="1">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="G1330" s="1">
         <v>0</v>
       </c>
       <c r="H1330" s="1">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="1331" spans="1:8" x14ac:dyDescent="0.15">
@@ -45648,13 +45648,13 @@
         <v>2824</v>
       </c>
       <c r="F1376" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="G1376" s="1">
         <v>0</v>
       </c>
       <c r="H1376" s="1">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="1377" spans="1:8" x14ac:dyDescent="0.15">
@@ -46272,13 +46272,13 @@
         <v>2881</v>
       </c>
       <c r="F1400" s="1">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="G1400" s="1">
         <v>0</v>
       </c>
       <c r="H1400" s="1">
-        <v>12</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1401" spans="1:8" x14ac:dyDescent="0.15">
@@ -46376,13 +46376,13 @@
         <v>2790</v>
       </c>
       <c r="F1404" s="1">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G1404" s="1">
         <v>0</v>
       </c>
       <c r="H1404" s="1">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="1405" spans="1:8" x14ac:dyDescent="0.15">
@@ -47676,13 +47676,13 @@
         <v>2809</v>
       </c>
       <c r="F1454" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G1454" s="1">
         <v>0</v>
       </c>
       <c r="H1454" s="1">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="1455" spans="1:8" x14ac:dyDescent="0.15">
@@ -47806,13 +47806,13 @@
         <v>2921</v>
       </c>
       <c r="F1459" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="G1459" s="1">
         <v>0</v>
       </c>
       <c r="H1459" s="1">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="1460" spans="1:8" x14ac:dyDescent="0.15">
@@ -48534,13 +48534,13 @@
         <v>334</v>
       </c>
       <c r="F1487" s="1">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G1487" s="1">
         <v>0</v>
       </c>
       <c r="H1487" s="1">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="1488" spans="1:8" x14ac:dyDescent="0.15">
@@ -49052,13 +49052,13 @@
         <v>350</v>
       </c>
       <c r="F1507" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G1507" s="1">
         <v>0</v>
       </c>
       <c r="H1507" s="1">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="1508" spans="1:8" x14ac:dyDescent="0.15">
